--- a/data/ton_chuanhap.xlsx
+++ b/data/ton_chuanhap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_Tonkho\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A570FBFA-17ED-4C62-8668-9C20FF57FA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D01B81-4558-4CD2-B019-7B838876EE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="426">
   <si>
     <t>KV</t>
   </si>
@@ -1315,6 +1315,24 @@
   </si>
   <si>
     <t>Doanh nghiệp tư nhân vàng Vĩnh Thạch 3</t>
+  </si>
+  <si>
+    <t>110501-GP&amp;DVKT/HĐMBLĐ-2026/QNI-CTTMDVNGHIATHANG</t>
+  </si>
+  <si>
+    <t>Công ty TNHH TM VÀ DỊCH VỤ Nghĩa Thắng</t>
+  </si>
+  <si>
+    <t>040501/HĐNLMT-2026/CNCTTHA-PHUQUYHAIHA</t>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH PHÚ QUÝ HẢI HÀ</t>
+  </si>
+  <si>
+    <t>06042026-3449/CNCTCTO-STRIDESS</t>
+  </si>
+  <si>
+    <t>STRIDE SOLAR</t>
   </si>
 </sst>
 </file>
@@ -1626,10 +1644,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </right>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1642,7 +1660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1848,7 +1866,11 @@
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1858,16 +1880,16 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2261,7 +2283,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F457DF4-8092-4544-B88B-9AF42554C254}">
-  <dimension ref="A1:M133"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.375" customWidth="1"/>
@@ -2321,4886 +2343,5001 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="82" t="s">
         <v>49</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81" t="s">
+      <c r="F2" s="83"/>
+      <c r="G2" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="79">
+      <c r="H2" s="91">
         <v>33</v>
       </c>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="80" t="s">
+      <c r="C3" s="82" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="80" t="s">
+      <c r="E3" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81" t="s">
+      <c r="F3" s="83"/>
+      <c r="G3" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="79">
+      <c r="H3" s="91">
         <v>178</v>
       </c>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="84" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="C4" s="82" t="s">
         <v>159</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="82" t="s">
+      <c r="E4" s="84" t="s">
         <v>160</v>
       </c>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81" t="s">
+      <c r="F4" s="83"/>
+      <c r="G4" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="79">
+      <c r="H4" s="91">
         <v>39</v>
       </c>
-      <c r="I4" s="81" t="s">
+      <c r="I4" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" s="81"/>
-      <c r="M4" s="81" t="s">
+      <c r="J4" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="80" t="s">
+      <c r="C5" s="82" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="80" t="s">
+      <c r="E5" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81" t="s">
+      <c r="F5" s="83"/>
+      <c r="G5" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="79">
+      <c r="H5" s="91">
         <v>120</v>
       </c>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="7" t="s">
+      <c r="I5" s="17"/>
+      <c r="J5" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="81"/>
+      <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="80" t="s">
+      <c r="C6" s="82" t="s">
         <v>63</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81" t="s">
+      <c r="F6" s="83"/>
+      <c r="G6" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="79">
+      <c r="H6" s="91">
         <v>163</v>
       </c>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" s="7" t="s">
+      <c r="I6" s="17"/>
+      <c r="J6" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="81"/>
+      <c r="M6" s="17"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="82" t="s">
         <v>67</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="80" t="s">
+      <c r="E7" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81" t="s">
+      <c r="F7" s="83"/>
+      <c r="G7" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="79">
+      <c r="H7" s="91">
         <v>489</v>
       </c>
-      <c r="I7" s="81" t="s">
+      <c r="I7" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J7" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="7" t="s">
+      <c r="J7" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="81" t="s">
+      <c r="M7" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="82" t="s">
         <v>73</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81" t="s">
+      <c r="F8" s="83"/>
+      <c r="G8" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="79">
+      <c r="H8" s="91">
         <v>18</v>
       </c>
-      <c r="I8" s="81"/>
-      <c r="J8" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" s="7" t="s">
+      <c r="I8" s="17"/>
+      <c r="J8" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="81" t="s">
+      <c r="M8" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="80" t="s">
+      <c r="C9" s="82" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="80" t="s">
+      <c r="E9" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81" t="s">
+      <c r="F9" s="83"/>
+      <c r="G9" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="79">
+      <c r="H9" s="91">
         <v>50</v>
       </c>
-      <c r="I9" s="81" t="s">
+      <c r="I9" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J9" s="81" t="s">
+      <c r="J9" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K9" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" s="81"/>
-      <c r="M9" s="81"/>
+      <c r="K9" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="80" t="s">
+      <c r="A10" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="80" t="s">
+      <c r="B10" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="80" t="s">
+      <c r="C10" s="82" t="s">
         <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="80" t="s">
+      <c r="E10" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81" t="s">
+      <c r="F10" s="83"/>
+      <c r="G10" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="79">
+      <c r="H10" s="91">
         <v>42</v>
       </c>
-      <c r="I10" s="81" t="s">
+      <c r="I10" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J10" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K10" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
+      <c r="J10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="82" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="80" t="s">
+      <c r="B11" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="80" t="s">
+      <c r="C11" s="82" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="80" t="s">
+      <c r="E11" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81" t="s">
+      <c r="F11" s="83"/>
+      <c r="G11" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H11" s="79">
+      <c r="H11" s="91">
         <v>1040</v>
       </c>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81" t="s">
+      <c r="I11" s="17"/>
+      <c r="J11" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="80" t="s">
+      <c r="A12" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="80" t="s">
+      <c r="C12" s="82" t="s">
         <v>89</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="80" t="s">
+      <c r="E12" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81" t="s">
+      <c r="F12" s="83"/>
+      <c r="G12" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="79">
+      <c r="H12" s="91">
         <v>871</v>
       </c>
-      <c r="I12" s="81" t="s">
+      <c r="I12" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L12" s="81"/>
-      <c r="M12" s="81" t="s">
+      <c r="J12" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="80" t="s">
+      <c r="A13" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="82" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="83" t="s">
+      <c r="E13" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81" t="s">
+      <c r="F13" s="83"/>
+      <c r="G13" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="79">
+      <c r="H13" s="91">
         <v>770</v>
       </c>
-      <c r="I13" s="81" t="s">
+      <c r="I13" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J13" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K13" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81" t="s">
+      <c r="J13" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="80" t="s">
+      <c r="C14" s="82" t="s">
         <v>76</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="80" t="e">
+      <c r="E14" s="82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81" t="s">
+      <c r="F14" s="83"/>
+      <c r="G14" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="79">
+      <c r="H14" s="91">
         <v>64</v>
       </c>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L14" s="81"/>
-      <c r="M14" s="81"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="80" t="s">
+      <c r="B15" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="80" t="s">
+      <c r="C15" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="80" t="s">
+      <c r="E15" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81" t="s">
+      <c r="F15" s="83"/>
+      <c r="G15" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="79">
+      <c r="H15" s="91">
         <v>32</v>
       </c>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K15" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="80" t="s">
+      <c r="A16" s="82" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="80" t="s">
+      <c r="C16" s="82" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="80" t="s">
+      <c r="E16" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81" t="s">
+      <c r="F16" s="83"/>
+      <c r="G16" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="79">
+      <c r="H16" s="91">
         <v>40</v>
       </c>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K16" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="82" t="s">
+      <c r="A17" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="80" t="s">
+      <c r="B17" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="82" t="s">
         <v>101</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="82" t="s">
+      <c r="E17" s="84" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81" t="s">
+      <c r="F17" s="83"/>
+      <c r="G17" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="79">
+      <c r="H17" s="91">
         <v>4876</v>
       </c>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K17" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="80" t="s">
+      <c r="A18" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="82" t="s">
         <v>104</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="80" t="s">
+      <c r="E18" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81" t="s">
+      <c r="F18" s="83"/>
+      <c r="G18" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="79">
+      <c r="H18" s="91">
         <v>16</v>
       </c>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K18" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81" t="s">
+      <c r="I18" s="17"/>
+      <c r="J18" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="80" t="s">
+      <c r="A19" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="80" t="s">
+      <c r="C19" s="82" t="s">
         <v>107</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="80" t="s">
+      <c r="E19" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="F19" s="81"/>
-      <c r="G19" s="81" t="s">
+      <c r="F19" s="83"/>
+      <c r="G19" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H19" s="79">
+      <c r="H19" s="91">
         <v>0</v>
       </c>
-      <c r="I19" s="81" t="s">
+      <c r="I19" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K19" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L19" s="81"/>
-      <c r="M19" s="81" t="s">
+      <c r="J19" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="80" t="s">
+      <c r="C20" s="82" t="s">
         <v>111</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="80" t="s">
+      <c r="E20" s="82" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81" t="s">
+      <c r="F20" s="83"/>
+      <c r="G20" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="79">
+      <c r="H20" s="91">
         <v>1218</v>
       </c>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K20" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L20" s="81"/>
-      <c r="M20" s="81"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="80" t="s">
+      <c r="B21" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="80" t="s">
+      <c r="C21" s="82" t="s">
         <v>115</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="80" t="s">
+      <c r="E21" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81" t="s">
+      <c r="F21" s="83"/>
+      <c r="G21" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H21" s="79">
+      <c r="H21" s="91">
         <v>40</v>
       </c>
-      <c r="I21" s="81" t="s">
+      <c r="I21" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J21" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K21" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L21" s="81"/>
-      <c r="M21" s="81" t="s">
+      <c r="J21" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="80" t="s">
+      <c r="A22" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="82" t="s">
         <v>118</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="80" t="s">
+      <c r="E22" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81" t="s">
+      <c r="F22" s="83"/>
+      <c r="G22" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="79">
+      <c r="H22" s="91">
         <v>40</v>
       </c>
-      <c r="I22" s="81" t="s">
+      <c r="I22" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K22" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L22" s="7" t="s">
+      <c r="J22" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M22" s="81" t="s">
+      <c r="M22" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="80" t="s">
+      <c r="A23" s="82" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="80" t="s">
+      <c r="C23" s="82" t="s">
         <v>121</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="80" t="s">
+      <c r="E23" s="82" t="s">
         <v>122</v>
       </c>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81" t="s">
+      <c r="F23" s="83"/>
+      <c r="G23" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="79">
+      <c r="H23" s="91">
         <v>162</v>
       </c>
-      <c r="I23" s="81" t="s">
+      <c r="I23" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J23" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K23" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L23" s="81"/>
-      <c r="M23" s="81" t="s">
+      <c r="J23" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="82" t="s">
         <v>123</v>
       </c>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="81"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="80" t="s">
+      <c r="E24" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="F24" s="81"/>
-      <c r="G24" s="81" t="s">
+      <c r="F24" s="83"/>
+      <c r="G24" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H24" s="79">
+      <c r="H24" s="91">
         <v>1326</v>
       </c>
-      <c r="I24" s="81" t="s">
+      <c r="I24" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J24" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K24" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L24" s="7" t="s">
+      <c r="J24" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M24" s="81" t="s">
+      <c r="M24" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="80" t="s">
+      <c r="A25" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="80" t="s">
+      <c r="B25" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="80" t="s">
+      <c r="C25" s="82" t="s">
         <v>126</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="80" t="s">
+      <c r="E25" s="82" t="s">
         <v>127</v>
       </c>
-      <c r="F25" s="81"/>
-      <c r="G25" s="81" t="s">
+      <c r="F25" s="83"/>
+      <c r="G25" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H25" s="79">
+      <c r="H25" s="91">
         <v>1626</v>
       </c>
-      <c r="I25" s="81" t="s">
+      <c r="I25" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J25" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K25" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L25" s="7" t="s">
+      <c r="J25" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="M25" s="81" t="s">
+      <c r="M25" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="84" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="80" t="s">
+      <c r="B26" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="80" t="s">
+      <c r="C26" s="82" t="s">
         <v>129</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="82" t="s">
+      <c r="E26" s="84" t="s">
         <v>130</v>
       </c>
-      <c r="F26" s="81"/>
-      <c r="G26" s="81" t="s">
+      <c r="F26" s="83"/>
+      <c r="G26" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H26" s="79">
+      <c r="H26" s="91">
         <v>526</v>
       </c>
-      <c r="I26" s="81" t="s">
+      <c r="I26" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J26" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K26" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L26" s="7" t="s">
+      <c r="J26" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="91" t="s">
         <v>131</v>
       </c>
-      <c r="M26" s="81" t="s">
+      <c r="M26" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="80" t="s">
+      <c r="A27" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="80" t="s">
+      <c r="B27" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="80" t="s">
+      <c r="C27" s="82" t="s">
         <v>133</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="80" t="s">
+      <c r="E27" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81" t="s">
+      <c r="F27" s="83"/>
+      <c r="G27" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H27" s="79">
+      <c r="H27" s="91">
         <v>64</v>
       </c>
-      <c r="I27" s="81" t="s">
+      <c r="I27" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K27" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="81"/>
-      <c r="M27" s="81" t="s">
+      <c r="J27" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="80" t="s">
+      <c r="C28" s="82" t="s">
         <v>136</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="80" t="s">
+      <c r="E28" s="82" t="s">
         <v>137</v>
       </c>
-      <c r="F28" s="81"/>
-      <c r="G28" s="81" t="s">
+      <c r="F28" s="83"/>
+      <c r="G28" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H28" s="79">
+      <c r="H28" s="91">
         <v>82</v>
       </c>
-      <c r="I28" s="81" t="s">
+      <c r="I28" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K28" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L28" s="81"/>
-      <c r="M28" s="81" t="s">
+      <c r="J28" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="80" t="s">
+      <c r="A29" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="B29" s="80" t="s">
+      <c r="B29" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="80" t="s">
+      <c r="C29" s="82" t="s">
         <v>139</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="80" t="s">
+      <c r="E29" s="82" t="s">
         <v>140</v>
       </c>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81" t="s">
+      <c r="F29" s="83"/>
+      <c r="G29" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H29" s="79">
+      <c r="H29" s="91">
         <v>800</v>
       </c>
-      <c r="I29" s="81" t="s">
+      <c r="I29" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J29" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K29" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L29" s="81"/>
-      <c r="M29" s="81" t="s">
+      <c r="J29" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="80" t="s">
+      <c r="A30" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C30" s="80" t="s">
+      <c r="C30" s="82" t="s">
         <v>143</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="80" t="s">
+      <c r="E30" s="82" t="s">
         <v>144</v>
       </c>
-      <c r="F30" s="81"/>
-      <c r="G30" s="81" t="s">
+      <c r="F30" s="83"/>
+      <c r="G30" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H30" s="79">
+      <c r="H30" s="91">
         <v>160</v>
       </c>
-      <c r="I30" s="81" t="s">
+      <c r="I30" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K30" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" s="7" t="s">
+      <c r="J30" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="M30" s="81" t="s">
+      <c r="M30" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="80" t="s">
+      <c r="A31" s="82" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C31" s="80" t="s">
+      <c r="C31" s="82" t="s">
         <v>147</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="80" t="s">
+      <c r="E31" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81" t="s">
+      <c r="F31" s="83"/>
+      <c r="G31" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H31" s="79">
+      <c r="H31" s="91">
         <v>1511</v>
       </c>
-      <c r="I31" s="81" t="s">
+      <c r="I31" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K31" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L31" s="81"/>
-      <c r="M31" s="81" t="s">
+      <c r="J31" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="80" t="s">
+      <c r="A32" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="80" t="s">
+      <c r="B32" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C32" s="80" t="s">
+      <c r="C32" s="82" t="s">
         <v>150</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="80" t="s">
+      <c r="E32" s="82" t="s">
         <v>151</v>
       </c>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81" t="s">
+      <c r="F32" s="83"/>
+      <c r="G32" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="79">
+      <c r="H32" s="91">
         <v>681</v>
       </c>
-      <c r="I32" s="81" t="s">
+      <c r="I32" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J32" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K32" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L32" s="81"/>
-      <c r="M32" s="81" t="s">
+      <c r="J32" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="80" t="s">
+      <c r="A33" s="82" t="s">
         <v>152</v>
       </c>
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="80" t="s">
+      <c r="C33" s="82" t="s">
         <v>153</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="80" t="s">
+      <c r="E33" s="82" t="s">
         <v>154</v>
       </c>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81" t="s">
+      <c r="F33" s="83"/>
+      <c r="G33" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H33" s="79">
+      <c r="H33" s="91">
         <v>330</v>
       </c>
-      <c r="I33" s="81" t="s">
+      <c r="I33" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J33" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K33" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L33" s="7" t="s">
+      <c r="J33" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M33" s="81" t="s">
+      <c r="M33" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="82" t="s">
+      <c r="A34" s="84" t="s">
         <v>155</v>
       </c>
-      <c r="B34" s="80" t="s">
+      <c r="B34" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C34" s="80" t="s">
+      <c r="C34" s="82" t="s">
         <v>156</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="82" t="s">
+      <c r="E34" s="84" t="s">
         <v>157</v>
       </c>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81" t="s">
+      <c r="F34" s="83"/>
+      <c r="G34" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H34" s="79">
+      <c r="H34" s="91">
         <v>1704</v>
       </c>
-      <c r="I34" s="81" t="s">
+      <c r="I34" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J34" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K34" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L34" s="81"/>
-      <c r="M34" s="81" t="s">
+      <c r="J34" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="82" t="s">
+      <c r="A35" s="84" t="s">
         <v>161</v>
       </c>
-      <c r="B35" s="80" t="s">
+      <c r="B35" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C35" s="80" t="s">
+      <c r="C35" s="82" t="s">
         <v>162</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="82" t="s">
+      <c r="E35" s="84" t="s">
         <v>163</v>
       </c>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81" t="s">
+      <c r="F35" s="83"/>
+      <c r="G35" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H35" s="79">
+      <c r="H35" s="91">
         <v>84</v>
       </c>
-      <c r="I35" s="81" t="s">
+      <c r="I35" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J35" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K35" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L35" s="81"/>
-      <c r="M35" s="81" t="s">
+      <c r="J35" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="80" t="s">
+      <c r="A36" s="82" t="s">
         <v>164</v>
       </c>
-      <c r="B36" s="80" t="s">
+      <c r="B36" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C36" s="80" t="s">
+      <c r="C36" s="82" t="s">
         <v>165</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E36" s="80" t="s">
+      <c r="E36" s="82" t="s">
         <v>157</v>
       </c>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81" t="s">
+      <c r="F36" s="83"/>
+      <c r="G36" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H36" s="79">
+      <c r="H36" s="91">
         <v>680</v>
       </c>
-      <c r="I36" s="81" t="s">
+      <c r="I36" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J36" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K36" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L36" s="81"/>
-      <c r="M36" s="81" t="s">
+      <c r="J36" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="80" t="s">
+      <c r="A37" s="82" t="s">
         <v>166</v>
       </c>
-      <c r="B37" s="80" t="s">
+      <c r="B37" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C37" s="80" t="s">
+      <c r="C37" s="82" t="s">
         <v>165</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E37" s="80" t="s">
+      <c r="E37" s="82" t="s">
         <v>167</v>
       </c>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81" t="s">
+      <c r="F37" s="83"/>
+      <c r="G37" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H37" s="79">
+      <c r="H37" s="91">
         <v>654</v>
       </c>
-      <c r="I37" s="81" t="s">
+      <c r="I37" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="J37" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K37" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L37" s="81"/>
-      <c r="M37" s="81" t="s">
+      <c r="J37" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="80">
+      <c r="A38" s="82">
         <v>20251678</v>
       </c>
-      <c r="B38" s="80" t="s">
+      <c r="B38" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="80" t="s">
+      <c r="C38" s="82" t="s">
         <v>169</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E38" s="80" t="s">
+      <c r="E38" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81" t="s">
+      <c r="F38" s="83"/>
+      <c r="G38" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H38" s="79">
+      <c r="H38" s="91">
         <v>732</v>
       </c>
-      <c r="I38" s="81" t="s">
+      <c r="I38" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J38" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K38" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L38" s="7" t="s">
+      <c r="J38" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M38" s="81" t="s">
+      <c r="M38" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="80" t="s">
+      <c r="A39" s="82" t="s">
         <v>171</v>
       </c>
-      <c r="B39" s="80" t="s">
+      <c r="B39" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C39" s="80" t="s">
+      <c r="C39" s="82" t="s">
         <v>172</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="80" t="s">
+      <c r="E39" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81" t="s">
+      <c r="F39" s="83"/>
+      <c r="G39" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H39" s="79">
+      <c r="H39" s="91">
         <v>204</v>
       </c>
-      <c r="I39" s="81" t="s">
+      <c r="I39" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J39" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K39" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L39" s="7" t="s">
+      <c r="J39" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M39" s="81" t="s">
+      <c r="M39" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="B40" s="80" t="s">
+      <c r="B40" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C40" s="80" t="s">
+      <c r="C40" s="82" t="s">
         <v>175</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E40" s="80" t="s">
+      <c r="E40" s="82" t="s">
         <v>176</v>
       </c>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81" t="s">
+      <c r="F40" s="83"/>
+      <c r="G40" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H40" s="79">
+      <c r="H40" s="91">
         <v>1229</v>
       </c>
-      <c r="I40" s="81" t="s">
+      <c r="I40" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J40" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K40" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L40" s="81"/>
-      <c r="M40" s="81" t="s">
+      <c r="J40" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K40" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="80" t="s">
+      <c r="A41" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C41" s="80" t="s">
+      <c r="C41" s="82" t="s">
         <v>178</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E41" s="80">
+      <c r="E41" s="82">
         <v>0</v>
       </c>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81" t="s">
+      <c r="F41" s="83"/>
+      <c r="G41" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H41" s="79">
+      <c r="H41" s="91">
         <v>180</v>
       </c>
-      <c r="I41" s="81" t="s">
+      <c r="I41" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J41" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K41" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L41" s="81"/>
-      <c r="M41" s="81" t="s">
+      <c r="J41" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="80" t="s">
+      <c r="A42" s="82" t="s">
         <v>179</v>
       </c>
-      <c r="B42" s="80" t="s">
+      <c r="B42" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C42" s="80" t="s">
+      <c r="C42" s="82" t="s">
         <v>180</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="80" t="e">
+      <c r="E42" s="82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81" t="s">
+      <c r="F42" s="83"/>
+      <c r="G42" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H42" s="79">
+      <c r="H42" s="91">
         <v>18</v>
       </c>
-      <c r="I42" s="81" t="s">
+      <c r="I42" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J42" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K42" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L42" s="7" t="s">
+      <c r="J42" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L42" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M42" s="81" t="s">
+      <c r="M42" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="80" t="s">
+      <c r="A43" s="82" t="s">
         <v>181</v>
       </c>
-      <c r="B43" s="80" t="s">
+      <c r="B43" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C43" s="80" t="s">
+      <c r="C43" s="82" t="s">
         <v>182</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="80" t="s">
+      <c r="E43" s="82" t="s">
         <v>183</v>
       </c>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81" t="s">
+      <c r="F43" s="83"/>
+      <c r="G43" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H43" s="79">
+      <c r="H43" s="91">
         <v>640</v>
       </c>
-      <c r="I43" s="81" t="s">
+      <c r="I43" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J43" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K43" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L43" s="7" t="s">
+      <c r="J43" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M43" s="81" t="s">
+      <c r="M43" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="80" t="s">
+      <c r="A44" s="82" t="s">
         <v>184</v>
       </c>
-      <c r="B44" s="80" t="s">
+      <c r="B44" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C44" s="80" t="s">
+      <c r="C44" s="82" t="s">
         <v>185</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="80" t="s">
+      <c r="E44" s="82" t="s">
         <v>186</v>
       </c>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81" t="s">
+      <c r="F44" s="83"/>
+      <c r="G44" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="79">
+      <c r="H44" s="91">
         <v>1542</v>
       </c>
-      <c r="I44" s="81" t="s">
+      <c r="I44" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J44" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K44" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L44" s="81"/>
-      <c r="M44" s="81" t="s">
+      <c r="J44" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="80" t="s">
+      <c r="A45" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="B45" s="80" t="s">
+      <c r="B45" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C45" s="80" t="s">
+      <c r="C45" s="82" t="s">
         <v>188</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="80" t="s">
+      <c r="E45" s="82" t="s">
         <v>189</v>
       </c>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81" t="s">
+      <c r="F45" s="83"/>
+      <c r="G45" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H45" s="79">
+      <c r="H45" s="91">
         <v>672</v>
       </c>
-      <c r="I45" s="81" t="s">
+      <c r="I45" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J45" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K45" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L45" s="7" t="s">
+      <c r="J45" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L45" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M45" s="81" t="s">
+      <c r="M45" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="80" t="s">
+      <c r="A46" s="82" t="s">
         <v>190</v>
       </c>
-      <c r="B46" s="80" t="s">
+      <c r="B46" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="80" t="s">
+      <c r="C46" s="82" t="s">
         <v>191</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="80" t="s">
+      <c r="E46" s="82" t="s">
         <v>192</v>
       </c>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81" t="s">
+      <c r="F46" s="83"/>
+      <c r="G46" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H46" s="79">
+      <c r="H46" s="91">
         <v>245</v>
       </c>
-      <c r="I46" s="81"/>
-      <c r="J46" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K46" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L46" s="81"/>
-      <c r="M46" s="81"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="82" t="s">
+      <c r="A47" s="84" t="s">
         <v>193</v>
       </c>
-      <c r="B47" s="80" t="s">
+      <c r="B47" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="80" t="s">
+      <c r="C47" s="82" t="s">
         <v>194</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="82" t="s">
+      <c r="E47" s="84" t="s">
         <v>195</v>
       </c>
-      <c r="F47" s="81"/>
-      <c r="G47" s="81" t="s">
+      <c r="F47" s="83"/>
+      <c r="G47" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H47" s="79">
+      <c r="H47" s="91">
         <v>93</v>
       </c>
-      <c r="I47" s="81"/>
-      <c r="J47" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K47" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L47" s="81"/>
-      <c r="M47" s="81" t="s">
+      <c r="I47" s="17"/>
+      <c r="J47" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="80" t="s">
+      <c r="A48" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="B48" s="80" t="s">
+      <c r="B48" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="81"/>
+      <c r="C48" s="83"/>
       <c r="D48" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="80" t="s">
+      <c r="E48" s="82" t="s">
         <v>197</v>
       </c>
-      <c r="F48" s="81"/>
-      <c r="G48" s="81" t="s">
+      <c r="F48" s="83"/>
+      <c r="G48" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H48" s="79">
+      <c r="H48" s="91">
         <v>88</v>
       </c>
-      <c r="I48" s="81"/>
-      <c r="J48" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K48" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L48" s="81"/>
-      <c r="M48" s="81" t="s">
+      <c r="I48" s="17"/>
+      <c r="J48" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="80" t="s">
+      <c r="A49" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="B49" s="80" t="s">
+      <c r="B49" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="80" t="s">
+      <c r="C49" s="82" t="s">
         <v>199</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="80" t="s">
+      <c r="E49" s="82" t="s">
         <v>200</v>
       </c>
-      <c r="F49" s="81"/>
-      <c r="G49" s="81" t="s">
+      <c r="F49" s="83"/>
+      <c r="G49" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H49" s="79">
+      <c r="H49" s="91">
         <v>357</v>
       </c>
-      <c r="I49" s="81"/>
-      <c r="J49" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K49" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L49" s="81"/>
-      <c r="M49" s="81" t="s">
+      <c r="I49" s="17"/>
+      <c r="J49" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="80" t="s">
+      <c r="A50" s="82" t="s">
         <v>201</v>
       </c>
-      <c r="B50" s="80" t="s">
+      <c r="B50" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="80" t="s">
+      <c r="C50" s="82" t="s">
         <v>202</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E50" s="80" t="s">
+      <c r="E50" s="82" t="s">
         <v>203</v>
       </c>
-      <c r="F50" s="81"/>
-      <c r="G50" s="81" t="s">
+      <c r="F50" s="83"/>
+      <c r="G50" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H50" s="79">
+      <c r="H50" s="91">
         <v>2617</v>
       </c>
-      <c r="I50" s="81"/>
-      <c r="J50" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K50" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L50" s="7" t="s">
+      <c r="I50" s="17"/>
+      <c r="J50" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K50" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="M50" s="81" t="s">
+      <c r="M50" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="80" t="s">
+      <c r="A51" s="82" t="s">
         <v>204</v>
       </c>
-      <c r="B51" s="80" t="s">
+      <c r="B51" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="80" t="s">
+      <c r="C51" s="82" t="s">
         <v>205</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="80" t="s">
+      <c r="E51" s="82" t="s">
         <v>206</v>
       </c>
-      <c r="F51" s="81"/>
-      <c r="G51" s="81" t="s">
+      <c r="F51" s="83"/>
+      <c r="G51" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H51" s="79">
+      <c r="H51" s="91">
         <v>6768</v>
       </c>
-      <c r="I51" s="81" t="s">
+      <c r="I51" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J51" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K51" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L51" s="81"/>
-      <c r="M51" s="81" t="s">
+      <c r="J51" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K51" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="80" t="s">
+      <c r="A52" s="82" t="s">
         <v>207</v>
       </c>
-      <c r="B52" s="80" t="s">
+      <c r="B52" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="80" t="s">
+      <c r="C52" s="82" t="s">
         <v>208</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="80" t="s">
+      <c r="E52" s="82" t="s">
         <v>209</v>
       </c>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81" t="s">
+      <c r="F52" s="83"/>
+      <c r="G52" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H52" s="79">
+      <c r="H52" s="91">
         <v>1625</v>
       </c>
-      <c r="I52" s="81"/>
-      <c r="J52" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K52" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L52" s="7" t="s">
+      <c r="I52" s="17"/>
+      <c r="J52" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K52" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="M52" s="81" t="s">
+      <c r="M52" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="80" t="s">
+      <c r="A53" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="B53" s="80" t="s">
+      <c r="B53" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="80" t="s">
+      <c r="C53" s="82" t="s">
         <v>211</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E53" s="80" t="s">
+      <c r="E53" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81" t="s">
+      <c r="F53" s="83"/>
+      <c r="G53" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H53" s="79">
+      <c r="H53" s="91">
         <v>1980</v>
       </c>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K53" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L53" s="81"/>
-      <c r="M53" s="81" t="s">
+      <c r="I53" s="17"/>
+      <c r="J53" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K53" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="80" t="s">
+      <c r="A54" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="B54" s="80" t="s">
+      <c r="B54" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="81"/>
+      <c r="C54" s="83"/>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E54" s="80" t="s">
+      <c r="E54" s="82" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="81"/>
-      <c r="G54" s="81" t="s">
+      <c r="F54" s="83"/>
+      <c r="G54" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H54" s="79">
+      <c r="H54" s="91">
         <v>381</v>
       </c>
-      <c r="I54" s="81"/>
-      <c r="J54" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K54" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L54" s="81"/>
-      <c r="M54" s="81" t="s">
+      <c r="I54" s="17"/>
+      <c r="J54" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K54" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="80" t="s">
+      <c r="A55" s="82" t="s">
         <v>215</v>
       </c>
-      <c r="B55" s="80" t="s">
+      <c r="B55" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="80" t="s">
+      <c r="C55" s="82" t="s">
         <v>216</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E55" s="80" t="s">
+      <c r="E55" s="82" t="s">
         <v>217</v>
       </c>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81" t="s">
+      <c r="F55" s="83"/>
+      <c r="G55" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H55" s="79">
+      <c r="H55" s="91">
         <v>177</v>
       </c>
-      <c r="I55" s="81"/>
-      <c r="J55" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K55" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L55" s="81"/>
-      <c r="M55" s="81"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K55" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="80" t="s">
+      <c r="A56" s="82" t="s">
         <v>218</v>
       </c>
-      <c r="B56" s="80" t="s">
+      <c r="B56" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="81"/>
+      <c r="C56" s="83"/>
       <c r="D56" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="80" t="s">
+      <c r="E56" s="82" t="s">
         <v>219</v>
       </c>
-      <c r="F56" s="81"/>
-      <c r="G56" s="81" t="s">
+      <c r="F56" s="83"/>
+      <c r="G56" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H56" s="79">
+      <c r="H56" s="91">
         <v>161</v>
       </c>
-      <c r="I56" s="81"/>
-      <c r="J56" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K56" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L56" s="81"/>
-      <c r="M56" s="81"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K56" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="80" t="s">
+      <c r="A57" s="82" t="s">
         <v>220</v>
       </c>
-      <c r="B57" s="80" t="s">
+      <c r="B57" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="80" t="s">
+      <c r="C57" s="82" t="s">
         <v>221</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E57" s="80" t="s">
+      <c r="E57" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="F57" s="81"/>
-      <c r="G57" s="81" t="s">
+      <c r="F57" s="83"/>
+      <c r="G57" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H57" s="79">
+      <c r="H57" s="91">
         <v>1286</v>
       </c>
-      <c r="I57" s="81"/>
-      <c r="J57" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K57" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L57" s="81"/>
-      <c r="M57" s="81" t="s">
+      <c r="I57" s="17"/>
+      <c r="J57" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K57" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="80" t="s">
+      <c r="A58" s="82" t="s">
         <v>223</v>
       </c>
-      <c r="B58" s="80" t="s">
+      <c r="B58" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="80" t="s">
+      <c r="C58" s="82" t="s">
         <v>76</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E58" s="80" t="s">
+      <c r="E58" s="82" t="s">
         <v>224</v>
       </c>
-      <c r="F58" s="81"/>
-      <c r="G58" s="81" t="s">
+      <c r="F58" s="83"/>
+      <c r="G58" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H58" s="79">
+      <c r="H58" s="91">
         <v>12</v>
       </c>
-      <c r="I58" s="81"/>
-      <c r="J58" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K58" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L58" s="7" t="s">
+      <c r="I58" s="17"/>
+      <c r="J58" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K58" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L58" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M58" s="81"/>
+      <c r="M58" s="17"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="84" t="s">
+      <c r="A59" s="86" t="s">
         <v>225</v>
       </c>
-      <c r="B59" s="80" t="s">
+      <c r="B59" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C59" s="80" t="s">
+      <c r="C59" s="82" t="s">
         <v>226</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="80" t="s">
+      <c r="E59" s="82" t="s">
         <v>227</v>
       </c>
-      <c r="F59" s="81"/>
-      <c r="G59" s="81" t="s">
+      <c r="F59" s="83"/>
+      <c r="G59" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H59" s="79">
+      <c r="H59" s="91">
         <v>100</v>
       </c>
-      <c r="I59" s="81"/>
-      <c r="J59" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K59" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L59" s="7" t="s">
+      <c r="I59" s="17"/>
+      <c r="J59" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K59" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L59" s="91" t="s">
         <v>228</v>
       </c>
-      <c r="M59" s="81"/>
+      <c r="M59" s="17"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="86" t="s">
         <v>229</v>
       </c>
-      <c r="B60" s="80" t="s">
+      <c r="B60" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C60" s="80" t="s">
+      <c r="C60" s="82" t="s">
         <v>230</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="80" t="s">
+      <c r="E60" s="82" t="s">
         <v>231</v>
       </c>
-      <c r="F60" s="81"/>
-      <c r="G60" s="81" t="s">
+      <c r="F60" s="83"/>
+      <c r="G60" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H60" s="79">
+      <c r="H60" s="91">
         <v>176</v>
       </c>
-      <c r="I60" s="81"/>
-      <c r="J60" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K60" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L60" s="81"/>
-      <c r="M60" s="81" t="s">
+      <c r="I60" s="17"/>
+      <c r="J60" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K60" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="80" t="s">
+      <c r="A61" s="82" t="s">
         <v>229</v>
       </c>
-      <c r="B61" s="80" t="s">
+      <c r="B61" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="80" t="s">
+      <c r="C61" s="82" t="s">
         <v>230</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="80" t="s">
+      <c r="E61" s="82" t="s">
         <v>231</v>
       </c>
-      <c r="F61" s="81"/>
-      <c r="G61" s="81" t="s">
+      <c r="F61" s="83"/>
+      <c r="G61" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H61" s="79">
+      <c r="H61" s="91">
         <v>800</v>
       </c>
-      <c r="I61" s="81"/>
-      <c r="J61" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K61" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L61" s="81"/>
-      <c r="M61" s="81" t="s">
+      <c r="I61" s="17"/>
+      <c r="J61" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K61" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="80" t="s">
+      <c r="A62" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="B62" s="80" t="s">
+      <c r="B62" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="80" t="s">
+      <c r="C62" s="82" t="s">
         <v>233</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E62" s="80" t="s">
+      <c r="E62" s="82" t="s">
         <v>137</v>
       </c>
-      <c r="F62" s="81"/>
-      <c r="G62" s="81" t="s">
+      <c r="F62" s="83"/>
+      <c r="G62" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H62" s="79">
+      <c r="H62" s="91">
         <v>324</v>
       </c>
-      <c r="I62" s="81"/>
-      <c r="J62" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K62" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L62" s="7" t="s">
+      <c r="I62" s="17"/>
+      <c r="J62" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K62" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L62" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="M62" s="81" t="s">
+      <c r="M62" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63" s="80" t="s">
+      <c r="A63" s="82" t="s">
         <v>234</v>
       </c>
-      <c r="B63" s="80" t="s">
+      <c r="B63" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="80" t="s">
+      <c r="C63" s="82" t="s">
         <v>235</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="80" t="s">
+      <c r="E63" s="82" t="s">
         <v>236</v>
       </c>
-      <c r="F63" s="81"/>
-      <c r="G63" s="81" t="s">
+      <c r="F63" s="83"/>
+      <c r="G63" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H63" s="79">
+      <c r="H63" s="91">
         <v>320</v>
       </c>
-      <c r="I63" s="81" t="s">
+      <c r="I63" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J63" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K63" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L63" s="7" t="s">
+      <c r="J63" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L63" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="M63" s="81" t="s">
+      <c r="M63" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="82" t="s">
+      <c r="A64" s="84" t="s">
         <v>237</v>
       </c>
-      <c r="B64" s="80" t="s">
+      <c r="B64" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="80" t="s">
+      <c r="C64" s="82" t="s">
         <v>238</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="82" t="s">
+      <c r="E64" s="84" t="s">
         <v>239</v>
       </c>
-      <c r="F64" s="81"/>
-      <c r="G64" s="81" t="s">
+      <c r="F64" s="83"/>
+      <c r="G64" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H64" s="79">
+      <c r="H64" s="91">
         <v>176</v>
       </c>
-      <c r="I64" s="81" t="s">
+      <c r="I64" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J64" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K64" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L64" s="7" t="s">
+      <c r="J64" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K64" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L64" s="91" t="s">
         <v>240</v>
       </c>
-      <c r="M64" s="81" t="s">
+      <c r="M64" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="80" t="s">
+      <c r="A65" s="82" t="s">
         <v>241</v>
       </c>
-      <c r="B65" s="80" t="s">
+      <c r="B65" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C65" s="80" t="s">
+      <c r="C65" s="82" t="s">
         <v>242</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E65" s="80" t="s">
+      <c r="E65" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="F65" s="81"/>
-      <c r="G65" s="81" t="s">
+      <c r="F65" s="83"/>
+      <c r="G65" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H65" s="79">
+      <c r="H65" s="91">
         <v>168</v>
       </c>
-      <c r="I65" s="81" t="s">
+      <c r="I65" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J65" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K65" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L65" s="81"/>
-      <c r="M65" s="81" t="s">
+      <c r="J65" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K65" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L65" s="17"/>
+      <c r="M65" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="80" t="s">
+      <c r="A66" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="B66" s="80" t="s">
+      <c r="B66" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="80" t="s">
+      <c r="C66" s="82" t="s">
         <v>245</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E66" s="80" t="s">
+      <c r="E66" s="82" t="s">
         <v>246</v>
       </c>
-      <c r="F66" s="81"/>
-      <c r="G66" s="81" t="s">
+      <c r="F66" s="83"/>
+      <c r="G66" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H66" s="79">
+      <c r="H66" s="91">
         <v>218</v>
       </c>
-      <c r="I66" s="81" t="s">
+      <c r="I66" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J66" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K66" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L66" s="81"/>
-      <c r="M66" s="81" t="s">
+      <c r="J66" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K66" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L66" s="17"/>
+      <c r="M66" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="80" t="s">
+      <c r="A67" s="82" t="s">
         <v>247</v>
       </c>
-      <c r="B67" s="80" t="s">
+      <c r="B67" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="80" t="s">
+      <c r="C67" s="82" t="s">
         <v>248</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E67" s="80" t="s">
+      <c r="E67" s="82" t="s">
         <v>249</v>
       </c>
-      <c r="F67" s="81"/>
-      <c r="G67" s="81" t="s">
+      <c r="F67" s="83"/>
+      <c r="G67" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H67" s="79">
+      <c r="H67" s="91">
         <v>244</v>
       </c>
-      <c r="I67" s="81" t="s">
+      <c r="I67" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J67" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K67" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L67" s="7" t="s">
+      <c r="J67" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K67" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L67" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="M67" s="81" t="s">
+      <c r="M67" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="80" t="s">
+      <c r="A68" s="82" t="s">
         <v>250</v>
       </c>
-      <c r="B68" s="80" t="s">
+      <c r="B68" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C68" s="80" t="s">
+      <c r="C68" s="82" t="s">
         <v>251</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E68" s="80" t="s">
+      <c r="E68" s="82" t="s">
         <v>252</v>
       </c>
-      <c r="F68" s="81"/>
-      <c r="G68" s="81" t="s">
+      <c r="F68" s="83"/>
+      <c r="G68" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H68" s="79">
+      <c r="H68" s="91">
         <v>0</v>
       </c>
-      <c r="I68" s="81"/>
-      <c r="J68" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K68" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L68" s="7" t="s">
+      <c r="I68" s="17"/>
+      <c r="J68" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K68" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L68" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="M68" s="81" t="s">
+      <c r="M68" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="82" t="s">
+      <c r="A69" s="84" t="s">
         <v>253</v>
       </c>
-      <c r="B69" s="80" t="s">
+      <c r="B69" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C69" s="80" t="s">
+      <c r="C69" s="82" t="s">
         <v>254</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="82" t="s">
+      <c r="E69" s="84" t="s">
         <v>249</v>
       </c>
-      <c r="F69" s="81"/>
-      <c r="G69" s="81" t="s">
+      <c r="F69" s="83"/>
+      <c r="G69" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H69" s="79">
+      <c r="H69" s="91">
         <v>162</v>
       </c>
-      <c r="I69" s="81" t="s">
+      <c r="I69" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J69" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K69" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L69" s="81"/>
-      <c r="M69" s="81" t="s">
+      <c r="J69" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L69" s="17"/>
+      <c r="M69" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="80" t="s">
+      <c r="A70" s="82" t="s">
         <v>255</v>
       </c>
-      <c r="B70" s="80" t="s">
+      <c r="B70" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C70" s="80" t="s">
+      <c r="C70" s="82" t="s">
         <v>256</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="80" t="s">
+      <c r="E70" s="82" t="s">
         <v>257</v>
       </c>
-      <c r="F70" s="81"/>
-      <c r="G70" s="81" t="s">
+      <c r="F70" s="83"/>
+      <c r="G70" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H70" s="79">
+      <c r="H70" s="91">
         <v>244</v>
       </c>
-      <c r="I70" s="81" t="s">
+      <c r="I70" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J70" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K70" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L70" s="81"/>
-      <c r="M70" s="81" t="s">
+      <c r="J70" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K70" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L70" s="17"/>
+      <c r="M70" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="80" t="s">
+      <c r="A71" s="82" t="s">
         <v>258</v>
       </c>
-      <c r="B71" s="80" t="s">
+      <c r="B71" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C71" s="80" t="s">
+      <c r="C71" s="82" t="s">
         <v>259</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E71" s="80" t="s">
+      <c r="E71" s="82" t="s">
         <v>260</v>
       </c>
-      <c r="F71" s="81"/>
-      <c r="G71" s="81" t="s">
+      <c r="F71" s="83"/>
+      <c r="G71" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H71" s="79">
+      <c r="H71" s="91">
         <v>390</v>
       </c>
-      <c r="I71" s="81" t="s">
+      <c r="I71" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J71" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K71" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L71" s="81"/>
-      <c r="M71" s="81" t="s">
+      <c r="J71" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K71" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L71" s="17"/>
+      <c r="M71" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="80" t="s">
+      <c r="A72" s="82" t="s">
         <v>261</v>
       </c>
-      <c r="B72" s="80" t="s">
+      <c r="B72" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C72" s="80" t="s">
+      <c r="C72" s="82" t="s">
         <v>262</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E72" s="80" t="s">
+      <c r="E72" s="82" t="s">
         <v>263</v>
       </c>
-      <c r="F72" s="81"/>
-      <c r="G72" s="81" t="s">
+      <c r="F72" s="83"/>
+      <c r="G72" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H72" s="79">
+      <c r="H72" s="91">
         <v>0</v>
       </c>
-      <c r="I72" s="81" t="s">
+      <c r="I72" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J72" s="81" t="s">
+      <c r="J72" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K72" s="81" t="s">
+      <c r="K72" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L72" s="81"/>
-      <c r="M72" s="81" t="s">
+      <c r="L72" s="17"/>
+      <c r="M72" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="80" t="s">
+      <c r="A73" s="82" t="s">
         <v>265</v>
       </c>
-      <c r="B73" s="80" t="s">
+      <c r="B73" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C73" s="80" t="s">
+      <c r="C73" s="82" t="s">
         <v>266</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E73" s="80" t="s">
+      <c r="E73" s="82" t="s">
         <v>267</v>
       </c>
-      <c r="F73" s="81"/>
-      <c r="G73" s="81" t="s">
+      <c r="F73" s="83"/>
+      <c r="G73" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H73" s="79">
+      <c r="H73" s="91">
         <v>160</v>
       </c>
-      <c r="I73" s="81" t="s">
+      <c r="I73" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J73" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K73" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L73" s="7" t="s">
+      <c r="J73" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K73" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L73" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="M73" s="81" t="s">
+      <c r="M73" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="80" t="s">
+      <c r="A74" s="82" t="s">
         <v>268</v>
       </c>
-      <c r="B74" s="80" t="s">
+      <c r="B74" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C74" s="80" t="s">
+      <c r="C74" s="82" t="s">
         <v>269</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E74" s="80" t="s">
+      <c r="E74" s="82" t="s">
         <v>270</v>
       </c>
-      <c r="F74" s="81"/>
-      <c r="G74" s="81" t="s">
+      <c r="F74" s="83"/>
+      <c r="G74" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H74" s="79">
+      <c r="H74" s="91">
         <v>492</v>
       </c>
-      <c r="I74" s="81" t="s">
+      <c r="I74" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="J74" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K74" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L74" s="81"/>
-      <c r="M74" s="81" t="s">
+      <c r="J74" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K74" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L74" s="17"/>
+      <c r="M74" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="80" t="s">
+      <c r="A75" s="82" t="s">
         <v>271</v>
       </c>
-      <c r="B75" s="80" t="s">
+      <c r="B75" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C75" s="80" t="s">
+      <c r="C75" s="82" t="s">
         <v>272</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E75" s="80" t="s">
+      <c r="E75" s="82" t="s">
         <v>273</v>
       </c>
-      <c r="F75" s="81"/>
-      <c r="G75" s="81" t="s">
+      <c r="F75" s="83"/>
+      <c r="G75" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="H75" s="79">
+      <c r="H75" s="91">
         <v>64</v>
       </c>
-      <c r="I75" s="81" t="s">
+      <c r="I75" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J75" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K75" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L75" s="81"/>
-      <c r="M75" s="81" t="s">
+      <c r="J75" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K75" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L75" s="17"/>
+      <c r="M75" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="82" t="s">
+      <c r="A76" s="84" t="s">
         <v>274</v>
       </c>
-      <c r="B76" s="80" t="s">
+      <c r="B76" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="80" t="s">
+      <c r="C76" s="82" t="s">
         <v>275</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="82" t="s">
+      <c r="E76" s="84" t="s">
         <v>276</v>
       </c>
-      <c r="F76" s="81"/>
-      <c r="G76" s="81" t="s">
+      <c r="F76" s="83"/>
+      <c r="G76" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="H76" s="79">
+      <c r="H76" s="91">
         <v>220</v>
       </c>
-      <c r="I76" s="81" t="s">
+      <c r="I76" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J76" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K76" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L76" s="7" t="s">
+      <c r="J76" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K76" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L76" s="91" t="s">
         <v>131</v>
       </c>
-      <c r="M76" s="81" t="s">
+      <c r="M76" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="85" t="s">
+      <c r="A77" s="87" t="s">
         <v>277</v>
       </c>
-      <c r="B77" s="85" t="s">
+      <c r="B77" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C77" s="85" t="s">
+      <c r="C77" s="87" t="s">
         <v>278</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E77" s="85" t="s">
+      <c r="E77" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="F77" s="81"/>
-      <c r="G77" s="85" t="s">
+      <c r="F77" s="83"/>
+      <c r="G77" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H77" s="79">
+      <c r="H77" s="91">
         <v>408</v>
       </c>
-      <c r="I77" s="85" t="s">
+      <c r="I77" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J77" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K77" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L77" s="81"/>
-      <c r="M77" s="85" t="s">
+      <c r="J77" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K77" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L77" s="17"/>
+      <c r="M77" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="85" t="s">
+      <c r="A78" s="87" t="s">
         <v>280</v>
       </c>
-      <c r="B78" s="85" t="s">
+      <c r="B78" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C78" s="85" t="s">
+      <c r="C78" s="87" t="s">
         <v>281</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E78" s="85" t="s">
+      <c r="E78" s="87" t="s">
         <v>282</v>
       </c>
-      <c r="F78" s="81"/>
-      <c r="G78" s="85" t="s">
+      <c r="F78" s="83"/>
+      <c r="G78" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H78" s="79">
+      <c r="H78" s="91">
         <v>832</v>
       </c>
-      <c r="I78" s="85" t="s">
+      <c r="I78" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J78" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K78" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L78" s="81"/>
-      <c r="M78" s="85" t="s">
+      <c r="J78" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K78" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L78" s="17"/>
+      <c r="M78" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="85" t="s">
+      <c r="A79" s="87" t="s">
         <v>283</v>
       </c>
-      <c r="B79" s="85" t="s">
+      <c r="B79" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C79" s="85" t="s">
+      <c r="C79" s="87" t="s">
         <v>76</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E79" s="85" t="s">
+      <c r="E79" s="87" t="s">
         <v>284</v>
       </c>
-      <c r="F79" s="81"/>
-      <c r="G79" s="85" t="s">
+      <c r="F79" s="83"/>
+      <c r="G79" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H79" s="79">
+      <c r="H79" s="91">
         <v>450</v>
       </c>
-      <c r="I79" s="85" t="s">
+      <c r="I79" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J79" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K79" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L79" s="81"/>
-      <c r="M79" s="85" t="s">
+      <c r="J79" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K79" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L79" s="17"/>
+      <c r="M79" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="85" t="s">
+      <c r="A80" s="87" t="s">
         <v>285</v>
       </c>
-      <c r="B80" s="85" t="s">
+      <c r="B80" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="C80" s="85" t="s">
+      <c r="C80" s="87" t="s">
         <v>286</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E80" s="85" t="s">
+      <c r="E80" s="87" t="s">
         <v>287</v>
       </c>
-      <c r="F80" s="81"/>
-      <c r="G80" s="85" t="s">
+      <c r="F80" s="83"/>
+      <c r="G80" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H80" s="79">
+      <c r="H80" s="91">
         <v>312</v>
       </c>
-      <c r="I80" s="85" t="s">
+      <c r="I80" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J80" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K80" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L80" s="81"/>
-      <c r="M80" s="85" t="s">
+      <c r="J80" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K80" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L80" s="17"/>
+      <c r="M80" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="85" t="s">
+      <c r="A81" s="87" t="s">
         <v>288</v>
       </c>
-      <c r="B81" s="85" t="s">
+      <c r="B81" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="C81" s="85" t="s">
+      <c r="C81" s="87" t="s">
         <v>289</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E81" s="85" t="s">
+      <c r="E81" s="87" t="s">
         <v>290</v>
       </c>
-      <c r="F81" s="81"/>
-      <c r="G81" s="85" t="s">
+      <c r="F81" s="83"/>
+      <c r="G81" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H81" s="79">
+      <c r="H81" s="91">
         <v>387</v>
       </c>
-      <c r="I81" s="85" t="s">
+      <c r="I81" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J81" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K81" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L81" s="81"/>
-      <c r="M81" s="85" t="s">
+      <c r="J81" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K81" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L81" s="17"/>
+      <c r="M81" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="85" t="s">
+      <c r="A82" s="87" t="s">
         <v>291</v>
       </c>
-      <c r="B82" s="85" t="s">
+      <c r="B82" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="85" t="s">
+      <c r="C82" s="87" t="s">
         <v>292</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E82" s="85" t="s">
+      <c r="E82" s="87" t="s">
         <v>293</v>
       </c>
-      <c r="F82" s="81"/>
-      <c r="G82" s="85" t="s">
+      <c r="F82" s="83"/>
+      <c r="G82" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H82" s="79">
+      <c r="H82" s="91">
         <v>1400</v>
       </c>
-      <c r="I82" s="85" t="s">
+      <c r="I82" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J82" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K82" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L82" s="81"/>
-      <c r="M82" s="85" t="s">
+      <c r="J82" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K82" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L82" s="17"/>
+      <c r="M82" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="85" t="s">
+      <c r="A83" s="87" t="s">
         <v>294</v>
       </c>
-      <c r="B83" s="85" t="s">
+      <c r="B83" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="C83" s="85" t="s">
+      <c r="C83" s="87" t="s">
         <v>295</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E83" s="85" t="s">
+      <c r="E83" s="87" t="s">
         <v>296</v>
       </c>
-      <c r="F83" s="81"/>
-      <c r="G83" s="85" t="s">
+      <c r="F83" s="83"/>
+      <c r="G83" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H83" s="79">
+      <c r="H83" s="91">
         <v>720</v>
       </c>
-      <c r="I83" s="85" t="s">
+      <c r="I83" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J83" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K83" s="88" t="s">
-        <v>53</v>
-      </c>
-      <c r="L83" s="81"/>
-      <c r="M83" s="85" t="s">
+      <c r="J83" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K83" s="93" t="s">
+        <v>53</v>
+      </c>
+      <c r="L83" s="17"/>
+      <c r="M83" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="85" t="s">
+      <c r="A84" s="87" t="s">
         <v>297</v>
       </c>
-      <c r="B84" s="85" t="s">
+      <c r="B84" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C84" s="85" t="s">
+      <c r="C84" s="87" t="s">
         <v>298</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="85" t="s">
+      <c r="E84" s="87" t="s">
         <v>299</v>
       </c>
-      <c r="F84" s="81"/>
-      <c r="G84" s="85" t="s">
+      <c r="F84" s="83"/>
+      <c r="G84" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H84" s="79">
+      <c r="H84" s="91">
         <v>219</v>
       </c>
-      <c r="I84" s="85" t="s">
+      <c r="I84" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J84" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K84" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L84" s="81"/>
-      <c r="M84" s="85" t="s">
+      <c r="J84" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K84" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L84" s="17"/>
+      <c r="M84" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="85" t="s">
+      <c r="A85" s="87" t="s">
         <v>300</v>
       </c>
-      <c r="B85" s="85" t="s">
+      <c r="B85" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="C85" s="85" t="s">
+      <c r="C85" s="87" t="s">
         <v>301</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="85" t="s">
+      <c r="E85" s="87" t="s">
         <v>302</v>
       </c>
-      <c r="F85" s="81"/>
-      <c r="G85" s="85" t="s">
+      <c r="F85" s="83"/>
+      <c r="G85" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="H85" s="79">
+      <c r="H85" s="91">
         <v>1524</v>
       </c>
-      <c r="I85" s="85" t="s">
+      <c r="I85" s="92" t="s">
         <v>168</v>
       </c>
-      <c r="J85" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K85" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L85" s="81"/>
-      <c r="M85" s="85" t="s">
+      <c r="J85" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K85" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L85" s="17"/>
+      <c r="M85" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="85" t="s">
+      <c r="A86" s="87" t="s">
         <v>303</v>
       </c>
-      <c r="B86" s="85" t="s">
+      <c r="B86" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C86" s="85" t="s">
+      <c r="C86" s="87" t="s">
         <v>304</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="85" t="s">
+      <c r="E86" s="87" t="s">
         <v>305</v>
       </c>
       <c r="F86" s="10">
         <v>2870896608</v>
       </c>
-      <c r="G86" s="85" t="s">
+      <c r="G86" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H86" s="79">
+      <c r="H86" s="91">
         <v>320</v>
       </c>
-      <c r="I86" s="85" t="s">
+      <c r="I86" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J86" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K86" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L86" s="81"/>
-      <c r="M86" s="85" t="s">
+      <c r="J86" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K86" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L86" s="17"/>
+      <c r="M86" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="85" t="s">
+      <c r="A87" s="87" t="s">
         <v>306</v>
       </c>
-      <c r="B87" s="85" t="s">
+      <c r="B87" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="C87" s="85" t="s">
+      <c r="C87" s="87" t="s">
         <v>307</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E87" s="85" t="s">
+      <c r="E87" s="87" t="s">
         <v>203</v>
       </c>
       <c r="F87" s="10">
         <v>13970595273</v>
       </c>
-      <c r="G87" s="85" t="s">
+      <c r="G87" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H87" s="79">
+      <c r="H87" s="91">
         <v>2342</v>
       </c>
-      <c r="I87" s="85" t="s">
+      <c r="I87" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J87" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K87" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L87" s="81"/>
-      <c r="M87" s="85" t="s">
+      <c r="J87" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K87" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L87" s="17"/>
+      <c r="M87" s="92" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="85" t="s">
+      <c r="A88" s="87" t="s">
         <v>308</v>
       </c>
-      <c r="B88" s="85" t="s">
+      <c r="B88" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C88" s="85" t="s">
+      <c r="C88" s="87" t="s">
         <v>309</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E88" s="85" t="s">
+      <c r="E88" s="87" t="s">
         <v>310</v>
       </c>
       <c r="F88" s="10">
         <v>259948145</v>
       </c>
-      <c r="G88" s="85" t="s">
+      <c r="G88" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H88" s="79">
+      <c r="H88" s="91">
         <v>34</v>
       </c>
-      <c r="I88" s="85" t="s">
+      <c r="I88" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J88" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K88" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L88" s="81"/>
-      <c r="M88" s="85" t="s">
+      <c r="J88" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K88" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L88" s="17"/>
+      <c r="M88" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="86" t="s">
+      <c r="A89" s="88" t="s">
         <v>311</v>
       </c>
-      <c r="B89" s="85" t="s">
+      <c r="B89" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C89" s="85" t="s">
+      <c r="C89" s="87" t="s">
         <v>309</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E89" s="85" t="s">
+      <c r="E89" s="87" t="s">
         <v>312</v>
       </c>
       <c r="F89" s="10">
         <v>834933960</v>
       </c>
-      <c r="G89" s="85" t="s">
+      <c r="G89" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H89" s="79">
+      <c r="H89" s="91">
         <v>224</v>
       </c>
-      <c r="I89" s="85" t="s">
+      <c r="I89" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J89" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K89" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L89" s="81"/>
-      <c r="M89" s="85" t="s">
+      <c r="J89" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K89" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L89" s="17"/>
+      <c r="M89" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="85" t="s">
+      <c r="A90" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="B90" s="85" t="s">
+      <c r="B90" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="C90" s="85" t="s">
+      <c r="C90" s="87" t="s">
         <v>309</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E90" s="85" t="s">
+      <c r="E90" s="87" t="s">
         <v>313</v>
       </c>
       <c r="F90" s="10">
         <v>723157595</v>
       </c>
-      <c r="G90" s="85" t="s">
+      <c r="G90" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H90" s="79">
+      <c r="H90" s="91">
         <v>138</v>
       </c>
-      <c r="I90" s="85" t="s">
+      <c r="I90" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J90" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K90" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L90" s="81"/>
-      <c r="M90" s="85" t="s">
+      <c r="J90" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K90" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L90" s="17"/>
+      <c r="M90" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="85" t="s">
+      <c r="A91" s="87" t="s">
         <v>314</v>
       </c>
-      <c r="B91" s="85" t="s">
+      <c r="B91" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="85" t="s">
+      <c r="C91" s="87" t="s">
         <v>309</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E91" s="85" t="s">
+      <c r="E91" s="87" t="s">
         <v>315</v>
       </c>
       <c r="F91" s="10">
         <v>805795560</v>
       </c>
-      <c r="G91" s="85" t="s">
+      <c r="G91" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H91" s="79">
+      <c r="H91" s="91">
         <v>56</v>
       </c>
-      <c r="I91" s="85" t="s">
+      <c r="I91" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J91" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K91" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L91" s="81"/>
-      <c r="M91" s="85" t="s">
+      <c r="J91" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K91" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L91" s="17"/>
+      <c r="M91" s="92" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="80" t="s">
+      <c r="A92" s="82" t="s">
         <v>316</v>
       </c>
-      <c r="B92" s="80" t="s">
+      <c r="B92" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C92" s="80" t="s">
+      <c r="C92" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E92" s="80" t="s">
+      <c r="E92" s="82" t="s">
         <v>317</v>
       </c>
       <c r="F92" s="10">
         <v>2165000000</v>
       </c>
-      <c r="G92" s="81" t="s">
+      <c r="G92" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H92" s="79">
+      <c r="H92" s="91">
         <v>928</v>
       </c>
-      <c r="I92" s="81" t="s">
+      <c r="I92" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J92" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K92" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L92" s="81"/>
-      <c r="M92" s="81" t="s">
+      <c r="J92" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K92" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L92" s="17"/>
+      <c r="M92" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="80" t="s">
+      <c r="A93" s="82" t="s">
         <v>318</v>
       </c>
-      <c r="B93" s="80" t="s">
+      <c r="B93" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C93" s="80" t="s">
+      <c r="C93" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E93" s="80" t="s">
+      <c r="E93" s="82" t="s">
         <v>319</v>
       </c>
       <c r="F93" s="10">
         <v>2959258280</v>
       </c>
-      <c r="G93" s="81" t="s">
+      <c r="G93" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H93" s="79">
+      <c r="H93" s="91">
         <v>600</v>
       </c>
-      <c r="I93" s="81" t="s">
+      <c r="I93" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J93" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K93" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L93" s="81"/>
-      <c r="M93" s="81" t="s">
+      <c r="J93" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K93" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L93" s="17"/>
+      <c r="M93" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="81" t="s">
+      <c r="A94" s="83" t="s">
         <v>320</v>
       </c>
-      <c r="B94" s="85" t="s">
+      <c r="B94" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C94" s="85" t="s">
+      <c r="C94" s="87" t="s">
         <v>309</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="85" t="s">
+      <c r="E94" s="87" t="s">
         <v>321</v>
       </c>
       <c r="F94" s="10">
         <v>199672220</v>
       </c>
-      <c r="G94" s="85" t="s">
+      <c r="G94" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H94" s="79">
+      <c r="H94" s="91">
         <v>33</v>
       </c>
-      <c r="I94" s="85" t="s">
+      <c r="I94" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="J94" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K94" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="L94" s="81"/>
-      <c r="M94" s="85" t="s">
+      <c r="J94" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K94" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="L94" s="17"/>
+      <c r="M94" s="92" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="84" t="s">
+      <c r="A95" s="86" t="s">
         <v>322</v>
       </c>
-      <c r="B95" s="80" t="s">
+      <c r="B95" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C95" s="80" t="s">
+      <c r="C95" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E95" s="80" t="s">
+      <c r="E95" s="82" t="s">
         <v>323</v>
       </c>
       <c r="F95" s="7">
         <v>5915704000</v>
       </c>
-      <c r="G95" s="81" t="s">
+      <c r="G95" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H95" s="79">
+      <c r="H95" s="91">
         <v>810</v>
       </c>
-      <c r="I95" s="81" t="s">
+      <c r="I95" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J95" s="81" t="s">
+      <c r="J95" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K95" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L95" s="81"/>
-      <c r="M95" s="81" t="s">
+      <c r="K95" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L95" s="17"/>
+      <c r="M95" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="84" t="s">
+      <c r="A96" s="86" t="s">
         <v>324</v>
       </c>
-      <c r="B96" s="83" t="s">
+      <c r="B96" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C96" s="83" t="s">
+      <c r="C96" s="85" t="s">
         <v>309</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E96" s="83" t="s">
+      <c r="E96" s="85" t="s">
         <v>325</v>
       </c>
       <c r="F96" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G96" s="81" t="s">
+      <c r="G96" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H96" s="79">
+      <c r="H96" s="91">
         <v>720</v>
       </c>
-      <c r="I96" s="81" t="s">
+      <c r="I96" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J96" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K96" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L96" s="81"/>
-      <c r="M96" s="81" t="s">
+      <c r="J96" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K96" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L96" s="17"/>
+      <c r="M96" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A97" s="84" t="s">
+      <c r="A97" s="86" t="s">
         <v>324</v>
       </c>
-      <c r="B97" s="83" t="s">
+      <c r="B97" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C97" s="83" t="s">
+      <c r="C97" s="85" t="s">
         <v>309</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E97" s="83" t="s">
+      <c r="E97" s="85" t="s">
         <v>325</v>
       </c>
       <c r="F97" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G97" s="81" t="s">
+      <c r="G97" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H97" s="79">
+      <c r="H97" s="91">
         <v>176</v>
       </c>
-      <c r="I97" s="81" t="s">
+      <c r="I97" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J97" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K97" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L97" s="81"/>
-      <c r="M97" s="81" t="s">
+      <c r="J97" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K97" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L97" s="17"/>
+      <c r="M97" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="84" t="s">
+      <c r="A98" s="86" t="s">
         <v>326</v>
       </c>
-      <c r="B98" s="80" t="s">
+      <c r="B98" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C98" s="80" t="s">
+      <c r="C98" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E98" s="80" t="s">
+      <c r="E98" s="82" t="s">
         <v>327</v>
       </c>
       <c r="F98" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G98" s="81" t="s">
+      <c r="G98" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H98" s="79">
+      <c r="H98" s="91">
         <v>-3</v>
       </c>
-      <c r="I98" s="81" t="s">
+      <c r="I98" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J98" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K98" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L98" s="81"/>
-      <c r="M98" s="81" t="s">
+      <c r="J98" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K98" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L98" s="17"/>
+      <c r="M98" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="80" t="s">
+      <c r="A99" s="82" t="s">
         <v>326</v>
       </c>
-      <c r="B99" s="80" t="s">
+      <c r="B99" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C99" s="80" t="s">
+      <c r="C99" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E99" s="80" t="s">
+      <c r="E99" s="82" t="s">
         <v>327</v>
       </c>
       <c r="F99" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G99" s="81" t="s">
+      <c r="G99" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="H99" s="79">
+      <c r="H99" s="91">
         <v>400</v>
       </c>
-      <c r="I99" s="81" t="s">
+      <c r="I99" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="J99" s="81" t="s">
+      <c r="J99" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K99" s="81" t="s">
+      <c r="K99" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L99" s="81"/>
-      <c r="M99" s="81" t="s">
+      <c r="L99" s="17"/>
+      <c r="M99" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="80" t="s">
+      <c r="A100" s="82" t="s">
         <v>352</v>
       </c>
-      <c r="B100" s="80" t="s">
+      <c r="B100" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C100" s="80" t="s">
+      <c r="C100" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E100" s="85" t="s">
+      <c r="E100" s="87" t="s">
         <v>203</v>
       </c>
-      <c r="F100" s="81"/>
-      <c r="G100" s="81" t="s">
+      <c r="F100" s="83"/>
+      <c r="G100" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H100" s="79">
+      <c r="H100" s="91">
         <v>-8</v>
       </c>
-      <c r="I100" s="81" t="s">
+      <c r="I100" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J100" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K100" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L100" s="81"/>
-      <c r="M100" s="81" t="s">
+      <c r="J100" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K100" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L100" s="17"/>
+      <c r="M100" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="80" t="s">
+      <c r="A101" s="82" t="s">
         <v>328</v>
       </c>
-      <c r="B101" s="80" t="s">
+      <c r="B101" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C101" s="80" t="s">
+      <c r="C101" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="85" t="s">
+      <c r="E101" s="87" t="s">
         <v>329</v>
       </c>
       <c r="F101" s="7">
         <v>11684429947</v>
       </c>
-      <c r="G101" s="81" t="s">
+      <c r="G101" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H101" s="79">
+      <c r="H101" s="91">
         <v>2556</v>
       </c>
-      <c r="I101" s="81" t="s">
+      <c r="I101" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J101" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K101" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L101" s="81"/>
-      <c r="M101" s="81" t="s">
+      <c r="J101" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K101" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L101" s="17"/>
+      <c r="M101" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="80" t="s">
+      <c r="A102" s="82" t="s">
         <v>330</v>
       </c>
-      <c r="B102" s="80" t="s">
+      <c r="B102" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C102" s="80" t="s">
+      <c r="C102" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E102" s="85" t="s">
+      <c r="E102" s="87" t="s">
         <v>331</v>
       </c>
-      <c r="F102" s="81"/>
-      <c r="G102" s="81" t="s">
+      <c r="F102" s="83"/>
+      <c r="G102" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H102" s="79">
+      <c r="H102" s="91">
         <v>968</v>
       </c>
-      <c r="I102" s="81" t="s">
+      <c r="I102" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J102" s="81" t="s">
+      <c r="J102" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K102" s="81" t="s">
+      <c r="K102" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L102" s="81"/>
-      <c r="M102" s="81" t="s">
+      <c r="L102" s="17"/>
+      <c r="M102" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="80" t="s">
+      <c r="A103" s="82" t="s">
         <v>332</v>
       </c>
-      <c r="B103" s="80" t="s">
+      <c r="B103" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C103" s="80" t="s">
+      <c r="C103" s="82" t="s">
         <v>333</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E103" s="85" t="s">
+      <c r="E103" s="87" t="s">
         <v>334</v>
       </c>
       <c r="F103" s="7">
         <v>2329683517</v>
       </c>
-      <c r="G103" s="81" t="s">
+      <c r="G103" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="H103" s="79">
-        <v>198</v>
-      </c>
-      <c r="I103" s="81" t="s">
+      <c r="H103" s="91">
+        <v>0</v>
+      </c>
+      <c r="I103" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J103" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K103" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L103" s="81"/>
-      <c r="M103" s="81" t="s">
+      <c r="J103" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K103" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L103" s="17"/>
+      <c r="M103" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="80" t="s">
+      <c r="A104" s="82" t="s">
         <v>335</v>
       </c>
-      <c r="B104" s="80" t="s">
+      <c r="B104" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C104" s="80" t="s">
+      <c r="C104" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="85" t="s">
+      <c r="E104" s="87" t="s">
         <v>336</v>
       </c>
       <c r="F104" s="7">
         <v>1545593000</v>
       </c>
-      <c r="G104" s="81" t="s">
+      <c r="G104" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H104" s="79">
-        <v>216</v>
-      </c>
-      <c r="I104" s="81" t="s">
+      <c r="H104" s="91">
+        <v>0</v>
+      </c>
+      <c r="I104" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J104" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K104" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="L104" s="81"/>
-      <c r="M104" s="81" t="s">
+      <c r="J104" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K104" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L104" s="17"/>
+      <c r="M104" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="80" t="s">
+      <c r="A105" s="82" t="s">
         <v>347</v>
       </c>
-      <c r="B105" s="80" t="s">
+      <c r="B105" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C105" s="80" t="s">
+      <c r="C105" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E105" s="85" t="s">
+      <c r="E105" s="87" t="s">
         <v>348</v>
       </c>
-      <c r="F105" s="81"/>
-      <c r="G105" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="H105" s="79">
+      <c r="F105" s="83"/>
+      <c r="G105" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="H105" s="91">
         <v>25</v>
       </c>
-      <c r="I105" s="81" t="s">
+      <c r="I105" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J105" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K105" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="L105" s="81"/>
-      <c r="M105" s="81" t="s">
+      <c r="J105" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K105" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L105" s="17"/>
+      <c r="M105" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="80" t="s">
+      <c r="A106" s="82" t="s">
         <v>349</v>
       </c>
-      <c r="B106" s="80" t="s">
+      <c r="B106" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C106" s="80" t="s">
+      <c r="C106" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E106" s="85" t="s">
+      <c r="E106" s="87" t="s">
         <v>350</v>
       </c>
       <c r="F106" s="7">
         <v>863631818.20000005</v>
       </c>
-      <c r="G106" s="81" t="s">
+      <c r="G106" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="H106" s="79">
+      <c r="H106" s="91">
         <v>0</v>
       </c>
-      <c r="I106" s="81" t="s">
+      <c r="I106" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J106" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K106" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L106" s="81"/>
-      <c r="M106" s="81" t="s">
+      <c r="J106" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K106" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L106" s="17"/>
+      <c r="M106" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="80" t="s">
+      <c r="A107" s="82" t="s">
         <v>353</v>
       </c>
-      <c r="B107" s="80" t="s">
+      <c r="B107" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C107" s="80" t="s">
+      <c r="C107" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E107" s="85" t="s">
+      <c r="E107" s="87" t="s">
         <v>354</v>
       </c>
       <c r="F107" s="7">
         <v>3338181818</v>
       </c>
-      <c r="G107" s="81" t="s">
+      <c r="G107" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="H107" s="79">
-        <v>576</v>
-      </c>
-      <c r="I107" s="81" t="s">
+      <c r="H107" s="91">
+        <v>0</v>
+      </c>
+      <c r="I107" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J107" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K107" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L107" s="81"/>
-      <c r="M107" s="81" t="s">
+      <c r="J107" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K107" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L107" s="17"/>
+      <c r="M107" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="80" t="s">
+      <c r="A108" s="82" t="s">
         <v>355</v>
       </c>
-      <c r="B108" s="80" t="s">
+      <c r="B108" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C108" s="80" t="s">
+      <c r="C108" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E108" s="85" t="s">
+      <c r="E108" s="87" t="s">
         <v>231</v>
       </c>
-      <c r="F108" s="81"/>
-      <c r="G108" s="81" t="s">
+      <c r="F108" s="83"/>
+      <c r="G108" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="H108" s="79">
+      <c r="H108" s="91">
         <v>126</v>
       </c>
-      <c r="I108" s="81" t="s">
+      <c r="I108" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="J108" s="81" t="s">
+      <c r="J108" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K108" s="81" t="s">
+      <c r="K108" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L108" s="81"/>
-      <c r="M108" s="81" t="s">
+      <c r="L108" s="17"/>
+      <c r="M108" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="80" t="s">
+      <c r="A109" s="82" t="s">
         <v>356</v>
       </c>
-      <c r="B109" s="80" t="s">
+      <c r="B109" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C109" s="80" t="s">
+      <c r="C109" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E109" s="85" t="s">
+      <c r="E109" s="87" t="s">
         <v>357</v>
       </c>
       <c r="F109" s="7">
         <v>719278000</v>
       </c>
-      <c r="G109" s="81" t="s">
+      <c r="G109" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H109" s="79">
+      <c r="H109" s="91">
         <v>0</v>
       </c>
-      <c r="I109" s="81" t="s">
+      <c r="I109" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J109" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K109" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L109" s="81"/>
-      <c r="M109" s="81" t="s">
+      <c r="J109" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K109" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L109" s="17"/>
+      <c r="M109" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="80" t="s">
+      <c r="A110" s="82" t="s">
         <v>358</v>
       </c>
-      <c r="B110" s="80" t="s">
+      <c r="B110" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C110" s="80" t="s">
+      <c r="C110" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E110" s="85" t="s">
+      <c r="E110" s="87" t="s">
         <v>359</v>
       </c>
       <c r="F110" s="7">
         <v>2186917438</v>
       </c>
-      <c r="G110" s="81" t="s">
+      <c r="G110" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H110" s="79">
+      <c r="H110" s="91">
         <v>0</v>
       </c>
-      <c r="I110" s="81" t="s">
+      <c r="I110" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J110" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K110" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L110" s="81"/>
-      <c r="M110" s="81" t="s">
+      <c r="J110" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K110" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L110" s="17"/>
+      <c r="M110" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A111" s="80" t="s">
+      <c r="A111" s="82" t="s">
         <v>366</v>
       </c>
-      <c r="B111" s="80" t="s">
+      <c r="B111" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C111" s="80" t="s">
+      <c r="C111" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E111" s="85" t="s">
+      <c r="E111" s="87" t="s">
         <v>367</v>
       </c>
       <c r="F111" s="7">
         <v>69307272.730000004</v>
       </c>
-      <c r="G111" s="81" t="s">
+      <c r="G111" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H111" s="79">
+      <c r="H111" s="91">
         <v>0</v>
       </c>
-      <c r="I111" s="81" t="s">
+      <c r="I111" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J111" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K111" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L111" s="81"/>
-      <c r="M111" s="81" t="s">
+      <c r="J111" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K111" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L111" s="17"/>
+      <c r="M111" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A112" s="80" t="s">
+      <c r="A112" s="82" t="s">
         <v>368</v>
       </c>
-      <c r="B112" s="80" t="s">
+      <c r="B112" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C112" s="80" t="s">
+      <c r="C112" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="85" t="s">
+      <c r="E112" s="87" t="s">
         <v>369</v>
       </c>
       <c r="F112" s="7">
         <v>140818181.80000001</v>
       </c>
-      <c r="G112" s="81" t="s">
+      <c r="G112" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H112" s="79">
+      <c r="H112" s="91">
         <v>0</v>
       </c>
-      <c r="I112" s="81" t="s">
+      <c r="I112" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J112" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K112" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L112" s="81"/>
-      <c r="M112" s="81" t="s">
+      <c r="J112" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K112" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L112" s="17"/>
+      <c r="M112" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="80" t="s">
+      <c r="A113" s="82" t="s">
         <v>370</v>
       </c>
-      <c r="B113" s="80" t="s">
+      <c r="B113" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C113" s="80" t="s">
+      <c r="C113" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E113" s="85" t="s">
+      <c r="E113" s="87" t="s">
         <v>371</v>
       </c>
       <c r="F113" s="7">
         <v>1196969505</v>
       </c>
-      <c r="G113" s="81" t="s">
+      <c r="G113" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H113" s="79">
-        <v>288</v>
-      </c>
-      <c r="I113" s="81" t="s">
+      <c r="H113" s="91">
+        <v>0</v>
+      </c>
+      <c r="I113" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J113" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K113" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L113" s="81"/>
-      <c r="M113" s="81" t="s">
+      <c r="J113" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K113" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L113" s="17"/>
+      <c r="M113" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="80" t="s">
+      <c r="A114" s="82" t="s">
         <v>372</v>
       </c>
-      <c r="B114" s="80" t="s">
+      <c r="B114" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C114" s="80" t="s">
+      <c r="C114" s="82" t="s">
         <v>373</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E114" s="85" t="s">
+      <c r="E114" s="87" t="s">
         <v>374</v>
       </c>
       <c r="F114" s="7">
         <v>3761066864</v>
       </c>
-      <c r="G114" s="81" t="s">
+      <c r="G114" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H114" s="79">
-        <v>96</v>
-      </c>
-      <c r="I114" s="81" t="s">
+      <c r="H114" s="91">
+        <v>0</v>
+      </c>
+      <c r="I114" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J114" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K114" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="L114" s="81"/>
-      <c r="M114" s="81" t="s">
+      <c r="J114" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K114" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L114" s="17"/>
+      <c r="M114" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="80" t="s">
+      <c r="A115" s="82" t="s">
         <v>375</v>
       </c>
-      <c r="B115" s="80" t="s">
+      <c r="B115" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C115" s="80" t="s">
+      <c r="C115" s="82" t="s">
         <v>376</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E115" s="85" t="s">
+      <c r="E115" s="87" t="s">
         <v>377</v>
       </c>
       <c r="F115" s="7">
         <v>1188000000</v>
       </c>
-      <c r="G115" s="81" t="s">
+      <c r="G115" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H115" s="79">
+      <c r="H115" s="91">
         <v>240</v>
       </c>
-      <c r="I115" s="81" t="s">
+      <c r="I115" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J115" s="81" t="s">
+      <c r="J115" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K115" s="81" t="s">
+      <c r="K115" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L115" s="81"/>
-      <c r="M115" s="81" t="s">
+      <c r="L115" s="17"/>
+      <c r="M115" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="80" t="s">
+      <c r="A116" s="82" t="s">
         <v>378</v>
       </c>
-      <c r="B116" s="80" t="s">
+      <c r="B116" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C116" s="80" t="s">
+      <c r="C116" s="82" t="s">
         <v>379</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E116" s="85" t="s">
+      <c r="E116" s="87" t="s">
         <v>380</v>
       </c>
       <c r="F116" s="7">
         <v>8578824307</v>
       </c>
-      <c r="G116" s="81" t="s">
+      <c r="G116" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H116" s="79">
+      <c r="H116" s="91">
         <v>700</v>
       </c>
-      <c r="I116" s="81" t="s">
+      <c r="I116" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J116" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K116" s="81" t="s">
+      <c r="J116" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K116" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="L116" s="81"/>
-      <c r="M116" s="81" t="s">
+      <c r="L116" s="17"/>
+      <c r="M116" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="80" t="s">
+      <c r="A117" s="82" t="s">
         <v>381</v>
       </c>
-      <c r="B117" s="80" t="s">
+      <c r="B117" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C117" s="80" t="s">
+      <c r="C117" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E117" s="85" t="s">
+      <c r="E117" s="87" t="s">
         <v>382</v>
       </c>
       <c r="F117" s="7">
         <v>2842500250</v>
       </c>
-      <c r="G117" s="81" t="s">
+      <c r="G117" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H117" s="79">
+      <c r="H117" s="91">
         <v>626</v>
       </c>
-      <c r="I117" s="81" t="s">
+      <c r="I117" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J117" s="81" t="s">
+      <c r="J117" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K117" s="81" t="s">
+      <c r="K117" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L117" s="81"/>
-      <c r="M117" s="81" t="s">
+      <c r="L117" s="17"/>
+      <c r="M117" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="80" t="s">
+      <c r="A118" s="82" t="s">
         <v>383</v>
       </c>
-      <c r="B118" s="81"/>
-      <c r="C118" s="81"/>
+      <c r="B118" s="83"/>
+      <c r="C118" s="83"/>
       <c r="D118" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E118" s="85" t="s">
+      <c r="E118" s="87" t="s">
         <v>384</v>
       </c>
       <c r="F118" s="9">
         <v>459000000</v>
       </c>
-      <c r="G118" s="81" t="s">
+      <c r="G118" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="H118" s="79">
+      <c r="H118" s="91">
         <v>80</v>
       </c>
-      <c r="I118" s="81" t="s">
+      <c r="I118" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J118" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K118" s="81" t="s">
+      <c r="J118" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K118" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="L118" s="81"/>
-      <c r="M118" s="81"/>
+      <c r="L118" s="17"/>
+      <c r="M118" s="17"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="80" t="s">
+      <c r="A119" s="82" t="s">
         <v>385</v>
       </c>
-      <c r="B119" s="80" t="s">
+      <c r="B119" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C119" s="80" t="s">
+      <c r="C119" s="82" t="s">
         <v>309</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E119" s="85" t="s">
+      <c r="E119" s="87" t="s">
         <v>385</v>
       </c>
       <c r="F119" s="7">
         <v>602440000</v>
       </c>
-      <c r="G119" s="81" t="s">
+      <c r="G119" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H119" s="79">
+      <c r="H119" s="91">
         <v>70</v>
       </c>
-      <c r="I119" s="81" t="s">
+      <c r="I119" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J119" s="81" t="s">
+      <c r="J119" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K119" s="81" t="s">
+      <c r="K119" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L119" s="81"/>
-      <c r="M119" s="81"/>
+      <c r="L119" s="17"/>
+      <c r="M119" s="17"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="85" t="s">
+      <c r="A120" s="87" t="s">
         <v>386</v>
       </c>
-      <c r="B120" s="80" t="s">
+      <c r="B120" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C120" s="85" t="s">
+      <c r="C120" s="87" t="s">
         <v>387</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E120" s="85" t="s">
+      <c r="E120" s="87" t="s">
         <v>388</v>
       </c>
       <c r="F120" s="7">
         <v>1847633000</v>
       </c>
-      <c r="G120" s="81" t="s">
+      <c r="G120" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H120" s="79">
+      <c r="H120" s="91">
+        <v>305</v>
+      </c>
+      <c r="I120" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J120" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K120" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I120" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J120" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K120" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="L120" s="81"/>
-      <c r="M120" s="81" t="s">
+      <c r="L120" s="17"/>
+      <c r="M120" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="85" t="s">
+      <c r="A121" s="87" t="s">
         <v>389</v>
       </c>
-      <c r="B121" s="80" t="s">
+      <c r="B121" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C121" s="85" t="s">
+      <c r="C121" s="87" t="s">
         <v>390</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E121" s="85" t="s">
+      <c r="E121" s="87" t="s">
         <v>391</v>
       </c>
       <c r="F121" s="7">
         <v>685000000</v>
       </c>
-      <c r="G121" s="81" t="s">
+      <c r="G121" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H121" s="79">
-        <v>156</v>
-      </c>
-      <c r="I121" s="81" t="s">
+      <c r="H121" s="91">
+        <v>0</v>
+      </c>
+      <c r="I121" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J121" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K121" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="L121" s="81"/>
-      <c r="M121" s="81" t="s">
+      <c r="J121" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K121" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L121" s="17"/>
+      <c r="M121" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="80" t="s">
+      <c r="A122" s="82" t="s">
         <v>392</v>
       </c>
-      <c r="B122" s="80" t="s">
+      <c r="B122" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="C122" s="85" t="s">
+      <c r="C122" s="87" t="s">
         <v>393</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E122" s="85" t="s">
+      <c r="E122" s="87" t="s">
         <v>392</v>
       </c>
       <c r="F122" s="7">
         <v>854545455</v>
       </c>
-      <c r="G122" s="81" t="s">
+      <c r="G122" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="H122" s="79">
+      <c r="H122" s="91">
         <v>0</v>
       </c>
-      <c r="I122" s="81" t="s">
+      <c r="I122" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J122" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K122" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="L122" s="81"/>
-      <c r="M122" s="81" t="s">
+      <c r="J122" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K122" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L122" s="17"/>
+      <c r="M122" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="85" t="s">
+      <c r="A123" s="87" t="s">
         <v>394</v>
       </c>
-      <c r="B123" s="80" t="s">
+      <c r="B123" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C123" s="85" t="s">
+      <c r="C123" s="87" t="s">
         <v>395</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="85" t="s">
+      <c r="E123" s="87" t="s">
         <v>396</v>
       </c>
       <c r="F123" s="7">
         <v>800000000</v>
       </c>
-      <c r="G123" s="81" t="s">
+      <c r="G123" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="H123" s="79">
+      <c r="H123" s="91">
         <v>159</v>
       </c>
-      <c r="I123" s="81" t="s">
+      <c r="I123" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J123" s="81" t="s">
+      <c r="J123" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K123" s="81" t="s">
+      <c r="K123" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L123" s="81"/>
-      <c r="M123" s="81" t="s">
+      <c r="L123" s="17"/>
+      <c r="M123" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="85" t="s">
+      <c r="A124" s="87" t="s">
         <v>397</v>
       </c>
-      <c r="B124" s="80" t="s">
+      <c r="B124" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C124" s="85" t="s">
+      <c r="C124" s="87" t="s">
         <v>398</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E124" s="85" t="s">
+      <c r="E124" s="87" t="s">
         <v>399</v>
       </c>
       <c r="F124" s="7">
         <v>1374545455</v>
       </c>
-      <c r="G124" s="81" t="s">
+      <c r="G124" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="H124" s="79">
-        <v>323</v>
-      </c>
-      <c r="I124" s="81" t="s">
+      <c r="H124" s="91">
+        <v>0</v>
+      </c>
+      <c r="I124" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J124" s="81" t="s">
+      <c r="J124" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K124" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L124" s="17"/>
+      <c r="M124" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="87" t="s">
+        <v>400</v>
+      </c>
+      <c r="B125" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="C125" s="87" t="s">
+        <v>401</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="87" t="s">
+        <v>402</v>
+      </c>
+      <c r="F125" s="7">
+        <v>214789091</v>
+      </c>
+      <c r="G125" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="H125" s="91">
+        <v>20</v>
+      </c>
+      <c r="I125" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J125" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K125" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L125" s="17"/>
+      <c r="M125" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="87" t="s">
+        <v>403</v>
+      </c>
+      <c r="B126" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="C126" s="87" t="s">
+        <v>404</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E126" s="87" t="s">
+        <v>405</v>
+      </c>
+      <c r="F126" s="83"/>
+      <c r="G126" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="H126" s="91">
+        <v>156</v>
+      </c>
+      <c r="I126" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J126" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K126" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L126" s="17"/>
+      <c r="M126" s="17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="87" t="s">
+        <v>406</v>
+      </c>
+      <c r="B127" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="C127" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E127" s="87" t="s">
+        <v>408</v>
+      </c>
+      <c r="F127" s="7">
+        <v>6320909091</v>
+      </c>
+      <c r="G127" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="H127" s="91">
+        <v>1280</v>
+      </c>
+      <c r="I127" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J127" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="K124" s="81" t="s">
+      <c r="K127" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="L127" s="17"/>
+      <c r="M127" s="17"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="83"/>
+      <c r="B128" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="C128" s="83"/>
+      <c r="D128" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E128" s="87" t="s">
+        <v>409</v>
+      </c>
+      <c r="F128" s="83"/>
+      <c r="G128" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="H128" s="91">
+        <v>160</v>
+      </c>
+      <c r="I128" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J128" s="17"/>
+      <c r="K128" s="17"/>
+      <c r="L128" s="17"/>
+      <c r="M128" s="17"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" s="83"/>
+      <c r="B129" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="C129" s="83"/>
+      <c r="D129" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E129" s="87" t="s">
+        <v>410</v>
+      </c>
+      <c r="F129" s="83"/>
+      <c r="G129" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="H129" s="91">
+        <v>160</v>
+      </c>
+      <c r="I129" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J129" s="17"/>
+      <c r="K129" s="17"/>
+      <c r="L129" s="17"/>
+      <c r="M129" s="17"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="87" t="s">
+        <v>411</v>
+      </c>
+      <c r="B130" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="C130" s="87" t="s">
+        <v>412</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E130" s="87" t="s">
+        <v>413</v>
+      </c>
+      <c r="F130" s="7">
+        <v>401749000</v>
+      </c>
+      <c r="G130" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="H130" s="91">
+        <v>50</v>
+      </c>
+      <c r="I130" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J130" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="K130" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L124" s="81"/>
-      <c r="M124" s="81" t="s">
+      <c r="L130" s="17"/>
+      <c r="M130" s="17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="83"/>
+      <c r="B131" s="82" t="s">
+        <v>39</v>
+      </c>
+      <c r="C131" s="83"/>
+      <c r="D131" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E131" s="87" t="s">
+        <v>414</v>
+      </c>
+      <c r="F131" s="83"/>
+      <c r="G131" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="H131" s="91">
+        <v>180</v>
+      </c>
+      <c r="I131" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J131" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="K131" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L131" s="17"/>
+      <c r="M131" s="17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" s="87" t="s">
+        <v>415</v>
+      </c>
+      <c r="B132" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="C132" s="87" t="s">
+        <v>416</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E132" s="87" t="s">
+        <v>417</v>
+      </c>
+      <c r="F132" s="7">
+        <v>134556481</v>
+      </c>
+      <c r="G132" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="H132" s="91">
+        <v>25</v>
+      </c>
+      <c r="I132" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J132" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="K132" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L132" s="17"/>
+      <c r="M132" s="17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" s="87" t="s">
+        <v>418</v>
+      </c>
+      <c r="B133" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="C133" s="87" t="s">
+        <v>416</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E133" s="87" t="s">
+        <v>419</v>
+      </c>
+      <c r="F133" s="7">
+        <v>318666815</v>
+      </c>
+      <c r="G133" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="H133" s="91">
+        <v>51</v>
+      </c>
+      <c r="I133" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J133" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="K133" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L133" s="17"/>
+      <c r="M133" s="17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" s="87" t="s">
+        <v>420</v>
+      </c>
+      <c r="B134" s="82" t="s">
+        <v>142</v>
+      </c>
+      <c r="C134" s="87" t="s">
+        <v>416</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E134" s="87" t="s">
+        <v>421</v>
+      </c>
+      <c r="F134" s="7">
+        <v>380721000</v>
+      </c>
+      <c r="G134" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="H134" s="91">
+        <v>96</v>
+      </c>
+      <c r="I134" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J134" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K134" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L134" s="17"/>
+      <c r="M134" s="17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="85" t="s">
-        <v>400</v>
-      </c>
-      <c r="B125" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="C125" s="85" t="s">
-        <v>401</v>
-      </c>
-      <c r="D125" s="87" t="s">
-        <v>10</v>
-      </c>
-      <c r="E125" s="85" t="s">
-        <v>402</v>
-      </c>
-      <c r="F125" s="10">
-        <v>214789091</v>
-      </c>
-      <c r="G125" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="H125" s="79">
-        <v>20</v>
-      </c>
-      <c r="I125" s="81" t="s">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="87" t="s">
+        <v>422</v>
+      </c>
+      <c r="B135" s="82" t="s">
+        <v>142</v>
+      </c>
+      <c r="C135" s="87" t="s">
+        <v>416</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E135" s="87" t="s">
+        <v>423</v>
+      </c>
+      <c r="F135" s="7">
+        <v>234545454.5</v>
+      </c>
+      <c r="G135" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="H135" s="91">
+        <v>0</v>
+      </c>
+      <c r="I135" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J125" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K125" s="81" t="s">
+      <c r="J135" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K135" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L135" s="17"/>
+      <c r="M135" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" s="87" t="s">
+        <v>424</v>
+      </c>
+      <c r="B136" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="C136" s="87" t="s">
+        <v>416</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E136" s="87" t="s">
+        <v>425</v>
+      </c>
+      <c r="F136" s="7">
+        <v>313269865</v>
+      </c>
+      <c r="G136" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="H136" s="91">
+        <v>46</v>
+      </c>
+      <c r="I136" s="17"/>
+      <c r="J136" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="K136" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L125" s="81"/>
-      <c r="M125" s="81" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="85" t="s">
-        <v>403</v>
-      </c>
-      <c r="B126" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="C126" s="85" t="s">
-        <v>404</v>
-      </c>
-      <c r="D126" s="87" t="s">
-        <v>15</v>
-      </c>
-      <c r="E126" s="85" t="s">
-        <v>405</v>
-      </c>
-      <c r="F126" s="81"/>
-      <c r="G126" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="H126" s="79">
-        <v>156</v>
-      </c>
-      <c r="I126" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J126" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K126" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="L126" s="81"/>
-      <c r="M126" s="81" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="85" t="s">
-        <v>406</v>
-      </c>
-      <c r="B127" s="81" t="s">
-        <v>114</v>
-      </c>
-      <c r="C127" s="85" t="s">
-        <v>407</v>
-      </c>
-      <c r="D127" s="87" t="s">
-        <v>43</v>
-      </c>
-      <c r="E127" s="85" t="s">
-        <v>408</v>
-      </c>
-      <c r="F127" s="10">
-        <v>6320909091</v>
-      </c>
-      <c r="G127" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="H127" s="79">
-        <v>1280</v>
-      </c>
-      <c r="I127" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J127" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K127" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="L127" s="81"/>
-      <c r="M127" s="81"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="81"/>
-      <c r="B128" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="C128" s="81"/>
-      <c r="D128" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="E128" s="81" t="s">
-        <v>409</v>
-      </c>
-      <c r="F128" s="81"/>
-      <c r="G128" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="H128" s="79">
-        <v>160</v>
-      </c>
-      <c r="I128" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J128" s="81"/>
-      <c r="K128" s="81"/>
-      <c r="L128" s="81"/>
-      <c r="M128" s="81"/>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="81"/>
-      <c r="B129" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="C129" s="81"/>
-      <c r="D129" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="E129" s="81" t="s">
-        <v>410</v>
-      </c>
-      <c r="F129" s="81"/>
-      <c r="G129" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="H129" s="79">
-        <v>160</v>
-      </c>
-      <c r="I129" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J129" s="81"/>
-      <c r="K129" s="81"/>
-      <c r="L129" s="81"/>
-      <c r="M129" s="81"/>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A130" s="85" t="s">
-        <v>411</v>
-      </c>
-      <c r="B130" s="81" t="s">
-        <v>114</v>
-      </c>
-      <c r="C130" s="85" t="s">
-        <v>412</v>
-      </c>
-      <c r="D130" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="E130" s="85" t="s">
-        <v>413</v>
-      </c>
-      <c r="F130" s="89">
-        <v>401749000</v>
-      </c>
-      <c r="G130" s="81" t="s">
-        <v>9</v>
-      </c>
-      <c r="H130" s="79">
-        <v>50</v>
-      </c>
-      <c r="I130" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J130" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K130" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="L130" s="81"/>
-      <c r="M130" s="81" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="81"/>
-      <c r="B131" s="81" t="s">
-        <v>39</v>
-      </c>
-      <c r="C131" s="81"/>
-      <c r="D131" s="87" t="s">
-        <v>39</v>
-      </c>
-      <c r="E131" s="81" t="s">
-        <v>414</v>
-      </c>
-      <c r="F131" s="81"/>
-      <c r="G131" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="H131" s="79">
-        <v>180</v>
-      </c>
-      <c r="I131" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J131" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K131" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="L131" s="81"/>
-      <c r="M131" s="81" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="85" t="s">
-        <v>415</v>
-      </c>
-      <c r="B132" s="81" t="s">
-        <v>114</v>
-      </c>
-      <c r="C132" s="85" t="s">
-        <v>416</v>
-      </c>
-      <c r="D132" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="E132" s="81" t="s">
-        <v>417</v>
-      </c>
-      <c r="F132" s="89">
-        <v>134556481</v>
-      </c>
-      <c r="G132" s="81" t="s">
-        <v>9</v>
-      </c>
-      <c r="H132" s="79">
-        <v>25</v>
-      </c>
-      <c r="I132" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J132" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K132" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="L132" s="81"/>
-      <c r="M132" s="81" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="85" t="s">
-        <v>418</v>
-      </c>
-      <c r="B133" s="81" t="s">
-        <v>114</v>
-      </c>
-      <c r="C133" s="85" t="s">
-        <v>416</v>
-      </c>
-      <c r="D133" s="87" t="s">
-        <v>23</v>
-      </c>
-      <c r="E133" s="81" t="s">
-        <v>419</v>
-      </c>
-      <c r="F133" s="89">
-        <v>318666815</v>
-      </c>
-      <c r="G133" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="H133" s="79">
-        <v>51</v>
-      </c>
-      <c r="I133" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="J133" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K133" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="L133" s="81"/>
-      <c r="M133" s="81" t="s">
+      <c r="L136" s="17"/>
+      <c r="M136" s="17" t="s">
         <v>264</v>
       </c>
     </row>
@@ -10309,338 +10446,338 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="91">
+      <c r="C2" s="81">
         <v>2</v>
       </c>
-      <c r="D2" s="87" t="s">
+      <c r="D2" s="79" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="91">
+      <c r="C3" s="81">
         <v>1</v>
       </c>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="79" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="91">
+      <c r="C4" s="81">
         <v>3</v>
       </c>
-      <c r="D4" s="87" t="s">
+      <c r="D4" s="79" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="91">
+      <c r="C5" s="81">
         <v>2</v>
       </c>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="91">
+      <c r="C6" s="81">
         <v>2</v>
       </c>
-      <c r="D6" s="87" t="s">
+      <c r="D6" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="91">
+      <c r="C7" s="81">
         <v>3</v>
       </c>
-      <c r="D7" s="87" t="s">
+      <c r="D7" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="91">
+      <c r="C8" s="81">
         <v>1</v>
       </c>
-      <c r="D8" s="87" t="s">
+      <c r="D8" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="91">
+      <c r="C9" s="81">
         <v>5</v>
       </c>
-      <c r="D9" s="87" t="s">
+      <c r="D9" s="79" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="90" t="s">
+      <c r="A10" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="91">
+      <c r="C10" s="81">
         <v>48</v>
       </c>
-      <c r="D10" s="87" t="s">
+      <c r="D10" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="91">
+      <c r="C11" s="81">
         <v>5</v>
       </c>
-      <c r="D11" s="87" t="s">
+      <c r="D11" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="90" t="s">
+      <c r="A12" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="91">
+      <c r="C12" s="81">
         <v>11</v>
       </c>
-      <c r="D12" s="87" t="s">
+      <c r="D12" s="79" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="91">
+      <c r="C13" s="81">
         <v>2</v>
       </c>
-      <c r="D13" s="87" t="s">
+      <c r="D13" s="79" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="90" t="s">
+      <c r="A14" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="90" t="s">
+      <c r="B14" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="91">
+      <c r="C14" s="81">
         <v>8</v>
       </c>
-      <c r="D14" s="87" t="s">
+      <c r="D14" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="90" t="s">
+      <c r="B15" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="91">
+      <c r="C15" s="81">
         <v>6</v>
       </c>
-      <c r="D15" s="87" t="s">
+      <c r="D15" s="79" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="90" t="s">
+      <c r="A16" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="90" t="s">
+      <c r="B16" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="91">
+      <c r="C16" s="81">
         <v>1</v>
       </c>
-      <c r="D16" s="87" t="s">
+      <c r="D16" s="79" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="90" t="s">
+      <c r="B17" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="91">
+      <c r="C17" s="81">
         <v>55</v>
       </c>
-      <c r="D17" s="87" t="s">
+      <c r="D17" s="79" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="90" t="s">
+      <c r="A18" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="90" t="s">
+      <c r="B18" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="91">
+      <c r="C18" s="81">
         <v>1</v>
       </c>
-      <c r="D18" s="87" t="s">
+      <c r="D18" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="90" t="s">
+      <c r="B19" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="91">
+      <c r="C19" s="81">
         <v>5</v>
       </c>
-      <c r="D19" s="87" t="s">
+      <c r="D19" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="90" t="s">
+      <c r="B20" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="91">
+      <c r="C20" s="81">
         <v>8</v>
       </c>
-      <c r="D20" s="87" t="s">
+      <c r="D20" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="90" t="s">
+      <c r="B21" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="91">
+      <c r="C21" s="81">
         <v>2</v>
       </c>
-      <c r="D21" s="87" t="s">
+      <c r="D21" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="90" t="s">
+      <c r="B22" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="91">
+      <c r="C22" s="81">
         <v>0</v>
       </c>
-      <c r="D22" s="87" t="s">
+      <c r="D22" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="90" t="s">
+      <c r="B23" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="91">
+      <c r="C23" s="81">
         <v>0</v>
       </c>
-      <c r="D23" s="87" t="s">
+      <c r="D23" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="90" t="s">
+      <c r="B24" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="91">
+      <c r="C24" s="81">
         <v>2</v>
       </c>
-      <c r="D24" s="87" t="s">
+      <c r="D24" s="79" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="90" t="s">
+      <c r="B25" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="91">
+      <c r="C25" s="81">
         <v>24</v>
       </c>
-      <c r="D25" s="87" t="s">
+      <c r="D25" s="79" t="s">
         <v>3</v>
       </c>
     </row>

--- a/data/ton_chuanhap.xlsx
+++ b/data/ton_chuanhap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_Tonkho\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D18F1AF-569C-42C4-A437-65B1DA10D189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A568A878-831E-4F80-A5C5-FD7845F049FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="vo_hong" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">B2B!$A$1:$M$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="464">
   <si>
     <t>KV</t>
   </si>
@@ -1445,6 +1448,9 @@
   </si>
   <si>
     <t>Công ty TNHH đầu tư xây dựng THT tỉnh Điện Biên</t>
+  </si>
+  <si>
+    <t>Đã có hàng hệ thống</t>
   </si>
 </sst>
 </file>
@@ -1759,7 +1765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1975,15 +1981,18 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2377,7 +2386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F457DF4-8092-4544-B88B-9AF42554C254}">
-  <dimension ref="A1:O151"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.375" customWidth="1"/>
@@ -2395,7 +2404,7 @@
     <col min="13" max="13" width="8.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>336</v>
       </c>
@@ -2436,6255 +2445,5574 @@
         <v>345</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="87" t="s">
         <v>49</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84" t="s">
+      <c r="F2" s="88"/>
+      <c r="G2" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="7">
         <v>33</v>
       </c>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84">
-        <v>33</v>
-      </c>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="I2" s="83"/>
+      <c r="J2" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="87" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="83" t="s">
+      <c r="E3" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84" t="s">
+      <c r="F3" s="88"/>
+      <c r="G3" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H3" s="7">
         <v>178</v>
       </c>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84">
-        <v>178</v>
-      </c>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N3" s="85"/>
-      <c r="O3" s="85"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="86" t="s">
+      <c r="I3" s="83"/>
+      <c r="J3" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="89" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="87" t="s">
         <v>158</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="89" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84" t="s">
+      <c r="F4" s="88"/>
+      <c r="G4" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="7">
         <v>39</v>
       </c>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84">
-        <v>39</v>
-      </c>
-      <c r="K4" s="84" t="s">
+      <c r="I4" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L4" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N4" s="85"/>
-      <c r="O4" s="85" t="s">
+      <c r="J4" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="83" t="s">
+      <c r="C5" s="87" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="83" t="s">
+      <c r="E5" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84" t="s">
+      <c r="F5" s="88"/>
+      <c r="G5" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H5" s="7">
         <v>120</v>
       </c>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84">
-        <v>120</v>
-      </c>
-      <c r="K5" s="84"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O5" s="85"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
+      <c r="M5" s="83"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="87" t="s">
         <v>63</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="83" t="s">
+      <c r="E6" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="84"/>
-      <c r="G6" s="84" t="s">
+      <c r="F6" s="88"/>
+      <c r="G6" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H6" s="7">
         <v>163</v>
       </c>
-      <c r="I6" s="84"/>
-      <c r="J6" s="84">
-        <v>163</v>
-      </c>
-      <c r="K6" s="84"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N6" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="O6" s="85"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
+      <c r="M6" s="83"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="87" t="s">
         <v>67</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="83" t="s">
+      <c r="E7" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84" t="s">
+      <c r="F7" s="88"/>
+      <c r="G7" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H7" s="7">
         <v>489</v>
       </c>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84">
-        <v>489</v>
-      </c>
-      <c r="K7" s="84" t="s">
+      <c r="I7" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J7" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M7" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N7" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="85" t="s">
+      <c r="M7" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="87" t="s">
         <v>73</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="83" t="s">
+      <c r="E8" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84" t="s">
+      <c r="F8" s="88"/>
+      <c r="G8" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H8" s="7">
         <v>18</v>
       </c>
-      <c r="I8" s="84"/>
-      <c r="J8" s="84">
-        <v>18</v>
-      </c>
-      <c r="K8" s="84"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L8" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M8" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="O8" s="85" t="s">
+      <c r="M8" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="83" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="87" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84" t="s">
+      <c r="F9" s="88"/>
+      <c r="G9" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H9" s="7">
         <v>50</v>
       </c>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84">
-        <v>50</v>
-      </c>
-      <c r="K9" s="84" t="s">
+      <c r="I9" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L9" s="84" t="s">
+      <c r="J9" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="M9" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N9" s="85"/>
-      <c r="O9" s="85"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="83" t="s">
+      <c r="K9" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="87" t="s">
         <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84" t="s">
+      <c r="F10" s="88"/>
+      <c r="G10" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H10" s="7">
         <v>42</v>
       </c>
-      <c r="I10" s="84"/>
-      <c r="J10" s="84">
-        <v>42</v>
-      </c>
-      <c r="K10" s="84" t="s">
+      <c r="I10" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L10" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M10" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N10" s="85"/>
-      <c r="O10" s="85"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
+      <c r="J10" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="83" t="s">
+      <c r="C11" s="87" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="83" t="s">
+      <c r="E11" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84" t="s">
+      <c r="F11" s="88"/>
+      <c r="G11" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H11" s="7">
-        <v>1040</v>
-      </c>
-      <c r="I11" s="84">
-        <v>1040</v>
-      </c>
-      <c r="J11" s="84">
         <v>0</v>
       </c>
-      <c r="K11" s="84"/>
-      <c r="L11" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N11" s="85"/>
-      <c r="O11" s="85" t="s">
+      <c r="I11" s="83"/>
+      <c r="J11" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="83" t="s">
+      <c r="C12" s="87" t="s">
         <v>89</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="83" t="s">
+      <c r="E12" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84" t="s">
+      <c r="F12" s="88"/>
+      <c r="G12" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H12" s="7">
-        <v>871</v>
-      </c>
-      <c r="I12" s="84">
-        <v>871</v>
-      </c>
-      <c r="J12" s="84">
         <v>0</v>
       </c>
-      <c r="K12" s="84" t="s">
+      <c r="I12" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L12" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M12" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N12" s="85"/>
-      <c r="O12" s="85" t="s">
+      <c r="J12" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="83"/>
+      <c r="M12" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="87" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="87" t="s">
+      <c r="E13" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84" t="s">
+      <c r="F13" s="88"/>
+      <c r="G13" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="7">
-        <v>770</v>
-      </c>
-      <c r="I13" s="84">
-        <v>770</v>
-      </c>
-      <c r="J13" s="84">
         <v>0</v>
       </c>
-      <c r="K13" s="84" t="s">
+      <c r="I13" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L13" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M13" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="85"/>
-      <c r="O13" s="85" t="s">
+      <c r="J13" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="83"/>
+      <c r="M13" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="87" t="s">
         <v>76</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="83" t="e">
+      <c r="E14" s="87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F14" s="84"/>
-      <c r="G14" s="84" t="s">
+      <c r="F14" s="88"/>
+      <c r="G14" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H14" s="7">
         <v>64</v>
       </c>
-      <c r="I14" s="84"/>
-      <c r="J14" s="84">
-        <v>64</v>
-      </c>
-      <c r="K14" s="84"/>
-      <c r="L14" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M14" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N14" s="85"/>
-      <c r="O14" s="85"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="83" t="s">
+      <c r="I14" s="83"/>
+      <c r="J14" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="83"/>
+      <c r="M14" s="83"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="83" t="s">
+      <c r="B15" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="83" t="s">
+      <c r="C15" s="87" t="s">
         <v>96</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="83" t="s">
+      <c r="E15" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84" t="s">
+      <c r="F15" s="88"/>
+      <c r="G15" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H15" s="7">
         <v>32</v>
       </c>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84">
-        <v>32</v>
-      </c>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M15" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N15" s="85"/>
-      <c r="O15" s="85"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="83" t="s">
+      <c r="I15" s="83"/>
+      <c r="J15" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="83"/>
+      <c r="M15" s="83"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="83" t="s">
+      <c r="C16" s="87" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="83" t="s">
+      <c r="E16" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="84"/>
-      <c r="G16" s="84" t="s">
+      <c r="F16" s="88"/>
+      <c r="G16" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="7">
         <v>40</v>
       </c>
-      <c r="I16" s="84"/>
-      <c r="J16" s="84">
-        <v>40</v>
-      </c>
-      <c r="K16" s="84"/>
-      <c r="L16" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M16" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N16" s="85"/>
-      <c r="O16" s="85"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="86" t="s">
+      <c r="I16" s="83"/>
+      <c r="J16" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="83"/>
+      <c r="M16" s="83"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="89" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="87" t="s">
         <v>101</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="86" t="s">
+      <c r="E17" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84" t="s">
+      <c r="F17" s="88"/>
+      <c r="G17" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H17" s="7">
         <v>4876</v>
       </c>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84">
-        <v>4876</v>
-      </c>
-      <c r="K17" s="84"/>
-      <c r="L17" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M17" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
+      <c r="I17" s="83"/>
+      <c r="J17" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="83"/>
+      <c r="M17" s="83"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="83" t="s">
+      <c r="C18" s="87" t="s">
         <v>104</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="83" t="s">
+      <c r="E18" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84" t="s">
+      <c r="F18" s="88"/>
+      <c r="G18" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H18" s="7">
         <v>16</v>
       </c>
-      <c r="I18" s="84"/>
-      <c r="J18" s="84">
-        <v>16</v>
-      </c>
-      <c r="K18" s="84"/>
-      <c r="L18" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M18" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N18" s="85"/>
-      <c r="O18" s="85" t="s">
+      <c r="I18" s="83"/>
+      <c r="J18" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="83"/>
+      <c r="M18" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="83" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="87" t="s">
         <v>107</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="83" t="s">
+      <c r="E19" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="F19" s="84"/>
-      <c r="G19" s="84" t="s">
+      <c r="F19" s="88"/>
+      <c r="G19" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H19" s="7">
-        <v>284</v>
-      </c>
-      <c r="I19" s="84">
-        <v>284</v>
-      </c>
-      <c r="J19" s="84">
         <v>0</v>
       </c>
-      <c r="K19" s="84" t="s">
+      <c r="I19" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L19" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M19" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N19" s="85"/>
-      <c r="O19" s="85" t="s">
+      <c r="J19" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="83"/>
+      <c r="M19" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="83" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="83" t="s">
+      <c r="B20" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="83" t="s">
+      <c r="C20" s="87" t="s">
         <v>110</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="84"/>
-      <c r="G20" s="84" t="s">
+      <c r="F20" s="88"/>
+      <c r="G20" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H20" s="7">
         <v>1218</v>
       </c>
-      <c r="I20" s="84"/>
-      <c r="J20" s="84">
-        <v>1218</v>
-      </c>
-      <c r="K20" s="84"/>
-      <c r="L20" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M20" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N20" s="85"/>
-      <c r="O20" s="85"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="83" t="s">
+      <c r="I20" s="83"/>
+      <c r="J20" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="83"/>
+      <c r="M20" s="83"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="B21" s="83" t="s">
+      <c r="B21" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="83" t="s">
+      <c r="C21" s="87" t="s">
         <v>114</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="83" t="s">
+      <c r="E21" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="84"/>
-      <c r="G21" s="84" t="s">
+      <c r="F21" s="88"/>
+      <c r="G21" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H21" s="7">
         <v>40</v>
       </c>
-      <c r="I21" s="84"/>
-      <c r="J21" s="84">
-        <v>40</v>
-      </c>
-      <c r="K21" s="84" t="s">
+      <c r="I21" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L21" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M21" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N21" s="85"/>
-      <c r="O21" s="85" t="s">
+      <c r="J21" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K21" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="83"/>
+      <c r="M21" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="83" t="s">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="83" t="s">
+      <c r="C22" s="87" t="s">
         <v>117</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="83" t="s">
+      <c r="E22" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84" t="s">
+      <c r="F22" s="88"/>
+      <c r="G22" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H22" s="7">
         <v>40</v>
       </c>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84">
-        <v>40</v>
-      </c>
-      <c r="K22" s="84" t="s">
+      <c r="I22" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J22" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L22" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M22" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N22" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O22" s="85" t="s">
+      <c r="M22" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="83" t="s">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="83" t="s">
+      <c r="C23" s="87" t="s">
         <v>120</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="83" t="s">
+      <c r="E23" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84" t="s">
+      <c r="F23" s="88"/>
+      <c r="G23" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H23" s="7">
         <v>162</v>
       </c>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84">
-        <v>162</v>
-      </c>
-      <c r="K23" s="84" t="s">
+      <c r="I23" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L23" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M23" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N23" s="85"/>
-      <c r="O23" s="85" t="s">
+      <c r="J23" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K23" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="83"/>
+      <c r="M23" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="83" t="s">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="83" t="s">
+      <c r="B24" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="84"/>
+      <c r="C24" s="88"/>
       <c r="D24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="83" t="s">
+      <c r="E24" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84" t="s">
+      <c r="F24" s="88"/>
+      <c r="G24" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H24" s="7">
         <v>1326</v>
       </c>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84">
-        <v>1326</v>
-      </c>
-      <c r="K24" s="84" t="s">
+      <c r="I24" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J24" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K24" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L24" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M24" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N24" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O24" s="85" t="s">
+      <c r="M24" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="83" t="s">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="83" t="s">
+      <c r="C25" s="87" t="s">
         <v>125</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="83" t="s">
+      <c r="E25" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="84"/>
-      <c r="G25" s="84" t="s">
+      <c r="F25" s="88"/>
+      <c r="G25" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H25" s="7">
         <v>1626</v>
       </c>
-      <c r="I25" s="84"/>
-      <c r="J25" s="84">
-        <v>1626</v>
-      </c>
-      <c r="K25" s="84" t="s">
+      <c r="I25" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J25" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K25" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L25" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M25" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N25" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="O25" s="85" t="s">
+      <c r="M25" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="86" t="s">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="83" t="s">
+      <c r="C26" s="87" t="s">
         <v>128</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="86" t="s">
+      <c r="E26" s="89" t="s">
         <v>129</v>
       </c>
-      <c r="F26" s="84"/>
-      <c r="G26" s="84" t="s">
+      <c r="F26" s="88"/>
+      <c r="G26" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H26" s="7">
         <v>526</v>
       </c>
-      <c r="I26" s="84"/>
-      <c r="J26" s="84">
-        <v>526</v>
-      </c>
-      <c r="K26" s="84" t="s">
+      <c r="I26" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J26" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K26" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L26" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M26" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N26" s="85" t="s">
         <v>130</v>
       </c>
-      <c r="O26" s="85" t="s">
+      <c r="M26" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="83" t="s">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="83" t="s">
+      <c r="B27" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C27" s="83" t="s">
+      <c r="C27" s="87" t="s">
         <v>132</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="83" t="s">
+      <c r="E27" s="87" t="s">
         <v>133</v>
       </c>
-      <c r="F27" s="84"/>
-      <c r="G27" s="84" t="s">
+      <c r="F27" s="88"/>
+      <c r="G27" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H27" s="7">
         <v>64</v>
       </c>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84">
-        <v>64</v>
-      </c>
-      <c r="K27" s="84" t="s">
+      <c r="I27" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L27" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M27" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N27" s="85"/>
-      <c r="O27" s="85" t="s">
+      <c r="J27" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K27" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="83"/>
+      <c r="M27" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="83" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="83" t="s">
+      <c r="C28" s="87" t="s">
         <v>135</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="83" t="s">
+      <c r="E28" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="84"/>
-      <c r="G28" s="84" t="s">
+      <c r="F28" s="88"/>
+      <c r="G28" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H28" s="7">
         <v>82</v>
       </c>
-      <c r="I28" s="84"/>
-      <c r="J28" s="84">
-        <v>82</v>
-      </c>
-      <c r="K28" s="84" t="s">
+      <c r="I28" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L28" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M28" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N28" s="85"/>
-      <c r="O28" s="85" t="s">
+      <c r="J28" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K28" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="83" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="87" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="83" t="s">
+      <c r="B29" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="87" t="s">
         <v>138</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="87" t="s">
         <v>139</v>
       </c>
-      <c r="F29" s="84"/>
-      <c r="G29" s="84" t="s">
+      <c r="F29" s="88"/>
+      <c r="G29" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H29" s="7">
         <v>800</v>
       </c>
-      <c r="I29" s="84"/>
-      <c r="J29" s="84">
-        <v>800</v>
-      </c>
-      <c r="K29" s="84" t="s">
+      <c r="I29" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L29" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M29" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N29" s="85"/>
-      <c r="O29" s="85" t="s">
+      <c r="J29" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K29" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="83"/>
+      <c r="M29" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="83" t="s">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="87" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="83" t="s">
+      <c r="B30" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="83" t="s">
+      <c r="C30" s="87" t="s">
         <v>142</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="83" t="s">
+      <c r="E30" s="87" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84" t="s">
+      <c r="F30" s="88"/>
+      <c r="G30" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H30" s="7">
         <v>160</v>
       </c>
-      <c r="I30" s="84"/>
-      <c r="J30" s="84">
-        <v>160</v>
-      </c>
-      <c r="K30" s="84" t="s">
+      <c r="I30" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J30" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K30" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L30" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M30" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N30" s="85" t="s">
         <v>144</v>
       </c>
-      <c r="O30" s="85" t="s">
+      <c r="M30" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="83" t="s">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="87" t="s">
         <v>145</v>
       </c>
-      <c r="B31" s="83" t="s">
+      <c r="B31" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C31" s="83" t="s">
+      <c r="C31" s="87" t="s">
         <v>146</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="87" t="s">
         <v>147</v>
       </c>
-      <c r="F31" s="84"/>
-      <c r="G31" s="84" t="s">
+      <c r="F31" s="88"/>
+      <c r="G31" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H31" s="7">
         <v>1511</v>
       </c>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84">
-        <v>1511</v>
-      </c>
-      <c r="K31" s="84" t="s">
+      <c r="I31" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L31" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M31" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N31" s="85"/>
-      <c r="O31" s="85" t="s">
+      <c r="J31" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K31" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="83"/>
+      <c r="M31" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="83" t="s">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="B32" s="83" t="s">
+      <c r="B32" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C32" s="83" t="s">
+      <c r="C32" s="87" t="s">
         <v>149</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="83" t="s">
+      <c r="E32" s="87" t="s">
         <v>150</v>
       </c>
-      <c r="F32" s="84"/>
-      <c r="G32" s="84" t="s">
+      <c r="F32" s="88"/>
+      <c r="G32" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="7">
         <v>681</v>
       </c>
-      <c r="I32" s="84"/>
-      <c r="J32" s="84">
-        <v>681</v>
-      </c>
-      <c r="K32" s="84" t="s">
+      <c r="I32" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L32" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M32" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N32" s="85"/>
-      <c r="O32" s="85" t="s">
+      <c r="J32" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K32" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="83"/>
+      <c r="M32" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="83" t="s">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="87" t="s">
         <v>151</v>
       </c>
-      <c r="B33" s="83" t="s">
+      <c r="B33" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="83" t="s">
+      <c r="C33" s="87" t="s">
         <v>152</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="83" t="s">
+      <c r="E33" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="F33" s="84"/>
-      <c r="G33" s="84" t="s">
+      <c r="F33" s="88"/>
+      <c r="G33" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H33" s="7">
         <v>330</v>
       </c>
-      <c r="I33" s="84"/>
-      <c r="J33" s="84">
-        <v>330</v>
-      </c>
-      <c r="K33" s="84" t="s">
+      <c r="I33" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J33" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K33" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L33" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M33" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N33" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O33" s="85" t="s">
+      <c r="M33" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="86" t="s">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="89" t="s">
         <v>154</v>
       </c>
-      <c r="B34" s="83" t="s">
+      <c r="B34" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="83" t="s">
+      <c r="C34" s="87" t="s">
         <v>155</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="86" t="s">
+      <c r="E34" s="89" t="s">
         <v>156</v>
       </c>
-      <c r="F34" s="84"/>
-      <c r="G34" s="84" t="s">
+      <c r="F34" s="88"/>
+      <c r="G34" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H34" s="7">
         <v>1704</v>
       </c>
-      <c r="I34" s="84"/>
-      <c r="J34" s="84">
-        <v>1704</v>
-      </c>
-      <c r="K34" s="84" t="s">
+      <c r="I34" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L34" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M34" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N34" s="85"/>
-      <c r="O34" s="85" t="s">
+      <c r="J34" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K34" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="83"/>
+      <c r="M34" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="86" t="s">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="89" t="s">
         <v>160</v>
       </c>
-      <c r="B35" s="83" t="s">
+      <c r="B35" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="83" t="s">
+      <c r="C35" s="87" t="s">
         <v>161</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="86" t="s">
+      <c r="E35" s="89" t="s">
         <v>162</v>
       </c>
-      <c r="F35" s="84"/>
-      <c r="G35" s="84" t="s">
+      <c r="F35" s="88"/>
+      <c r="G35" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H35" s="7">
         <v>84</v>
       </c>
-      <c r="I35" s="84"/>
-      <c r="J35" s="84">
-        <v>84</v>
-      </c>
-      <c r="K35" s="84" t="s">
+      <c r="I35" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L35" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M35" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N35" s="85"/>
-      <c r="O35" s="85" t="s">
+      <c r="J35" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K35" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" s="83"/>
+      <c r="M35" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="83" t="s">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="87" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="83" t="s">
+      <c r="B36" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="83" t="s">
+      <c r="C36" s="87" t="s">
         <v>164</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E36" s="83" t="s">
+      <c r="E36" s="87" t="s">
         <v>156</v>
       </c>
-      <c r="F36" s="84"/>
-      <c r="G36" s="84" t="s">
+      <c r="F36" s="88"/>
+      <c r="G36" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H36" s="7">
         <v>680</v>
       </c>
-      <c r="I36" s="84"/>
-      <c r="J36" s="84">
-        <v>680</v>
-      </c>
-      <c r="K36" s="84" t="s">
+      <c r="I36" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L36" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M36" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N36" s="85"/>
-      <c r="O36" s="85" t="s">
+      <c r="J36" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K36" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="83"/>
+      <c r="M36" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="83" t="s">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="87" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="83" t="s">
+      <c r="B37" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="83" t="s">
+      <c r="C37" s="87" t="s">
         <v>164</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E37" s="83" t="s">
+      <c r="E37" s="87" t="s">
         <v>166</v>
       </c>
-      <c r="F37" s="84"/>
-      <c r="G37" s="84" t="s">
+      <c r="F37" s="88"/>
+      <c r="G37" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H37" s="7">
         <v>654</v>
       </c>
-      <c r="I37" s="84"/>
-      <c r="J37" s="84">
-        <v>654</v>
-      </c>
-      <c r="K37" s="84" t="s">
+      <c r="I37" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="L37" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M37" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N37" s="85"/>
-      <c r="O37" s="85" t="s">
+      <c r="J37" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K37" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="83"/>
+      <c r="M37" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="83">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="87">
         <v>20251678</v>
       </c>
-      <c r="B38" s="83" t="s">
+      <c r="B38" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C38" s="83" t="s">
+      <c r="C38" s="87" t="s">
         <v>168</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E38" s="83" t="s">
+      <c r="E38" s="87" t="s">
         <v>169</v>
       </c>
-      <c r="F38" s="84"/>
-      <c r="G38" s="84" t="s">
+      <c r="F38" s="88"/>
+      <c r="G38" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H38" s="7">
         <v>732</v>
       </c>
-      <c r="I38" s="84"/>
-      <c r="J38" s="84">
-        <v>732</v>
-      </c>
-      <c r="K38" s="84" t="s">
+      <c r="I38" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J38" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K38" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L38" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M38" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N38" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O38" s="85" t="s">
+      <c r="M38" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="83" t="s">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="87" t="s">
         <v>170</v>
       </c>
-      <c r="B39" s="83" t="s">
+      <c r="B39" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="83" t="s">
+      <c r="C39" s="87" t="s">
         <v>171</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="83" t="s">
+      <c r="E39" s="87" t="s">
         <v>172</v>
       </c>
-      <c r="F39" s="84"/>
-      <c r="G39" s="84" t="s">
+      <c r="F39" s="88"/>
+      <c r="G39" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H39" s="7">
         <v>204</v>
       </c>
-      <c r="I39" s="84"/>
-      <c r="J39" s="84">
-        <v>204</v>
-      </c>
-      <c r="K39" s="84" t="s">
+      <c r="I39" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J39" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K39" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L39" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M39" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N39" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O39" s="85" t="s">
+      <c r="M39" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="83" t="s">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="87" t="s">
         <v>173</v>
       </c>
-      <c r="B40" s="83" t="s">
+      <c r="B40" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C40" s="83" t="s">
+      <c r="C40" s="87" t="s">
         <v>174</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E40" s="83" t="s">
+      <c r="E40" s="87" t="s">
         <v>175</v>
       </c>
-      <c r="F40" s="84"/>
-      <c r="G40" s="84" t="s">
+      <c r="F40" s="88"/>
+      <c r="G40" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H40" s="7">
         <v>1229</v>
       </c>
-      <c r="I40" s="84"/>
-      <c r="J40" s="84">
-        <v>1229</v>
-      </c>
-      <c r="K40" s="84" t="s">
+      <c r="I40" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L40" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M40" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N40" s="85"/>
-      <c r="O40" s="85" t="s">
+      <c r="J40" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K40" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="83"/>
+      <c r="M40" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="83" t="s">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="87" t="s">
         <v>176</v>
       </c>
-      <c r="B41" s="83" t="s">
+      <c r="B41" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="83" t="s">
+      <c r="C41" s="87" t="s">
         <v>177</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E41" s="83">
+      <c r="E41" s="87">
         <v>0</v>
       </c>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84" t="s">
+      <c r="F41" s="88"/>
+      <c r="G41" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H41" s="7">
         <v>180</v>
       </c>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84">
-        <v>180</v>
-      </c>
-      <c r="K41" s="84" t="s">
+      <c r="I41" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L41" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M41" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N41" s="85"/>
-      <c r="O41" s="85" t="s">
+      <c r="J41" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K41" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="83"/>
+      <c r="M41" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="83" t="s">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="87" t="s">
         <v>178</v>
       </c>
-      <c r="B42" s="83" t="s">
+      <c r="B42" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="83" t="s">
+      <c r="C42" s="87" t="s">
         <v>179</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="83" t="e">
+      <c r="E42" s="87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84" t="s">
+      <c r="F42" s="88"/>
+      <c r="G42" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H42" s="7">
         <v>18</v>
       </c>
-      <c r="I42" s="84"/>
-      <c r="J42" s="84">
-        <v>18</v>
-      </c>
-      <c r="K42" s="84" t="s">
+      <c r="I42" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J42" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K42" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L42" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M42" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N42" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O42" s="85" t="s">
+      <c r="M42" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="83" t="s">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="87" t="s">
         <v>180</v>
       </c>
-      <c r="B43" s="83" t="s">
+      <c r="B43" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C43" s="83" t="s">
+      <c r="C43" s="87" t="s">
         <v>181</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="83" t="s">
+      <c r="E43" s="87" t="s">
         <v>182</v>
       </c>
-      <c r="F43" s="84"/>
-      <c r="G43" s="84" t="s">
+      <c r="F43" s="88"/>
+      <c r="G43" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H43" s="7">
         <v>640</v>
       </c>
-      <c r="I43" s="84"/>
-      <c r="J43" s="84">
-        <v>640</v>
-      </c>
-      <c r="K43" s="84" t="s">
+      <c r="I43" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J43" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K43" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L43" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M43" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N43" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O43" s="85" t="s">
+      <c r="M43" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="83" t="s">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="87" t="s">
         <v>183</v>
       </c>
-      <c r="B44" s="83" t="s">
+      <c r="B44" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="83" t="s">
+      <c r="C44" s="87" t="s">
         <v>184</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="83" t="s">
+      <c r="E44" s="87" t="s">
         <v>185</v>
       </c>
-      <c r="F44" s="84"/>
-      <c r="G44" s="84" t="s">
+      <c r="F44" s="88"/>
+      <c r="G44" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H44" s="7">
         <v>1542</v>
       </c>
-      <c r="I44" s="84"/>
-      <c r="J44" s="84">
-        <v>1542</v>
-      </c>
-      <c r="K44" s="84" t="s">
+      <c r="I44" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L44" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M44" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N44" s="85"/>
-      <c r="O44" s="85" t="s">
+      <c r="J44" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K44" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L44" s="83"/>
+      <c r="M44" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="83" t="s">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="87" t="s">
         <v>186</v>
       </c>
-      <c r="B45" s="83" t="s">
+      <c r="B45" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C45" s="83" t="s">
+      <c r="C45" s="87" t="s">
         <v>187</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="83" t="s">
+      <c r="E45" s="87" t="s">
         <v>188</v>
       </c>
-      <c r="F45" s="84"/>
-      <c r="G45" s="84" t="s">
+      <c r="F45" s="88"/>
+      <c r="G45" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H45" s="7">
         <v>672</v>
       </c>
-      <c r="I45" s="84"/>
-      <c r="J45" s="84">
-        <v>672</v>
-      </c>
-      <c r="K45" s="84" t="s">
+      <c r="I45" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J45" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K45" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L45" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M45" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N45" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O45" s="85" t="s">
+      <c r="M45" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="83" t="s">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="87" t="s">
         <v>189</v>
       </c>
-      <c r="B46" s="83" t="s">
+      <c r="B46" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="83" t="s">
+      <c r="C46" s="87" t="s">
         <v>190</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="83" t="s">
+      <c r="E46" s="87" t="s">
         <v>191</v>
       </c>
-      <c r="F46" s="84"/>
-      <c r="G46" s="84" t="s">
+      <c r="F46" s="88"/>
+      <c r="G46" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H46" s="7">
         <v>245</v>
       </c>
-      <c r="I46" s="84"/>
-      <c r="J46" s="84">
-        <v>245</v>
-      </c>
-      <c r="K46" s="84"/>
-      <c r="L46" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M46" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N46" s="85"/>
-      <c r="O46" s="85"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="86" t="s">
+      <c r="I46" s="83"/>
+      <c r="J46" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K46" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L46" s="83"/>
+      <c r="M46" s="83"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="89" t="s">
         <v>192</v>
       </c>
-      <c r="B47" s="83" t="s">
+      <c r="B47" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="83" t="s">
+      <c r="C47" s="87" t="s">
         <v>193</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="86" t="s">
+      <c r="E47" s="89" t="s">
         <v>194</v>
       </c>
-      <c r="F47" s="84"/>
-      <c r="G47" s="84" t="s">
+      <c r="F47" s="88"/>
+      <c r="G47" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H47" s="7">
         <v>93</v>
       </c>
-      <c r="I47" s="84"/>
-      <c r="J47" s="84">
-        <v>93</v>
-      </c>
-      <c r="K47" s="84"/>
-      <c r="L47" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M47" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N47" s="85"/>
-      <c r="O47" s="85" t="s">
+      <c r="I47" s="83"/>
+      <c r="J47" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K47" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="83"/>
+      <c r="M47" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="83" t="s">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="87" t="s">
         <v>195</v>
       </c>
-      <c r="B48" s="83" t="s">
+      <c r="B48" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="84"/>
+      <c r="C48" s="88"/>
       <c r="D48" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="83" t="s">
+      <c r="E48" s="87" t="s">
         <v>196</v>
       </c>
-      <c r="F48" s="84"/>
-      <c r="G48" s="84" t="s">
+      <c r="F48" s="88"/>
+      <c r="G48" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H48" s="7">
         <v>88</v>
       </c>
-      <c r="I48" s="84"/>
-      <c r="J48" s="84">
-        <v>88</v>
-      </c>
-      <c r="K48" s="84"/>
-      <c r="L48" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M48" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N48" s="85"/>
-      <c r="O48" s="85" t="s">
+      <c r="I48" s="83"/>
+      <c r="J48" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K48" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="83"/>
+      <c r="M48" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="83" t="s">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="87" t="s">
         <v>197</v>
       </c>
-      <c r="B49" s="83" t="s">
+      <c r="B49" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="83" t="s">
+      <c r="C49" s="87" t="s">
         <v>198</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="83" t="s">
+      <c r="E49" s="87" t="s">
         <v>199</v>
       </c>
-      <c r="F49" s="84"/>
-      <c r="G49" s="84" t="s">
+      <c r="F49" s="88"/>
+      <c r="G49" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H49" s="7">
         <v>357</v>
       </c>
-      <c r="I49" s="84"/>
-      <c r="J49" s="84">
-        <v>357</v>
-      </c>
-      <c r="K49" s="84"/>
-      <c r="L49" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M49" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N49" s="85"/>
-      <c r="O49" s="85" t="s">
+      <c r="I49" s="83"/>
+      <c r="J49" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K49" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L49" s="83"/>
+      <c r="M49" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="83" t="s">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="87" t="s">
         <v>200</v>
       </c>
-      <c r="B50" s="83" t="s">
+      <c r="B50" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="83" t="s">
+      <c r="C50" s="87" t="s">
         <v>201</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E50" s="83" t="s">
+      <c r="E50" s="87" t="s">
         <v>202</v>
       </c>
-      <c r="F50" s="84"/>
-      <c r="G50" s="84" t="s">
+      <c r="F50" s="88"/>
+      <c r="G50" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H50" s="7">
         <v>2617</v>
       </c>
-      <c r="I50" s="84"/>
-      <c r="J50" s="84">
-        <v>2617</v>
-      </c>
-      <c r="K50" s="84"/>
+      <c r="I50" s="83"/>
+      <c r="J50" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K50" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L50" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M50" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N50" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="O50" s="85" t="s">
+      <c r="M50" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="83" t="s">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="87" t="s">
         <v>203</v>
       </c>
-      <c r="B51" s="83" t="s">
+      <c r="B51" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="83" t="s">
+      <c r="C51" s="87" t="s">
         <v>204</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="83" t="s">
+      <c r="E51" s="87" t="s">
         <v>205</v>
       </c>
-      <c r="F51" s="84"/>
-      <c r="G51" s="84" t="s">
+      <c r="F51" s="88"/>
+      <c r="G51" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H51" s="7">
         <v>6768</v>
       </c>
-      <c r="I51" s="84"/>
-      <c r="J51" s="84">
-        <v>6768</v>
-      </c>
-      <c r="K51" s="84" t="s">
+      <c r="I51" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L51" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M51" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N51" s="85"/>
-      <c r="O51" s="85" t="s">
+      <c r="J51" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K51" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L51" s="83"/>
+      <c r="M51" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="83" t="s">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="87" t="s">
         <v>206</v>
       </c>
-      <c r="B52" s="83" t="s">
+      <c r="B52" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="83" t="s">
+      <c r="C52" s="87" t="s">
         <v>207</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="83" t="s">
+      <c r="E52" s="87" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="84"/>
-      <c r="G52" s="84" t="s">
+      <c r="F52" s="88"/>
+      <c r="G52" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H52" s="7">
         <v>1625</v>
       </c>
-      <c r="I52" s="84"/>
-      <c r="J52" s="84">
-        <v>1625</v>
-      </c>
-      <c r="K52" s="84"/>
+      <c r="I52" s="83"/>
+      <c r="J52" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K52" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L52" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M52" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N52" s="85" t="s">
         <v>144</v>
       </c>
-      <c r="O52" s="85" t="s">
+      <c r="M52" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="83" t="s">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="87" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="83" t="s">
+      <c r="B53" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="83" t="s">
+      <c r="C53" s="87" t="s">
         <v>210</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E53" s="83" t="s">
+      <c r="E53" s="87" t="s">
         <v>211</v>
       </c>
-      <c r="F53" s="84"/>
-      <c r="G53" s="84" t="s">
+      <c r="F53" s="88"/>
+      <c r="G53" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H53" s="7">
         <v>1980</v>
       </c>
-      <c r="I53" s="84"/>
-      <c r="J53" s="84">
-        <v>1980</v>
-      </c>
-      <c r="K53" s="84"/>
-      <c r="L53" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M53" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N53" s="85"/>
-      <c r="O53" s="85" t="s">
+      <c r="I53" s="83"/>
+      <c r="J53" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K53" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="83"/>
+      <c r="M53" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="83" t="s">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="87" t="s">
         <v>212</v>
       </c>
-      <c r="B54" s="83" t="s">
+      <c r="B54" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="84"/>
+      <c r="C54" s="88"/>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E54" s="83" t="s">
+      <c r="E54" s="87" t="s">
         <v>213</v>
       </c>
-      <c r="F54" s="84"/>
-      <c r="G54" s="84" t="s">
+      <c r="F54" s="88"/>
+      <c r="G54" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H54" s="7">
         <v>381</v>
       </c>
-      <c r="I54" s="84"/>
-      <c r="J54" s="84">
-        <v>381</v>
-      </c>
-      <c r="K54" s="84"/>
-      <c r="L54" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M54" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N54" s="85"/>
-      <c r="O54" s="85" t="s">
+      <c r="I54" s="83"/>
+      <c r="J54" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K54" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L54" s="83"/>
+      <c r="M54" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="83" t="s">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="87" t="s">
         <v>214</v>
       </c>
-      <c r="B55" s="83" t="s">
+      <c r="B55" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="83" t="s">
+      <c r="C55" s="87" t="s">
         <v>215</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E55" s="83" t="s">
+      <c r="E55" s="87" t="s">
         <v>216</v>
       </c>
-      <c r="F55" s="84"/>
-      <c r="G55" s="84" t="s">
+      <c r="F55" s="88"/>
+      <c r="G55" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H55" s="7">
         <v>177</v>
       </c>
-      <c r="I55" s="84"/>
-      <c r="J55" s="84">
-        <v>177</v>
-      </c>
-      <c r="K55" s="84"/>
-      <c r="L55" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M55" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N55" s="85"/>
-      <c r="O55" s="85"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="83" t="s">
+      <c r="I55" s="83"/>
+      <c r="J55" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K55" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L55" s="83"/>
+      <c r="M55" s="83"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="87" t="s">
         <v>217</v>
       </c>
-      <c r="B56" s="83" t="s">
+      <c r="B56" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="84"/>
+      <c r="C56" s="88"/>
       <c r="D56" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="83" t="s">
+      <c r="E56" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="F56" s="84"/>
-      <c r="G56" s="84" t="s">
+      <c r="F56" s="88"/>
+      <c r="G56" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H56" s="7">
         <v>161</v>
       </c>
-      <c r="I56" s="84"/>
-      <c r="J56" s="84">
-        <v>161</v>
-      </c>
-      <c r="K56" s="84"/>
-      <c r="L56" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M56" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N56" s="85"/>
-      <c r="O56" s="85"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="83" t="s">
+      <c r="I56" s="83"/>
+      <c r="J56" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K56" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L56" s="83"/>
+      <c r="M56" s="83"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="B57" s="83" t="s">
+      <c r="B57" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="83" t="s">
+      <c r="C57" s="87" t="s">
         <v>220</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E57" s="83" t="s">
+      <c r="E57" s="87" t="s">
         <v>221</v>
       </c>
-      <c r="F57" s="84"/>
-      <c r="G57" s="84" t="s">
+      <c r="F57" s="88"/>
+      <c r="G57" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H57" s="7">
         <v>1286</v>
       </c>
-      <c r="I57" s="84"/>
-      <c r="J57" s="84">
-        <v>1286</v>
-      </c>
-      <c r="K57" s="84"/>
-      <c r="L57" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M57" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N57" s="85"/>
-      <c r="O57" s="85" t="s">
+      <c r="I57" s="83"/>
+      <c r="J57" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K57" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L57" s="83"/>
+      <c r="M57" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="83" t="s">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="B58" s="83" t="s">
+      <c r="B58" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="83" t="s">
+      <c r="C58" s="87" t="s">
         <v>76</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E58" s="83" t="s">
+      <c r="E58" s="87" t="s">
         <v>223</v>
       </c>
-      <c r="F58" s="84"/>
-      <c r="G58" s="84" t="s">
+      <c r="F58" s="88"/>
+      <c r="G58" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H58" s="7">
         <v>12</v>
       </c>
-      <c r="I58" s="84"/>
-      <c r="J58" s="84">
-        <v>12</v>
-      </c>
-      <c r="K58" s="84"/>
+      <c r="I58" s="83"/>
+      <c r="J58" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K58" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L58" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M58" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N58" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O58" s="85"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="88" t="s">
+      <c r="M58" s="83"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="91" t="s">
         <v>224</v>
       </c>
-      <c r="B59" s="83" t="s">
+      <c r="B59" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C59" s="83" t="s">
+      <c r="C59" s="87" t="s">
         <v>225</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="83" t="s">
+      <c r="E59" s="87" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="84"/>
-      <c r="G59" s="84" t="s">
+      <c r="F59" s="88"/>
+      <c r="G59" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H59" s="7">
         <v>100</v>
       </c>
-      <c r="I59" s="84"/>
-      <c r="J59" s="84">
-        <v>100</v>
-      </c>
-      <c r="K59" s="84"/>
+      <c r="I59" s="83"/>
+      <c r="J59" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K59" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L59" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M59" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N59" s="85" t="s">
         <v>227</v>
       </c>
-      <c r="O59" s="85"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="88" t="s">
+      <c r="M59" s="83"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="91" t="s">
         <v>228</v>
       </c>
-      <c r="B60" s="83" t="s">
+      <c r="B60" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C60" s="83" t="s">
+      <c r="C60" s="87" t="s">
         <v>229</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="83" t="s">
+      <c r="E60" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="F60" s="84"/>
-      <c r="G60" s="84" t="s">
+      <c r="F60" s="88"/>
+      <c r="G60" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H60" s="7">
         <v>176</v>
       </c>
-      <c r="I60" s="84"/>
-      <c r="J60" s="84">
-        <v>176</v>
-      </c>
-      <c r="K60" s="84"/>
-      <c r="L60" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M60" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N60" s="85"/>
-      <c r="O60" s="85" t="s">
+      <c r="I60" s="83"/>
+      <c r="J60" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K60" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L60" s="83"/>
+      <c r="M60" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="83" t="s">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="87" t="s">
         <v>228</v>
       </c>
-      <c r="B61" s="83" t="s">
+      <c r="B61" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="83" t="s">
+      <c r="C61" s="87" t="s">
         <v>229</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="83" t="s">
+      <c r="E61" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="F61" s="84"/>
-      <c r="G61" s="84" t="s">
+      <c r="F61" s="88"/>
+      <c r="G61" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H61" s="7">
         <v>800</v>
       </c>
-      <c r="I61" s="84"/>
-      <c r="J61" s="84">
-        <v>800</v>
-      </c>
-      <c r="K61" s="84"/>
-      <c r="L61" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M61" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N61" s="85"/>
-      <c r="O61" s="85" t="s">
+      <c r="I61" s="83"/>
+      <c r="J61" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K61" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" s="83"/>
+      <c r="M61" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="83" t="s">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="87" t="s">
         <v>231</v>
       </c>
-      <c r="B62" s="83" t="s">
+      <c r="B62" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="83" t="s">
+      <c r="C62" s="87" t="s">
         <v>232</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E62" s="83" t="s">
+      <c r="E62" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="F62" s="84"/>
-      <c r="G62" s="84" t="s">
+      <c r="F62" s="88"/>
+      <c r="G62" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H62" s="7">
         <v>324</v>
       </c>
-      <c r="I62" s="84"/>
-      <c r="J62" s="84">
-        <v>324</v>
-      </c>
-      <c r="K62" s="84"/>
+      <c r="I62" s="83"/>
+      <c r="J62" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K62" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L62" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M62" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N62" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="O62" s="85" t="s">
+      <c r="M62" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="83" t="s">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="87" t="s">
         <v>233</v>
       </c>
-      <c r="B63" s="83" t="s">
+      <c r="B63" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="83" t="s">
+      <c r="C63" s="87" t="s">
         <v>234</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="83" t="s">
+      <c r="E63" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="F63" s="84"/>
-      <c r="G63" s="84" t="s">
+      <c r="F63" s="88"/>
+      <c r="G63" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H63" s="7">
         <v>320</v>
       </c>
-      <c r="I63" s="84"/>
-      <c r="J63" s="84">
-        <v>320</v>
-      </c>
-      <c r="K63" s="84" t="s">
+      <c r="I63" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J63" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K63" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L63" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M63" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N63" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="O63" s="85" t="s">
+      <c r="M63" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="86" t="s">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" s="89" t="s">
         <v>236</v>
       </c>
-      <c r="B64" s="83" t="s">
+      <c r="B64" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="83" t="s">
+      <c r="C64" s="87" t="s">
         <v>237</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="86" t="s">
+      <c r="E64" s="89" t="s">
         <v>238</v>
       </c>
-      <c r="F64" s="84"/>
-      <c r="G64" s="84" t="s">
+      <c r="F64" s="88"/>
+      <c r="G64" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H64" s="7">
         <v>176</v>
       </c>
-      <c r="I64" s="84"/>
-      <c r="J64" s="84">
-        <v>176</v>
-      </c>
-      <c r="K64" s="84" t="s">
+      <c r="I64" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J64" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K64" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L64" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M64" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N64" s="85" t="s">
         <v>239</v>
       </c>
-      <c r="O64" s="85" t="s">
+      <c r="M64" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="83" t="s">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="B65" s="83" t="s">
+      <c r="B65" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C65" s="83" t="s">
+      <c r="C65" s="87" t="s">
         <v>241</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E65" s="83" t="s">
+      <c r="E65" s="87" t="s">
         <v>242</v>
       </c>
-      <c r="F65" s="84"/>
-      <c r="G65" s="84" t="s">
+      <c r="F65" s="88"/>
+      <c r="G65" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H65" s="7">
         <v>168</v>
       </c>
-      <c r="I65" s="84"/>
-      <c r="J65" s="84">
-        <v>168</v>
-      </c>
-      <c r="K65" s="84" t="s">
+      <c r="I65" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L65" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M65" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N65" s="85"/>
-      <c r="O65" s="85" t="s">
+      <c r="J65" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K65" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L65" s="83"/>
+      <c r="M65" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="83" t="s">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="87" t="s">
         <v>243</v>
       </c>
-      <c r="B66" s="83" t="s">
+      <c r="B66" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="83" t="s">
+      <c r="C66" s="87" t="s">
         <v>244</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E66" s="83" t="s">
+      <c r="E66" s="87" t="s">
         <v>245</v>
       </c>
-      <c r="F66" s="84"/>
-      <c r="G66" s="84" t="s">
+      <c r="F66" s="88"/>
+      <c r="G66" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H66" s="7">
         <v>218</v>
       </c>
-      <c r="I66" s="84"/>
-      <c r="J66" s="84">
-        <v>218</v>
-      </c>
-      <c r="K66" s="84" t="s">
+      <c r="I66" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L66" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M66" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N66" s="85"/>
-      <c r="O66" s="85" t="s">
+      <c r="J66" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K66" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L66" s="83"/>
+      <c r="M66" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="83" t="s">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="87" t="s">
         <v>246</v>
       </c>
-      <c r="B67" s="83" t="s">
+      <c r="B67" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="83" t="s">
+      <c r="C67" s="87" t="s">
         <v>247</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E67" s="83" t="s">
+      <c r="E67" s="87" t="s">
         <v>248</v>
       </c>
-      <c r="F67" s="84"/>
-      <c r="G67" s="84" t="s">
+      <c r="F67" s="88"/>
+      <c r="G67" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H67" s="7">
         <v>244</v>
       </c>
-      <c r="I67" s="84"/>
-      <c r="J67" s="84">
-        <v>244</v>
-      </c>
-      <c r="K67" s="84" t="s">
+      <c r="I67" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J67" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K67" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L67" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M67" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N67" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="O67" s="85" t="s">
+      <c r="M67" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="83" t="s">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="B68" s="83" t="s">
+      <c r="B68" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C68" s="83" t="s">
+      <c r="C68" s="87" t="s">
         <v>250</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E68" s="83" t="s">
+      <c r="E68" s="87" t="s">
         <v>251</v>
       </c>
-      <c r="F68" s="84"/>
-      <c r="G68" s="84" t="s">
+      <c r="F68" s="88"/>
+      <c r="G68" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="H68" s="7"/>
-      <c r="I68" s="84"/>
-      <c r="J68" s="84">
+      <c r="H68" s="7">
         <v>0</v>
       </c>
-      <c r="K68" s="84"/>
+      <c r="I68" s="83"/>
+      <c r="J68" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K68" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L68" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M68" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N68" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="O68" s="85" t="s">
+      <c r="M68" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="86" t="s">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="89" t="s">
         <v>252</v>
       </c>
-      <c r="B69" s="83" t="s">
+      <c r="B69" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C69" s="83" t="s">
+      <c r="C69" s="87" t="s">
         <v>253</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="86" t="s">
+      <c r="E69" s="89" t="s">
         <v>248</v>
       </c>
-      <c r="F69" s="84"/>
-      <c r="G69" s="84" t="s">
+      <c r="F69" s="88"/>
+      <c r="G69" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H69" s="7">
         <v>162</v>
       </c>
-      <c r="I69" s="84"/>
-      <c r="J69" s="84">
-        <v>162</v>
-      </c>
-      <c r="K69" s="84" t="s">
+      <c r="I69" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L69" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M69" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N69" s="85"/>
-      <c r="O69" s="85" t="s">
+      <c r="J69" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K69" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L69" s="83"/>
+      <c r="M69" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="83" t="s">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="87" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="83" t="s">
+      <c r="B70" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C70" s="83" t="s">
+      <c r="C70" s="87" t="s">
         <v>255</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="83" t="s">
+      <c r="E70" s="87" t="s">
         <v>256</v>
       </c>
-      <c r="F70" s="84"/>
-      <c r="G70" s="84" t="s">
+      <c r="F70" s="88"/>
+      <c r="G70" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H70" s="7">
         <v>244</v>
       </c>
-      <c r="I70" s="84"/>
-      <c r="J70" s="84">
-        <v>244</v>
-      </c>
-      <c r="K70" s="84" t="s">
+      <c r="I70" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L70" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M70" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N70" s="85"/>
-      <c r="O70" s="85" t="s">
+      <c r="J70" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K70" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L70" s="83"/>
+      <c r="M70" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="83" t="s">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="87" t="s">
         <v>257</v>
       </c>
-      <c r="B71" s="83" t="s">
+      <c r="B71" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C71" s="83" t="s">
+      <c r="C71" s="87" t="s">
         <v>258</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E71" s="83" t="s">
+      <c r="E71" s="87" t="s">
         <v>259</v>
       </c>
-      <c r="F71" s="84"/>
-      <c r="G71" s="84" t="s">
+      <c r="F71" s="88"/>
+      <c r="G71" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H71" s="7">
         <v>390</v>
       </c>
-      <c r="I71" s="84"/>
-      <c r="J71" s="84">
-        <v>390</v>
-      </c>
-      <c r="K71" s="84" t="s">
+      <c r="I71" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L71" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M71" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N71" s="85"/>
-      <c r="O71" s="85" t="s">
+      <c r="J71" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K71" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L71" s="83"/>
+      <c r="M71" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="83" t="s">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="87" t="s">
         <v>260</v>
       </c>
-      <c r="B72" s="83" t="s">
+      <c r="B72" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C72" s="83" t="s">
+      <c r="C72" s="87" t="s">
         <v>261</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E72" s="83" t="s">
+      <c r="E72" s="87" t="s">
         <v>262</v>
       </c>
-      <c r="F72" s="84"/>
-      <c r="G72" s="84" t="s">
+      <c r="F72" s="88"/>
+      <c r="G72" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="H72" s="7"/>
-      <c r="I72" s="84"/>
-      <c r="J72" s="84">
+      <c r="H72" s="7">
         <v>0</v>
       </c>
-      <c r="K72" s="84" t="s">
+      <c r="I72" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L72" s="84" t="s">
+      <c r="J72" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="M72" s="84" t="s">
+      <c r="K72" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="N72" s="85"/>
-      <c r="O72" s="85" t="s">
+      <c r="L72" s="83"/>
+      <c r="M72" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="83" t="s">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="87" t="s">
         <v>264</v>
       </c>
-      <c r="B73" s="83" t="s">
+      <c r="B73" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C73" s="83" t="s">
+      <c r="C73" s="87" t="s">
         <v>265</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E73" s="83" t="s">
+      <c r="E73" s="87" t="s">
         <v>266</v>
       </c>
-      <c r="F73" s="84"/>
-      <c r="G73" s="84" t="s">
+      <c r="F73" s="88"/>
+      <c r="G73" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H73" s="7">
         <v>160</v>
       </c>
-      <c r="I73" s="84"/>
-      <c r="J73" s="84">
-        <v>160</v>
-      </c>
-      <c r="K73" s="84" t="s">
+      <c r="I73" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J73" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K73" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L73" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M73" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N73" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="O73" s="85" t="s">
+      <c r="M73" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A74" s="83" t="s">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="87" t="s">
         <v>267</v>
       </c>
-      <c r="B74" s="83" t="s">
+      <c r="B74" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C74" s="83" t="s">
+      <c r="C74" s="87" t="s">
         <v>268</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E74" s="83" t="s">
+      <c r="E74" s="87" t="s">
         <v>269</v>
       </c>
-      <c r="F74" s="84"/>
-      <c r="G74" s="84" t="s">
+      <c r="F74" s="88"/>
+      <c r="G74" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H74" s="7">
         <v>492</v>
       </c>
-      <c r="I74" s="84"/>
-      <c r="J74" s="84">
-        <v>492</v>
-      </c>
-      <c r="K74" s="84" t="s">
+      <c r="I74" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="L74" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M74" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N74" s="85"/>
-      <c r="O74" s="85" t="s">
+      <c r="J74" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K74" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L74" s="83"/>
+      <c r="M74" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" s="83" t="s">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="87" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="83" t="s">
+      <c r="B75" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C75" s="83" t="s">
+      <c r="C75" s="87" t="s">
         <v>271</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E75" s="83" t="s">
+      <c r="E75" s="87" t="s">
         <v>272</v>
       </c>
-      <c r="F75" s="84"/>
-      <c r="G75" s="84" t="s">
+      <c r="F75" s="88"/>
+      <c r="G75" s="88" t="s">
         <v>51</v>
       </c>
       <c r="H75" s="7">
         <v>64</v>
       </c>
-      <c r="I75" s="84"/>
-      <c r="J75" s="84">
-        <v>64</v>
-      </c>
-      <c r="K75" s="84" t="s">
+      <c r="I75" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L75" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M75" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N75" s="85"/>
-      <c r="O75" s="85" t="s">
+      <c r="J75" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K75" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L75" s="83"/>
+      <c r="M75" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" s="86" t="s">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="89" t="s">
         <v>273</v>
       </c>
-      <c r="B76" s="83" t="s">
+      <c r="B76" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="83" t="s">
+      <c r="C76" s="87" t="s">
         <v>274</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="86" t="s">
+      <c r="E76" s="89" t="s">
         <v>275</v>
       </c>
-      <c r="F76" s="84"/>
-      <c r="G76" s="84" t="s">
+      <c r="F76" s="88"/>
+      <c r="G76" s="88" t="s">
         <v>69</v>
       </c>
       <c r="H76" s="7">
         <v>220</v>
       </c>
-      <c r="I76" s="84"/>
-      <c r="J76" s="84">
-        <v>220</v>
-      </c>
-      <c r="K76" s="84" t="s">
+      <c r="I76" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J76" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K76" s="83" t="s">
+        <v>53</v>
+      </c>
       <c r="L76" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M76" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N76" s="85" t="s">
         <v>130</v>
       </c>
-      <c r="O76" s="85" t="s">
+      <c r="M76" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="89" t="s">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" s="92" t="s">
         <v>276</v>
       </c>
-      <c r="B77" s="89" t="s">
+      <c r="B77" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="C77" s="89" t="s">
+      <c r="C77" s="92" t="s">
         <v>277</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E77" s="89" t="s">
+      <c r="E77" s="92" t="s">
         <v>278</v>
       </c>
-      <c r="F77" s="84"/>
-      <c r="G77" s="89" t="s">
+      <c r="F77" s="88"/>
+      <c r="G77" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H77" s="7">
         <v>408</v>
       </c>
-      <c r="I77" s="89"/>
-      <c r="J77" s="89">
-        <v>408</v>
-      </c>
-      <c r="K77" s="89" t="s">
+      <c r="I77" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L77" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M77" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N77" s="85"/>
-      <c r="O77" s="85" t="s">
+      <c r="J77" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K77" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L77" s="83"/>
+      <c r="M77" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" s="89" t="s">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" s="92" t="s">
         <v>279</v>
       </c>
-      <c r="B78" s="89" t="s">
+      <c r="B78" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="C78" s="89" t="s">
+      <c r="C78" s="92" t="s">
         <v>280</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E78" s="89" t="s">
+      <c r="E78" s="92" t="s">
         <v>281</v>
       </c>
-      <c r="F78" s="84"/>
-      <c r="G78" s="89" t="s">
+      <c r="F78" s="88"/>
+      <c r="G78" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H78" s="7">
         <v>832</v>
       </c>
-      <c r="I78" s="89"/>
-      <c r="J78" s="89">
-        <v>832</v>
-      </c>
-      <c r="K78" s="89" t="s">
+      <c r="I78" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L78" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M78" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N78" s="85"/>
-      <c r="O78" s="85" t="s">
+      <c r="J78" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K78" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L78" s="83"/>
+      <c r="M78" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="89" t="s">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="92" t="s">
         <v>282</v>
       </c>
-      <c r="B79" s="89" t="s">
+      <c r="B79" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="C79" s="89" t="s">
+      <c r="C79" s="92" t="s">
         <v>76</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E79" s="89" t="s">
+      <c r="E79" s="92" t="s">
         <v>283</v>
       </c>
-      <c r="F79" s="84"/>
-      <c r="G79" s="89" t="s">
+      <c r="F79" s="88"/>
+      <c r="G79" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H79" s="7">
         <v>450</v>
       </c>
-      <c r="I79" s="89"/>
-      <c r="J79" s="89">
-        <v>450</v>
-      </c>
-      <c r="K79" s="89" t="s">
+      <c r="I79" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L79" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M79" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N79" s="85"/>
-      <c r="O79" s="85" t="s">
+      <c r="J79" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K79" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L79" s="83"/>
+      <c r="M79" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" s="89" t="s">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" s="92" t="s">
         <v>284</v>
       </c>
-      <c r="B80" s="89" t="s">
+      <c r="B80" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="C80" s="89" t="s">
+      <c r="C80" s="92" t="s">
         <v>285</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E80" s="89" t="s">
+      <c r="E80" s="92" t="s">
         <v>286</v>
       </c>
-      <c r="F80" s="84"/>
-      <c r="G80" s="89" t="s">
+      <c r="F80" s="88"/>
+      <c r="G80" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H80" s="7">
         <v>312</v>
       </c>
-      <c r="I80" s="89"/>
-      <c r="J80" s="89">
-        <v>312</v>
-      </c>
-      <c r="K80" s="89" t="s">
+      <c r="I80" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L80" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M80" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N80" s="85"/>
-      <c r="O80" s="85" t="s">
+      <c r="J80" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K80" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L80" s="83"/>
+      <c r="M80" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A81" s="89" t="s">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="92" t="s">
         <v>287</v>
       </c>
-      <c r="B81" s="89" t="s">
+      <c r="B81" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="C81" s="89" t="s">
+      <c r="C81" s="92" t="s">
         <v>288</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E81" s="89" t="s">
+      <c r="E81" s="92" t="s">
         <v>289</v>
       </c>
-      <c r="F81" s="84"/>
-      <c r="G81" s="89" t="s">
+      <c r="F81" s="88"/>
+      <c r="G81" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H81" s="7">
         <v>387</v>
       </c>
-      <c r="I81" s="89"/>
-      <c r="J81" s="89">
-        <v>387</v>
-      </c>
-      <c r="K81" s="89" t="s">
+      <c r="I81" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L81" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M81" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N81" s="85"/>
-      <c r="O81" s="85" t="s">
+      <c r="J81" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K81" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L81" s="83"/>
+      <c r="M81" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A82" s="89" t="s">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="92" t="s">
         <v>290</v>
       </c>
-      <c r="B82" s="89" t="s">
+      <c r="B82" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="89" t="s">
+      <c r="C82" s="92" t="s">
         <v>291</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E82" s="89" t="s">
+      <c r="E82" s="92" t="s">
         <v>292</v>
       </c>
-      <c r="F82" s="84"/>
-      <c r="G82" s="89" t="s">
+      <c r="F82" s="88"/>
+      <c r="G82" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H82" s="7">
         <v>1400</v>
       </c>
-      <c r="I82" s="89"/>
-      <c r="J82" s="89">
-        <v>1400</v>
-      </c>
-      <c r="K82" s="89" t="s">
+      <c r="I82" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L82" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M82" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N82" s="85"/>
-      <c r="O82" s="85" t="s">
+      <c r="J82" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K82" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L82" s="83"/>
+      <c r="M82" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A83" s="89" t="s">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" s="92" t="s">
         <v>293</v>
       </c>
-      <c r="B83" s="89" t="s">
+      <c r="B83" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="C83" s="89" t="s">
+      <c r="C83" s="92" t="s">
         <v>294</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E83" s="89" t="s">
+      <c r="E83" s="92" t="s">
         <v>295</v>
       </c>
-      <c r="F83" s="84"/>
-      <c r="G83" s="89" t="s">
+      <c r="F83" s="88"/>
+      <c r="G83" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H83" s="7">
         <v>720</v>
       </c>
-      <c r="I83" s="89"/>
-      <c r="J83" s="89">
-        <v>720</v>
-      </c>
-      <c r="K83" s="90" t="s">
+      <c r="I83" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L83" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M83" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N83" s="85"/>
-      <c r="O83" s="85" t="s">
+      <c r="J83" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K83" s="86" t="s">
+        <v>53</v>
+      </c>
+      <c r="L83" s="83"/>
+      <c r="M83" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" s="89" t="s">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="92" t="s">
         <v>296</v>
       </c>
-      <c r="B84" s="89" t="s">
+      <c r="B84" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="C84" s="89" t="s">
+      <c r="C84" s="92" t="s">
         <v>297</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="89" t="s">
+      <c r="E84" s="92" t="s">
         <v>298</v>
       </c>
-      <c r="F84" s="84"/>
-      <c r="G84" s="89" t="s">
+      <c r="F84" s="88"/>
+      <c r="G84" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H84" s="7">
         <v>219</v>
       </c>
-      <c r="I84" s="89"/>
-      <c r="J84" s="89">
-        <v>219</v>
-      </c>
-      <c r="K84" s="89" t="s">
+      <c r="I84" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L84" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M84" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N84" s="85"/>
-      <c r="O84" s="85" t="s">
+      <c r="J84" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K84" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L84" s="83"/>
+      <c r="M84" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" s="89" t="s">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="92" t="s">
         <v>299</v>
       </c>
-      <c r="B85" s="89" t="s">
+      <c r="B85" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="89" t="s">
+      <c r="C85" s="92" t="s">
         <v>300</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="89" t="s">
+      <c r="E85" s="92" t="s">
         <v>301</v>
       </c>
-      <c r="F85" s="84"/>
-      <c r="G85" s="89" t="s">
+      <c r="F85" s="88"/>
+      <c r="G85" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H85" s="7">
         <v>1524</v>
       </c>
-      <c r="I85" s="89"/>
-      <c r="J85" s="89">
-        <v>1524</v>
-      </c>
-      <c r="K85" s="89" t="s">
+      <c r="I85" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="L85" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M85" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N85" s="85"/>
-      <c r="O85" s="85" t="s">
+      <c r="J85" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K85" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L85" s="83"/>
+      <c r="M85" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" s="89" t="s">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" s="92" t="s">
         <v>302</v>
       </c>
-      <c r="B86" s="89" t="s">
+      <c r="B86" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="C86" s="89" t="s">
+      <c r="C86" s="92" t="s">
         <v>303</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="89" t="s">
+      <c r="E86" s="92" t="s">
         <v>304</v>
       </c>
       <c r="F86" s="10">
         <v>2870896608</v>
       </c>
-      <c r="G86" s="89" t="s">
+      <c r="G86" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H86" s="7">
         <v>320</v>
       </c>
-      <c r="I86" s="89"/>
-      <c r="J86" s="89">
-        <v>320</v>
-      </c>
-      <c r="K86" s="89" t="s">
+      <c r="I86" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L86" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M86" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N86" s="85"/>
-      <c r="O86" s="85" t="s">
+      <c r="J86" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K86" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L86" s="83"/>
+      <c r="M86" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" s="89" t="s">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" s="92" t="s">
         <v>305</v>
       </c>
-      <c r="B87" s="89" t="s">
+      <c r="B87" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="C87" s="89" t="s">
+      <c r="C87" s="92" t="s">
         <v>306</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E87" s="89" t="s">
+      <c r="E87" s="92" t="s">
         <v>202</v>
       </c>
       <c r="F87" s="10">
         <v>13970595273</v>
       </c>
-      <c r="G87" s="89" t="s">
+      <c r="G87" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H87" s="7">
         <v>2342</v>
       </c>
-      <c r="I87" s="89"/>
-      <c r="J87" s="89">
-        <v>2342</v>
-      </c>
-      <c r="K87" s="89" t="s">
+      <c r="I87" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L87" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M87" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N87" s="85"/>
-      <c r="O87" s="85" t="s">
+      <c r="J87" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K87" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L87" s="83"/>
+      <c r="M87" s="85" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" s="89" t="s">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="B88" s="89" t="s">
+      <c r="B88" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="C88" s="89" t="s">
+      <c r="C88" s="92" t="s">
         <v>308</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E88" s="89" t="s">
+      <c r="E88" s="92" t="s">
         <v>309</v>
       </c>
       <c r="F88" s="10">
         <v>259948145</v>
       </c>
-      <c r="G88" s="89" t="s">
+      <c r="G88" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H88" s="7">
         <v>34</v>
       </c>
-      <c r="I88" s="89"/>
-      <c r="J88" s="89">
-        <v>34</v>
-      </c>
-      <c r="K88" s="89" t="s">
+      <c r="I88" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L88" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M88" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N88" s="85"/>
-      <c r="O88" s="85" t="s">
+      <c r="J88" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K88" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L88" s="83"/>
+      <c r="M88" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A89" s="91" t="s">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="93" t="s">
         <v>310</v>
       </c>
-      <c r="B89" s="89" t="s">
+      <c r="B89" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="C89" s="89" t="s">
+      <c r="C89" s="92" t="s">
         <v>308</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E89" s="89" t="s">
+      <c r="E89" s="92" t="s">
         <v>311</v>
       </c>
       <c r="F89" s="10">
         <v>834933960</v>
       </c>
-      <c r="G89" s="89" t="s">
+      <c r="G89" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H89" s="7">
         <v>224</v>
       </c>
-      <c r="I89" s="89"/>
-      <c r="J89" s="89">
-        <v>224</v>
-      </c>
-      <c r="K89" s="89" t="s">
+      <c r="I89" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L89" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M89" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N89" s="85"/>
-      <c r="O89" s="85" t="s">
+      <c r="J89" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K89" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L89" s="83"/>
+      <c r="M89" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" s="89" t="s">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" s="92" t="s">
         <v>350</v>
       </c>
-      <c r="B90" s="89" t="s">
+      <c r="B90" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="C90" s="89" t="s">
+      <c r="C90" s="92" t="s">
         <v>308</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E90" s="89" t="s">
+      <c r="E90" s="92" t="s">
         <v>312</v>
       </c>
       <c r="F90" s="10">
         <v>723157595</v>
       </c>
-      <c r="G90" s="89" t="s">
+      <c r="G90" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H90" s="7">
         <v>138</v>
       </c>
-      <c r="I90" s="89"/>
-      <c r="J90" s="89">
-        <v>138</v>
-      </c>
-      <c r="K90" s="89" t="s">
+      <c r="I90" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L90" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M90" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N90" s="85"/>
-      <c r="O90" s="85" t="s">
+      <c r="J90" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K90" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L90" s="83"/>
+      <c r="M90" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" s="89" t="s">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" s="92" t="s">
         <v>313</v>
       </c>
-      <c r="B91" s="89" t="s">
+      <c r="B91" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="89" t="s">
+      <c r="C91" s="92" t="s">
         <v>308</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E91" s="89" t="s">
+      <c r="E91" s="92" t="s">
         <v>314</v>
       </c>
       <c r="F91" s="10">
         <v>805795560</v>
       </c>
-      <c r="G91" s="89" t="s">
+      <c r="G91" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H91" s="7">
         <v>56</v>
       </c>
-      <c r="I91" s="89"/>
-      <c r="J91" s="89">
-        <v>56</v>
-      </c>
-      <c r="K91" s="89" t="s">
+      <c r="I91" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L91" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M91" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N91" s="85"/>
-      <c r="O91" s="85" t="s">
+      <c r="J91" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K91" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L91" s="83"/>
+      <c r="M91" s="85" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" s="83" t="s">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" s="87" t="s">
         <v>315</v>
       </c>
-      <c r="B92" s="83" t="s">
+      <c r="B92" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C92" s="83" t="s">
+      <c r="C92" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E92" s="83" t="s">
+      <c r="E92" s="87" t="s">
         <v>316</v>
       </c>
       <c r="F92" s="10">
         <v>2165000000</v>
       </c>
-      <c r="G92" s="84" t="s">
+      <c r="G92" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H92" s="7">
         <v>928</v>
       </c>
-      <c r="I92" s="84"/>
-      <c r="J92" s="84">
-        <v>928</v>
-      </c>
-      <c r="K92" s="84" t="s">
+      <c r="I92" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L92" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M92" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N92" s="85"/>
-      <c r="O92" s="85" t="s">
+      <c r="J92" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K92" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L92" s="83"/>
+      <c r="M92" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A93" s="83" t="s">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" s="87" t="s">
         <v>317</v>
       </c>
-      <c r="B93" s="83" t="s">
+      <c r="B93" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C93" s="83" t="s">
+      <c r="C93" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E93" s="83" t="s">
+      <c r="E93" s="87" t="s">
         <v>318</v>
       </c>
       <c r="F93" s="10">
         <v>2959258280</v>
       </c>
-      <c r="G93" s="84" t="s">
+      <c r="G93" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H93" s="7">
         <v>600</v>
       </c>
-      <c r="I93" s="84"/>
-      <c r="J93" s="84">
-        <v>600</v>
-      </c>
-      <c r="K93" s="84" t="s">
+      <c r="I93" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L93" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M93" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N93" s="85"/>
-      <c r="O93" s="85" t="s">
+      <c r="J93" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K93" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L93" s="83"/>
+      <c r="M93" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="84" t="s">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" s="88" t="s">
         <v>319</v>
       </c>
-      <c r="B94" s="89" t="s">
+      <c r="B94" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="C94" s="89" t="s">
+      <c r="C94" s="92" t="s">
         <v>308</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="89" t="s">
+      <c r="E94" s="92" t="s">
         <v>320</v>
       </c>
       <c r="F94" s="10">
         <v>199672220</v>
       </c>
-      <c r="G94" s="89" t="s">
+      <c r="G94" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H94" s="7">
         <v>33</v>
       </c>
-      <c r="I94" s="89"/>
-      <c r="J94" s="89">
-        <v>33</v>
-      </c>
-      <c r="K94" s="89" t="s">
+      <c r="I94" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L94" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M94" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="N94" s="85"/>
-      <c r="O94" s="85" t="s">
+      <c r="J94" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K94" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L94" s="83"/>
+      <c r="M94" s="85" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" s="88" t="s">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" s="91" t="s">
         <v>321</v>
       </c>
-      <c r="B95" s="83" t="s">
+      <c r="B95" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C95" s="83" t="s">
+      <c r="C95" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E95" s="83" t="s">
+      <c r="E95" s="87" t="s">
         <v>322</v>
       </c>
       <c r="F95" s="7">
         <v>5915704000</v>
       </c>
-      <c r="G95" s="84" t="s">
+      <c r="G95" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H95" s="7">
         <v>810</v>
       </c>
-      <c r="I95" s="84"/>
-      <c r="J95" s="84">
-        <v>810</v>
-      </c>
-      <c r="K95" s="84" t="s">
+      <c r="I95" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L95" s="84" t="s">
+      <c r="J95" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="M95" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N95" s="85"/>
-      <c r="O95" s="85" t="s">
+      <c r="K95" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L95" s="83"/>
+      <c r="M95" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" s="88" t="s">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" s="91" t="s">
         <v>323</v>
       </c>
-      <c r="B96" s="87" t="s">
+      <c r="B96" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="C96" s="87" t="s">
+      <c r="C96" s="90" t="s">
         <v>308</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E96" s="87" t="s">
+      <c r="E96" s="90" t="s">
         <v>324</v>
       </c>
       <c r="F96" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G96" s="84" t="s">
+      <c r="G96" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H96" s="7">
-        <v>720</v>
-      </c>
-      <c r="I96" s="84">
-        <v>720</v>
-      </c>
-      <c r="J96" s="84">
         <v>0</v>
       </c>
-      <c r="K96" s="84" t="s">
+      <c r="I96" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L96" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M96" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N96" s="85"/>
-      <c r="O96" s="85" t="s">
+      <c r="J96" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K96" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L96" s="83"/>
+      <c r="M96" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A97" s="88" t="s">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" s="91" t="s">
         <v>323</v>
       </c>
-      <c r="B97" s="87" t="s">
+      <c r="B97" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="C97" s="87" t="s">
+      <c r="C97" s="90" t="s">
         <v>308</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E97" s="87" t="s">
+      <c r="E97" s="90" t="s">
         <v>324</v>
       </c>
       <c r="F97" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G97" s="84" t="s">
+      <c r="G97" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H97" s="7">
-        <v>176</v>
-      </c>
-      <c r="I97" s="84">
-        <v>176</v>
-      </c>
-      <c r="J97" s="84">
         <v>0</v>
       </c>
-      <c r="K97" s="84" t="s">
+      <c r="I97" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L97" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M97" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N97" s="85"/>
-      <c r="O97" s="85" t="s">
+      <c r="J97" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K97" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L97" s="83"/>
+      <c r="M97" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" s="88" t="s">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" s="91" t="s">
         <v>325</v>
       </c>
-      <c r="B98" s="83" t="s">
+      <c r="B98" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C98" s="83" t="s">
+      <c r="C98" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E98" s="83" t="s">
+      <c r="E98" s="87" t="s">
         <v>326</v>
       </c>
       <c r="F98" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G98" s="84" t="s">
+      <c r="G98" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H98" s="7">
-        <v>480</v>
-      </c>
-      <c r="I98" s="84">
-        <v>483</v>
-      </c>
-      <c r="J98" s="84">
         <v>-3</v>
       </c>
-      <c r="K98" s="84" t="s">
+      <c r="I98" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L98" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M98" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N98" s="85"/>
-      <c r="O98" s="85" t="s">
+      <c r="J98" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K98" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L98" s="83"/>
+      <c r="M98" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A99" s="83" t="s">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" s="87" t="s">
         <v>325</v>
       </c>
-      <c r="B99" s="83" t="s">
+      <c r="B99" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C99" s="83" t="s">
+      <c r="C99" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E99" s="83" t="s">
+      <c r="E99" s="87" t="s">
         <v>326</v>
       </c>
       <c r="F99" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G99" s="84" t="s">
+      <c r="G99" s="88" t="s">
         <v>57</v>
       </c>
       <c r="H99" s="7">
-        <v>483</v>
-      </c>
-      <c r="I99" s="84">
-        <v>483</v>
-      </c>
-      <c r="J99" s="84">
         <v>0</v>
       </c>
-      <c r="K99" s="84" t="s">
+      <c r="I99" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="L99" s="84" t="s">
+      <c r="J99" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="M99" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N99" s="85"/>
-      <c r="O99" s="85" t="s">
+      <c r="K99" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L99" s="83"/>
+      <c r="M99" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" s="83" t="s">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="B100" s="83" t="s">
+      <c r="B100" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C100" s="83" t="s">
+      <c r="C100" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E100" s="89" t="s">
+      <c r="E100" s="92" t="s">
         <v>202</v>
       </c>
-      <c r="F100" s="84"/>
-      <c r="G100" s="84" t="s">
+      <c r="F100" s="88"/>
+      <c r="G100" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H100" s="7">
-        <v>4478</v>
-      </c>
-      <c r="I100" s="84">
-        <v>4486</v>
-      </c>
-      <c r="J100" s="84">
         <v>-8</v>
       </c>
-      <c r="K100" s="84" t="s">
+      <c r="I100" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L100" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M100" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N100" s="85"/>
-      <c r="O100" s="85" t="s">
+      <c r="J100" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K100" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L100" s="83"/>
+      <c r="M100" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A101" s="83" t="s">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="87" t="s">
         <v>327</v>
       </c>
-      <c r="B101" s="83" t="s">
+      <c r="B101" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C101" s="83" t="s">
+      <c r="C101" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="89" t="s">
+      <c r="E101" s="92" t="s">
         <v>328</v>
       </c>
       <c r="F101" s="7">
         <v>11684429947</v>
       </c>
-      <c r="G101" s="84" t="s">
+      <c r="G101" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H101" s="7">
-        <v>2556</v>
-      </c>
-      <c r="I101" s="84">
-        <v>2545</v>
-      </c>
-      <c r="J101" s="84">
         <v>11</v>
       </c>
-      <c r="K101" s="84" t="s">
+      <c r="I101" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L101" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M101" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N101" s="85"/>
-      <c r="O101" s="85" t="s">
+      <c r="J101" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K101" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L101" s="83"/>
+      <c r="M101" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A102" s="83" t="s">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="87" t="s">
         <v>329</v>
       </c>
-      <c r="B102" s="83" t="s">
+      <c r="B102" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C102" s="83" t="s">
+      <c r="C102" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E102" s="89" t="s">
+      <c r="E102" s="92" t="s">
         <v>330</v>
       </c>
-      <c r="F102" s="84"/>
-      <c r="G102" s="84" t="s">
+      <c r="F102" s="88"/>
+      <c r="G102" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H102" s="7">
-        <v>968</v>
-      </c>
-      <c r="I102" s="84">
-        <v>968</v>
-      </c>
-      <c r="J102" s="84">
         <v>0</v>
       </c>
-      <c r="K102" s="84" t="s">
+      <c r="I102" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L102" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M102" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N102" s="85"/>
-      <c r="O102" s="85" t="s">
+      <c r="J102" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K102" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L102" s="83"/>
+      <c r="M102" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="83" t="s">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="87" t="s">
         <v>331</v>
       </c>
-      <c r="B103" s="83" t="s">
+      <c r="B103" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C103" s="83" t="s">
+      <c r="C103" s="87" t="s">
         <v>332</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E103" s="89" t="s">
+      <c r="E103" s="92" t="s">
         <v>333</v>
       </c>
       <c r="F103" s="7">
         <v>2329683517</v>
       </c>
-      <c r="G103" s="84" t="s">
+      <c r="G103" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H103" s="7">
-        <v>198</v>
-      </c>
-      <c r="I103" s="84">
-        <v>198</v>
-      </c>
-      <c r="J103" s="84">
         <v>0</v>
       </c>
-      <c r="K103" s="84" t="s">
+      <c r="I103" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L103" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M103" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N103" s="85"/>
-      <c r="O103" s="85" t="s">
+      <c r="J103" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K103" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L103" s="83"/>
+      <c r="M103" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A104" s="83" t="s">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" s="87" t="s">
         <v>334</v>
       </c>
-      <c r="B104" s="83" t="s">
+      <c r="B104" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C104" s="83" t="s">
+      <c r="C104" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="89" t="s">
+      <c r="E104" s="92" t="s">
         <v>335</v>
       </c>
       <c r="F104" s="7">
         <v>1545593000</v>
       </c>
-      <c r="G104" s="84" t="s">
+      <c r="G104" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H104" s="7">
-        <v>216</v>
-      </c>
-      <c r="I104" s="84">
-        <v>216</v>
-      </c>
-      <c r="J104" s="84">
         <v>0</v>
       </c>
-      <c r="K104" s="84" t="s">
+      <c r="I104" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L104" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M104" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N104" s="85"/>
-      <c r="O104" s="85" t="s">
+      <c r="J104" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K104" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L104" s="83"/>
+      <c r="M104" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A105" s="83" t="s">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="87" t="s">
         <v>346</v>
       </c>
-      <c r="B105" s="83" t="s">
+      <c r="B105" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C105" s="83" t="s">
+      <c r="C105" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E105" s="89" t="s">
+      <c r="E105" s="92" t="s">
         <v>347</v>
       </c>
-      <c r="F105" s="84"/>
-      <c r="G105" s="84" t="s">
+      <c r="F105" s="88"/>
+      <c r="G105" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H105" s="7">
         <v>25</v>
       </c>
-      <c r="I105" s="84"/>
-      <c r="J105" s="84">
-        <v>25</v>
-      </c>
-      <c r="K105" s="84" t="s">
+      <c r="I105" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L105" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M105" s="84" t="s">
+      <c r="J105" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K105" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="N105" s="85"/>
-      <c r="O105" s="85" t="s">
+      <c r="L105" s="83"/>
+      <c r="M105" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A106" s="83" t="s">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="87" t="s">
         <v>348</v>
       </c>
-      <c r="B106" s="83" t="s">
+      <c r="B106" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C106" s="83" t="s">
+      <c r="C106" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E106" s="89" t="s">
+      <c r="E106" s="92" t="s">
         <v>349</v>
       </c>
       <c r="F106" s="7">
         <v>863631818.20000005</v>
       </c>
-      <c r="G106" s="84" t="s">
+      <c r="G106" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H106" s="7">
-        <v>160</v>
-      </c>
-      <c r="I106" s="84">
-        <v>160</v>
-      </c>
-      <c r="J106" s="84">
         <v>0</v>
       </c>
-      <c r="K106" s="84" t="s">
+      <c r="I106" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L106" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M106" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N106" s="85"/>
-      <c r="O106" s="85" t="s">
+      <c r="J106" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K106" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L106" s="83"/>
+      <c r="M106" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A107" s="83" t="s">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="87" t="s">
         <v>352</v>
       </c>
-      <c r="B107" s="83" t="s">
+      <c r="B107" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C107" s="83" t="s">
+      <c r="C107" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E107" s="89" t="s">
+      <c r="E107" s="92" t="s">
         <v>353</v>
       </c>
       <c r="F107" s="7">
         <v>3338181818</v>
       </c>
-      <c r="G107" s="84" t="s">
+      <c r="G107" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H107" s="7">
-        <v>726</v>
-      </c>
-      <c r="I107" s="84">
-        <v>726</v>
-      </c>
-      <c r="J107" s="84">
         <v>0</v>
       </c>
-      <c r="K107" s="84" t="s">
+      <c r="I107" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L107" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M107" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N107" s="85"/>
-      <c r="O107" s="85" t="s">
+      <c r="J107" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K107" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L107" s="83"/>
+      <c r="M107" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A108" s="83" t="s">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="87" t="s">
         <v>354</v>
       </c>
-      <c r="B108" s="83" t="s">
+      <c r="B108" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C108" s="83" t="s">
+      <c r="C108" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E108" s="89" t="s">
+      <c r="E108" s="92" t="s">
         <v>230</v>
       </c>
-      <c r="F108" s="84"/>
-      <c r="G108" s="84" t="s">
+      <c r="F108" s="88"/>
+      <c r="G108" s="88" t="s">
         <v>87</v>
       </c>
       <c r="H108" s="7">
-        <v>126</v>
-      </c>
-      <c r="I108" s="84">
-        <v>126</v>
-      </c>
-      <c r="J108" s="84">
         <v>0</v>
       </c>
-      <c r="K108" s="84" t="s">
+      <c r="I108" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="L108" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M108" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N108" s="85"/>
-      <c r="O108" s="85" t="s">
+      <c r="J108" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K108" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L108" s="83"/>
+      <c r="M108" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A109" s="83" t="s">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="87" t="s">
         <v>355</v>
       </c>
-      <c r="B109" s="83" t="s">
+      <c r="B109" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C109" s="83" t="s">
+      <c r="C109" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E109" s="89" t="s">
+      <c r="E109" s="92" t="s">
         <v>356</v>
       </c>
       <c r="F109" s="7">
         <v>719278000</v>
       </c>
-      <c r="G109" s="84" t="s">
+      <c r="G109" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H109" s="7">
-        <v>159</v>
-      </c>
-      <c r="I109" s="84">
-        <v>159</v>
-      </c>
-      <c r="J109" s="84">
         <v>0</v>
       </c>
-      <c r="K109" s="84" t="s">
+      <c r="I109" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L109" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M109" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N109" s="85"/>
-      <c r="O109" s="85" t="s">
+      <c r="J109" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K109" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L109" s="83"/>
+      <c r="M109" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A110" s="83" t="s">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" s="87" t="s">
         <v>357</v>
       </c>
-      <c r="B110" s="83" t="s">
+      <c r="B110" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C110" s="83" t="s">
+      <c r="C110" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E110" s="89" t="s">
+      <c r="E110" s="92" t="s">
         <v>358</v>
       </c>
       <c r="F110" s="7">
         <v>2186917438</v>
       </c>
-      <c r="G110" s="84" t="s">
+      <c r="G110" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H110" s="7">
-        <v>488</v>
-      </c>
-      <c r="I110" s="84">
-        <v>488</v>
-      </c>
-      <c r="J110" s="84">
         <v>0</v>
       </c>
-      <c r="K110" s="84" t="s">
+      <c r="I110" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L110" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M110" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N110" s="85"/>
-      <c r="O110" s="85" t="s">
+      <c r="J110" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K110" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L110" s="83"/>
+      <c r="M110" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A111" s="83" t="s">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" s="87" t="s">
         <v>365</v>
       </c>
-      <c r="B111" s="83" t="s">
+      <c r="B111" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C111" s="83" t="s">
+      <c r="C111" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E111" s="89" t="s">
+      <c r="E111" s="92" t="s">
         <v>366</v>
       </c>
       <c r="F111" s="7">
         <v>69307272.730000004</v>
       </c>
-      <c r="G111" s="84" t="s">
+      <c r="G111" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H111" s="7">
-        <v>12</v>
-      </c>
-      <c r="I111" s="84">
-        <v>12</v>
-      </c>
-      <c r="J111" s="84">
         <v>0</v>
       </c>
-      <c r="K111" s="84" t="s">
+      <c r="I111" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L111" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M111" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N111" s="85"/>
-      <c r="O111" s="85" t="s">
+      <c r="J111" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K111" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L111" s="83"/>
+      <c r="M111" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A112" s="83" t="s">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" s="87" t="s">
         <v>367</v>
       </c>
-      <c r="B112" s="83" t="s">
+      <c r="B112" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C112" s="83" t="s">
+      <c r="C112" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="89" t="s">
+      <c r="E112" s="92" t="s">
         <v>368</v>
       </c>
       <c r="F112" s="7">
         <v>140818181.80000001</v>
       </c>
-      <c r="G112" s="84" t="s">
+      <c r="G112" s="88" t="s">
         <v>1</v>
       </c>
       <c r="H112" s="7">
-        <v>20</v>
-      </c>
-      <c r="I112" s="84">
-        <v>20</v>
-      </c>
-      <c r="J112" s="84">
         <v>0</v>
       </c>
-      <c r="K112" s="84" t="s">
+      <c r="I112" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L112" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M112" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N112" s="85"/>
-      <c r="O112" s="85" t="s">
+      <c r="J112" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K112" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L112" s="83"/>
+      <c r="M112" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A113" s="83" t="s">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="87" t="s">
         <v>369</v>
       </c>
-      <c r="B113" s="83" t="s">
+      <c r="B113" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C113" s="83" t="s">
+      <c r="C113" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E113" s="89" t="s">
+      <c r="E113" s="92" t="s">
         <v>370</v>
       </c>
       <c r="F113" s="7">
         <v>1196969505</v>
       </c>
-      <c r="G113" s="84" t="s">
+      <c r="G113" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H113" s="7">
-        <v>288</v>
-      </c>
-      <c r="I113" s="84">
-        <v>288</v>
-      </c>
-      <c r="J113" s="84">
         <v>0</v>
       </c>
-      <c r="K113" s="84" t="s">
+      <c r="I113" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L113" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M113" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N113" s="85"/>
-      <c r="O113" s="85" t="s">
+      <c r="J113" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K113" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L113" s="83"/>
+      <c r="M113" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A114" s="83" t="s">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="87" t="s">
         <v>371</v>
       </c>
-      <c r="B114" s="83" t="s">
+      <c r="B114" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C114" s="83" t="s">
+      <c r="C114" s="87" t="s">
         <v>372</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E114" s="89" t="s">
+      <c r="E114" s="92" t="s">
         <v>373</v>
       </c>
       <c r="F114" s="7">
         <v>3761066864</v>
       </c>
-      <c r="G114" s="84" t="s">
+      <c r="G114" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H114" s="7">
-        <v>960</v>
-      </c>
-      <c r="I114" s="84">
-        <v>960</v>
-      </c>
-      <c r="J114" s="84">
         <v>0</v>
       </c>
-      <c r="K114" s="84" t="s">
+      <c r="I114" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L114" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M114" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N114" s="85"/>
-      <c r="O114" s="85" t="s">
+      <c r="J114" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K114" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L114" s="83"/>
+      <c r="M114" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A115" s="83" t="s">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="87" t="s">
         <v>374</v>
       </c>
-      <c r="B115" s="83" t="s">
+      <c r="B115" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C115" s="83" t="s">
+      <c r="C115" s="87" t="s">
         <v>375</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E115" s="89" t="s">
+      <c r="E115" s="92" t="s">
         <v>376</v>
       </c>
       <c r="F115" s="7">
         <v>1188000000</v>
       </c>
-      <c r="G115" s="84" t="s">
+      <c r="G115" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H115" s="7">
         <v>240</v>
       </c>
-      <c r="I115" s="84">
-        <v>0</v>
-      </c>
-      <c r="J115" s="84">
-        <v>240</v>
-      </c>
-      <c r="K115" s="84" t="s">
+      <c r="I115" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L115" s="84" t="s">
-        <v>78</v>
-      </c>
-      <c r="M115" s="84" t="s">
-        <v>79</v>
-      </c>
-      <c r="N115" s="85"/>
-      <c r="O115" s="85" t="s">
+      <c r="J115" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K115" s="83" t="s">
+        <v>463</v>
+      </c>
+      <c r="L115" s="83"/>
+      <c r="M115" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A116" s="83" t="s">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="87" t="s">
         <v>377</v>
       </c>
-      <c r="B116" s="83" t="s">
+      <c r="B116" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C116" s="83" t="s">
+      <c r="C116" s="87" t="s">
         <v>378</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E116" s="89" t="s">
+      <c r="E116" s="92" t="s">
         <v>379</v>
       </c>
       <c r="F116" s="7">
         <v>8578824307</v>
       </c>
-      <c r="G116" s="84" t="s">
+      <c r="G116" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H116" s="7">
-        <v>700</v>
-      </c>
-      <c r="I116" s="84">
-        <v>700</v>
-      </c>
-      <c r="J116" s="84">
         <v>0</v>
       </c>
-      <c r="K116" s="84" t="s">
+      <c r="I116" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L116" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M116" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N116" s="85"/>
-      <c r="O116" s="85" t="s">
+      <c r="J116" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K116" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L116" s="83"/>
+      <c r="M116" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A117" s="83" t="s">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="87" t="s">
         <v>380</v>
       </c>
-      <c r="B117" s="83" t="s">
+      <c r="B117" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C117" s="83" t="s">
+      <c r="C117" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E117" s="89" t="s">
+      <c r="E117" s="92" t="s">
         <v>381</v>
       </c>
       <c r="F117" s="7">
         <v>2842500250</v>
       </c>
-      <c r="G117" s="84" t="s">
+      <c r="G117" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H117" s="7">
-        <v>626</v>
-      </c>
-      <c r="I117" s="84">
-        <v>626</v>
-      </c>
-      <c r="J117" s="84">
         <v>0</v>
       </c>
-      <c r="K117" s="84" t="s">
+      <c r="I117" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L117" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M117" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N117" s="85"/>
-      <c r="O117" s="85" t="s">
+      <c r="J117" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K117" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L117" s="83"/>
+      <c r="M117" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A118" s="83" t="s">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="87" t="s">
         <v>382</v>
       </c>
-      <c r="B118" s="84"/>
-      <c r="C118" s="84"/>
+      <c r="B118" s="88"/>
+      <c r="C118" s="88"/>
       <c r="D118" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E118" s="89" t="s">
+      <c r="E118" s="92" t="s">
         <v>383</v>
       </c>
       <c r="F118" s="9">
         <v>459000000</v>
       </c>
-      <c r="G118" s="84" t="s">
+      <c r="G118" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H118" s="7">
-        <v>80</v>
-      </c>
-      <c r="I118" s="84">
-        <v>80</v>
-      </c>
-      <c r="J118" s="84">
         <v>0</v>
       </c>
-      <c r="K118" s="84" t="s">
+      <c r="I118" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L118" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M118" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N118" s="85"/>
-      <c r="O118" s="85"/>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A119" s="83" t="s">
+      <c r="J118" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K118" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L118" s="83"/>
+      <c r="M118" s="83"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="87" t="s">
         <v>384</v>
       </c>
-      <c r="B119" s="83" t="s">
+      <c r="B119" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C119" s="83" t="s">
+      <c r="C119" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E119" s="89" t="s">
+      <c r="E119" s="92" t="s">
         <v>384</v>
       </c>
       <c r="F119" s="7">
         <v>602440000</v>
       </c>
-      <c r="G119" s="84" t="s">
+      <c r="G119" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H119" s="7">
         <v>0</v>
       </c>
-      <c r="I119" s="84"/>
-      <c r="J119" s="84">
-        <v>0</v>
-      </c>
-      <c r="K119" s="84" t="s">
+      <c r="I119" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L119" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M119" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N119" s="85"/>
-      <c r="O119" s="85"/>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A120" s="89" t="s">
+      <c r="J119" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K119" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L119" s="83"/>
+      <c r="M119" s="83"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="92" t="s">
         <v>385</v>
       </c>
-      <c r="B120" s="83" t="s">
+      <c r="B120" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C120" s="89" t="s">
+      <c r="C120" s="92" t="s">
         <v>386</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E120" s="89" t="s">
+      <c r="E120" s="92" t="s">
         <v>387</v>
       </c>
       <c r="F120" s="7">
         <v>1847633000</v>
       </c>
-      <c r="G120" s="84" t="s">
+      <c r="G120" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H120" s="7">
-        <v>305</v>
-      </c>
-      <c r="I120" s="84">
-        <v>305</v>
-      </c>
-      <c r="J120" s="84">
         <v>0</v>
       </c>
-      <c r="K120" s="84" t="s">
+      <c r="I120" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L120" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M120" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N120" s="85"/>
-      <c r="O120" s="85" t="s">
+      <c r="J120" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K120" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L120" s="83"/>
+      <c r="M120" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A121" s="89" t="s">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="92" t="s">
         <v>388</v>
       </c>
-      <c r="B121" s="83" t="s">
+      <c r="B121" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C121" s="89" t="s">
+      <c r="C121" s="92" t="s">
         <v>389</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E121" s="89" t="s">
+      <c r="E121" s="92" t="s">
         <v>390</v>
       </c>
       <c r="F121" s="7">
         <v>685000000</v>
       </c>
-      <c r="G121" s="84" t="s">
+      <c r="G121" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H121" s="7">
-        <v>156</v>
-      </c>
-      <c r="I121" s="84">
-        <v>156</v>
-      </c>
-      <c r="J121" s="84">
         <v>0</v>
       </c>
-      <c r="K121" s="84" t="s">
+      <c r="I121" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L121" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M121" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N121" s="85"/>
-      <c r="O121" s="85" t="s">
+      <c r="J121" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K121" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L121" s="83"/>
+      <c r="M121" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A122" s="83" t="s">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="87" t="s">
         <v>391</v>
       </c>
-      <c r="B122" s="83" t="s">
+      <c r="B122" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C122" s="89" t="s">
+      <c r="C122" s="92" t="s">
         <v>392</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E122" s="89" t="s">
+      <c r="E122" s="92" t="s">
         <v>391</v>
       </c>
       <c r="F122" s="7">
         <v>854545455</v>
       </c>
-      <c r="G122" s="84" t="s">
+      <c r="G122" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H122" s="7">
-        <v>130</v>
-      </c>
-      <c r="I122" s="84">
-        <v>130</v>
-      </c>
-      <c r="J122" s="84">
         <v>0</v>
       </c>
-      <c r="K122" s="84" t="s">
+      <c r="I122" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L122" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M122" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N122" s="85"/>
-      <c r="O122" s="85" t="s">
+      <c r="J122" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K122" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L122" s="83"/>
+      <c r="M122" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A123" s="89" t="s">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="92" t="s">
         <v>393</v>
       </c>
-      <c r="B123" s="83" t="s">
+      <c r="B123" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C123" s="89" t="s">
+      <c r="C123" s="92" t="s">
         <v>394</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="89" t="s">
+      <c r="E123" s="92" t="s">
         <v>395</v>
       </c>
       <c r="F123" s="7">
         <v>800000000</v>
       </c>
-      <c r="G123" s="84" t="s">
+      <c r="G123" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H123" s="7">
-        <v>159</v>
-      </c>
-      <c r="I123" s="84">
-        <v>159</v>
-      </c>
-      <c r="J123" s="84">
         <v>0</v>
       </c>
-      <c r="K123" s="84" t="s">
+      <c r="I123" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L123" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M123" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N123" s="85"/>
-      <c r="O123" s="85" t="s">
+      <c r="J123" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K123" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L123" s="83"/>
+      <c r="M123" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A124" s="89" t="s">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="92" t="s">
         <v>396</v>
       </c>
-      <c r="B124" s="83" t="s">
+      <c r="B124" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C124" s="89" t="s">
+      <c r="C124" s="92" t="s">
         <v>397</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E124" s="89" t="s">
+      <c r="E124" s="92" t="s">
         <v>398</v>
       </c>
       <c r="F124" s="7">
         <v>1374545455</v>
       </c>
-      <c r="G124" s="84" t="s">
+      <c r="G124" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H124" s="7">
-        <v>323</v>
-      </c>
-      <c r="I124" s="84">
-        <v>323</v>
-      </c>
-      <c r="J124" s="84">
         <v>0</v>
       </c>
-      <c r="K124" s="84" t="s">
+      <c r="I124" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L124" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M124" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N124" s="85"/>
-      <c r="O124" s="85" t="s">
+      <c r="J124" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K124" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L124" s="83"/>
+      <c r="M124" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A125" s="89" t="s">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="92" t="s">
         <v>399</v>
       </c>
-      <c r="B125" s="83" t="s">
+      <c r="B125" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C125" s="89" t="s">
+      <c r="C125" s="92" t="s">
         <v>308</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E125" s="89" t="s">
+      <c r="E125" s="92" t="s">
         <v>401</v>
       </c>
       <c r="F125" s="7">
         <v>214789091</v>
       </c>
-      <c r="G125" s="84" t="s">
+      <c r="G125" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H125" s="7">
-        <v>20</v>
-      </c>
-      <c r="I125" s="84">
-        <v>20</v>
-      </c>
-      <c r="J125" s="84">
         <v>0</v>
       </c>
-      <c r="K125" s="84" t="s">
+      <c r="I125" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L125" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M125" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N125" s="85"/>
-      <c r="O125" s="85" t="s">
+      <c r="J125" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K125" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L125" s="83"/>
+      <c r="M125" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A126" s="89" t="s">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="92" t="s">
         <v>402</v>
       </c>
-      <c r="B126" s="83" t="s">
+      <c r="B126" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C126" s="89" t="s">
+      <c r="C126" s="92" t="s">
         <v>403</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E126" s="89" t="s">
+      <c r="E126" s="92" t="s">
         <v>404</v>
       </c>
-      <c r="F126" s="84"/>
-      <c r="G126" s="84" t="s">
+      <c r="F126" s="88"/>
+      <c r="G126" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H126" s="7">
         <v>156</v>
       </c>
-      <c r="I126" s="84"/>
-      <c r="J126" s="84">
-        <v>156</v>
-      </c>
-      <c r="K126" s="84" t="s">
+      <c r="I126" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L126" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M126" s="84" t="s">
+      <c r="J126" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K126" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="N126" s="85"/>
-      <c r="O126" s="85" t="s">
+      <c r="L126" s="83"/>
+      <c r="M126" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A127" s="89" t="s">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="92" t="s">
         <v>405</v>
       </c>
-      <c r="B127" s="83" t="s">
+      <c r="B127" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C127" s="89" t="s">
+      <c r="C127" s="92" t="s">
         <v>406</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E127" s="89" t="s">
+      <c r="E127" s="92" t="s">
         <v>407</v>
       </c>
       <c r="F127" s="7">
         <v>6320909091</v>
       </c>
-      <c r="G127" s="84" t="s">
+      <c r="G127" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H127" s="7">
-        <v>1280</v>
-      </c>
-      <c r="I127" s="84">
-        <v>1280</v>
-      </c>
-      <c r="J127" s="84">
         <v>0</v>
       </c>
-      <c r="K127" s="84" t="s">
+      <c r="I127" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L127" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M127" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N127" s="85"/>
-      <c r="O127" s="85"/>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A128" s="84" t="s">
+      <c r="J127" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K127" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L127" s="83"/>
+      <c r="M127" s="83"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="88" t="s">
         <v>408</v>
       </c>
-      <c r="B128" s="83" t="s">
+      <c r="B128" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C128" s="84" t="s">
+      <c r="C128" s="88" t="s">
         <v>409</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E128" s="89" t="s">
+      <c r="E128" s="92" t="s">
         <v>410</v>
       </c>
-      <c r="F128" s="84">
+      <c r="F128" s="88">
         <v>401749000</v>
       </c>
-      <c r="G128" s="84" t="s">
+      <c r="G128" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H128" s="7">
-        <v>50</v>
-      </c>
-      <c r="I128" s="84">
-        <v>50</v>
-      </c>
-      <c r="J128" s="84">
         <v>0</v>
       </c>
-      <c r="K128" s="84" t="s">
+      <c r="I128" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L128" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M128" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N128" s="85"/>
-      <c r="O128" s="85" t="s">
+      <c r="J128" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K128" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L128" s="83"/>
+      <c r="M128" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A129" s="84" t="s">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" s="88" t="s">
         <v>411</v>
       </c>
-      <c r="B129" s="83" t="s">
+      <c r="B129" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C129" s="84" t="s">
+      <c r="C129" s="88" t="s">
         <v>412</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E129" s="89" t="s">
+      <c r="E129" s="92" t="s">
         <v>413</v>
       </c>
-      <c r="F129" s="84">
+      <c r="F129" s="88">
         <v>134556481</v>
       </c>
-      <c r="G129" s="84" t="s">
+      <c r="G129" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H129" s="7">
-        <v>25</v>
-      </c>
-      <c r="I129" s="84">
-        <v>25</v>
-      </c>
-      <c r="J129" s="84">
         <v>0</v>
       </c>
-      <c r="K129" s="84" t="s">
+      <c r="I129" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L129" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M129" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N129" s="85"/>
-      <c r="O129" s="85" t="s">
+      <c r="J129" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K129" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L129" s="83"/>
+      <c r="M129" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A130" s="89" t="s">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="92" t="s">
         <v>421</v>
       </c>
-      <c r="B130" s="83" t="s">
+      <c r="B130" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C130" s="89" t="s">
+      <c r="C130" s="92" t="s">
         <v>412</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E130" s="89" t="s">
+      <c r="E130" s="92" t="s">
         <v>414</v>
       </c>
       <c r="F130" s="7">
         <v>318666815</v>
       </c>
-      <c r="G130" s="84" t="s">
+      <c r="G130" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H130" s="7">
-        <v>51</v>
-      </c>
-      <c r="I130" s="84">
-        <v>51</v>
-      </c>
-      <c r="J130" s="84">
         <v>0</v>
       </c>
-      <c r="K130" s="84" t="s">
+      <c r="I130" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L130" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M130" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N130" s="85"/>
-      <c r="O130" s="85" t="s">
+      <c r="J130" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K130" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L130" s="83"/>
+      <c r="M130" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A131" s="84" t="s">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="88" t="s">
         <v>415</v>
       </c>
-      <c r="B131" s="83" t="s">
+      <c r="B131" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C131" s="84" t="s">
+      <c r="C131" s="88" t="s">
         <v>412</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E131" s="89" t="s">
+      <c r="E131" s="92" t="s">
         <v>416</v>
       </c>
-      <c r="F131" s="84">
+      <c r="F131" s="88">
         <v>380721000</v>
       </c>
-      <c r="G131" s="84" t="s">
+      <c r="G131" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H131" s="7">
-        <v>96</v>
-      </c>
-      <c r="I131" s="84">
-        <v>96</v>
-      </c>
-      <c r="J131" s="84">
         <v>0</v>
       </c>
-      <c r="K131" s="84" t="s">
+      <c r="I131" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L131" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M131" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N131" s="85"/>
-      <c r="O131" s="85" t="s">
+      <c r="J131" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K131" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L131" s="83"/>
+      <c r="M131" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A132" s="89" t="s">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" s="92" t="s">
         <v>417</v>
       </c>
-      <c r="B132" s="83" t="s">
+      <c r="B132" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C132" s="89" t="s">
+      <c r="C132" s="92" t="s">
         <v>412</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E132" s="89" t="s">
+      <c r="E132" s="92" t="s">
         <v>418</v>
       </c>
       <c r="F132" s="7">
         <v>234545454.5</v>
       </c>
-      <c r="G132" s="84" t="s">
+      <c r="G132" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H132" s="7">
-        <v>33</v>
-      </c>
-      <c r="I132" s="84">
-        <v>33</v>
-      </c>
-      <c r="J132" s="84">
         <v>0</v>
       </c>
-      <c r="K132" s="84" t="s">
+      <c r="I132" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L132" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M132" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N132" s="85"/>
-      <c r="O132" s="85" t="s">
+      <c r="J132" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K132" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L132" s="83"/>
+      <c r="M132" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A133" s="89" t="s">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" s="92" t="s">
         <v>419</v>
       </c>
-      <c r="B133" s="83" t="s">
+      <c r="B133" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C133" s="89" t="s">
+      <c r="C133" s="92" t="s">
         <v>412</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="89" t="s">
+      <c r="E133" s="92" t="s">
         <v>420</v>
       </c>
       <c r="F133" s="7">
         <v>313269865</v>
       </c>
-      <c r="G133" s="84" t="s">
+      <c r="G133" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H133" s="7">
         <v>46</v>
       </c>
-      <c r="I133" s="84"/>
-      <c r="J133" s="84">
-        <v>46</v>
-      </c>
-      <c r="K133" s="84"/>
-      <c r="L133" s="84" t="s">
+      <c r="I133" s="83"/>
+      <c r="J133" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="M133" s="84" t="s">
+      <c r="K133" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="N133" s="85"/>
-      <c r="O133" s="85" t="s">
+      <c r="L133" s="83"/>
+      <c r="M133" s="83" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A134" s="89" t="s">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" s="92" t="s">
         <v>422</v>
       </c>
-      <c r="B134" s="83" t="s">
+      <c r="B134" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C134" s="89" t="s">
+      <c r="C134" s="92" t="s">
         <v>308</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E134" s="89" t="s">
+      <c r="E134" s="92" t="s">
         <v>423</v>
       </c>
       <c r="F134" s="7">
         <v>970417742</v>
       </c>
-      <c r="G134" s="84" t="s">
+      <c r="G134" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H134" s="7">
-        <v>160</v>
-      </c>
-      <c r="I134" s="84">
-        <v>160</v>
-      </c>
-      <c r="J134" s="84">
         <v>0</v>
       </c>
-      <c r="K134" s="84" t="s">
+      <c r="I134" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L134" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M134" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N134" s="85"/>
-      <c r="O134" s="85"/>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A135" s="89" t="s">
+      <c r="J134" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K134" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L134" s="83"/>
+      <c r="M134" s="83"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="92" t="s">
         <v>424</v>
       </c>
-      <c r="B135" s="83" t="s">
+      <c r="B135" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C135" s="89" t="s">
+      <c r="C135" s="92" t="s">
         <v>412</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E135" s="89" t="s">
+      <c r="E135" s="92" t="s">
         <v>425</v>
       </c>
       <c r="F135" s="7">
         <v>694444444</v>
       </c>
-      <c r="G135" s="84" t="s">
+      <c r="G135" s="88" t="s">
         <v>11</v>
       </c>
       <c r="H135" s="7">
         <v>180</v>
       </c>
-      <c r="I135" s="84"/>
-      <c r="J135" s="84">
-        <v>180</v>
-      </c>
-      <c r="K135" s="84" t="s">
+      <c r="I135" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L135" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M135" s="84" t="s">
+      <c r="J135" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K135" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="N135" s="85"/>
-      <c r="O135" s="85" t="s">
+      <c r="L135" s="83"/>
+      <c r="M135" s="83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A136" s="89" t="s">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" s="92" t="s">
         <v>426</v>
       </c>
-      <c r="B136" s="83" t="s">
+      <c r="B136" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C136" s="89" t="s">
+      <c r="C136" s="92" t="s">
         <v>427</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E136" s="89" t="s">
+      <c r="E136" s="92" t="s">
         <v>50</v>
       </c>
       <c r="F136" s="82">
         <v>178334509</v>
       </c>
-      <c r="G136" s="84" t="s">
+      <c r="G136" s="88" t="s">
         <v>9</v>
       </c>
       <c r="H136" s="7">
-        <v>14</v>
-      </c>
-      <c r="I136" s="84">
-        <v>14</v>
-      </c>
-      <c r="J136" s="84">
         <v>0</v>
       </c>
-      <c r="K136" s="84" t="s">
+      <c r="I136" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="L136" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="M136" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="N136" s="85"/>
-      <c r="O136" s="85"/>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A137" s="85" t="s">
+      <c r="J136" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K136" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L136" s="83"/>
+      <c r="M136" s="83"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" s="94" t="s">
         <v>428</v>
       </c>
-      <c r="B137" s="85" t="s">
+      <c r="B137" s="94" t="s">
         <v>113</v>
       </c>
-      <c r="C137" s="85" t="s">
+      <c r="C137" s="94" t="s">
         <v>429</v>
       </c>
-      <c r="D137" s="85" t="s">
+      <c r="D137" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="E137" s="85" t="s">
+      <c r="E137" s="94" t="s">
         <v>430</v>
       </c>
-      <c r="F137" s="92">
+      <c r="F137" s="95">
         <v>206363636</v>
       </c>
-      <c r="G137" s="85" t="s">
+      <c r="G137" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="H137" s="85">
+      <c r="H137" s="84">
+        <v>0</v>
+      </c>
+      <c r="I137" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J137" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="K137" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L137" s="84"/>
+      <c r="M137" s="84"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" s="94" t="s">
+        <v>431</v>
+      </c>
+      <c r="B138" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C138" s="94" t="s">
+        <v>432</v>
+      </c>
+      <c r="D138" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="E138" s="94" t="s">
+        <v>433</v>
+      </c>
+      <c r="F138" s="95">
+        <v>2787523658</v>
+      </c>
+      <c r="G138" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H138" s="84">
+        <v>0</v>
+      </c>
+      <c r="I138" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J138" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="K138" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L138" s="84"/>
+      <c r="M138" s="84"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" s="94" t="s">
+        <v>434</v>
+      </c>
+      <c r="B139" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C139" s="94" t="s">
+        <v>435</v>
+      </c>
+      <c r="D139" s="94" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139" s="94" t="s">
+        <v>436</v>
+      </c>
+      <c r="F139" s="95">
+        <v>183500000</v>
+      </c>
+      <c r="G139" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H139" s="84">
+        <v>32</v>
+      </c>
+      <c r="I139" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J139" s="84"/>
+      <c r="K139" s="84"/>
+      <c r="L139" s="84"/>
+      <c r="M139" s="84"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="94" t="s">
+        <v>437</v>
+      </c>
+      <c r="B140" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C140" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="D140" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="E140" s="94" t="s">
+        <v>439</v>
+      </c>
+      <c r="F140" s="95">
+        <v>107018182</v>
+      </c>
+      <c r="G140" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="H140" s="84">
+        <v>0</v>
+      </c>
+      <c r="I140" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J140" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="K140" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L140" s="84"/>
+      <c r="M140" s="84" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" s="94" t="s">
+        <v>440</v>
+      </c>
+      <c r="B141" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="C141" s="94" t="s">
+        <v>77</v>
+      </c>
+      <c r="D141" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E141" s="94" t="s">
+        <v>77</v>
+      </c>
+      <c r="F141" s="95">
+        <v>131753127</v>
+      </c>
+      <c r="G141" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H141" s="84">
+        <v>0</v>
+      </c>
+      <c r="I141" s="84"/>
+      <c r="J141" s="84"/>
+      <c r="K141" s="84"/>
+      <c r="L141" s="84"/>
+      <c r="M141" s="84"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" s="94" t="s">
+        <v>441</v>
+      </c>
+      <c r="B142" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="C142" s="94" t="s">
+        <v>427</v>
+      </c>
+      <c r="D142" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="E142" s="94" t="s">
+        <v>442</v>
+      </c>
+      <c r="F142" s="95">
+        <v>2209199764</v>
+      </c>
+      <c r="G142" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="84"/>
+      <c r="I142" s="84" t="s">
+        <v>167</v>
+      </c>
+      <c r="J142" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="K142" s="84" t="s">
+        <v>79</v>
+      </c>
+      <c r="L142" s="84"/>
+      <c r="M142" s="84" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" s="94" t="s">
+        <v>443</v>
+      </c>
+      <c r="B143" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C143" s="94" t="s">
+        <v>444</v>
+      </c>
+      <c r="D143" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="I137" s="85">
+      <c r="E143" s="94" t="s">
+        <v>445</v>
+      </c>
+      <c r="F143" s="95">
+        <v>2292994051</v>
+      </c>
+      <c r="G143" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H143" s="84">
+        <v>0</v>
+      </c>
+      <c r="I143" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J143" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="K143" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L143" s="84"/>
+      <c r="M143" s="84" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" s="94" t="s">
+        <v>446</v>
+      </c>
+      <c r="B144" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="C144" s="94" t="s">
+        <v>447</v>
+      </c>
+      <c r="D144" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="E144" s="94" t="s">
+        <v>188</v>
+      </c>
+      <c r="F144" s="94">
+        <v>955130246</v>
+      </c>
+      <c r="G144" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H144" s="84">
+        <v>0</v>
+      </c>
+      <c r="I144" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J144" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="K144" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L144" s="84"/>
+      <c r="M144" s="84" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" s="94" t="s">
+        <v>448</v>
+      </c>
+      <c r="B145" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="C145" s="94" t="s">
+        <v>412</v>
+      </c>
+      <c r="D145" s="94" t="s">
+        <v>38</v>
+      </c>
+      <c r="E145" s="94" t="s">
+        <v>449</v>
+      </c>
+      <c r="F145" s="94">
+        <v>1728000000</v>
+      </c>
+      <c r="G145" s="94" t="s">
+        <v>1</v>
+      </c>
+      <c r="H145" s="84">
+        <v>0</v>
+      </c>
+      <c r="I145" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J145" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="K145" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L145" s="84"/>
+      <c r="M145" s="84" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" s="94" t="s">
+        <v>450</v>
+      </c>
+      <c r="B146" s="94"/>
+      <c r="C146" s="94" t="s">
+        <v>400</v>
+      </c>
+      <c r="D146" s="94" t="s">
+        <v>10</v>
+      </c>
+      <c r="E146" s="94"/>
+      <c r="F146" s="95">
+        <v>174715000</v>
+      </c>
+      <c r="G146" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H146" s="84">
+        <v>20</v>
+      </c>
+      <c r="I146" s="84"/>
+      <c r="J146" s="84"/>
+      <c r="K146" s="84"/>
+      <c r="L146" s="84"/>
+      <c r="M146" s="84"/>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" s="94" t="s">
+        <v>451</v>
+      </c>
+      <c r="B147" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="C147" s="94" t="s">
+        <v>452</v>
+      </c>
+      <c r="D147" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E147" s="94"/>
+      <c r="F147" s="95">
+        <v>128812000</v>
+      </c>
+      <c r="G147" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H147" s="84">
+        <v>0</v>
+      </c>
+      <c r="I147" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J147" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="K147" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L147" s="84"/>
+      <c r="M147" s="84"/>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" s="94" t="s">
+        <v>453</v>
+      </c>
+      <c r="B148" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="C148" s="94" t="s">
+        <v>454</v>
+      </c>
+      <c r="D148" s="94" t="s">
+        <v>41</v>
+      </c>
+      <c r="E148" s="94"/>
+      <c r="F148" s="95">
+        <v>2106000000</v>
+      </c>
+      <c r="G148" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H148" s="84">
+        <v>720</v>
+      </c>
+      <c r="I148" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J148" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="K148" s="84" t="s">
+        <v>79</v>
+      </c>
+      <c r="L148" s="84"/>
+      <c r="M148" s="84"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" s="94" t="s">
+        <v>455</v>
+      </c>
+      <c r="B149" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C149" s="94" t="s">
+        <v>456</v>
+      </c>
+      <c r="D149" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="E149" s="94" t="s">
+        <v>439</v>
+      </c>
+      <c r="F149" s="95">
+        <v>170640000</v>
+      </c>
+      <c r="G149" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="H149" s="84">
+        <v>0</v>
+      </c>
+      <c r="I149" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="J149" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="K149" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L149" s="84"/>
+      <c r="M149" s="84" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" s="94" t="s">
+        <v>457</v>
+      </c>
+      <c r="B150" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C150" s="94" t="s">
+        <v>458</v>
+      </c>
+      <c r="D150" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="J137" s="85">
-        <v>0</v>
-      </c>
-      <c r="K137" s="85" t="s">
+      <c r="E150" s="94" t="s">
+        <v>459</v>
+      </c>
+      <c r="F150" s="94">
+        <v>4875624485</v>
+      </c>
+      <c r="G150" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H150" s="84">
+        <v>1008</v>
+      </c>
+      <c r="I150" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="L137" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="M137" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="N137" s="85"/>
-      <c r="O137" s="85"/>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A138" s="85" t="s">
-        <v>431</v>
-      </c>
-      <c r="B138" s="85" t="s">
-        <v>48</v>
-      </c>
-      <c r="C138" s="85" t="s">
-        <v>432</v>
-      </c>
-      <c r="D138" s="85" t="s">
-        <v>24</v>
-      </c>
-      <c r="E138" s="85" t="s">
-        <v>433</v>
-      </c>
-      <c r="F138" s="92">
-        <v>2787523658</v>
-      </c>
-      <c r="G138" s="85" t="s">
+      <c r="J150" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="K150" s="84" t="s">
+        <v>79</v>
+      </c>
+      <c r="L150" s="84"/>
+      <c r="M150" s="84" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" s="94" t="s">
+        <v>460</v>
+      </c>
+      <c r="B151" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="C151" s="94" t="s">
+        <v>461</v>
+      </c>
+      <c r="D151" s="94" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151" s="94" t="s">
+        <v>462</v>
+      </c>
+      <c r="F151" s="95">
+        <v>125710000</v>
+      </c>
+      <c r="G151" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="H138" s="85">
-        <v>576</v>
-      </c>
-      <c r="I138" s="85">
-        <v>576</v>
-      </c>
-      <c r="J138" s="85">
-        <v>0</v>
-      </c>
-      <c r="K138" s="85" t="s">
+      <c r="H151" s="84">
+        <v>12</v>
+      </c>
+      <c r="I151" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="L138" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="M138" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="N138" s="85"/>
-      <c r="O138" s="85"/>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A139" s="85" t="s">
-        <v>434</v>
-      </c>
-      <c r="B139" s="85" t="s">
-        <v>48</v>
-      </c>
-      <c r="C139" s="85" t="s">
-        <v>435</v>
-      </c>
-      <c r="D139" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="E139" s="85" t="s">
-        <v>436</v>
-      </c>
-      <c r="F139" s="92">
-        <v>183500000</v>
-      </c>
-      <c r="G139" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H139" s="85">
-        <v>32</v>
-      </c>
-      <c r="I139" s="85"/>
-      <c r="J139" s="85">
-        <v>32</v>
-      </c>
-      <c r="K139" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="L139" s="85"/>
-      <c r="M139" s="85"/>
-      <c r="N139" s="85"/>
-      <c r="O139" s="85"/>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A140" s="85" t="s">
-        <v>437</v>
-      </c>
-      <c r="B140" s="85" t="s">
-        <v>48</v>
-      </c>
-      <c r="C140" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D140" s="85" t="s">
-        <v>25</v>
-      </c>
-      <c r="E140" s="85" t="s">
-        <v>439</v>
-      </c>
-      <c r="F140" s="92">
-        <v>107018182</v>
-      </c>
-      <c r="G140" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="H140" s="85">
-        <v>6</v>
-      </c>
-      <c r="I140" s="85">
-        <v>6</v>
-      </c>
-      <c r="J140" s="85">
-        <v>0</v>
-      </c>
-      <c r="K140" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="L140" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="M140" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="N140" s="85"/>
-      <c r="O140" s="85" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A141" s="85" t="s">
-        <v>440</v>
-      </c>
-      <c r="B141" s="85" t="s">
-        <v>113</v>
-      </c>
-      <c r="C141" s="85" t="s">
-        <v>77</v>
-      </c>
-      <c r="D141" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="E141" s="85" t="s">
-        <v>77</v>
-      </c>
-      <c r="F141" s="92">
-        <v>131753127</v>
-      </c>
-      <c r="G141" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H141" s="85"/>
-      <c r="I141" s="85"/>
-      <c r="J141" s="85">
-        <v>0</v>
-      </c>
-      <c r="K141" s="85"/>
-      <c r="L141" s="85"/>
-      <c r="M141" s="85"/>
-      <c r="N141" s="85"/>
-      <c r="O141" s="85"/>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A142" s="85" t="s">
-        <v>441</v>
-      </c>
-      <c r="B142" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="C142" s="85" t="s">
-        <v>427</v>
-      </c>
-      <c r="D142" s="85" t="s">
-        <v>20</v>
-      </c>
-      <c r="E142" s="85" t="s">
-        <v>442</v>
-      </c>
-      <c r="F142" s="92">
-        <v>2209199764</v>
-      </c>
-      <c r="G142" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H142" s="85">
-        <v>320</v>
-      </c>
-      <c r="I142" s="85"/>
-      <c r="J142" s="85"/>
-      <c r="K142" s="85" t="s">
-        <v>167</v>
-      </c>
-      <c r="L142" s="85" t="s">
-        <v>78</v>
-      </c>
-      <c r="M142" s="85" t="s">
-        <v>79</v>
-      </c>
-      <c r="N142" s="85"/>
-      <c r="O142" s="85" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A143" s="85" t="s">
-        <v>443</v>
-      </c>
-      <c r="B143" s="85" t="s">
-        <v>48</v>
-      </c>
-      <c r="C143" s="85" t="s">
-        <v>444</v>
-      </c>
-      <c r="D143" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="E143" s="85" t="s">
-        <v>445</v>
-      </c>
-      <c r="F143" s="92">
-        <v>2292994051</v>
-      </c>
-      <c r="G143" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H143" s="85">
-        <v>480</v>
-      </c>
-      <c r="I143" s="85">
-        <v>480</v>
-      </c>
-      <c r="J143" s="85">
-        <v>0</v>
-      </c>
-      <c r="K143" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="L143" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="M143" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="N143" s="85"/>
-      <c r="O143" s="85" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A144" s="85" t="s">
-        <v>446</v>
-      </c>
-      <c r="B144" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="C144" s="85" t="s">
-        <v>447</v>
-      </c>
-      <c r="D144" s="85" t="s">
-        <v>40</v>
-      </c>
-      <c r="E144" s="85" t="s">
-        <v>188</v>
-      </c>
-      <c r="F144" s="85">
-        <v>955130246</v>
-      </c>
-      <c r="G144" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H144" s="85">
-        <v>210</v>
-      </c>
-      <c r="I144" s="85">
-        <v>210</v>
-      </c>
-      <c r="J144" s="85">
-        <v>0</v>
-      </c>
-      <c r="K144" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="L144" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="M144" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="N144" s="85"/>
-      <c r="O144" s="85" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A145" s="85" t="s">
-        <v>448</v>
-      </c>
-      <c r="B145" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="C145" s="85" t="s">
-        <v>412</v>
-      </c>
-      <c r="D145" s="85" t="s">
-        <v>38</v>
-      </c>
-      <c r="E145" s="85" t="s">
-        <v>449</v>
-      </c>
-      <c r="F145" s="85">
-        <v>1728000000</v>
-      </c>
-      <c r="G145" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="H145" s="85">
-        <v>151</v>
-      </c>
-      <c r="I145" s="85">
-        <v>151</v>
-      </c>
-      <c r="J145" s="85">
-        <v>0</v>
-      </c>
-      <c r="K145" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="L145" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="M145" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="N145" s="85"/>
-      <c r="O145" s="85" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A146" s="85" t="s">
-        <v>450</v>
-      </c>
-      <c r="B146" s="85"/>
-      <c r="C146" s="85" t="s">
-        <v>400</v>
-      </c>
-      <c r="D146" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="E146" s="85"/>
-      <c r="F146" s="92">
-        <v>174715000</v>
-      </c>
-      <c r="G146" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H146" s="85">
-        <v>20</v>
-      </c>
-      <c r="I146" s="85"/>
-      <c r="J146" s="85">
-        <v>20</v>
-      </c>
-      <c r="K146" s="85"/>
-      <c r="L146" s="85"/>
-      <c r="M146" s="85"/>
-      <c r="N146" s="85"/>
-      <c r="O146" s="85"/>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A147" s="85" t="s">
-        <v>451</v>
-      </c>
-      <c r="B147" s="85" t="s">
-        <v>113</v>
-      </c>
-      <c r="C147" s="85" t="s">
-        <v>452</v>
-      </c>
-      <c r="D147" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="E147" s="85"/>
-      <c r="F147" s="92">
-        <v>128812000</v>
-      </c>
-      <c r="G147" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H147" s="85">
-        <v>30</v>
-      </c>
-      <c r="I147" s="85">
-        <v>30</v>
-      </c>
-      <c r="J147" s="85">
-        <v>0</v>
-      </c>
-      <c r="K147" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="L147" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="M147" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="N147" s="85"/>
-      <c r="O147" s="85"/>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A148" s="85" t="s">
-        <v>453</v>
-      </c>
-      <c r="B148" s="85" t="s">
-        <v>113</v>
-      </c>
-      <c r="C148" s="85" t="s">
-        <v>454</v>
-      </c>
-      <c r="D148" s="85" t="s">
-        <v>41</v>
-      </c>
-      <c r="E148" s="85"/>
-      <c r="F148" s="92">
-        <v>2106000000</v>
-      </c>
-      <c r="G148" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H148" s="85">
-        <v>720</v>
-      </c>
-      <c r="I148" s="85"/>
-      <c r="J148" s="85">
-        <v>720</v>
-      </c>
-      <c r="K148" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="L148" s="85" t="s">
-        <v>78</v>
-      </c>
-      <c r="M148" s="85" t="s">
-        <v>79</v>
-      </c>
-      <c r="N148" s="85"/>
-      <c r="O148" s="85"/>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A149" s="85" t="s">
-        <v>455</v>
-      </c>
-      <c r="B149" s="85" t="s">
-        <v>48</v>
-      </c>
-      <c r="C149" s="85" t="s">
-        <v>456</v>
-      </c>
-      <c r="D149" s="85" t="s">
-        <v>25</v>
-      </c>
-      <c r="E149" s="85" t="s">
-        <v>439</v>
-      </c>
-      <c r="F149" s="92">
-        <v>170640000</v>
-      </c>
-      <c r="G149" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="H149" s="85">
-        <v>10</v>
-      </c>
-      <c r="I149" s="85">
-        <v>10</v>
-      </c>
-      <c r="J149" s="85">
-        <v>0</v>
-      </c>
-      <c r="K149" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="L149" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="M149" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="N149" s="85"/>
-      <c r="O149" s="85" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A150" s="85" t="s">
-        <v>457</v>
-      </c>
-      <c r="B150" s="85" t="s">
-        <v>48</v>
-      </c>
-      <c r="C150" s="85" t="s">
-        <v>458</v>
-      </c>
-      <c r="D150" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="E150" s="85" t="s">
-        <v>459</v>
-      </c>
-      <c r="F150" s="85">
-        <v>4875624485</v>
-      </c>
-      <c r="G150" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H150" s="85">
-        <v>1008</v>
-      </c>
-      <c r="I150" s="85"/>
-      <c r="J150" s="85">
-        <v>1008</v>
-      </c>
-      <c r="K150" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="L150" s="85" t="s">
-        <v>78</v>
-      </c>
-      <c r="M150" s="85" t="s">
-        <v>79</v>
-      </c>
-      <c r="N150" s="85"/>
-      <c r="O150" s="85" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A151" s="85" t="s">
-        <v>460</v>
-      </c>
-      <c r="B151" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="C151" s="85" t="s">
-        <v>461</v>
-      </c>
-      <c r="D151" s="85" t="s">
-        <v>18</v>
-      </c>
-      <c r="E151" s="85" t="s">
-        <v>462</v>
-      </c>
-      <c r="F151" s="92">
-        <v>125710000</v>
-      </c>
-      <c r="G151" s="85"/>
-      <c r="H151" s="85"/>
-      <c r="I151" s="85"/>
-      <c r="J151" s="85">
-        <v>0</v>
-      </c>
-      <c r="K151" s="85"/>
-      <c r="L151" s="85"/>
-      <c r="M151" s="85"/>
-      <c r="N151" s="85"/>
-      <c r="O151" s="85"/>
+      <c r="J151" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="K151" s="84"/>
+      <c r="L151" s="84"/>
+      <c r="M151" s="84"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M1" xr:uid="{1F457DF4-8092-4544-B88B-9AF42554C254}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/ton_chuanhap.xlsx
+++ b/data/ton_chuanhap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_Tonkho\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A568A878-831E-4F80-A5C5-FD7845F049FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9896B7E5-95AF-4791-84C4-7CEA65B5E454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1765,7 +1765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1985,15 +1985,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2461,8 +2458,8 @@
       <c r="E2" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88" t="s">
+      <c r="F2" s="83"/>
+      <c r="G2" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="7">
@@ -2494,8 +2491,8 @@
       <c r="E3" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88" t="s">
+      <c r="F3" s="83"/>
+      <c r="G3" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H3" s="7">
@@ -2512,7 +2509,7 @@
       <c r="M3" s="83"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="88" t="s">
         <v>157</v>
       </c>
       <c r="B4" s="87" t="s">
@@ -2524,11 +2521,11 @@
       <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="89" t="s">
+      <c r="E4" s="88" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88" t="s">
+      <c r="F4" s="83"/>
+      <c r="G4" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="7">
@@ -2564,8 +2561,8 @@
       <c r="E5" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88" t="s">
+      <c r="F5" s="83"/>
+      <c r="G5" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H5" s="7">
@@ -2599,8 +2596,8 @@
       <c r="E6" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88" t="s">
+      <c r="F6" s="83"/>
+      <c r="G6" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H6" s="7">
@@ -2634,8 +2631,8 @@
       <c r="E7" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88" t="s">
+      <c r="F7" s="83"/>
+      <c r="G7" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H7" s="7">
@@ -2673,8 +2670,8 @@
       <c r="E8" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88" t="s">
+      <c r="F8" s="83"/>
+      <c r="G8" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H8" s="7">
@@ -2710,8 +2707,8 @@
       <c r="E9" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="88"/>
-      <c r="G9" s="88" t="s">
+      <c r="F9" s="83"/>
+      <c r="G9" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H9" s="7">
@@ -2745,8 +2742,8 @@
       <c r="E10" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88" t="s">
+      <c r="F10" s="83"/>
+      <c r="G10" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H10" s="7">
@@ -2780,8 +2777,8 @@
       <c r="E11" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88" t="s">
+      <c r="F11" s="83"/>
+      <c r="G11" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H11" s="7">
@@ -2815,8 +2812,8 @@
       <c r="E12" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88" t="s">
+      <c r="F12" s="83"/>
+      <c r="G12" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H12" s="7">
@@ -2849,11 +2846,11 @@
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="90" t="s">
+      <c r="E13" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88" t="s">
+      <c r="F13" s="83"/>
+      <c r="G13" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="7">
@@ -2889,8 +2886,8 @@
       <c r="E14" s="87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F14" s="88"/>
-      <c r="G14" s="88" t="s">
+      <c r="F14" s="83"/>
+      <c r="G14" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H14" s="7">
@@ -2922,8 +2919,8 @@
       <c r="E15" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88" t="s">
+      <c r="F15" s="83"/>
+      <c r="G15" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H15" s="7">
@@ -2955,8 +2952,8 @@
       <c r="E16" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="88"/>
-      <c r="G16" s="88" t="s">
+      <c r="F16" s="83"/>
+      <c r="G16" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="7">
@@ -2973,7 +2970,7 @@
       <c r="M16" s="83"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="88" t="s">
         <v>100</v>
       </c>
       <c r="B17" s="87" t="s">
@@ -2985,11 +2982,11 @@
       <c r="D17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="89" t="s">
+      <c r="E17" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="88"/>
-      <c r="G17" s="88" t="s">
+      <c r="F17" s="83"/>
+      <c r="G17" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H17" s="7">
@@ -3021,8 +3018,8 @@
       <c r="E18" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88" t="s">
+      <c r="F18" s="83"/>
+      <c r="G18" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H18" s="7">
@@ -3056,8 +3053,8 @@
       <c r="E19" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88" t="s">
+      <c r="F19" s="83"/>
+      <c r="G19" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H19" s="7">
@@ -3093,8 +3090,8 @@
       <c r="E20" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88" t="s">
+      <c r="F20" s="83"/>
+      <c r="G20" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H20" s="7">
@@ -3126,8 +3123,8 @@
       <c r="E21" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="88"/>
-      <c r="G21" s="88" t="s">
+      <c r="F21" s="83"/>
+      <c r="G21" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H21" s="7">
@@ -3163,8 +3160,8 @@
       <c r="E22" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="F22" s="88"/>
-      <c r="G22" s="88" t="s">
+      <c r="F22" s="83"/>
+      <c r="G22" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H22" s="7">
@@ -3202,8 +3199,8 @@
       <c r="E23" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="F23" s="88"/>
-      <c r="G23" s="88" t="s">
+      <c r="F23" s="83"/>
+      <c r="G23" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H23" s="7">
@@ -3230,15 +3227,15 @@
       <c r="B24" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="88"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88" t="s">
+      <c r="F24" s="83"/>
+      <c r="G24" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H24" s="7">
@@ -3276,8 +3273,8 @@
       <c r="E25" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="88"/>
-      <c r="G25" s="88" t="s">
+      <c r="F25" s="83"/>
+      <c r="G25" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H25" s="7">
@@ -3300,7 +3297,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="88" t="s">
         <v>127</v>
       </c>
       <c r="B26" s="87" t="s">
@@ -3312,11 +3309,11 @@
       <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="89" t="s">
+      <c r="E26" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="F26" s="88"/>
-      <c r="G26" s="88" t="s">
+      <c r="F26" s="83"/>
+      <c r="G26" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H26" s="7">
@@ -3354,8 +3351,8 @@
       <c r="E27" s="87" t="s">
         <v>133</v>
       </c>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88" t="s">
+      <c r="F27" s="83"/>
+      <c r="G27" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H27" s="7">
@@ -3391,8 +3388,8 @@
       <c r="E28" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="88"/>
-      <c r="G28" s="88" t="s">
+      <c r="F28" s="83"/>
+      <c r="G28" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H28" s="7">
@@ -3428,8 +3425,8 @@
       <c r="E29" s="87" t="s">
         <v>139</v>
       </c>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88" t="s">
+      <c r="F29" s="83"/>
+      <c r="G29" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H29" s="7">
@@ -3465,8 +3462,8 @@
       <c r="E30" s="87" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88" t="s">
+      <c r="F30" s="83"/>
+      <c r="G30" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H30" s="7">
@@ -3504,8 +3501,8 @@
       <c r="E31" s="87" t="s">
         <v>147</v>
       </c>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88" t="s">
+      <c r="F31" s="83"/>
+      <c r="G31" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H31" s="7">
@@ -3541,8 +3538,8 @@
       <c r="E32" s="87" t="s">
         <v>150</v>
       </c>
-      <c r="F32" s="88"/>
-      <c r="G32" s="88" t="s">
+      <c r="F32" s="83"/>
+      <c r="G32" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="7">
@@ -3578,8 +3575,8 @@
       <c r="E33" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88" t="s">
+      <c r="F33" s="83"/>
+      <c r="G33" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H33" s="7">
@@ -3602,7 +3599,7 @@
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="89" t="s">
+      <c r="A34" s="88" t="s">
         <v>154</v>
       </c>
       <c r="B34" s="87" t="s">
@@ -3614,11 +3611,11 @@
       <c r="D34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="89" t="s">
+      <c r="E34" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88" t="s">
+      <c r="F34" s="83"/>
+      <c r="G34" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H34" s="7">
@@ -3639,7 +3636,7 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="89" t="s">
+      <c r="A35" s="88" t="s">
         <v>160</v>
       </c>
       <c r="B35" s="87" t="s">
@@ -3651,11 +3648,11 @@
       <c r="D35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="89" t="s">
+      <c r="E35" s="88" t="s">
         <v>162</v>
       </c>
-      <c r="F35" s="88"/>
-      <c r="G35" s="88" t="s">
+      <c r="F35" s="83"/>
+      <c r="G35" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H35" s="7">
@@ -3691,8 +3688,8 @@
       <c r="E36" s="87" t="s">
         <v>156</v>
       </c>
-      <c r="F36" s="88"/>
-      <c r="G36" s="88" t="s">
+      <c r="F36" s="83"/>
+      <c r="G36" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H36" s="7">
@@ -3728,8 +3725,8 @@
       <c r="E37" s="87" t="s">
         <v>166</v>
       </c>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88" t="s">
+      <c r="F37" s="83"/>
+      <c r="G37" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H37" s="7">
@@ -3765,8 +3762,8 @@
       <c r="E38" s="87" t="s">
         <v>169</v>
       </c>
-      <c r="F38" s="88"/>
-      <c r="G38" s="88" t="s">
+      <c r="F38" s="83"/>
+      <c r="G38" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H38" s="7">
@@ -3804,8 +3801,8 @@
       <c r="E39" s="87" t="s">
         <v>172</v>
       </c>
-      <c r="F39" s="88"/>
-      <c r="G39" s="88" t="s">
+      <c r="F39" s="83"/>
+      <c r="G39" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H39" s="7">
@@ -3843,8 +3840,8 @@
       <c r="E40" s="87" t="s">
         <v>175</v>
       </c>
-      <c r="F40" s="88"/>
-      <c r="G40" s="88" t="s">
+      <c r="F40" s="83"/>
+      <c r="G40" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H40" s="7">
@@ -3880,8 +3877,8 @@
       <c r="E41" s="87">
         <v>0</v>
       </c>
-      <c r="F41" s="88"/>
-      <c r="G41" s="88" t="s">
+      <c r="F41" s="83"/>
+      <c r="G41" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H41" s="7">
@@ -3917,8 +3914,8 @@
       <c r="E42" s="87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F42" s="88"/>
-      <c r="G42" s="88" t="s">
+      <c r="F42" s="83"/>
+      <c r="G42" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H42" s="7">
@@ -3956,8 +3953,8 @@
       <c r="E43" s="87" t="s">
         <v>182</v>
       </c>
-      <c r="F43" s="88"/>
-      <c r="G43" s="88" t="s">
+      <c r="F43" s="83"/>
+      <c r="G43" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H43" s="7">
@@ -3995,8 +3992,8 @@
       <c r="E44" s="87" t="s">
         <v>185</v>
       </c>
-      <c r="F44" s="88"/>
-      <c r="G44" s="88" t="s">
+      <c r="F44" s="83"/>
+      <c r="G44" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H44" s="7">
@@ -4032,8 +4029,8 @@
       <c r="E45" s="87" t="s">
         <v>188</v>
       </c>
-      <c r="F45" s="88"/>
-      <c r="G45" s="88" t="s">
+      <c r="F45" s="83"/>
+      <c r="G45" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H45" s="7">
@@ -4071,8 +4068,8 @@
       <c r="E46" s="87" t="s">
         <v>191</v>
       </c>
-      <c r="F46" s="88"/>
-      <c r="G46" s="88" t="s">
+      <c r="F46" s="83"/>
+      <c r="G46" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H46" s="7">
@@ -4089,7 +4086,7 @@
       <c r="M46" s="83"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="89" t="s">
+      <c r="A47" s="88" t="s">
         <v>192</v>
       </c>
       <c r="B47" s="87" t="s">
@@ -4101,11 +4098,11 @@
       <c r="D47" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="89" t="s">
+      <c r="E47" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="F47" s="88"/>
-      <c r="G47" s="88" t="s">
+      <c r="F47" s="83"/>
+      <c r="G47" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H47" s="7">
@@ -4130,15 +4127,15 @@
       <c r="B48" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="88"/>
+      <c r="C48" s="83"/>
       <c r="D48" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E48" s="87" t="s">
         <v>196</v>
       </c>
-      <c r="F48" s="88"/>
-      <c r="G48" s="88" t="s">
+      <c r="F48" s="83"/>
+      <c r="G48" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H48" s="7">
@@ -4172,8 +4169,8 @@
       <c r="E49" s="87" t="s">
         <v>199</v>
       </c>
-      <c r="F49" s="88"/>
-      <c r="G49" s="88" t="s">
+      <c r="F49" s="83"/>
+      <c r="G49" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H49" s="7">
@@ -4207,8 +4204,8 @@
       <c r="E50" s="87" t="s">
         <v>202</v>
       </c>
-      <c r="F50" s="88"/>
-      <c r="G50" s="88" t="s">
+      <c r="F50" s="83"/>
+      <c r="G50" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H50" s="7">
@@ -4244,8 +4241,8 @@
       <c r="E51" s="87" t="s">
         <v>205</v>
       </c>
-      <c r="F51" s="88"/>
-      <c r="G51" s="88" t="s">
+      <c r="F51" s="83"/>
+      <c r="G51" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H51" s="7">
@@ -4281,8 +4278,8 @@
       <c r="E52" s="87" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="88"/>
-      <c r="G52" s="88" t="s">
+      <c r="F52" s="83"/>
+      <c r="G52" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H52" s="7">
@@ -4318,8 +4315,8 @@
       <c r="E53" s="87" t="s">
         <v>211</v>
       </c>
-      <c r="F53" s="88"/>
-      <c r="G53" s="88" t="s">
+      <c r="F53" s="83"/>
+      <c r="G53" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H53" s="7">
@@ -4344,15 +4341,15 @@
       <c r="B54" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="88"/>
+      <c r="C54" s="83"/>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="87" t="s">
         <v>213</v>
       </c>
-      <c r="F54" s="88"/>
-      <c r="G54" s="88" t="s">
+      <c r="F54" s="83"/>
+      <c r="G54" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H54" s="7">
@@ -4386,8 +4383,8 @@
       <c r="E55" s="87" t="s">
         <v>216</v>
       </c>
-      <c r="F55" s="88"/>
-      <c r="G55" s="88" t="s">
+      <c r="F55" s="83"/>
+      <c r="G55" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H55" s="7">
@@ -4410,15 +4407,15 @@
       <c r="B56" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="88"/>
+      <c r="C56" s="83"/>
       <c r="D56" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E56" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="F56" s="88"/>
-      <c r="G56" s="88" t="s">
+      <c r="F56" s="83"/>
+      <c r="G56" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H56" s="7">
@@ -4450,8 +4447,8 @@
       <c r="E57" s="87" t="s">
         <v>221</v>
       </c>
-      <c r="F57" s="88"/>
-      <c r="G57" s="88" t="s">
+      <c r="F57" s="83"/>
+      <c r="G57" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H57" s="7">
@@ -4485,8 +4482,8 @@
       <c r="E58" s="87" t="s">
         <v>223</v>
       </c>
-      <c r="F58" s="88"/>
-      <c r="G58" s="88" t="s">
+      <c r="F58" s="83"/>
+      <c r="G58" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H58" s="7">
@@ -4505,7 +4502,7 @@
       <c r="M58" s="83"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="91" t="s">
+      <c r="A59" s="90" t="s">
         <v>224</v>
       </c>
       <c r="B59" s="87" t="s">
@@ -4520,8 +4517,8 @@
       <c r="E59" s="87" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="88"/>
-      <c r="G59" s="88" t="s">
+      <c r="F59" s="83"/>
+      <c r="G59" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H59" s="7">
@@ -4540,7 +4537,7 @@
       <c r="M59" s="83"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="91" t="s">
+      <c r="A60" s="90" t="s">
         <v>228</v>
       </c>
       <c r="B60" s="87" t="s">
@@ -4555,8 +4552,8 @@
       <c r="E60" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="F60" s="88"/>
-      <c r="G60" s="88" t="s">
+      <c r="F60" s="83"/>
+      <c r="G60" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H60" s="7">
@@ -4590,8 +4587,8 @@
       <c r="E61" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="F61" s="88"/>
-      <c r="G61" s="88" t="s">
+      <c r="F61" s="83"/>
+      <c r="G61" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H61" s="7">
@@ -4625,8 +4622,8 @@
       <c r="E62" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88" t="s">
+      <c r="F62" s="83"/>
+      <c r="G62" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H62" s="7">
@@ -4662,8 +4659,8 @@
       <c r="E63" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="F63" s="88"/>
-      <c r="G63" s="88" t="s">
+      <c r="F63" s="83"/>
+      <c r="G63" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H63" s="7">
@@ -4686,7 +4683,7 @@
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="89" t="s">
+      <c r="A64" s="88" t="s">
         <v>236</v>
       </c>
       <c r="B64" s="87" t="s">
@@ -4698,11 +4695,11 @@
       <c r="D64" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="89" t="s">
+      <c r="E64" s="88" t="s">
         <v>238</v>
       </c>
-      <c r="F64" s="88"/>
-      <c r="G64" s="88" t="s">
+      <c r="F64" s="83"/>
+      <c r="G64" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H64" s="7">
@@ -4740,8 +4737,8 @@
       <c r="E65" s="87" t="s">
         <v>242</v>
       </c>
-      <c r="F65" s="88"/>
-      <c r="G65" s="88" t="s">
+      <c r="F65" s="83"/>
+      <c r="G65" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H65" s="7">
@@ -4777,8 +4774,8 @@
       <c r="E66" s="87" t="s">
         <v>245</v>
       </c>
-      <c r="F66" s="88"/>
-      <c r="G66" s="88" t="s">
+      <c r="F66" s="83"/>
+      <c r="G66" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H66" s="7">
@@ -4814,8 +4811,8 @@
       <c r="E67" s="87" t="s">
         <v>248</v>
       </c>
-      <c r="F67" s="88"/>
-      <c r="G67" s="88" t="s">
+      <c r="F67" s="83"/>
+      <c r="G67" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H67" s="7">
@@ -4853,8 +4850,8 @@
       <c r="E68" s="87" t="s">
         <v>251</v>
       </c>
-      <c r="F68" s="88"/>
-      <c r="G68" s="88" t="s">
+      <c r="F68" s="83"/>
+      <c r="G68" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H68" s="7">
@@ -4875,7 +4872,7 @@
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="89" t="s">
+      <c r="A69" s="88" t="s">
         <v>252</v>
       </c>
       <c r="B69" s="87" t="s">
@@ -4887,11 +4884,11 @@
       <c r="D69" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="89" t="s">
+      <c r="E69" s="88" t="s">
         <v>248</v>
       </c>
-      <c r="F69" s="88"/>
-      <c r="G69" s="88" t="s">
+      <c r="F69" s="83"/>
+      <c r="G69" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H69" s="7">
@@ -4927,8 +4924,8 @@
       <c r="E70" s="87" t="s">
         <v>256</v>
       </c>
-      <c r="F70" s="88"/>
-      <c r="G70" s="88" t="s">
+      <c r="F70" s="83"/>
+      <c r="G70" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H70" s="7">
@@ -4964,8 +4961,8 @@
       <c r="E71" s="87" t="s">
         <v>259</v>
       </c>
-      <c r="F71" s="88"/>
-      <c r="G71" s="88" t="s">
+      <c r="F71" s="83"/>
+      <c r="G71" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H71" s="7">
@@ -5001,8 +4998,8 @@
       <c r="E72" s="87" t="s">
         <v>262</v>
       </c>
-      <c r="F72" s="88"/>
-      <c r="G72" s="88" t="s">
+      <c r="F72" s="83"/>
+      <c r="G72" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H72" s="7">
@@ -5038,8 +5035,8 @@
       <c r="E73" s="87" t="s">
         <v>266</v>
       </c>
-      <c r="F73" s="88"/>
-      <c r="G73" s="88" t="s">
+      <c r="F73" s="83"/>
+      <c r="G73" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H73" s="7">
@@ -5077,8 +5074,8 @@
       <c r="E74" s="87" t="s">
         <v>269</v>
       </c>
-      <c r="F74" s="88"/>
-      <c r="G74" s="88" t="s">
+      <c r="F74" s="83"/>
+      <c r="G74" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H74" s="7">
@@ -5114,8 +5111,8 @@
       <c r="E75" s="87" t="s">
         <v>272</v>
       </c>
-      <c r="F75" s="88"/>
-      <c r="G75" s="88" t="s">
+      <c r="F75" s="83"/>
+      <c r="G75" s="83" t="s">
         <v>51</v>
       </c>
       <c r="H75" s="7">
@@ -5136,7 +5133,7 @@
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="89" t="s">
+      <c r="A76" s="88" t="s">
         <v>273</v>
       </c>
       <c r="B76" s="87" t="s">
@@ -5148,11 +5145,11 @@
       <c r="D76" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="89" t="s">
+      <c r="E76" s="88" t="s">
         <v>275</v>
       </c>
-      <c r="F76" s="88"/>
-      <c r="G76" s="88" t="s">
+      <c r="F76" s="83"/>
+      <c r="G76" s="83" t="s">
         <v>69</v>
       </c>
       <c r="H76" s="7">
@@ -5175,23 +5172,23 @@
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="92" t="s">
+      <c r="A77" s="85" t="s">
         <v>276</v>
       </c>
-      <c r="B77" s="92" t="s">
+      <c r="B77" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C77" s="92" t="s">
+      <c r="C77" s="85" t="s">
         <v>277</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E77" s="92" t="s">
+      <c r="E77" s="85" t="s">
         <v>278</v>
       </c>
-      <c r="F77" s="88"/>
-      <c r="G77" s="92" t="s">
+      <c r="F77" s="83"/>
+      <c r="G77" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H77" s="7">
@@ -5212,23 +5209,23 @@
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="92" t="s">
+      <c r="A78" s="85" t="s">
         <v>279</v>
       </c>
-      <c r="B78" s="92" t="s">
+      <c r="B78" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C78" s="92" t="s">
+      <c r="C78" s="85" t="s">
         <v>280</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E78" s="92" t="s">
+      <c r="E78" s="85" t="s">
         <v>281</v>
       </c>
-      <c r="F78" s="88"/>
-      <c r="G78" s="92" t="s">
+      <c r="F78" s="83"/>
+      <c r="G78" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H78" s="7">
@@ -5249,23 +5246,23 @@
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="92" t="s">
+      <c r="A79" s="85" t="s">
         <v>282</v>
       </c>
-      <c r="B79" s="92" t="s">
+      <c r="B79" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C79" s="92" t="s">
+      <c r="C79" s="85" t="s">
         <v>76</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E79" s="92" t="s">
+      <c r="E79" s="85" t="s">
         <v>283</v>
       </c>
-      <c r="F79" s="88"/>
-      <c r="G79" s="92" t="s">
+      <c r="F79" s="83"/>
+      <c r="G79" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H79" s="7">
@@ -5286,23 +5283,23 @@
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="92" t="s">
+      <c r="A80" s="85" t="s">
         <v>284</v>
       </c>
-      <c r="B80" s="92" t="s">
+      <c r="B80" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="C80" s="92" t="s">
+      <c r="C80" s="85" t="s">
         <v>285</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E80" s="92" t="s">
+      <c r="E80" s="85" t="s">
         <v>286</v>
       </c>
-      <c r="F80" s="88"/>
-      <c r="G80" s="92" t="s">
+      <c r="F80" s="83"/>
+      <c r="G80" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H80" s="7">
@@ -5323,23 +5320,23 @@
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="92" t="s">
+      <c r="A81" s="85" t="s">
         <v>287</v>
       </c>
-      <c r="B81" s="92" t="s">
+      <c r="B81" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="C81" s="92" t="s">
+      <c r="C81" s="85" t="s">
         <v>288</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E81" s="92" t="s">
+      <c r="E81" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="F81" s="88"/>
-      <c r="G81" s="92" t="s">
+      <c r="F81" s="83"/>
+      <c r="G81" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H81" s="7">
@@ -5360,23 +5357,23 @@
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="92" t="s">
+      <c r="A82" s="85" t="s">
         <v>290</v>
       </c>
-      <c r="B82" s="92" t="s">
+      <c r="B82" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="92" t="s">
+      <c r="C82" s="85" t="s">
         <v>291</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E82" s="92" t="s">
+      <c r="E82" s="85" t="s">
         <v>292</v>
       </c>
-      <c r="F82" s="88"/>
-      <c r="G82" s="92" t="s">
+      <c r="F82" s="83"/>
+      <c r="G82" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H82" s="7">
@@ -5397,23 +5394,23 @@
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="92" t="s">
+      <c r="A83" s="85" t="s">
         <v>293</v>
       </c>
-      <c r="B83" s="92" t="s">
+      <c r="B83" s="85" t="s">
         <v>141</v>
       </c>
-      <c r="C83" s="92" t="s">
+      <c r="C83" s="85" t="s">
         <v>294</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E83" s="92" t="s">
+      <c r="E83" s="85" t="s">
         <v>295</v>
       </c>
-      <c r="F83" s="88"/>
-      <c r="G83" s="92" t="s">
+      <c r="F83" s="83"/>
+      <c r="G83" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H83" s="7">
@@ -5434,23 +5431,23 @@
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="92" t="s">
+      <c r="A84" s="85" t="s">
         <v>296</v>
       </c>
-      <c r="B84" s="92" t="s">
+      <c r="B84" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="C84" s="92" t="s">
+      <c r="C84" s="85" t="s">
         <v>297</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="92" t="s">
+      <c r="E84" s="85" t="s">
         <v>298</v>
       </c>
-      <c r="F84" s="88"/>
-      <c r="G84" s="92" t="s">
+      <c r="F84" s="83"/>
+      <c r="G84" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H84" s="7">
@@ -5471,23 +5468,23 @@
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="92" t="s">
+      <c r="A85" s="85" t="s">
         <v>299</v>
       </c>
-      <c r="B85" s="92" t="s">
+      <c r="B85" s="85" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="92" t="s">
+      <c r="C85" s="85" t="s">
         <v>300</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="92" t="s">
+      <c r="E85" s="85" t="s">
         <v>301</v>
       </c>
-      <c r="F85" s="88"/>
-      <c r="G85" s="92" t="s">
+      <c r="F85" s="83"/>
+      <c r="G85" s="85" t="s">
         <v>87</v>
       </c>
       <c r="H85" s="7">
@@ -5508,25 +5505,25 @@
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="92" t="s">
+      <c r="A86" s="85" t="s">
         <v>302</v>
       </c>
-      <c r="B86" s="92" t="s">
+      <c r="B86" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="C86" s="92" t="s">
+      <c r="C86" s="85" t="s">
         <v>303</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="92" t="s">
+      <c r="E86" s="85" t="s">
         <v>304</v>
       </c>
       <c r="F86" s="10">
         <v>2870896608</v>
       </c>
-      <c r="G86" s="92" t="s">
+      <c r="G86" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H86" s="7">
@@ -5547,25 +5544,25 @@
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="92" t="s">
+      <c r="A87" s="85" t="s">
         <v>305</v>
       </c>
-      <c r="B87" s="92" t="s">
+      <c r="B87" s="85" t="s">
         <v>141</v>
       </c>
-      <c r="C87" s="92" t="s">
+      <c r="C87" s="85" t="s">
         <v>306</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E87" s="92" t="s">
+      <c r="E87" s="85" t="s">
         <v>202</v>
       </c>
       <c r="F87" s="10">
         <v>13970595273</v>
       </c>
-      <c r="G87" s="92" t="s">
+      <c r="G87" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H87" s="7">
@@ -5586,25 +5583,25 @@
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="92" t="s">
+      <c r="A88" s="85" t="s">
         <v>307</v>
       </c>
-      <c r="B88" s="92" t="s">
+      <c r="B88" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C88" s="92" t="s">
+      <c r="C88" s="85" t="s">
         <v>308</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E88" s="92" t="s">
+      <c r="E88" s="85" t="s">
         <v>309</v>
       </c>
       <c r="F88" s="10">
         <v>259948145</v>
       </c>
-      <c r="G88" s="92" t="s">
+      <c r="G88" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H88" s="7">
@@ -5625,25 +5622,25 @@
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="93" t="s">
+      <c r="A89" s="91" t="s">
         <v>310</v>
       </c>
-      <c r="B89" s="92" t="s">
+      <c r="B89" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C89" s="92" t="s">
+      <c r="C89" s="85" t="s">
         <v>308</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E89" s="92" t="s">
+      <c r="E89" s="85" t="s">
         <v>311</v>
       </c>
       <c r="F89" s="10">
         <v>834933960</v>
       </c>
-      <c r="G89" s="92" t="s">
+      <c r="G89" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H89" s="7">
@@ -5664,25 +5661,25 @@
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="92" t="s">
+      <c r="A90" s="85" t="s">
         <v>350</v>
       </c>
-      <c r="B90" s="92" t="s">
+      <c r="B90" s="85" t="s">
         <v>141</v>
       </c>
-      <c r="C90" s="92" t="s">
+      <c r="C90" s="85" t="s">
         <v>308</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E90" s="92" t="s">
+      <c r="E90" s="85" t="s">
         <v>312</v>
       </c>
       <c r="F90" s="10">
         <v>723157595</v>
       </c>
-      <c r="G90" s="92" t="s">
+      <c r="G90" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H90" s="7">
@@ -5703,25 +5700,25 @@
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="92" t="s">
+      <c r="A91" s="85" t="s">
         <v>313</v>
       </c>
-      <c r="B91" s="92" t="s">
+      <c r="B91" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="92" t="s">
+      <c r="C91" s="85" t="s">
         <v>308</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E91" s="92" t="s">
+      <c r="E91" s="85" t="s">
         <v>314</v>
       </c>
       <c r="F91" s="10">
         <v>805795560</v>
       </c>
-      <c r="G91" s="92" t="s">
+      <c r="G91" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H91" s="7">
@@ -5760,7 +5757,7 @@
       <c r="F92" s="10">
         <v>2165000000</v>
       </c>
-      <c r="G92" s="88" t="s">
+      <c r="G92" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H92" s="7">
@@ -5799,7 +5796,7 @@
       <c r="F93" s="10">
         <v>2959258280</v>
       </c>
-      <c r="G93" s="88" t="s">
+      <c r="G93" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H93" s="7">
@@ -5820,25 +5817,25 @@
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="88" t="s">
+      <c r="A94" s="83" t="s">
         <v>319</v>
       </c>
-      <c r="B94" s="92" t="s">
+      <c r="B94" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="C94" s="92" t="s">
+      <c r="C94" s="85" t="s">
         <v>308</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="92" t="s">
+      <c r="E94" s="85" t="s">
         <v>320</v>
       </c>
       <c r="F94" s="10">
         <v>199672220</v>
       </c>
-      <c r="G94" s="92" t="s">
+      <c r="G94" s="85" t="s">
         <v>1</v>
       </c>
       <c r="H94" s="7">
@@ -5859,7 +5856,7 @@
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="91" t="s">
+      <c r="A95" s="90" t="s">
         <v>321</v>
       </c>
       <c r="B95" s="87" t="s">
@@ -5877,7 +5874,7 @@
       <c r="F95" s="7">
         <v>5915704000</v>
       </c>
-      <c r="G95" s="88" t="s">
+      <c r="G95" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H95" s="7">
@@ -5898,25 +5895,25 @@
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="91" t="s">
+      <c r="A96" s="90" t="s">
         <v>323</v>
       </c>
-      <c r="B96" s="90" t="s">
+      <c r="B96" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="C96" s="90" t="s">
+      <c r="C96" s="89" t="s">
         <v>308</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E96" s="90" t="s">
+      <c r="E96" s="89" t="s">
         <v>324</v>
       </c>
       <c r="F96" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G96" s="88" t="s">
+      <c r="G96" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H96" s="7">
@@ -5937,25 +5934,25 @@
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A97" s="91" t="s">
+      <c r="A97" s="90" t="s">
         <v>323</v>
       </c>
-      <c r="B97" s="90" t="s">
+      <c r="B97" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="C97" s="90" t="s">
+      <c r="C97" s="89" t="s">
         <v>308</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E97" s="90" t="s">
+      <c r="E97" s="89" t="s">
         <v>324</v>
       </c>
       <c r="F97" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G97" s="88" t="s">
+      <c r="G97" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H97" s="7">
@@ -5976,7 +5973,7 @@
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="91" t="s">
+      <c r="A98" s="90" t="s">
         <v>325</v>
       </c>
       <c r="B98" s="87" t="s">
@@ -5994,7 +5991,7 @@
       <c r="F98" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G98" s="88" t="s">
+      <c r="G98" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H98" s="7">
@@ -6033,7 +6030,7 @@
       <c r="F99" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G99" s="88" t="s">
+      <c r="G99" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H99" s="7">
@@ -6066,11 +6063,11 @@
       <c r="D100" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E100" s="92" t="s">
+      <c r="E100" s="85" t="s">
         <v>202</v>
       </c>
-      <c r="F100" s="88"/>
-      <c r="G100" s="88" t="s">
+      <c r="F100" s="83"/>
+      <c r="G100" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H100" s="7">
@@ -6103,13 +6100,13 @@
       <c r="D101" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="92" t="s">
+      <c r="E101" s="85" t="s">
         <v>328</v>
       </c>
       <c r="F101" s="7">
         <v>11684429947</v>
       </c>
-      <c r="G101" s="88" t="s">
+      <c r="G101" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H101" s="7">
@@ -6142,11 +6139,11 @@
       <c r="D102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E102" s="92" t="s">
+      <c r="E102" s="85" t="s">
         <v>330</v>
       </c>
-      <c r="F102" s="88"/>
-      <c r="G102" s="88" t="s">
+      <c r="F102" s="83"/>
+      <c r="G102" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H102" s="7">
@@ -6179,13 +6176,13 @@
       <c r="D103" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E103" s="92" t="s">
+      <c r="E103" s="85" t="s">
         <v>333</v>
       </c>
       <c r="F103" s="7">
         <v>2329683517</v>
       </c>
-      <c r="G103" s="88" t="s">
+      <c r="G103" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H103" s="7">
@@ -6218,13 +6215,13 @@
       <c r="D104" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="92" t="s">
+      <c r="E104" s="85" t="s">
         <v>335</v>
       </c>
       <c r="F104" s="7">
         <v>1545593000</v>
       </c>
-      <c r="G104" s="88" t="s">
+      <c r="G104" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H104" s="7">
@@ -6257,11 +6254,11 @@
       <c r="D105" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E105" s="92" t="s">
+      <c r="E105" s="85" t="s">
         <v>347</v>
       </c>
-      <c r="F105" s="88"/>
-      <c r="G105" s="88" t="s">
+      <c r="F105" s="83"/>
+      <c r="G105" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H105" s="7">
@@ -6294,13 +6291,13 @@
       <c r="D106" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E106" s="92" t="s">
+      <c r="E106" s="85" t="s">
         <v>349</v>
       </c>
       <c r="F106" s="7">
         <v>863631818.20000005</v>
       </c>
-      <c r="G106" s="88" t="s">
+      <c r="G106" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H106" s="7">
@@ -6333,13 +6330,13 @@
       <c r="D107" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E107" s="92" t="s">
+      <c r="E107" s="85" t="s">
         <v>353</v>
       </c>
       <c r="F107" s="7">
         <v>3338181818</v>
       </c>
-      <c r="G107" s="88" t="s">
+      <c r="G107" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H107" s="7">
@@ -6372,11 +6369,11 @@
       <c r="D108" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E108" s="92" t="s">
+      <c r="E108" s="85" t="s">
         <v>230</v>
       </c>
-      <c r="F108" s="88"/>
-      <c r="G108" s="88" t="s">
+      <c r="F108" s="83"/>
+      <c r="G108" s="83" t="s">
         <v>87</v>
       </c>
       <c r="H108" s="7">
@@ -6409,13 +6406,13 @@
       <c r="D109" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E109" s="92" t="s">
+      <c r="E109" s="85" t="s">
         <v>356</v>
       </c>
       <c r="F109" s="7">
         <v>719278000</v>
       </c>
-      <c r="G109" s="88" t="s">
+      <c r="G109" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H109" s="7">
@@ -6448,13 +6445,13 @@
       <c r="D110" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E110" s="92" t="s">
+      <c r="E110" s="85" t="s">
         <v>358</v>
       </c>
       <c r="F110" s="7">
         <v>2186917438</v>
       </c>
-      <c r="G110" s="88" t="s">
+      <c r="G110" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H110" s="7">
@@ -6487,13 +6484,13 @@
       <c r="D111" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E111" s="92" t="s">
+      <c r="E111" s="85" t="s">
         <v>366</v>
       </c>
       <c r="F111" s="7">
         <v>69307272.730000004</v>
       </c>
-      <c r="G111" s="88" t="s">
+      <c r="G111" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H111" s="7">
@@ -6526,13 +6523,13 @@
       <c r="D112" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="92" t="s">
+      <c r="E112" s="85" t="s">
         <v>368</v>
       </c>
       <c r="F112" s="7">
         <v>140818181.80000001</v>
       </c>
-      <c r="G112" s="88" t="s">
+      <c r="G112" s="83" t="s">
         <v>1</v>
       </c>
       <c r="H112" s="7">
@@ -6565,13 +6562,13 @@
       <c r="D113" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E113" s="92" t="s">
+      <c r="E113" s="85" t="s">
         <v>370</v>
       </c>
       <c r="F113" s="7">
         <v>1196969505</v>
       </c>
-      <c r="G113" s="88" t="s">
+      <c r="G113" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H113" s="7">
@@ -6604,13 +6601,13 @@
       <c r="D114" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E114" s="92" t="s">
+      <c r="E114" s="85" t="s">
         <v>373</v>
       </c>
       <c r="F114" s="7">
         <v>3761066864</v>
       </c>
-      <c r="G114" s="88" t="s">
+      <c r="G114" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H114" s="7">
@@ -6643,13 +6640,13 @@
       <c r="D115" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E115" s="92" t="s">
+      <c r="E115" s="85" t="s">
         <v>376</v>
       </c>
       <c r="F115" s="7">
         <v>1188000000</v>
       </c>
-      <c r="G115" s="88" t="s">
+      <c r="G115" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H115" s="7">
@@ -6682,13 +6679,13 @@
       <c r="D116" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E116" s="92" t="s">
+      <c r="E116" s="85" t="s">
         <v>379</v>
       </c>
       <c r="F116" s="7">
         <v>8578824307</v>
       </c>
-      <c r="G116" s="88" t="s">
+      <c r="G116" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H116" s="7">
@@ -6721,13 +6718,13 @@
       <c r="D117" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E117" s="92" t="s">
+      <c r="E117" s="85" t="s">
         <v>381</v>
       </c>
       <c r="F117" s="7">
         <v>2842500250</v>
       </c>
-      <c r="G117" s="88" t="s">
+      <c r="G117" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H117" s="7">
@@ -6751,18 +6748,18 @@
       <c r="A118" s="87" t="s">
         <v>382</v>
       </c>
-      <c r="B118" s="88"/>
-      <c r="C118" s="88"/>
+      <c r="B118" s="83"/>
+      <c r="C118" s="83"/>
       <c r="D118" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E118" s="92" t="s">
+      <c r="E118" s="85" t="s">
         <v>383</v>
       </c>
       <c r="F118" s="9">
         <v>459000000</v>
       </c>
-      <c r="G118" s="88" t="s">
+      <c r="G118" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H118" s="7">
@@ -6793,13 +6790,13 @@
       <c r="D119" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E119" s="92" t="s">
+      <c r="E119" s="85" t="s">
         <v>384</v>
       </c>
       <c r="F119" s="7">
         <v>602440000</v>
       </c>
-      <c r="G119" s="88" t="s">
+      <c r="G119" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H119" s="7">
@@ -6818,25 +6815,25 @@
       <c r="M119" s="83"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="92" t="s">
+      <c r="A120" s="85" t="s">
         <v>385</v>
       </c>
       <c r="B120" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C120" s="92" t="s">
+      <c r="C120" s="85" t="s">
         <v>386</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E120" s="92" t="s">
+      <c r="E120" s="85" t="s">
         <v>387</v>
       </c>
       <c r="F120" s="7">
         <v>1847633000</v>
       </c>
-      <c r="G120" s="88" t="s">
+      <c r="G120" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H120" s="7">
@@ -6857,25 +6854,25 @@
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="92" t="s">
+      <c r="A121" s="85" t="s">
         <v>388</v>
       </c>
       <c r="B121" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C121" s="92" t="s">
+      <c r="C121" s="85" t="s">
         <v>389</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E121" s="92" t="s">
+      <c r="E121" s="85" t="s">
         <v>390</v>
       </c>
       <c r="F121" s="7">
         <v>685000000</v>
       </c>
-      <c r="G121" s="88" t="s">
+      <c r="G121" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H121" s="7">
@@ -6902,19 +6899,19 @@
       <c r="B122" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C122" s="92" t="s">
+      <c r="C122" s="85" t="s">
         <v>392</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E122" s="92" t="s">
+      <c r="E122" s="85" t="s">
         <v>391</v>
       </c>
       <c r="F122" s="7">
         <v>854545455</v>
       </c>
-      <c r="G122" s="88" t="s">
+      <c r="G122" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H122" s="7">
@@ -6935,25 +6932,25 @@
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="92" t="s">
+      <c r="A123" s="85" t="s">
         <v>393</v>
       </c>
       <c r="B123" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C123" s="92" t="s">
+      <c r="C123" s="85" t="s">
         <v>394</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="92" t="s">
+      <c r="E123" s="85" t="s">
         <v>395</v>
       </c>
       <c r="F123" s="7">
         <v>800000000</v>
       </c>
-      <c r="G123" s="88" t="s">
+      <c r="G123" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H123" s="7">
@@ -6974,25 +6971,25 @@
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="92" t="s">
+      <c r="A124" s="85" t="s">
         <v>396</v>
       </c>
       <c r="B124" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C124" s="92" t="s">
+      <c r="C124" s="85" t="s">
         <v>397</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E124" s="92" t="s">
+      <c r="E124" s="85" t="s">
         <v>398</v>
       </c>
       <c r="F124" s="7">
         <v>1374545455</v>
       </c>
-      <c r="G124" s="88" t="s">
+      <c r="G124" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H124" s="7">
@@ -7013,25 +7010,25 @@
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="92" t="s">
+      <c r="A125" s="85" t="s">
         <v>399</v>
       </c>
       <c r="B125" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C125" s="92" t="s">
+      <c r="C125" s="85" t="s">
         <v>308</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E125" s="92" t="s">
+      <c r="E125" s="85" t="s">
         <v>401</v>
       </c>
       <c r="F125" s="7">
         <v>214789091</v>
       </c>
-      <c r="G125" s="88" t="s">
+      <c r="G125" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H125" s="7">
@@ -7052,23 +7049,23 @@
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="92" t="s">
+      <c r="A126" s="85" t="s">
         <v>402</v>
       </c>
       <c r="B126" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C126" s="92" t="s">
+      <c r="C126" s="85" t="s">
         <v>403</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E126" s="92" t="s">
+      <c r="E126" s="85" t="s">
         <v>404</v>
       </c>
-      <c r="F126" s="88"/>
-      <c r="G126" s="88" t="s">
+      <c r="F126" s="83"/>
+      <c r="G126" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H126" s="7">
@@ -7089,25 +7086,25 @@
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="92" t="s">
+      <c r="A127" s="85" t="s">
         <v>405</v>
       </c>
       <c r="B127" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C127" s="92" t="s">
+      <c r="C127" s="85" t="s">
         <v>406</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E127" s="92" t="s">
+      <c r="E127" s="85" t="s">
         <v>407</v>
       </c>
       <c r="F127" s="7">
         <v>6320909091</v>
       </c>
-      <c r="G127" s="88" t="s">
+      <c r="G127" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H127" s="7">
@@ -7126,25 +7123,25 @@
       <c r="M127" s="83"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="88" t="s">
+      <c r="A128" s="83" t="s">
         <v>408</v>
       </c>
       <c r="B128" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C128" s="88" t="s">
+      <c r="C128" s="83" t="s">
         <v>409</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E128" s="92" t="s">
+      <c r="E128" s="85" t="s">
         <v>410</v>
       </c>
-      <c r="F128" s="88">
+      <c r="F128" s="83">
         <v>401749000</v>
       </c>
-      <c r="G128" s="88" t="s">
+      <c r="G128" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H128" s="7">
@@ -7165,25 +7162,25 @@
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="88" t="s">
+      <c r="A129" s="83" t="s">
         <v>411</v>
       </c>
       <c r="B129" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C129" s="88" t="s">
+      <c r="C129" s="83" t="s">
         <v>412</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E129" s="92" t="s">
+      <c r="E129" s="85" t="s">
         <v>413</v>
       </c>
-      <c r="F129" s="88">
+      <c r="F129" s="83">
         <v>134556481</v>
       </c>
-      <c r="G129" s="88" t="s">
+      <c r="G129" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H129" s="7">
@@ -7204,25 +7201,25 @@
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A130" s="92" t="s">
+      <c r="A130" s="85" t="s">
         <v>421</v>
       </c>
       <c r="B130" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C130" s="92" t="s">
+      <c r="C130" s="85" t="s">
         <v>412</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E130" s="92" t="s">
+      <c r="E130" s="85" t="s">
         <v>414</v>
       </c>
       <c r="F130" s="7">
         <v>318666815</v>
       </c>
-      <c r="G130" s="88" t="s">
+      <c r="G130" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H130" s="7">
@@ -7243,25 +7240,25 @@
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="88" t="s">
+      <c r="A131" s="83" t="s">
         <v>415</v>
       </c>
       <c r="B131" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C131" s="88" t="s">
+      <c r="C131" s="83" t="s">
         <v>412</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E131" s="92" t="s">
+      <c r="E131" s="85" t="s">
         <v>416</v>
       </c>
-      <c r="F131" s="88">
+      <c r="F131" s="83">
         <v>380721000</v>
       </c>
-      <c r="G131" s="88" t="s">
+      <c r="G131" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H131" s="7">
@@ -7282,25 +7279,25 @@
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="92" t="s">
+      <c r="A132" s="85" t="s">
         <v>417</v>
       </c>
       <c r="B132" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C132" s="92" t="s">
+      <c r="C132" s="85" t="s">
         <v>412</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E132" s="92" t="s">
+      <c r="E132" s="85" t="s">
         <v>418</v>
       </c>
       <c r="F132" s="7">
         <v>234545454.5</v>
       </c>
-      <c r="G132" s="88" t="s">
+      <c r="G132" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H132" s="7">
@@ -7321,25 +7318,25 @@
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="92" t="s">
+      <c r="A133" s="85" t="s">
         <v>419</v>
       </c>
       <c r="B133" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C133" s="92" t="s">
+      <c r="C133" s="85" t="s">
         <v>412</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="92" t="s">
+      <c r="E133" s="85" t="s">
         <v>420</v>
       </c>
       <c r="F133" s="7">
         <v>313269865</v>
       </c>
-      <c r="G133" s="88" t="s">
+      <c r="G133" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H133" s="7">
@@ -7358,25 +7355,25 @@
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="92" t="s">
+      <c r="A134" s="85" t="s">
         <v>422</v>
       </c>
       <c r="B134" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C134" s="92" t="s">
+      <c r="C134" s="85" t="s">
         <v>308</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E134" s="92" t="s">
+      <c r="E134" s="85" t="s">
         <v>423</v>
       </c>
       <c r="F134" s="7">
         <v>970417742</v>
       </c>
-      <c r="G134" s="88" t="s">
+      <c r="G134" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H134" s="7">
@@ -7395,25 +7392,25 @@
       <c r="M134" s="83"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A135" s="92" t="s">
+      <c r="A135" s="85" t="s">
         <v>424</v>
       </c>
       <c r="B135" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C135" s="92" t="s">
+      <c r="C135" s="85" t="s">
         <v>412</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E135" s="92" t="s">
+      <c r="E135" s="85" t="s">
         <v>425</v>
       </c>
       <c r="F135" s="7">
         <v>694444444</v>
       </c>
-      <c r="G135" s="88" t="s">
+      <c r="G135" s="83" t="s">
         <v>11</v>
       </c>
       <c r="H135" s="7">
@@ -7434,25 +7431,25 @@
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A136" s="92" t="s">
+      <c r="A136" s="85" t="s">
         <v>426</v>
       </c>
       <c r="B136" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C136" s="92" t="s">
+      <c r="C136" s="85" t="s">
         <v>427</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E136" s="92" t="s">
+      <c r="E136" s="85" t="s">
         <v>50</v>
       </c>
       <c r="F136" s="82">
         <v>178334509</v>
       </c>
-      <c r="G136" s="88" t="s">
+      <c r="G136" s="83" t="s">
         <v>9</v>
       </c>
       <c r="H136" s="7">
@@ -7471,25 +7468,25 @@
       <c r="M136" s="83"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="94" t="s">
+      <c r="A137" s="84" t="s">
         <v>428</v>
       </c>
-      <c r="B137" s="94" t="s">
+      <c r="B137" s="84" t="s">
         <v>113</v>
       </c>
-      <c r="C137" s="94" t="s">
+      <c r="C137" s="84" t="s">
         <v>429</v>
       </c>
-      <c r="D137" s="94" t="s">
+      <c r="D137" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="E137" s="94" t="s">
+      <c r="E137" s="84" t="s">
         <v>430</v>
       </c>
-      <c r="F137" s="95">
+      <c r="F137" s="92">
         <v>206363636</v>
       </c>
-      <c r="G137" s="94" t="s">
+      <c r="G137" s="84" t="s">
         <v>11</v>
       </c>
       <c r="H137" s="84">
@@ -7508,25 +7505,25 @@
       <c r="M137" s="84"/>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A138" s="94" t="s">
+      <c r="A138" s="84" t="s">
         <v>431</v>
       </c>
-      <c r="B138" s="94" t="s">
+      <c r="B138" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C138" s="94" t="s">
+      <c r="C138" s="84" t="s">
         <v>432</v>
       </c>
-      <c r="D138" s="94" t="s">
+      <c r="D138" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="E138" s="94" t="s">
+      <c r="E138" s="84" t="s">
         <v>433</v>
       </c>
-      <c r="F138" s="95">
+      <c r="F138" s="92">
         <v>2787523658</v>
       </c>
-      <c r="G138" s="94" t="s">
+      <c r="G138" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H138" s="84">
@@ -7545,25 +7542,25 @@
       <c r="M138" s="84"/>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A139" s="94" t="s">
+      <c r="A139" s="84" t="s">
         <v>434</v>
       </c>
-      <c r="B139" s="94" t="s">
+      <c r="B139" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C139" s="94" t="s">
+      <c r="C139" s="84" t="s">
         <v>435</v>
       </c>
-      <c r="D139" s="94" t="s">
+      <c r="D139" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="E139" s="94" t="s">
+      <c r="E139" s="84" t="s">
         <v>436</v>
       </c>
-      <c r="F139" s="95">
+      <c r="F139" s="92">
         <v>183500000</v>
       </c>
-      <c r="G139" s="94" t="s">
+      <c r="G139" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H139" s="84">
@@ -7578,25 +7575,25 @@
       <c r="M139" s="84"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A140" s="94" t="s">
+      <c r="A140" s="84" t="s">
         <v>437</v>
       </c>
-      <c r="B140" s="94" t="s">
+      <c r="B140" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C140" s="94" t="s">
+      <c r="C140" s="84" t="s">
         <v>438</v>
       </c>
-      <c r="D140" s="94" t="s">
+      <c r="D140" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="E140" s="94" t="s">
+      <c r="E140" s="84" t="s">
         <v>439</v>
       </c>
-      <c r="F140" s="95">
+      <c r="F140" s="92">
         <v>107018182</v>
       </c>
-      <c r="G140" s="94" t="s">
+      <c r="G140" s="84" t="s">
         <v>11</v>
       </c>
       <c r="H140" s="84">
@@ -7617,25 +7614,25 @@
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A141" s="94" t="s">
+      <c r="A141" s="84" t="s">
         <v>440</v>
       </c>
-      <c r="B141" s="94" t="s">
+      <c r="B141" s="84" t="s">
         <v>113</v>
       </c>
-      <c r="C141" s="94" t="s">
+      <c r="C141" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="D141" s="94" t="s">
+      <c r="D141" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="E141" s="94" t="s">
+      <c r="E141" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="F141" s="95">
+      <c r="F141" s="92">
         <v>131753127</v>
       </c>
-      <c r="G141" s="94" t="s">
+      <c r="G141" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H141" s="84">
@@ -7648,25 +7645,25 @@
       <c r="M141" s="84"/>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A142" s="94" t="s">
+      <c r="A142" s="84" t="s">
         <v>441</v>
       </c>
-      <c r="B142" s="94" t="s">
+      <c r="B142" s="84" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="94" t="s">
+      <c r="C142" s="84" t="s">
         <v>427</v>
       </c>
-      <c r="D142" s="94" t="s">
+      <c r="D142" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="E142" s="94" t="s">
+      <c r="E142" s="84" t="s">
         <v>442</v>
       </c>
-      <c r="F142" s="95">
+      <c r="F142" s="92">
         <v>2209199764</v>
       </c>
-      <c r="G142" s="94" t="s">
+      <c r="G142" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H142" s="84"/>
@@ -7685,25 +7682,25 @@
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A143" s="94" t="s">
+      <c r="A143" s="84" t="s">
         <v>443</v>
       </c>
-      <c r="B143" s="94" t="s">
+      <c r="B143" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C143" s="94" t="s">
+      <c r="C143" s="84" t="s">
         <v>444</v>
       </c>
-      <c r="D143" s="94" t="s">
+      <c r="D143" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="E143" s="94" t="s">
+      <c r="E143" s="84" t="s">
         <v>445</v>
       </c>
-      <c r="F143" s="95">
+      <c r="F143" s="92">
         <v>2292994051</v>
       </c>
-      <c r="G143" s="94" t="s">
+      <c r="G143" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H143" s="84">
@@ -7724,25 +7721,25 @@
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A144" s="94" t="s">
+      <c r="A144" s="84" t="s">
         <v>446</v>
       </c>
-      <c r="B144" s="94" t="s">
+      <c r="B144" s="84" t="s">
         <v>141</v>
       </c>
-      <c r="C144" s="94" t="s">
+      <c r="C144" s="84" t="s">
         <v>447</v>
       </c>
-      <c r="D144" s="94" t="s">
+      <c r="D144" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="E144" s="94" t="s">
+      <c r="E144" s="84" t="s">
         <v>188</v>
       </c>
-      <c r="F144" s="94">
+      <c r="F144" s="84">
         <v>955130246</v>
       </c>
-      <c r="G144" s="94" t="s">
+      <c r="G144" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H144" s="84">
@@ -7763,25 +7760,25 @@
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A145" s="94" t="s">
+      <c r="A145" s="84" t="s">
         <v>448</v>
       </c>
-      <c r="B145" s="94" t="s">
+      <c r="B145" s="84" t="s">
         <v>141</v>
       </c>
-      <c r="C145" s="94" t="s">
+      <c r="C145" s="84" t="s">
         <v>412</v>
       </c>
-      <c r="D145" s="94" t="s">
+      <c r="D145" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="E145" s="94" t="s">
+      <c r="E145" s="84" t="s">
         <v>449</v>
       </c>
-      <c r="F145" s="94">
+      <c r="F145" s="84">
         <v>1728000000</v>
       </c>
-      <c r="G145" s="94" t="s">
+      <c r="G145" s="84" t="s">
         <v>1</v>
       </c>
       <c r="H145" s="84">
@@ -7802,21 +7799,21 @@
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A146" s="94" t="s">
+      <c r="A146" s="84" t="s">
         <v>450</v>
       </c>
-      <c r="B146" s="94"/>
-      <c r="C146" s="94" t="s">
+      <c r="B146" s="84"/>
+      <c r="C146" s="84" t="s">
         <v>400</v>
       </c>
-      <c r="D146" s="94" t="s">
+      <c r="D146" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="E146" s="94"/>
-      <c r="F146" s="95">
+      <c r="E146" s="84"/>
+      <c r="F146" s="92">
         <v>174715000</v>
       </c>
-      <c r="G146" s="94" t="s">
+      <c r="G146" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H146" s="84">
@@ -7829,23 +7826,23 @@
       <c r="M146" s="84"/>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A147" s="94" t="s">
+      <c r="A147" s="84" t="s">
         <v>451</v>
       </c>
-      <c r="B147" s="94" t="s">
+      <c r="B147" s="84" t="s">
         <v>113</v>
       </c>
-      <c r="C147" s="94" t="s">
+      <c r="C147" s="84" t="s">
         <v>452</v>
       </c>
-      <c r="D147" s="94" t="s">
+      <c r="D147" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="94"/>
-      <c r="F147" s="95">
+      <c r="E147" s="84"/>
+      <c r="F147" s="92">
         <v>128812000</v>
       </c>
-      <c r="G147" s="94" t="s">
+      <c r="G147" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H147" s="84">
@@ -7864,23 +7861,23 @@
       <c r="M147" s="84"/>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A148" s="94" t="s">
+      <c r="A148" s="84" t="s">
         <v>453</v>
       </c>
-      <c r="B148" s="94" t="s">
+      <c r="B148" s="84" t="s">
         <v>113</v>
       </c>
-      <c r="C148" s="94" t="s">
+      <c r="C148" s="84" t="s">
         <v>454</v>
       </c>
-      <c r="D148" s="94" t="s">
+      <c r="D148" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="E148" s="94"/>
-      <c r="F148" s="95">
+      <c r="E148" s="84"/>
+      <c r="F148" s="92">
         <v>2106000000</v>
       </c>
-      <c r="G148" s="94" t="s">
+      <c r="G148" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H148" s="84">
@@ -7899,25 +7896,25 @@
       <c r="M148" s="84"/>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A149" s="94" t="s">
+      <c r="A149" s="84" t="s">
         <v>455</v>
       </c>
-      <c r="B149" s="94" t="s">
+      <c r="B149" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C149" s="94" t="s">
+      <c r="C149" s="84" t="s">
         <v>456</v>
       </c>
-      <c r="D149" s="94" t="s">
+      <c r="D149" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="E149" s="94" t="s">
+      <c r="E149" s="84" t="s">
         <v>439</v>
       </c>
-      <c r="F149" s="95">
+      <c r="F149" s="92">
         <v>170640000</v>
       </c>
-      <c r="G149" s="94" t="s">
+      <c r="G149" s="84" t="s">
         <v>11</v>
       </c>
       <c r="H149" s="84">
@@ -7938,25 +7935,25 @@
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A150" s="94" t="s">
+      <c r="A150" s="84" t="s">
         <v>457</v>
       </c>
-      <c r="B150" s="94" t="s">
+      <c r="B150" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C150" s="94" t="s">
+      <c r="C150" s="84" t="s">
         <v>458</v>
       </c>
-      <c r="D150" s="94" t="s">
+      <c r="D150" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="E150" s="94" t="s">
+      <c r="E150" s="84" t="s">
         <v>459</v>
       </c>
-      <c r="F150" s="94">
+      <c r="F150" s="84">
         <v>4875624485</v>
       </c>
-      <c r="G150" s="94" t="s">
+      <c r="G150" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H150" s="84">
@@ -7977,25 +7974,25 @@
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A151" s="94" t="s">
+      <c r="A151" s="84" t="s">
         <v>460</v>
       </c>
-      <c r="B151" s="94" t="s">
+      <c r="B151" s="84" t="s">
         <v>141</v>
       </c>
-      <c r="C151" s="94" t="s">
+      <c r="C151" s="84" t="s">
         <v>461</v>
       </c>
-      <c r="D151" s="94" t="s">
+      <c r="D151" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="E151" s="94" t="s">
+      <c r="E151" s="84" t="s">
         <v>462</v>
       </c>
-      <c r="F151" s="95">
+      <c r="F151" s="92">
         <v>125710000</v>
       </c>
-      <c r="G151" s="94" t="s">
+      <c r="G151" s="84" t="s">
         <v>9</v>
       </c>
       <c r="H151" s="84">
@@ -11649,7 +11646,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">

--- a/data/ton_chuanhap.xlsx
+++ b/data/ton_chuanhap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_Tonkho\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9896B7E5-95AF-4791-84C4-7CEA65B5E454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987D2D01-D3F3-419A-8787-5444D42862EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">B2B!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">B2B!$A$1:$M$151</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="464">
   <si>
     <t>KV</t>
   </si>
@@ -1765,7 +1765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1991,6 +1991,9 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2391,7 +2394,7 @@
     <col min="3" max="3" width="62" customWidth="1"/>
     <col min="4" max="4" width="7.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
     <col min="7" max="7" width="9.25" customWidth="1"/>
     <col min="8" max="8" width="8.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.625" bestFit="1" customWidth="1"/>
@@ -7514,7 +7517,7 @@
       <c r="C138" s="84" t="s">
         <v>432</v>
       </c>
-      <c r="D138" s="84" t="s">
+      <c r="D138" s="93" t="s">
         <v>24</v>
       </c>
       <c r="E138" s="84" t="s">
@@ -7551,7 +7554,7 @@
       <c r="C139" s="84" t="s">
         <v>435</v>
       </c>
-      <c r="D139" s="84" t="s">
+      <c r="D139" s="93" t="s">
         <v>10</v>
       </c>
       <c r="E139" s="84" t="s">
@@ -7570,7 +7573,9 @@
         <v>70</v>
       </c>
       <c r="J139" s="84"/>
-      <c r="K139" s="84"/>
+      <c r="K139" s="83" t="s">
+        <v>79</v>
+      </c>
       <c r="L139" s="84"/>
       <c r="M139" s="84"/>
     </row>
@@ -7623,7 +7628,7 @@
       <c r="C141" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="D141" s="84" t="s">
+      <c r="D141" s="93" t="s">
         <v>23</v>
       </c>
       <c r="E141" s="84" t="s">
@@ -7640,7 +7645,9 @@
       </c>
       <c r="I141" s="84"/>
       <c r="J141" s="84"/>
-      <c r="K141" s="84"/>
+      <c r="K141" s="83" t="s">
+        <v>79</v>
+      </c>
       <c r="L141" s="84"/>
       <c r="M141" s="84"/>
     </row>
@@ -7654,7 +7661,7 @@
       <c r="C142" s="84" t="s">
         <v>427</v>
       </c>
-      <c r="D142" s="84" t="s">
+      <c r="D142" s="93" t="s">
         <v>20</v>
       </c>
       <c r="E142" s="84" t="s">
@@ -7673,7 +7680,7 @@
       <c r="J142" s="84" t="s">
         <v>78</v>
       </c>
-      <c r="K142" s="84" t="s">
+      <c r="K142" s="83" t="s">
         <v>79</v>
       </c>
       <c r="L142" s="84"/>
@@ -7691,7 +7698,7 @@
       <c r="C143" s="84" t="s">
         <v>444</v>
       </c>
-      <c r="D143" s="84" t="s">
+      <c r="D143" s="93" t="s">
         <v>35</v>
       </c>
       <c r="E143" s="84" t="s">
@@ -7730,7 +7737,7 @@
       <c r="C144" s="84" t="s">
         <v>447</v>
       </c>
-      <c r="D144" s="84" t="s">
+      <c r="D144" s="93" t="s">
         <v>40</v>
       </c>
       <c r="E144" s="84" t="s">
@@ -7806,7 +7813,7 @@
       <c r="C146" s="84" t="s">
         <v>400</v>
       </c>
-      <c r="D146" s="84" t="s">
+      <c r="D146" s="93" t="s">
         <v>10</v>
       </c>
       <c r="E146" s="84"/>
@@ -7821,7 +7828,9 @@
       </c>
       <c r="I146" s="84"/>
       <c r="J146" s="84"/>
-      <c r="K146" s="84"/>
+      <c r="K146" s="83" t="s">
+        <v>79</v>
+      </c>
       <c r="L146" s="84"/>
       <c r="M146" s="84"/>
     </row>
@@ -7835,7 +7844,7 @@
       <c r="C147" s="84" t="s">
         <v>452</v>
       </c>
-      <c r="D147" s="84" t="s">
+      <c r="D147" s="93" t="s">
         <v>23</v>
       </c>
       <c r="E147" s="84"/>
@@ -7870,7 +7879,7 @@
       <c r="C148" s="84" t="s">
         <v>454</v>
       </c>
-      <c r="D148" s="84" t="s">
+      <c r="D148" s="93" t="s">
         <v>41</v>
       </c>
       <c r="E148" s="84"/>
@@ -7889,7 +7898,7 @@
       <c r="J148" s="84" t="s">
         <v>78</v>
       </c>
-      <c r="K148" s="84" t="s">
+      <c r="K148" s="83" t="s">
         <v>79</v>
       </c>
       <c r="L148" s="84"/>
@@ -7944,7 +7953,7 @@
       <c r="C150" s="84" t="s">
         <v>458</v>
       </c>
-      <c r="D150" s="84" t="s">
+      <c r="D150" s="93" t="s">
         <v>35</v>
       </c>
       <c r="E150" s="84" t="s">
@@ -7965,7 +7974,7 @@
       <c r="J150" s="84" t="s">
         <v>78</v>
       </c>
-      <c r="K150" s="84" t="s">
+      <c r="K150" s="83" t="s">
         <v>79</v>
       </c>
       <c r="L150" s="84"/>
@@ -7983,7 +7992,7 @@
       <c r="C151" s="84" t="s">
         <v>461</v>
       </c>
-      <c r="D151" s="84" t="s">
+      <c r="D151" s="93" t="s">
         <v>18</v>
       </c>
       <c r="E151" s="84" t="s">
@@ -8004,12 +8013,14 @@
       <c r="J151" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="K151" s="84"/>
+      <c r="K151" s="83" t="s">
+        <v>79</v>
+      </c>
       <c r="L151" s="84"/>
       <c r="M151" s="84"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{1F457DF4-8092-4544-B88B-9AF42554C254}"/>
+  <autoFilter ref="A1:M151" xr:uid="{1F457DF4-8092-4544-B88B-9AF42554C254}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/ton_chuanhap.xlsx
+++ b/data/ton_chuanhap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_Tonkho\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987D2D01-D3F3-419A-8787-5444D42862EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BD7705-297D-4976-AA80-7799B66551C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="464">
   <si>
     <t>KV</t>
   </si>
@@ -1765,7 +1765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1985,15 +1985,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2446,23 +2449,23 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="88" t="s">
         <v>49</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="87" t="s">
+      <c r="E2" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83" t="s">
+      <c r="F2" s="89"/>
+      <c r="G2" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="7">
@@ -2479,23 +2482,23 @@
       <c r="M2" s="83"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="88" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="87" t="s">
+      <c r="E3" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83" t="s">
+      <c r="F3" s="89"/>
+      <c r="G3" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H3" s="7">
@@ -2512,23 +2515,23 @@
       <c r="M3" s="83"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="88" t="s">
+      <c r="A4" s="90" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="87" t="s">
+      <c r="C4" s="88" t="s">
         <v>158</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="88" t="s">
+      <c r="E4" s="90" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83" t="s">
+      <c r="F4" s="89"/>
+      <c r="G4" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="7">
@@ -2549,23 +2552,23 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="87" t="s">
+      <c r="C5" s="88" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="87" t="s">
+      <c r="E5" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83" t="s">
+      <c r="F5" s="89"/>
+      <c r="G5" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H5" s="7">
@@ -2584,23 +2587,23 @@
       <c r="M5" s="83"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="87" t="s">
+      <c r="C6" s="88" t="s">
         <v>63</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="87" t="s">
+      <c r="E6" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83" t="s">
+      <c r="F6" s="89"/>
+      <c r="G6" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H6" s="7">
@@ -2619,23 +2622,23 @@
       <c r="M6" s="83"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="88" t="s">
         <v>67</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="87" t="s">
+      <c r="E7" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83" t="s">
+      <c r="F7" s="89"/>
+      <c r="G7" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H7" s="7">
@@ -2658,23 +2661,23 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="87" t="s">
+      <c r="C8" s="88" t="s">
         <v>73</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="87" t="s">
+      <c r="E8" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83" t="s">
+      <c r="F8" s="89"/>
+      <c r="G8" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H8" s="7">
@@ -2695,23 +2698,23 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="88" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="87" t="s">
+      <c r="E9" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83" t="s">
+      <c r="F9" s="89"/>
+      <c r="G9" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H9" s="7">
@@ -2730,23 +2733,23 @@
       <c r="M9" s="83"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="87" t="s">
+      <c r="C10" s="88" t="s">
         <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="87" t="s">
+      <c r="E10" s="88" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83" t="s">
+      <c r="F10" s="89"/>
+      <c r="G10" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H10" s="7">
@@ -2765,23 +2768,23 @@
       <c r="M10" s="83"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="88" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="87" t="s">
+      <c r="C11" s="88" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="87" t="s">
+      <c r="E11" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83" t="s">
+      <c r="F11" s="89"/>
+      <c r="G11" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H11" s="7">
@@ -2800,23 +2803,23 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="87" t="s">
+      <c r="B12" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="87" t="s">
+      <c r="C12" s="88" t="s">
         <v>89</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="87" t="s">
+      <c r="E12" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83" t="s">
+      <c r="F12" s="89"/>
+      <c r="G12" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H12" s="7">
@@ -2837,23 +2840,23 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="87" t="s">
+      <c r="B13" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="88" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="89" t="s">
+      <c r="E13" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83" t="s">
+      <c r="F13" s="89"/>
+      <c r="G13" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="7">
@@ -2874,23 +2877,23 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="88" t="s">
         <v>76</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="87" t="e">
+      <c r="E14" s="88" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83" t="s">
+      <c r="F14" s="89"/>
+      <c r="G14" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H14" s="7">
@@ -2907,23 +2910,23 @@
       <c r="M14" s="83"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="87" t="s">
+      <c r="C15" s="88" t="s">
         <v>96</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="87" t="s">
+      <c r="E15" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83" t="s">
+      <c r="F15" s="89"/>
+      <c r="G15" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H15" s="7">
@@ -2940,23 +2943,23 @@
       <c r="M15" s="83"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="88" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="87" t="s">
+      <c r="C16" s="88" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="87" t="s">
+      <c r="E16" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83" t="s">
+      <c r="F16" s="89"/>
+      <c r="G16" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="7">
@@ -2973,23 +2976,23 @@
       <c r="M16" s="83"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="90" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="87" t="s">
+      <c r="C17" s="88" t="s">
         <v>101</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="88" t="s">
+      <c r="E17" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83" t="s">
+      <c r="F17" s="89"/>
+      <c r="G17" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H17" s="7">
@@ -3006,23 +3009,23 @@
       <c r="M17" s="83"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="88" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="87" t="s">
+      <c r="C18" s="88" t="s">
         <v>104</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="87" t="s">
+      <c r="E18" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83" t="s">
+      <c r="F18" s="89"/>
+      <c r="G18" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H18" s="7">
@@ -3041,23 +3044,23 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="87" t="s">
+      <c r="A19" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="88" t="s">
         <v>107</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="87" t="s">
+      <c r="E19" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83" t="s">
+      <c r="F19" s="89"/>
+      <c r="G19" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H19" s="7">
@@ -3078,23 +3081,23 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="87" t="s">
+      <c r="C20" s="88" t="s">
         <v>110</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="87" t="s">
+      <c r="E20" s="88" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83" t="s">
+      <c r="F20" s="89"/>
+      <c r="G20" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H20" s="7">
@@ -3111,23 +3114,23 @@
       <c r="M20" s="83"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="87" t="s">
+      <c r="A21" s="88" t="s">
         <v>112</v>
       </c>
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="87" t="s">
+      <c r="C21" s="88" t="s">
         <v>114</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="87" t="s">
+      <c r="E21" s="88" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83" t="s">
+      <c r="F21" s="89"/>
+      <c r="G21" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H21" s="7">
@@ -3148,23 +3151,23 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="87" t="s">
+      <c r="A22" s="88" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="87" t="s">
+      <c r="B22" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="87" t="s">
+      <c r="C22" s="88" t="s">
         <v>117</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="87" t="s">
+      <c r="E22" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83" t="s">
+      <c r="F22" s="89"/>
+      <c r="G22" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H22" s="7">
@@ -3187,23 +3190,23 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="88" t="s">
         <v>119</v>
       </c>
-      <c r="B23" s="87" t="s">
+      <c r="B23" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="87" t="s">
+      <c r="C23" s="88" t="s">
         <v>120</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="87" t="s">
+      <c r="E23" s="88" t="s">
         <v>121</v>
       </c>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83" t="s">
+      <c r="F23" s="89"/>
+      <c r="G23" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H23" s="7">
@@ -3224,21 +3227,21 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="88" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="87" t="s">
+      <c r="B24" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="83"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="87" t="s">
+      <c r="E24" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83" t="s">
+      <c r="F24" s="89"/>
+      <c r="G24" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H24" s="7">
@@ -3261,23 +3264,23 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="87" t="s">
+      <c r="A25" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="87" t="s">
+      <c r="B25" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="87" t="s">
+      <c r="C25" s="88" t="s">
         <v>125</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="87" t="s">
+      <c r="E25" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83" t="s">
+      <c r="F25" s="89"/>
+      <c r="G25" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H25" s="7">
@@ -3300,23 +3303,23 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="88" t="s">
+      <c r="A26" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="87" t="s">
+      <c r="B26" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="87" t="s">
+      <c r="C26" s="88" t="s">
         <v>128</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="88" t="s">
+      <c r="E26" s="90" t="s">
         <v>129</v>
       </c>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83" t="s">
+      <c r="F26" s="89"/>
+      <c r="G26" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H26" s="7">
@@ -3339,23 +3342,23 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="87" t="s">
+      <c r="B27" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C27" s="87" t="s">
+      <c r="C27" s="88" t="s">
         <v>132</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="87" t="s">
+      <c r="E27" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83" t="s">
+      <c r="F27" s="89"/>
+      <c r="G27" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H27" s="7">
@@ -3376,23 +3379,23 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="87" t="s">
+      <c r="A28" s="88" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="87" t="s">
+      <c r="B28" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="87" t="s">
+      <c r="C28" s="88" t="s">
         <v>135</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="87" t="s">
+      <c r="E28" s="88" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83" t="s">
+      <c r="F28" s="89"/>
+      <c r="G28" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H28" s="7">
@@ -3413,23 +3416,23 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="87" t="s">
+      <c r="A29" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="87" t="s">
+      <c r="B29" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="87" t="s">
+      <c r="C29" s="88" t="s">
         <v>138</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="87" t="s">
+      <c r="E29" s="88" t="s">
         <v>139</v>
       </c>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83" t="s">
+      <c r="F29" s="89"/>
+      <c r="G29" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H29" s="7">
@@ -3450,23 +3453,23 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="87" t="s">
+      <c r="A30" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="87" t="s">
+      <c r="B30" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="87" t="s">
+      <c r="C30" s="88" t="s">
         <v>142</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="87" t="s">
+      <c r="E30" s="88" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83" t="s">
+      <c r="F30" s="89"/>
+      <c r="G30" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H30" s="7">
@@ -3489,23 +3492,23 @@
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="88" t="s">
         <v>145</v>
       </c>
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="88" t="s">
         <v>146</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="87" t="s">
+      <c r="E31" s="88" t="s">
         <v>147</v>
       </c>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83" t="s">
+      <c r="F31" s="89"/>
+      <c r="G31" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H31" s="7">
@@ -3526,23 +3529,23 @@
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="87" t="s">
+      <c r="A32" s="88" t="s">
         <v>148</v>
       </c>
-      <c r="B32" s="87" t="s">
+      <c r="B32" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C32" s="87" t="s">
+      <c r="C32" s="88" t="s">
         <v>149</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="87" t="s">
+      <c r="E32" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="F32" s="83"/>
-      <c r="G32" s="83" t="s">
+      <c r="F32" s="89"/>
+      <c r="G32" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="7">
@@ -3563,23 +3566,23 @@
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="87" t="s">
+      <c r="A33" s="88" t="s">
         <v>151</v>
       </c>
-      <c r="B33" s="87" t="s">
+      <c r="B33" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="87" t="s">
+      <c r="C33" s="88" t="s">
         <v>152</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="87" t="s">
+      <c r="E33" s="88" t="s">
         <v>153</v>
       </c>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83" t="s">
+      <c r="F33" s="89"/>
+      <c r="G33" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H33" s="7">
@@ -3602,23 +3605,23 @@
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="88" t="s">
+      <c r="A34" s="90" t="s">
         <v>154</v>
       </c>
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>155</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="88" t="s">
+      <c r="E34" s="90" t="s">
         <v>156</v>
       </c>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83" t="s">
+      <c r="F34" s="89"/>
+      <c r="G34" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H34" s="7">
@@ -3639,23 +3642,23 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="88" t="s">
+      <c r="A35" s="90" t="s">
         <v>160</v>
       </c>
-      <c r="B35" s="87" t="s">
+      <c r="B35" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="87" t="s">
+      <c r="C35" s="88" t="s">
         <v>161</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="88" t="s">
+      <c r="E35" s="90" t="s">
         <v>162</v>
       </c>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83" t="s">
+      <c r="F35" s="89"/>
+      <c r="G35" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H35" s="7">
@@ -3676,23 +3679,23 @@
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="87" t="s">
+      <c r="A36" s="88" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="87" t="s">
+      <c r="B36" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="87" t="s">
+      <c r="C36" s="88" t="s">
         <v>164</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E36" s="87" t="s">
+      <c r="E36" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83" t="s">
+      <c r="F36" s="89"/>
+      <c r="G36" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H36" s="7">
@@ -3713,23 +3716,23 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="87" t="s">
+      <c r="A37" s="88" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="87" t="s">
+      <c r="B37" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="87" t="s">
+      <c r="C37" s="88" t="s">
         <v>164</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E37" s="87" t="s">
+      <c r="E37" s="88" t="s">
         <v>166</v>
       </c>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83" t="s">
+      <c r="F37" s="89"/>
+      <c r="G37" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H37" s="7">
@@ -3750,23 +3753,23 @@
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="87">
+      <c r="A38" s="88">
         <v>20251678</v>
       </c>
-      <c r="B38" s="87" t="s">
+      <c r="B38" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C38" s="87" t="s">
+      <c r="C38" s="88" t="s">
         <v>168</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E38" s="87" t="s">
+      <c r="E38" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83" t="s">
+      <c r="F38" s="89"/>
+      <c r="G38" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H38" s="7">
@@ -3789,23 +3792,23 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="87" t="s">
+      <c r="A39" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="87" t="s">
+      <c r="C39" s="88" t="s">
         <v>171</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="87" t="s">
+      <c r="E39" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83" t="s">
+      <c r="F39" s="89"/>
+      <c r="G39" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H39" s="7">
@@ -3828,23 +3831,23 @@
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="87" t="s">
+      <c r="A40" s="88" t="s">
         <v>173</v>
       </c>
-      <c r="B40" s="87" t="s">
+      <c r="B40" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C40" s="87" t="s">
+      <c r="C40" s="88" t="s">
         <v>174</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E40" s="87" t="s">
+      <c r="E40" s="88" t="s">
         <v>175</v>
       </c>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83" t="s">
+      <c r="F40" s="89"/>
+      <c r="G40" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H40" s="7">
@@ -3865,23 +3868,23 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="87" t="s">
+      <c r="A41" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="B41" s="87" t="s">
+      <c r="B41" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="87" t="s">
+      <c r="C41" s="88" t="s">
         <v>177</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E41" s="87">
+      <c r="E41" s="88">
         <v>0</v>
       </c>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83" t="s">
+      <c r="F41" s="89"/>
+      <c r="G41" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H41" s="7">
@@ -3902,23 +3905,23 @@
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="87" t="s">
+      <c r="A42" s="88" t="s">
         <v>178</v>
       </c>
-      <c r="B42" s="87" t="s">
+      <c r="B42" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="87" t="s">
+      <c r="C42" s="88" t="s">
         <v>179</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="87" t="e">
+      <c r="E42" s="88" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83" t="s">
+      <c r="F42" s="89"/>
+      <c r="G42" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H42" s="7">
@@ -3941,23 +3944,23 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="87" t="s">
+      <c r="A43" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="B43" s="87" t="s">
+      <c r="B43" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C43" s="87" t="s">
+      <c r="C43" s="88" t="s">
         <v>181</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="87" t="s">
+      <c r="E43" s="88" t="s">
         <v>182</v>
       </c>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83" t="s">
+      <c r="F43" s="89"/>
+      <c r="G43" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H43" s="7">
@@ -3980,23 +3983,23 @@
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="87" t="s">
+      <c r="A44" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="B44" s="87" t="s">
+      <c r="B44" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="87" t="s">
+      <c r="C44" s="88" t="s">
         <v>184</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="87" t="s">
+      <c r="E44" s="88" t="s">
         <v>185</v>
       </c>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83" t="s">
+      <c r="F44" s="89"/>
+      <c r="G44" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H44" s="7">
@@ -4017,23 +4020,23 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="87" t="s">
+      <c r="A45" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="B45" s="87" t="s">
+      <c r="B45" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C45" s="87" t="s">
+      <c r="C45" s="88" t="s">
         <v>187</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="87" t="s">
+      <c r="E45" s="88" t="s">
         <v>188</v>
       </c>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83" t="s">
+      <c r="F45" s="89"/>
+      <c r="G45" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H45" s="7">
@@ -4056,23 +4059,23 @@
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="87" t="s">
+      <c r="A46" s="88" t="s">
         <v>189</v>
       </c>
-      <c r="B46" s="87" t="s">
+      <c r="B46" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="87" t="s">
+      <c r="C46" s="88" t="s">
         <v>190</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="87" t="s">
+      <c r="E46" s="88" t="s">
         <v>191</v>
       </c>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83" t="s">
+      <c r="F46" s="89"/>
+      <c r="G46" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H46" s="7">
@@ -4089,23 +4092,23 @@
       <c r="M46" s="83"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="88" t="s">
+      <c r="A47" s="90" t="s">
         <v>192</v>
       </c>
-      <c r="B47" s="87" t="s">
+      <c r="B47" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="87" t="s">
+      <c r="C47" s="88" t="s">
         <v>193</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="88" t="s">
+      <c r="E47" s="90" t="s">
         <v>194</v>
       </c>
-      <c r="F47" s="83"/>
-      <c r="G47" s="83" t="s">
+      <c r="F47" s="89"/>
+      <c r="G47" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H47" s="7">
@@ -4124,21 +4127,21 @@
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="87" t="s">
+      <c r="A48" s="88" t="s">
         <v>195</v>
       </c>
-      <c r="B48" s="87" t="s">
+      <c r="B48" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="83"/>
+      <c r="C48" s="89"/>
       <c r="D48" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="87" t="s">
+      <c r="E48" s="88" t="s">
         <v>196</v>
       </c>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83" t="s">
+      <c r="F48" s="89"/>
+      <c r="G48" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H48" s="7">
@@ -4157,23 +4160,23 @@
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="87" t="s">
+      <c r="A49" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="B49" s="87" t="s">
+      <c r="B49" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="87" t="s">
+      <c r="C49" s="88" t="s">
         <v>198</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="87" t="s">
+      <c r="E49" s="88" t="s">
         <v>199</v>
       </c>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83" t="s">
+      <c r="F49" s="89"/>
+      <c r="G49" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H49" s="7">
@@ -4192,23 +4195,23 @@
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="87" t="s">
+      <c r="A50" s="88" t="s">
         <v>200</v>
       </c>
-      <c r="B50" s="87" t="s">
+      <c r="B50" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="87" t="s">
+      <c r="C50" s="88" t="s">
         <v>201</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E50" s="87" t="s">
+      <c r="E50" s="88" t="s">
         <v>202</v>
       </c>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83" t="s">
+      <c r="F50" s="89"/>
+      <c r="G50" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H50" s="7">
@@ -4229,23 +4232,23 @@
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="87" t="s">
+      <c r="A51" s="88" t="s">
         <v>203</v>
       </c>
-      <c r="B51" s="87" t="s">
+      <c r="B51" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="87" t="s">
+      <c r="C51" s="88" t="s">
         <v>204</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="87" t="s">
+      <c r="E51" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83" t="s">
+      <c r="F51" s="89"/>
+      <c r="G51" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H51" s="7">
@@ -4266,23 +4269,23 @@
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="87" t="s">
+      <c r="A52" s="88" t="s">
         <v>206</v>
       </c>
-      <c r="B52" s="87" t="s">
+      <c r="B52" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="87" t="s">
+      <c r="C52" s="88" t="s">
         <v>207</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="87" t="s">
+      <c r="E52" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83" t="s">
+      <c r="F52" s="89"/>
+      <c r="G52" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H52" s="7">
@@ -4303,23 +4306,23 @@
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="87" t="s">
+      <c r="A53" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="87" t="s">
+      <c r="B53" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="87" t="s">
+      <c r="C53" s="88" t="s">
         <v>210</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E53" s="87" t="s">
+      <c r="E53" s="88" t="s">
         <v>211</v>
       </c>
-      <c r="F53" s="83"/>
-      <c r="G53" s="83" t="s">
+      <c r="F53" s="89"/>
+      <c r="G53" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H53" s="7">
@@ -4338,21 +4341,21 @@
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="87" t="s">
+      <c r="A54" s="88" t="s">
         <v>212</v>
       </c>
-      <c r="B54" s="87" t="s">
+      <c r="B54" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="83"/>
+      <c r="C54" s="89"/>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E54" s="87" t="s">
+      <c r="E54" s="88" t="s">
         <v>213</v>
       </c>
-      <c r="F54" s="83"/>
-      <c r="G54" s="83" t="s">
+      <c r="F54" s="89"/>
+      <c r="G54" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H54" s="7">
@@ -4371,23 +4374,23 @@
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="87" t="s">
+      <c r="A55" s="88" t="s">
         <v>214</v>
       </c>
-      <c r="B55" s="87" t="s">
+      <c r="B55" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="87" t="s">
+      <c r="C55" s="88" t="s">
         <v>215</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E55" s="87" t="s">
+      <c r="E55" s="88" t="s">
         <v>216</v>
       </c>
-      <c r="F55" s="83"/>
-      <c r="G55" s="83" t="s">
+      <c r="F55" s="89"/>
+      <c r="G55" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H55" s="7">
@@ -4404,21 +4407,21 @@
       <c r="M55" s="83"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="87" t="s">
+      <c r="A56" s="88" t="s">
         <v>217</v>
       </c>
-      <c r="B56" s="87" t="s">
+      <c r="B56" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="83"/>
+      <c r="C56" s="89"/>
       <c r="D56" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="87" t="s">
+      <c r="E56" s="88" t="s">
         <v>218</v>
       </c>
-      <c r="F56" s="83"/>
-      <c r="G56" s="83" t="s">
+      <c r="F56" s="89"/>
+      <c r="G56" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H56" s="7">
@@ -4435,23 +4438,23 @@
       <c r="M56" s="83"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="87" t="s">
+      <c r="A57" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="B57" s="87" t="s">
+      <c r="B57" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="87" t="s">
+      <c r="C57" s="88" t="s">
         <v>220</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E57" s="87" t="s">
+      <c r="E57" s="88" t="s">
         <v>221</v>
       </c>
-      <c r="F57" s="83"/>
-      <c r="G57" s="83" t="s">
+      <c r="F57" s="89"/>
+      <c r="G57" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H57" s="7">
@@ -4470,23 +4473,23 @@
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="87" t="s">
+      <c r="A58" s="88" t="s">
         <v>222</v>
       </c>
-      <c r="B58" s="87" t="s">
+      <c r="B58" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="87" t="s">
+      <c r="C58" s="88" t="s">
         <v>76</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E58" s="87" t="s">
+      <c r="E58" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="F58" s="83"/>
-      <c r="G58" s="83" t="s">
+      <c r="F58" s="89"/>
+      <c r="G58" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H58" s="7">
@@ -4505,23 +4508,23 @@
       <c r="M58" s="83"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="90" t="s">
+      <c r="A59" s="92" t="s">
         <v>224</v>
       </c>
-      <c r="B59" s="87" t="s">
+      <c r="B59" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C59" s="87" t="s">
+      <c r="C59" s="88" t="s">
         <v>225</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="87" t="s">
+      <c r="E59" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="83"/>
-      <c r="G59" s="83" t="s">
+      <c r="F59" s="89"/>
+      <c r="G59" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H59" s="7">
@@ -4540,23 +4543,23 @@
       <c r="M59" s="83"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="90" t="s">
+      <c r="A60" s="92" t="s">
         <v>228</v>
       </c>
-      <c r="B60" s="87" t="s">
+      <c r="B60" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C60" s="87" t="s">
+      <c r="C60" s="88" t="s">
         <v>229</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="87" t="s">
+      <c r="E60" s="88" t="s">
         <v>230</v>
       </c>
-      <c r="F60" s="83"/>
-      <c r="G60" s="83" t="s">
+      <c r="F60" s="89"/>
+      <c r="G60" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H60" s="7">
@@ -4575,23 +4578,23 @@
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="87" t="s">
+      <c r="A61" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="B61" s="87" t="s">
+      <c r="B61" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="87" t="s">
+      <c r="C61" s="88" t="s">
         <v>229</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="87" t="s">
+      <c r="E61" s="88" t="s">
         <v>230</v>
       </c>
-      <c r="F61" s="83"/>
-      <c r="G61" s="83" t="s">
+      <c r="F61" s="89"/>
+      <c r="G61" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H61" s="7">
@@ -4610,23 +4613,23 @@
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="87" t="s">
+      <c r="A62" s="88" t="s">
         <v>231</v>
       </c>
-      <c r="B62" s="87" t="s">
+      <c r="B62" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="87" t="s">
+      <c r="C62" s="88" t="s">
         <v>232</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E62" s="87" t="s">
+      <c r="E62" s="88" t="s">
         <v>136</v>
       </c>
-      <c r="F62" s="83"/>
-      <c r="G62" s="83" t="s">
+      <c r="F62" s="89"/>
+      <c r="G62" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H62" s="7">
@@ -4647,23 +4650,23 @@
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63" s="87" t="s">
+      <c r="A63" s="88" t="s">
         <v>233</v>
       </c>
-      <c r="B63" s="87" t="s">
+      <c r="B63" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="87" t="s">
+      <c r="C63" s="88" t="s">
         <v>234</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="87" t="s">
+      <c r="E63" s="88" t="s">
         <v>235</v>
       </c>
-      <c r="F63" s="83"/>
-      <c r="G63" s="83" t="s">
+      <c r="F63" s="89"/>
+      <c r="G63" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H63" s="7">
@@ -4686,23 +4689,23 @@
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="88" t="s">
+      <c r="A64" s="90" t="s">
         <v>236</v>
       </c>
-      <c r="B64" s="87" t="s">
+      <c r="B64" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="87" t="s">
+      <c r="C64" s="88" t="s">
         <v>237</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="88" t="s">
+      <c r="E64" s="90" t="s">
         <v>238</v>
       </c>
-      <c r="F64" s="83"/>
-      <c r="G64" s="83" t="s">
+      <c r="F64" s="89"/>
+      <c r="G64" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H64" s="7">
@@ -4725,23 +4728,23 @@
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="87" t="s">
+      <c r="A65" s="88" t="s">
         <v>240</v>
       </c>
-      <c r="B65" s="87" t="s">
+      <c r="B65" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C65" s="87" t="s">
+      <c r="C65" s="88" t="s">
         <v>241</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E65" s="87" t="s">
+      <c r="E65" s="88" t="s">
         <v>242</v>
       </c>
-      <c r="F65" s="83"/>
-      <c r="G65" s="83" t="s">
+      <c r="F65" s="89"/>
+      <c r="G65" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H65" s="7">
@@ -4762,23 +4765,23 @@
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="87" t="s">
+      <c r="A66" s="88" t="s">
         <v>243</v>
       </c>
-      <c r="B66" s="87" t="s">
+      <c r="B66" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="87" t="s">
+      <c r="C66" s="88" t="s">
         <v>244</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E66" s="87" t="s">
+      <c r="E66" s="88" t="s">
         <v>245</v>
       </c>
-      <c r="F66" s="83"/>
-      <c r="G66" s="83" t="s">
+      <c r="F66" s="89"/>
+      <c r="G66" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H66" s="7">
@@ -4799,23 +4802,23 @@
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="87" t="s">
+      <c r="A67" s="88" t="s">
         <v>246</v>
       </c>
-      <c r="B67" s="87" t="s">
+      <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="87" t="s">
+      <c r="C67" s="88" t="s">
         <v>247</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E67" s="87" t="s">
+      <c r="E67" s="88" t="s">
         <v>248</v>
       </c>
-      <c r="F67" s="83"/>
-      <c r="G67" s="83" t="s">
+      <c r="F67" s="89"/>
+      <c r="G67" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H67" s="7">
@@ -4838,23 +4841,23 @@
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="88" t="s">
         <v>249</v>
       </c>
-      <c r="B68" s="87" t="s">
+      <c r="B68" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C68" s="87" t="s">
+      <c r="C68" s="88" t="s">
         <v>250</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E68" s="87" t="s">
+      <c r="E68" s="88" t="s">
         <v>251</v>
       </c>
-      <c r="F68" s="83"/>
-      <c r="G68" s="83" t="s">
+      <c r="F68" s="89"/>
+      <c r="G68" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H68" s="7">
@@ -4875,23 +4878,23 @@
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="88" t="s">
+      <c r="A69" s="90" t="s">
         <v>252</v>
       </c>
-      <c r="B69" s="87" t="s">
+      <c r="B69" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C69" s="87" t="s">
+      <c r="C69" s="88" t="s">
         <v>253</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="88" t="s">
+      <c r="E69" s="90" t="s">
         <v>248</v>
       </c>
-      <c r="F69" s="83"/>
-      <c r="G69" s="83" t="s">
+      <c r="F69" s="89"/>
+      <c r="G69" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H69" s="7">
@@ -4912,23 +4915,23 @@
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="87" t="s">
+      <c r="A70" s="88" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="87" t="s">
+      <c r="B70" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C70" s="87" t="s">
+      <c r="C70" s="88" t="s">
         <v>255</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="87" t="s">
+      <c r="E70" s="88" t="s">
         <v>256</v>
       </c>
-      <c r="F70" s="83"/>
-      <c r="G70" s="83" t="s">
+      <c r="F70" s="89"/>
+      <c r="G70" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H70" s="7">
@@ -4949,23 +4952,23 @@
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="87" t="s">
+      <c r="A71" s="88" t="s">
         <v>257</v>
       </c>
-      <c r="B71" s="87" t="s">
+      <c r="B71" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C71" s="87" t="s">
+      <c r="C71" s="88" t="s">
         <v>258</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E71" s="87" t="s">
+      <c r="E71" s="88" t="s">
         <v>259</v>
       </c>
-      <c r="F71" s="83"/>
-      <c r="G71" s="83" t="s">
+      <c r="F71" s="89"/>
+      <c r="G71" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H71" s="7">
@@ -4986,23 +4989,23 @@
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="87" t="s">
+      <c r="A72" s="88" t="s">
         <v>260</v>
       </c>
-      <c r="B72" s="87" t="s">
+      <c r="B72" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C72" s="87" t="s">
+      <c r="C72" s="88" t="s">
         <v>261</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E72" s="87" t="s">
+      <c r="E72" s="88" t="s">
         <v>262</v>
       </c>
-      <c r="F72" s="83"/>
-      <c r="G72" s="83" t="s">
+      <c r="F72" s="89"/>
+      <c r="G72" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H72" s="7">
@@ -5023,23 +5026,23 @@
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="87" t="s">
+      <c r="A73" s="88" t="s">
         <v>264</v>
       </c>
-      <c r="B73" s="87" t="s">
+      <c r="B73" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C73" s="87" t="s">
+      <c r="C73" s="88" t="s">
         <v>265</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E73" s="87" t="s">
+      <c r="E73" s="88" t="s">
         <v>266</v>
       </c>
-      <c r="F73" s="83"/>
-      <c r="G73" s="83" t="s">
+      <c r="F73" s="89"/>
+      <c r="G73" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H73" s="7">
@@ -5062,23 +5065,23 @@
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="87" t="s">
+      <c r="A74" s="88" t="s">
         <v>267</v>
       </c>
-      <c r="B74" s="87" t="s">
+      <c r="B74" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C74" s="87" t="s">
+      <c r="C74" s="88" t="s">
         <v>268</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E74" s="87" t="s">
+      <c r="E74" s="88" t="s">
         <v>269</v>
       </c>
-      <c r="F74" s="83"/>
-      <c r="G74" s="83" t="s">
+      <c r="F74" s="89"/>
+      <c r="G74" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H74" s="7">
@@ -5099,23 +5102,23 @@
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="87" t="s">
+      <c r="A75" s="88" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="87" t="s">
+      <c r="B75" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C75" s="87" t="s">
+      <c r="C75" s="88" t="s">
         <v>271</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E75" s="87" t="s">
+      <c r="E75" s="88" t="s">
         <v>272</v>
       </c>
-      <c r="F75" s="83"/>
-      <c r="G75" s="83" t="s">
+      <c r="F75" s="89"/>
+      <c r="G75" s="89" t="s">
         <v>51</v>
       </c>
       <c r="H75" s="7">
@@ -5136,23 +5139,23 @@
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="90" t="s">
         <v>273</v>
       </c>
-      <c r="B76" s="87" t="s">
+      <c r="B76" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="87" t="s">
+      <c r="C76" s="88" t="s">
         <v>274</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="88" t="s">
+      <c r="E76" s="90" t="s">
         <v>275</v>
       </c>
-      <c r="F76" s="83"/>
-      <c r="G76" s="83" t="s">
+      <c r="F76" s="89"/>
+      <c r="G76" s="89" t="s">
         <v>69</v>
       </c>
       <c r="H76" s="7">
@@ -5175,23 +5178,23 @@
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="85" t="s">
+      <c r="A77" s="93" t="s">
         <v>276</v>
       </c>
-      <c r="B77" s="85" t="s">
+      <c r="B77" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="C77" s="85" t="s">
+      <c r="C77" s="93" t="s">
         <v>277</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E77" s="85" t="s">
+      <c r="E77" s="93" t="s">
         <v>278</v>
       </c>
-      <c r="F77" s="83"/>
-      <c r="G77" s="85" t="s">
+      <c r="F77" s="89"/>
+      <c r="G77" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H77" s="7">
@@ -5212,23 +5215,23 @@
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="85" t="s">
+      <c r="A78" s="93" t="s">
         <v>279</v>
       </c>
-      <c r="B78" s="85" t="s">
+      <c r="B78" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="C78" s="85" t="s">
+      <c r="C78" s="93" t="s">
         <v>280</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E78" s="85" t="s">
+      <c r="E78" s="93" t="s">
         <v>281</v>
       </c>
-      <c r="F78" s="83"/>
-      <c r="G78" s="85" t="s">
+      <c r="F78" s="89"/>
+      <c r="G78" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H78" s="7">
@@ -5249,23 +5252,23 @@
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="85" t="s">
+      <c r="A79" s="93" t="s">
         <v>282</v>
       </c>
-      <c r="B79" s="85" t="s">
+      <c r="B79" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="C79" s="85" t="s">
+      <c r="C79" s="93" t="s">
         <v>76</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E79" s="85" t="s">
+      <c r="E79" s="93" t="s">
         <v>283</v>
       </c>
-      <c r="F79" s="83"/>
-      <c r="G79" s="85" t="s">
+      <c r="F79" s="89"/>
+      <c r="G79" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H79" s="7">
@@ -5286,23 +5289,23 @@
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="85" t="s">
+      <c r="A80" s="93" t="s">
         <v>284</v>
       </c>
-      <c r="B80" s="85" t="s">
+      <c r="B80" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C80" s="85" t="s">
+      <c r="C80" s="93" t="s">
         <v>285</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E80" s="85" t="s">
+      <c r="E80" s="93" t="s">
         <v>286</v>
       </c>
-      <c r="F80" s="83"/>
-      <c r="G80" s="85" t="s">
+      <c r="F80" s="89"/>
+      <c r="G80" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H80" s="7">
@@ -5323,23 +5326,23 @@
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="85" t="s">
+      <c r="A81" s="93" t="s">
         <v>287</v>
       </c>
-      <c r="B81" s="85" t="s">
+      <c r="B81" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="C81" s="85" t="s">
+      <c r="C81" s="93" t="s">
         <v>288</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E81" s="85" t="s">
+      <c r="E81" s="93" t="s">
         <v>289</v>
       </c>
-      <c r="F81" s="83"/>
-      <c r="G81" s="85" t="s">
+      <c r="F81" s="89"/>
+      <c r="G81" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H81" s="7">
@@ -5360,23 +5363,23 @@
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="85" t="s">
+      <c r="A82" s="93" t="s">
         <v>290</v>
       </c>
-      <c r="B82" s="85" t="s">
+      <c r="B82" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="85" t="s">
+      <c r="C82" s="93" t="s">
         <v>291</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E82" s="85" t="s">
+      <c r="E82" s="93" t="s">
         <v>292</v>
       </c>
-      <c r="F82" s="83"/>
-      <c r="G82" s="85" t="s">
+      <c r="F82" s="89"/>
+      <c r="G82" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H82" s="7">
@@ -5397,23 +5400,23 @@
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="85" t="s">
+      <c r="A83" s="93" t="s">
         <v>293</v>
       </c>
-      <c r="B83" s="85" t="s">
+      <c r="B83" s="93" t="s">
         <v>141</v>
       </c>
-      <c r="C83" s="85" t="s">
+      <c r="C83" s="93" t="s">
         <v>294</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E83" s="85" t="s">
+      <c r="E83" s="93" t="s">
         <v>295</v>
       </c>
-      <c r="F83" s="83"/>
-      <c r="G83" s="85" t="s">
+      <c r="F83" s="89"/>
+      <c r="G83" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H83" s="7">
@@ -5434,23 +5437,23 @@
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="85" t="s">
+      <c r="A84" s="93" t="s">
         <v>296</v>
       </c>
-      <c r="B84" s="85" t="s">
+      <c r="B84" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="C84" s="85" t="s">
+      <c r="C84" s="93" t="s">
         <v>297</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="85" t="s">
+      <c r="E84" s="93" t="s">
         <v>298</v>
       </c>
-      <c r="F84" s="83"/>
-      <c r="G84" s="85" t="s">
+      <c r="F84" s="89"/>
+      <c r="G84" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H84" s="7">
@@ -5471,23 +5474,23 @@
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="85" t="s">
+      <c r="A85" s="93" t="s">
         <v>299</v>
       </c>
-      <c r="B85" s="85" t="s">
+      <c r="B85" s="93" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="85" t="s">
+      <c r="C85" s="93" t="s">
         <v>300</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="85" t="s">
+      <c r="E85" s="93" t="s">
         <v>301</v>
       </c>
-      <c r="F85" s="83"/>
-      <c r="G85" s="85" t="s">
+      <c r="F85" s="89"/>
+      <c r="G85" s="93" t="s">
         <v>87</v>
       </c>
       <c r="H85" s="7">
@@ -5508,25 +5511,25 @@
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="85" t="s">
+      <c r="A86" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="B86" s="85" t="s">
+      <c r="B86" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="C86" s="85" t="s">
+      <c r="C86" s="93" t="s">
         <v>303</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="85" t="s">
+      <c r="E86" s="93" t="s">
         <v>304</v>
       </c>
       <c r="F86" s="10">
         <v>2870896608</v>
       </c>
-      <c r="G86" s="85" t="s">
+      <c r="G86" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H86" s="7">
@@ -5547,25 +5550,25 @@
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="85" t="s">
+      <c r="A87" s="93" t="s">
         <v>305</v>
       </c>
-      <c r="B87" s="85" t="s">
+      <c r="B87" s="93" t="s">
         <v>141</v>
       </c>
-      <c r="C87" s="85" t="s">
+      <c r="C87" s="93" t="s">
         <v>306</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E87" s="85" t="s">
+      <c r="E87" s="93" t="s">
         <v>202</v>
       </c>
       <c r="F87" s="10">
         <v>13970595273</v>
       </c>
-      <c r="G87" s="85" t="s">
+      <c r="G87" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H87" s="7">
@@ -5586,25 +5589,25 @@
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="85" t="s">
+      <c r="A88" s="93" t="s">
         <v>307</v>
       </c>
-      <c r="B88" s="85" t="s">
+      <c r="B88" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="C88" s="85" t="s">
+      <c r="C88" s="93" t="s">
         <v>308</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E88" s="85" t="s">
+      <c r="E88" s="93" t="s">
         <v>309</v>
       </c>
       <c r="F88" s="10">
         <v>259948145</v>
       </c>
-      <c r="G88" s="85" t="s">
+      <c r="G88" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H88" s="7">
@@ -5625,25 +5628,25 @@
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="91" t="s">
+      <c r="A89" s="94" t="s">
         <v>310</v>
       </c>
-      <c r="B89" s="85" t="s">
+      <c r="B89" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="C89" s="85" t="s">
+      <c r="C89" s="93" t="s">
         <v>308</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E89" s="85" t="s">
+      <c r="E89" s="93" t="s">
         <v>311</v>
       </c>
       <c r="F89" s="10">
         <v>834933960</v>
       </c>
-      <c r="G89" s="85" t="s">
+      <c r="G89" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H89" s="7">
@@ -5664,25 +5667,25 @@
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="85" t="s">
+      <c r="A90" s="93" t="s">
         <v>350</v>
       </c>
-      <c r="B90" s="85" t="s">
+      <c r="B90" s="93" t="s">
         <v>141</v>
       </c>
-      <c r="C90" s="85" t="s">
+      <c r="C90" s="93" t="s">
         <v>308</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E90" s="85" t="s">
+      <c r="E90" s="93" t="s">
         <v>312</v>
       </c>
       <c r="F90" s="10">
         <v>723157595</v>
       </c>
-      <c r="G90" s="85" t="s">
+      <c r="G90" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H90" s="7">
@@ -5703,25 +5706,25 @@
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="85" t="s">
+      <c r="A91" s="93" t="s">
         <v>313</v>
       </c>
-      <c r="B91" s="85" t="s">
+      <c r="B91" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="85" t="s">
+      <c r="C91" s="93" t="s">
         <v>308</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E91" s="85" t="s">
+      <c r="E91" s="93" t="s">
         <v>314</v>
       </c>
       <c r="F91" s="10">
         <v>805795560</v>
       </c>
-      <c r="G91" s="85" t="s">
+      <c r="G91" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H91" s="7">
@@ -5742,25 +5745,25 @@
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="88" t="s">
         <v>315</v>
       </c>
-      <c r="B92" s="87" t="s">
+      <c r="B92" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C92" s="87" t="s">
+      <c r="C92" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E92" s="87" t="s">
+      <c r="E92" s="88" t="s">
         <v>316</v>
       </c>
       <c r="F92" s="10">
         <v>2165000000</v>
       </c>
-      <c r="G92" s="83" t="s">
+      <c r="G92" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H92" s="7">
@@ -5781,25 +5784,25 @@
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="87" t="s">
+      <c r="A93" s="88" t="s">
         <v>317</v>
       </c>
-      <c r="B93" s="87" t="s">
+      <c r="B93" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C93" s="87" t="s">
+      <c r="C93" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E93" s="87" t="s">
+      <c r="E93" s="88" t="s">
         <v>318</v>
       </c>
       <c r="F93" s="10">
         <v>2959258280</v>
       </c>
-      <c r="G93" s="83" t="s">
+      <c r="G93" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H93" s="7">
@@ -5820,25 +5823,25 @@
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="83" t="s">
+      <c r="A94" s="89" t="s">
         <v>319</v>
       </c>
-      <c r="B94" s="85" t="s">
+      <c r="B94" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="C94" s="85" t="s">
+      <c r="C94" s="93" t="s">
         <v>308</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="85" t="s">
+      <c r="E94" s="93" t="s">
         <v>320</v>
       </c>
       <c r="F94" s="10">
         <v>199672220</v>
       </c>
-      <c r="G94" s="85" t="s">
+      <c r="G94" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H94" s="7">
@@ -5859,25 +5862,25 @@
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="90" t="s">
+      <c r="A95" s="92" t="s">
         <v>321</v>
       </c>
-      <c r="B95" s="87" t="s">
+      <c r="B95" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C95" s="87" t="s">
+      <c r="C95" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E95" s="87" t="s">
+      <c r="E95" s="88" t="s">
         <v>322</v>
       </c>
       <c r="F95" s="7">
         <v>5915704000</v>
       </c>
-      <c r="G95" s="83" t="s">
+      <c r="G95" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H95" s="7">
@@ -5898,25 +5901,25 @@
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="90" t="s">
+      <c r="A96" s="92" t="s">
         <v>323</v>
       </c>
-      <c r="B96" s="89" t="s">
+      <c r="B96" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C96" s="89" t="s">
+      <c r="C96" s="91" t="s">
         <v>308</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E96" s="89" t="s">
+      <c r="E96" s="91" t="s">
         <v>324</v>
       </c>
       <c r="F96" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G96" s="83" t="s">
+      <c r="G96" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H96" s="7">
@@ -5937,25 +5940,25 @@
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A97" s="90" t="s">
+      <c r="A97" s="92" t="s">
         <v>323</v>
       </c>
-      <c r="B97" s="89" t="s">
+      <c r="B97" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C97" s="89" t="s">
+      <c r="C97" s="91" t="s">
         <v>308</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E97" s="89" t="s">
+      <c r="E97" s="91" t="s">
         <v>324</v>
       </c>
       <c r="F97" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G97" s="83" t="s">
+      <c r="G97" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H97" s="7">
@@ -5976,25 +5979,25 @@
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="90" t="s">
+      <c r="A98" s="92" t="s">
         <v>325</v>
       </c>
-      <c r="B98" s="87" t="s">
+      <c r="B98" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C98" s="87" t="s">
+      <c r="C98" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E98" s="87" t="s">
+      <c r="E98" s="88" t="s">
         <v>326</v>
       </c>
       <c r="F98" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G98" s="83" t="s">
+      <c r="G98" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H98" s="7">
@@ -6015,25 +6018,25 @@
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="87" t="s">
+      <c r="A99" s="88" t="s">
         <v>325</v>
       </c>
-      <c r="B99" s="87" t="s">
+      <c r="B99" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C99" s="87" t="s">
+      <c r="C99" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E99" s="87" t="s">
+      <c r="E99" s="88" t="s">
         <v>326</v>
       </c>
       <c r="F99" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G99" s="83" t="s">
+      <c r="G99" s="89" t="s">
         <v>57</v>
       </c>
       <c r="H99" s="7">
@@ -6054,23 +6057,23 @@
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="87" t="s">
+      <c r="A100" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="B100" s="87" t="s">
+      <c r="B100" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C100" s="87" t="s">
+      <c r="C100" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E100" s="85" t="s">
+      <c r="E100" s="93" t="s">
         <v>202</v>
       </c>
-      <c r="F100" s="83"/>
-      <c r="G100" s="83" t="s">
+      <c r="F100" s="89"/>
+      <c r="G100" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H100" s="7">
@@ -6091,25 +6094,25 @@
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="87" t="s">
+      <c r="A101" s="88" t="s">
         <v>327</v>
       </c>
-      <c r="B101" s="87" t="s">
+      <c r="B101" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C101" s="87" t="s">
+      <c r="C101" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="85" t="s">
+      <c r="E101" s="93" t="s">
         <v>328</v>
       </c>
       <c r="F101" s="7">
         <v>11684429947</v>
       </c>
-      <c r="G101" s="83" t="s">
+      <c r="G101" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H101" s="7">
@@ -6130,23 +6133,23 @@
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="87" t="s">
+      <c r="A102" s="88" t="s">
         <v>329</v>
       </c>
-      <c r="B102" s="87" t="s">
+      <c r="B102" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C102" s="87" t="s">
+      <c r="C102" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E102" s="85" t="s">
+      <c r="E102" s="93" t="s">
         <v>330</v>
       </c>
-      <c r="F102" s="83"/>
-      <c r="G102" s="83" t="s">
+      <c r="F102" s="89"/>
+      <c r="G102" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H102" s="7">
@@ -6167,25 +6170,25 @@
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="87" t="s">
+      <c r="A103" s="88" t="s">
         <v>331</v>
       </c>
-      <c r="B103" s="87" t="s">
+      <c r="B103" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C103" s="87" t="s">
+      <c r="C103" s="88" t="s">
         <v>332</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E103" s="85" t="s">
+      <c r="E103" s="93" t="s">
         <v>333</v>
       </c>
       <c r="F103" s="7">
         <v>2329683517</v>
       </c>
-      <c r="G103" s="83" t="s">
+      <c r="G103" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H103" s="7">
@@ -6206,25 +6209,25 @@
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="87" t="s">
+      <c r="A104" s="88" t="s">
         <v>334</v>
       </c>
-      <c r="B104" s="87" t="s">
+      <c r="B104" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C104" s="87" t="s">
+      <c r="C104" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="85" t="s">
+      <c r="E104" s="93" t="s">
         <v>335</v>
       </c>
       <c r="F104" s="7">
         <v>1545593000</v>
       </c>
-      <c r="G104" s="83" t="s">
+      <c r="G104" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H104" s="7">
@@ -6245,23 +6248,23 @@
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="87" t="s">
+      <c r="A105" s="88" t="s">
         <v>346</v>
       </c>
-      <c r="B105" s="87" t="s">
+      <c r="B105" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C105" s="87" t="s">
+      <c r="C105" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E105" s="85" t="s">
+      <c r="E105" s="93" t="s">
         <v>347</v>
       </c>
-      <c r="F105" s="83"/>
-      <c r="G105" s="83" t="s">
+      <c r="F105" s="89"/>
+      <c r="G105" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H105" s="7">
@@ -6282,25 +6285,25 @@
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="87" t="s">
+      <c r="A106" s="88" t="s">
         <v>348</v>
       </c>
-      <c r="B106" s="87" t="s">
+      <c r="B106" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C106" s="87" t="s">
+      <c r="C106" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E106" s="85" t="s">
+      <c r="E106" s="93" t="s">
         <v>349</v>
       </c>
       <c r="F106" s="7">
         <v>863631818.20000005</v>
       </c>
-      <c r="G106" s="83" t="s">
+      <c r="G106" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H106" s="7">
@@ -6321,25 +6324,25 @@
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="87" t="s">
+      <c r="A107" s="88" t="s">
         <v>352</v>
       </c>
-      <c r="B107" s="87" t="s">
+      <c r="B107" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C107" s="87" t="s">
+      <c r="C107" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E107" s="85" t="s">
+      <c r="E107" s="93" t="s">
         <v>353</v>
       </c>
       <c r="F107" s="7">
         <v>3338181818</v>
       </c>
-      <c r="G107" s="83" t="s">
+      <c r="G107" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H107" s="7">
@@ -6360,23 +6363,23 @@
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="87" t="s">
+      <c r="A108" s="88" t="s">
         <v>354</v>
       </c>
-      <c r="B108" s="87" t="s">
+      <c r="B108" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C108" s="87" t="s">
+      <c r="C108" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E108" s="85" t="s">
+      <c r="E108" s="93" t="s">
         <v>230</v>
       </c>
-      <c r="F108" s="83"/>
-      <c r="G108" s="83" t="s">
+      <c r="F108" s="89"/>
+      <c r="G108" s="89" t="s">
         <v>87</v>
       </c>
       <c r="H108" s="7">
@@ -6397,25 +6400,25 @@
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="87" t="s">
+      <c r="A109" s="88" t="s">
         <v>355</v>
       </c>
-      <c r="B109" s="87" t="s">
+      <c r="B109" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C109" s="87" t="s">
+      <c r="C109" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E109" s="85" t="s">
+      <c r="E109" s="93" t="s">
         <v>356</v>
       </c>
       <c r="F109" s="7">
         <v>719278000</v>
       </c>
-      <c r="G109" s="83" t="s">
+      <c r="G109" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H109" s="7">
@@ -6436,25 +6439,25 @@
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="87" t="s">
+      <c r="A110" s="88" t="s">
         <v>357</v>
       </c>
-      <c r="B110" s="87" t="s">
+      <c r="B110" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C110" s="87" t="s">
+      <c r="C110" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E110" s="85" t="s">
+      <c r="E110" s="93" t="s">
         <v>358</v>
       </c>
       <c r="F110" s="7">
         <v>2186917438</v>
       </c>
-      <c r="G110" s="83" t="s">
+      <c r="G110" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H110" s="7">
@@ -6475,25 +6478,25 @@
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A111" s="87" t="s">
+      <c r="A111" s="88" t="s">
         <v>365</v>
       </c>
-      <c r="B111" s="87" t="s">
+      <c r="B111" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C111" s="87" t="s">
+      <c r="C111" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E111" s="85" t="s">
+      <c r="E111" s="93" t="s">
         <v>366</v>
       </c>
       <c r="F111" s="7">
         <v>69307272.730000004</v>
       </c>
-      <c r="G111" s="83" t="s">
+      <c r="G111" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H111" s="7">
@@ -6514,25 +6517,25 @@
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A112" s="87" t="s">
+      <c r="A112" s="88" t="s">
         <v>367</v>
       </c>
-      <c r="B112" s="87" t="s">
+      <c r="B112" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C112" s="87" t="s">
+      <c r="C112" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="85" t="s">
+      <c r="E112" s="93" t="s">
         <v>368</v>
       </c>
       <c r="F112" s="7">
         <v>140818181.80000001</v>
       </c>
-      <c r="G112" s="83" t="s">
+      <c r="G112" s="89" t="s">
         <v>1</v>
       </c>
       <c r="H112" s="7">
@@ -6553,25 +6556,25 @@
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="87" t="s">
+      <c r="A113" s="88" t="s">
         <v>369</v>
       </c>
-      <c r="B113" s="87" t="s">
+      <c r="B113" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C113" s="87" t="s">
+      <c r="C113" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E113" s="85" t="s">
+      <c r="E113" s="93" t="s">
         <v>370</v>
       </c>
       <c r="F113" s="7">
         <v>1196969505</v>
       </c>
-      <c r="G113" s="83" t="s">
+      <c r="G113" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H113" s="7">
@@ -6592,25 +6595,25 @@
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="87" t="s">
+      <c r="A114" s="88" t="s">
         <v>371</v>
       </c>
-      <c r="B114" s="87" t="s">
+      <c r="B114" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C114" s="87" t="s">
+      <c r="C114" s="88" t="s">
         <v>372</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E114" s="85" t="s">
+      <c r="E114" s="93" t="s">
         <v>373</v>
       </c>
       <c r="F114" s="7">
         <v>3761066864</v>
       </c>
-      <c r="G114" s="83" t="s">
+      <c r="G114" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H114" s="7">
@@ -6631,25 +6634,25 @@
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="87" t="s">
+      <c r="A115" s="88" t="s">
         <v>374</v>
       </c>
-      <c r="B115" s="87" t="s">
+      <c r="B115" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C115" s="87" t="s">
+      <c r="C115" s="88" t="s">
         <v>375</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E115" s="85" t="s">
+      <c r="E115" s="93" t="s">
         <v>376</v>
       </c>
       <c r="F115" s="7">
         <v>1188000000</v>
       </c>
-      <c r="G115" s="83" t="s">
+      <c r="G115" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H115" s="7">
@@ -6670,25 +6673,25 @@
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="87" t="s">
+      <c r="A116" s="88" t="s">
         <v>377</v>
       </c>
-      <c r="B116" s="87" t="s">
+      <c r="B116" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C116" s="87" t="s">
+      <c r="C116" s="88" t="s">
         <v>378</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E116" s="85" t="s">
+      <c r="E116" s="93" t="s">
         <v>379</v>
       </c>
       <c r="F116" s="7">
         <v>8578824307</v>
       </c>
-      <c r="G116" s="83" t="s">
+      <c r="G116" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H116" s="7">
@@ -6709,25 +6712,25 @@
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="87" t="s">
+      <c r="A117" s="88" t="s">
         <v>380</v>
       </c>
-      <c r="B117" s="87" t="s">
+      <c r="B117" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C117" s="87" t="s">
+      <c r="C117" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E117" s="85" t="s">
+      <c r="E117" s="93" t="s">
         <v>381</v>
       </c>
       <c r="F117" s="7">
         <v>2842500250</v>
       </c>
-      <c r="G117" s="83" t="s">
+      <c r="G117" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H117" s="7">
@@ -6748,21 +6751,21 @@
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="87" t="s">
+      <c r="A118" s="88" t="s">
         <v>382</v>
       </c>
-      <c r="B118" s="83"/>
-      <c r="C118" s="83"/>
+      <c r="B118" s="89"/>
+      <c r="C118" s="89"/>
       <c r="D118" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E118" s="85" t="s">
+      <c r="E118" s="93" t="s">
         <v>383</v>
       </c>
       <c r="F118" s="9">
         <v>459000000</v>
       </c>
-      <c r="G118" s="83" t="s">
+      <c r="G118" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H118" s="7">
@@ -6781,25 +6784,25 @@
       <c r="M118" s="83"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="87" t="s">
+      <c r="A119" s="88" t="s">
         <v>384</v>
       </c>
-      <c r="B119" s="87" t="s">
+      <c r="B119" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C119" s="87" t="s">
+      <c r="C119" s="88" t="s">
         <v>308</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E119" s="85" t="s">
+      <c r="E119" s="93" t="s">
         <v>384</v>
       </c>
       <c r="F119" s="7">
         <v>602440000</v>
       </c>
-      <c r="G119" s="83" t="s">
+      <c r="G119" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H119" s="7">
@@ -6818,25 +6821,25 @@
       <c r="M119" s="83"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="85" t="s">
+      <c r="A120" s="93" t="s">
         <v>385</v>
       </c>
-      <c r="B120" s="87" t="s">
+      <c r="B120" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C120" s="85" t="s">
+      <c r="C120" s="93" t="s">
         <v>386</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E120" s="85" t="s">
+      <c r="E120" s="93" t="s">
         <v>387</v>
       </c>
       <c r="F120" s="7">
         <v>1847633000</v>
       </c>
-      <c r="G120" s="83" t="s">
+      <c r="G120" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H120" s="7">
@@ -6857,25 +6860,25 @@
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="85" t="s">
+      <c r="A121" s="93" t="s">
         <v>388</v>
       </c>
-      <c r="B121" s="87" t="s">
+      <c r="B121" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C121" s="85" t="s">
+      <c r="C121" s="93" t="s">
         <v>389</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E121" s="85" t="s">
+      <c r="E121" s="93" t="s">
         <v>390</v>
       </c>
       <c r="F121" s="7">
         <v>685000000</v>
       </c>
-      <c r="G121" s="83" t="s">
+      <c r="G121" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H121" s="7">
@@ -6896,25 +6899,25 @@
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="87" t="s">
+      <c r="A122" s="88" t="s">
         <v>391</v>
       </c>
-      <c r="B122" s="87" t="s">
+      <c r="B122" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C122" s="85" t="s">
+      <c r="C122" s="93" t="s">
         <v>392</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E122" s="85" t="s">
+      <c r="E122" s="93" t="s">
         <v>391</v>
       </c>
       <c r="F122" s="7">
         <v>854545455</v>
       </c>
-      <c r="G122" s="83" t="s">
+      <c r="G122" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H122" s="7">
@@ -6935,25 +6938,25 @@
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="85" t="s">
+      <c r="A123" s="93" t="s">
         <v>393</v>
       </c>
-      <c r="B123" s="87" t="s">
+      <c r="B123" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C123" s="85" t="s">
+      <c r="C123" s="93" t="s">
         <v>394</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="85" t="s">
+      <c r="E123" s="93" t="s">
         <v>395</v>
       </c>
       <c r="F123" s="7">
         <v>800000000</v>
       </c>
-      <c r="G123" s="83" t="s">
+      <c r="G123" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H123" s="7">
@@ -6974,25 +6977,25 @@
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="85" t="s">
+      <c r="A124" s="93" t="s">
         <v>396</v>
       </c>
-      <c r="B124" s="87" t="s">
+      <c r="B124" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C124" s="85" t="s">
+      <c r="C124" s="93" t="s">
         <v>397</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E124" s="85" t="s">
+      <c r="E124" s="93" t="s">
         <v>398</v>
       </c>
       <c r="F124" s="7">
         <v>1374545455</v>
       </c>
-      <c r="G124" s="83" t="s">
+      <c r="G124" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H124" s="7">
@@ -7013,25 +7016,25 @@
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="85" t="s">
+      <c r="A125" s="93" t="s">
         <v>399</v>
       </c>
-      <c r="B125" s="87" t="s">
+      <c r="B125" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C125" s="85" t="s">
+      <c r="C125" s="93" t="s">
         <v>308</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E125" s="85" t="s">
+      <c r="E125" s="93" t="s">
         <v>401</v>
       </c>
       <c r="F125" s="7">
         <v>214789091</v>
       </c>
-      <c r="G125" s="83" t="s">
+      <c r="G125" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H125" s="7">
@@ -7052,23 +7055,23 @@
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="85" t="s">
+      <c r="A126" s="93" t="s">
         <v>402</v>
       </c>
-      <c r="B126" s="87" t="s">
+      <c r="B126" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C126" s="85" t="s">
+      <c r="C126" s="93" t="s">
         <v>403</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E126" s="85" t="s">
+      <c r="E126" s="93" t="s">
         <v>404</v>
       </c>
-      <c r="F126" s="83"/>
-      <c r="G126" s="83" t="s">
+      <c r="F126" s="89"/>
+      <c r="G126" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H126" s="7">
@@ -7089,25 +7092,25 @@
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="85" t="s">
+      <c r="A127" s="93" t="s">
         <v>405</v>
       </c>
-      <c r="B127" s="87" t="s">
+      <c r="B127" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C127" s="85" t="s">
+      <c r="C127" s="93" t="s">
         <v>406</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E127" s="85" t="s">
+      <c r="E127" s="93" t="s">
         <v>407</v>
       </c>
       <c r="F127" s="7">
         <v>6320909091</v>
       </c>
-      <c r="G127" s="83" t="s">
+      <c r="G127" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H127" s="7">
@@ -7126,25 +7129,25 @@
       <c r="M127" s="83"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="83" t="s">
+      <c r="A128" s="89" t="s">
         <v>408</v>
       </c>
-      <c r="B128" s="87" t="s">
+      <c r="B128" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C128" s="83" t="s">
+      <c r="C128" s="89" t="s">
         <v>409</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E128" s="85" t="s">
+      <c r="E128" s="93" t="s">
         <v>410</v>
       </c>
-      <c r="F128" s="83">
+      <c r="F128" s="89">
         <v>401749000</v>
       </c>
-      <c r="G128" s="83" t="s">
+      <c r="G128" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H128" s="7">
@@ -7165,25 +7168,25 @@
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="83" t="s">
+      <c r="A129" s="89" t="s">
         <v>411</v>
       </c>
-      <c r="B129" s="87" t="s">
+      <c r="B129" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C129" s="83" t="s">
+      <c r="C129" s="89" t="s">
         <v>412</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E129" s="85" t="s">
+      <c r="E129" s="93" t="s">
         <v>413</v>
       </c>
-      <c r="F129" s="83">
+      <c r="F129" s="89">
         <v>134556481</v>
       </c>
-      <c r="G129" s="83" t="s">
+      <c r="G129" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H129" s="7">
@@ -7204,25 +7207,25 @@
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A130" s="85" t="s">
+      <c r="A130" s="93" t="s">
         <v>421</v>
       </c>
-      <c r="B130" s="87" t="s">
+      <c r="B130" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C130" s="85" t="s">
+      <c r="C130" s="93" t="s">
         <v>412</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E130" s="85" t="s">
+      <c r="E130" s="93" t="s">
         <v>414</v>
       </c>
       <c r="F130" s="7">
         <v>318666815</v>
       </c>
-      <c r="G130" s="83" t="s">
+      <c r="G130" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H130" s="7">
@@ -7243,25 +7246,25 @@
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="83" t="s">
+      <c r="A131" s="89" t="s">
         <v>415</v>
       </c>
-      <c r="B131" s="87" t="s">
+      <c r="B131" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C131" s="83" t="s">
+      <c r="C131" s="89" t="s">
         <v>412</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E131" s="85" t="s">
+      <c r="E131" s="93" t="s">
         <v>416</v>
       </c>
-      <c r="F131" s="83">
+      <c r="F131" s="89">
         <v>380721000</v>
       </c>
-      <c r="G131" s="83" t="s">
+      <c r="G131" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H131" s="7">
@@ -7282,25 +7285,25 @@
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="85" t="s">
+      <c r="A132" s="93" t="s">
         <v>417</v>
       </c>
-      <c r="B132" s="87" t="s">
+      <c r="B132" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C132" s="85" t="s">
+      <c r="C132" s="93" t="s">
         <v>412</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E132" s="85" t="s">
+      <c r="E132" s="93" t="s">
         <v>418</v>
       </c>
       <c r="F132" s="7">
         <v>234545454.5</v>
       </c>
-      <c r="G132" s="83" t="s">
+      <c r="G132" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H132" s="7">
@@ -7321,25 +7324,25 @@
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="85" t="s">
+      <c r="A133" s="93" t="s">
         <v>419</v>
       </c>
-      <c r="B133" s="87" t="s">
+      <c r="B133" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C133" s="85" t="s">
+      <c r="C133" s="93" t="s">
         <v>412</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="85" t="s">
+      <c r="E133" s="93" t="s">
         <v>420</v>
       </c>
       <c r="F133" s="7">
         <v>313269865</v>
       </c>
-      <c r="G133" s="83" t="s">
+      <c r="G133" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H133" s="7">
@@ -7358,25 +7361,25 @@
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="85" t="s">
+      <c r="A134" s="93" t="s">
         <v>422</v>
       </c>
-      <c r="B134" s="87" t="s">
+      <c r="B134" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C134" s="85" t="s">
+      <c r="C134" s="93" t="s">
         <v>308</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E134" s="85" t="s">
+      <c r="E134" s="93" t="s">
         <v>423</v>
       </c>
       <c r="F134" s="7">
         <v>970417742</v>
       </c>
-      <c r="G134" s="83" t="s">
+      <c r="G134" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H134" s="7">
@@ -7395,25 +7398,25 @@
       <c r="M134" s="83"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A135" s="85" t="s">
+      <c r="A135" s="93" t="s">
         <v>424</v>
       </c>
-      <c r="B135" s="87" t="s">
+      <c r="B135" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="C135" s="85" t="s">
+      <c r="C135" s="93" t="s">
         <v>412</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E135" s="85" t="s">
+      <c r="E135" s="93" t="s">
         <v>425</v>
       </c>
       <c r="F135" s="7">
         <v>694444444</v>
       </c>
-      <c r="G135" s="83" t="s">
+      <c r="G135" s="89" t="s">
         <v>11</v>
       </c>
       <c r="H135" s="7">
@@ -7434,25 +7437,25 @@
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A136" s="85" t="s">
+      <c r="A136" s="93" t="s">
         <v>426</v>
       </c>
-      <c r="B136" s="87" t="s">
+      <c r="B136" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C136" s="85" t="s">
+      <c r="C136" s="93" t="s">
         <v>427</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E136" s="85" t="s">
+      <c r="E136" s="93" t="s">
         <v>50</v>
       </c>
       <c r="F136" s="82">
         <v>178334509</v>
       </c>
-      <c r="G136" s="83" t="s">
+      <c r="G136" s="89" t="s">
         <v>9</v>
       </c>
       <c r="H136" s="7">
@@ -7471,25 +7474,25 @@
       <c r="M136" s="83"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="84" t="s">
+      <c r="A137" s="95" t="s">
         <v>428</v>
       </c>
-      <c r="B137" s="84" t="s">
+      <c r="B137" s="95" t="s">
         <v>113</v>
       </c>
-      <c r="C137" s="84" t="s">
+      <c r="C137" s="95" t="s">
         <v>429</v>
       </c>
-      <c r="D137" s="84" t="s">
+      <c r="D137" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="E137" s="84" t="s">
+      <c r="E137" s="95" t="s">
         <v>430</v>
       </c>
-      <c r="F137" s="92">
+      <c r="F137" s="96">
         <v>206363636</v>
       </c>
-      <c r="G137" s="84" t="s">
+      <c r="G137" s="95" t="s">
         <v>11</v>
       </c>
       <c r="H137" s="84">
@@ -7508,25 +7511,25 @@
       <c r="M137" s="84"/>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A138" s="84" t="s">
+      <c r="A138" s="95" t="s">
         <v>431</v>
       </c>
-      <c r="B138" s="84" t="s">
+      <c r="B138" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="C138" s="84" t="s">
+      <c r="C138" s="95" t="s">
         <v>432</v>
       </c>
-      <c r="D138" s="93" t="s">
+      <c r="D138" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="E138" s="84" t="s">
+      <c r="E138" s="95" t="s">
         <v>433</v>
       </c>
-      <c r="F138" s="92">
+      <c r="F138" s="96">
         <v>2787523658</v>
       </c>
-      <c r="G138" s="84" t="s">
+      <c r="G138" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H138" s="84">
@@ -7545,25 +7548,25 @@
       <c r="M138" s="84"/>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A139" s="84" t="s">
+      <c r="A139" s="95" t="s">
         <v>434</v>
       </c>
-      <c r="B139" s="84" t="s">
+      <c r="B139" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="C139" s="84" t="s">
+      <c r="C139" s="95" t="s">
         <v>435</v>
       </c>
-      <c r="D139" s="93" t="s">
+      <c r="D139" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="E139" s="84" t="s">
+      <c r="E139" s="95" t="s">
         <v>436</v>
       </c>
-      <c r="F139" s="92">
+      <c r="F139" s="96">
         <v>183500000</v>
       </c>
-      <c r="G139" s="84" t="s">
+      <c r="G139" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H139" s="84">
@@ -7573,32 +7576,30 @@
         <v>70</v>
       </c>
       <c r="J139" s="84"/>
-      <c r="K139" s="83" t="s">
-        <v>79</v>
-      </c>
+      <c r="K139" s="83"/>
       <c r="L139" s="84"/>
       <c r="M139" s="84"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A140" s="84" t="s">
+      <c r="A140" s="95" t="s">
         <v>437</v>
       </c>
-      <c r="B140" s="84" t="s">
+      <c r="B140" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="C140" s="84" t="s">
+      <c r="C140" s="95" t="s">
         <v>438</v>
       </c>
-      <c r="D140" s="84" t="s">
+      <c r="D140" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="E140" s="84" t="s">
+      <c r="E140" s="95" t="s">
         <v>439</v>
       </c>
-      <c r="F140" s="92">
+      <c r="F140" s="96">
         <v>107018182</v>
       </c>
-      <c r="G140" s="84" t="s">
+      <c r="G140" s="95" t="s">
         <v>11</v>
       </c>
       <c r="H140" s="84">
@@ -7619,25 +7620,25 @@
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A141" s="84" t="s">
+      <c r="A141" s="95" t="s">
         <v>440</v>
       </c>
-      <c r="B141" s="84" t="s">
+      <c r="B141" s="95" t="s">
         <v>113</v>
       </c>
-      <c r="C141" s="84" t="s">
+      <c r="C141" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D141" s="93" t="s">
+      <c r="D141" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="E141" s="84" t="s">
+      <c r="E141" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="F141" s="92">
+      <c r="F141" s="96">
         <v>131753127</v>
       </c>
-      <c r="G141" s="84" t="s">
+      <c r="G141" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H141" s="84">
@@ -7645,32 +7646,30 @@
       </c>
       <c r="I141" s="84"/>
       <c r="J141" s="84"/>
-      <c r="K141" s="83" t="s">
-        <v>79</v>
-      </c>
+      <c r="K141" s="83"/>
       <c r="L141" s="84"/>
       <c r="M141" s="84"/>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A142" s="84" t="s">
+      <c r="A142" s="95" t="s">
         <v>441</v>
       </c>
-      <c r="B142" s="84" t="s">
+      <c r="B142" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="84" t="s">
+      <c r="C142" s="95" t="s">
         <v>427</v>
       </c>
-      <c r="D142" s="93" t="s">
+      <c r="D142" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="E142" s="84" t="s">
+      <c r="E142" s="95" t="s">
         <v>442</v>
       </c>
-      <c r="F142" s="92">
+      <c r="F142" s="96">
         <v>2209199764</v>
       </c>
-      <c r="G142" s="84" t="s">
+      <c r="G142" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H142" s="84"/>
@@ -7689,25 +7688,25 @@
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A143" s="84" t="s">
+      <c r="A143" s="95" t="s">
         <v>443</v>
       </c>
-      <c r="B143" s="84" t="s">
+      <c r="B143" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="C143" s="84" t="s">
+      <c r="C143" s="95" t="s">
         <v>444</v>
       </c>
-      <c r="D143" s="93" t="s">
+      <c r="D143" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="E143" s="84" t="s">
+      <c r="E143" s="95" t="s">
         <v>445</v>
       </c>
-      <c r="F143" s="92">
+      <c r="F143" s="96">
         <v>2292994051</v>
       </c>
-      <c r="G143" s="84" t="s">
+      <c r="G143" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H143" s="84">
@@ -7728,25 +7727,25 @@
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A144" s="84" t="s">
+      <c r="A144" s="95" t="s">
         <v>446</v>
       </c>
-      <c r="B144" s="84" t="s">
+      <c r="B144" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="C144" s="84" t="s">
+      <c r="C144" s="95" t="s">
         <v>447</v>
       </c>
-      <c r="D144" s="93" t="s">
+      <c r="D144" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="E144" s="84" t="s">
+      <c r="E144" s="95" t="s">
         <v>188</v>
       </c>
-      <c r="F144" s="84">
+      <c r="F144" s="95">
         <v>955130246</v>
       </c>
-      <c r="G144" s="84" t="s">
+      <c r="G144" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H144" s="84">
@@ -7767,25 +7766,25 @@
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A145" s="84" t="s">
+      <c r="A145" s="95" t="s">
         <v>448</v>
       </c>
-      <c r="B145" s="84" t="s">
+      <c r="B145" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="C145" s="84" t="s">
+      <c r="C145" s="95" t="s">
         <v>412</v>
       </c>
-      <c r="D145" s="84" t="s">
+      <c r="D145" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="E145" s="84" t="s">
+      <c r="E145" s="95" t="s">
         <v>449</v>
       </c>
-      <c r="F145" s="84">
+      <c r="F145" s="95">
         <v>1728000000</v>
       </c>
-      <c r="G145" s="84" t="s">
+      <c r="G145" s="95" t="s">
         <v>1</v>
       </c>
       <c r="H145" s="84">
@@ -7806,21 +7805,21 @@
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A146" s="84" t="s">
+      <c r="A146" s="95" t="s">
         <v>450</v>
       </c>
-      <c r="B146" s="84"/>
-      <c r="C146" s="84" t="s">
+      <c r="B146" s="95"/>
+      <c r="C146" s="95" t="s">
         <v>400</v>
       </c>
-      <c r="D146" s="93" t="s">
+      <c r="D146" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="E146" s="84"/>
-      <c r="F146" s="92">
+      <c r="E146" s="95"/>
+      <c r="F146" s="96">
         <v>174715000</v>
       </c>
-      <c r="G146" s="84" t="s">
+      <c r="G146" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H146" s="84">
@@ -7828,30 +7827,28 @@
       </c>
       <c r="I146" s="84"/>
       <c r="J146" s="84"/>
-      <c r="K146" s="83" t="s">
-        <v>79</v>
-      </c>
+      <c r="K146" s="83"/>
       <c r="L146" s="84"/>
       <c r="M146" s="84"/>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A147" s="84" t="s">
+      <c r="A147" s="95" t="s">
         <v>451</v>
       </c>
-      <c r="B147" s="84" t="s">
+      <c r="B147" s="95" t="s">
         <v>113</v>
       </c>
-      <c r="C147" s="84" t="s">
+      <c r="C147" s="95" t="s">
         <v>452</v>
       </c>
-      <c r="D147" s="93" t="s">
+      <c r="D147" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="84"/>
-      <c r="F147" s="92">
+      <c r="E147" s="95"/>
+      <c r="F147" s="96">
         <v>128812000</v>
       </c>
-      <c r="G147" s="84" t="s">
+      <c r="G147" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H147" s="84">
@@ -7870,23 +7867,23 @@
       <c r="M147" s="84"/>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A148" s="84" t="s">
+      <c r="A148" s="95" t="s">
         <v>453</v>
       </c>
-      <c r="B148" s="84" t="s">
+      <c r="B148" s="95" t="s">
         <v>113</v>
       </c>
-      <c r="C148" s="84" t="s">
+      <c r="C148" s="95" t="s">
         <v>454</v>
       </c>
-      <c r="D148" s="93" t="s">
+      <c r="D148" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="E148" s="84"/>
-      <c r="F148" s="92">
+      <c r="E148" s="95"/>
+      <c r="F148" s="96">
         <v>2106000000</v>
       </c>
-      <c r="G148" s="84" t="s">
+      <c r="G148" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H148" s="84">
@@ -7905,25 +7902,25 @@
       <c r="M148" s="84"/>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A149" s="84" t="s">
+      <c r="A149" s="95" t="s">
         <v>455</v>
       </c>
-      <c r="B149" s="84" t="s">
+      <c r="B149" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="C149" s="84" t="s">
+      <c r="C149" s="95" t="s">
         <v>456</v>
       </c>
-      <c r="D149" s="84" t="s">
+      <c r="D149" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="E149" s="84" t="s">
+      <c r="E149" s="95" t="s">
         <v>439</v>
       </c>
-      <c r="F149" s="92">
+      <c r="F149" s="96">
         <v>170640000</v>
       </c>
-      <c r="G149" s="84" t="s">
+      <c r="G149" s="95" t="s">
         <v>11</v>
       </c>
       <c r="H149" s="84">
@@ -7944,25 +7941,25 @@
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A150" s="84" t="s">
+      <c r="A150" s="95" t="s">
         <v>457</v>
       </c>
-      <c r="B150" s="84" t="s">
+      <c r="B150" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="C150" s="84" t="s">
+      <c r="C150" s="95" t="s">
         <v>458</v>
       </c>
-      <c r="D150" s="93" t="s">
+      <c r="D150" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="E150" s="84" t="s">
+      <c r="E150" s="95" t="s">
         <v>459</v>
       </c>
-      <c r="F150" s="84">
+      <c r="F150" s="95">
         <v>4875624485</v>
       </c>
-      <c r="G150" s="84" t="s">
+      <c r="G150" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H150" s="84">
@@ -7983,25 +7980,25 @@
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A151" s="84" t="s">
+      <c r="A151" s="95" t="s">
         <v>460</v>
       </c>
-      <c r="B151" s="84" t="s">
+      <c r="B151" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="C151" s="84" t="s">
+      <c r="C151" s="95" t="s">
         <v>461</v>
       </c>
-      <c r="D151" s="93" t="s">
+      <c r="D151" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="E151" s="84" t="s">
+      <c r="E151" s="95" t="s">
         <v>462</v>
       </c>
-      <c r="F151" s="92">
+      <c r="F151" s="96">
         <v>125710000</v>
       </c>
-      <c r="G151" s="84" t="s">
+      <c r="G151" s="95" t="s">
         <v>9</v>
       </c>
       <c r="H151" s="84">

--- a/data/ton_chuanhap.xlsx
+++ b/data/ton_chuanhap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_Tonkho\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BD7705-297D-4976-AA80-7799B66551C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DB4F24-DDB0-4879-9389-5226ACD50BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="467">
   <si>
     <t>KV</t>
   </si>
@@ -1451,6 +1451,15 @@
   </si>
   <si>
     <t>Đã có hàng hệ thống</t>
+  </si>
+  <si>
+    <t>300501-GP&amp;DVKT/HĐMBLĐ-2026/PTO-BIATHUDO</t>
+  </si>
+  <si>
+    <t>LẮP ĐẶT HỆ THỐNG ĐIỆN NĂNG LƯỢNG MẶT TRỜI ÁP MÁI CÔNG SUẤT 213,28 kWp</t>
+  </si>
+  <si>
+    <t>Công ty CP thực phẩm và đồ uống Thủ đô</t>
   </si>
 </sst>
 </file>
@@ -1765,7 +1774,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1997,6 +2006,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2389,7 +2399,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F457DF4-8092-4544-B88B-9AF42554C254}">
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.375" customWidth="1"/>
@@ -8016,6 +8026,35 @@
       <c r="L151" s="84"/>
       <c r="M151" s="84"/>
     </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" s="97" t="s">
+        <v>464</v>
+      </c>
+      <c r="B152" s="97" t="s">
+        <v>48</v>
+      </c>
+      <c r="C152" s="97" t="s">
+        <v>465</v>
+      </c>
+      <c r="D152" s="97" t="s">
+        <v>36</v>
+      </c>
+      <c r="E152" s="97" t="s">
+        <v>466</v>
+      </c>
+      <c r="F152" s="97">
+        <v>1057743460</v>
+      </c>
+      <c r="G152" s="97" t="s">
+        <v>9</v>
+      </c>
+      <c r="H152">
+        <v>344</v>
+      </c>
+      <c r="I152" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M151" xr:uid="{1F457DF4-8092-4544-B88B-9AF42554C254}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/ton_chuanhap.xlsx
+++ b/data/ton_chuanhap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_Tonkho\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DB4F24-DDB0-4879-9389-5226ACD50BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783E65EA-DD97-44C2-BAB5-CB0EB861721E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C203BC54-74DB-473A-A6AA-C9BDC8E827D3}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="470">
   <si>
     <t>KV</t>
   </si>
@@ -1460,6 +1460,15 @@
   </si>
   <si>
     <t>Công ty CP thực phẩm và đồ uống Thủ đô</t>
+  </si>
+  <si>
+    <t>080601 /2026/TT-VT</t>
+  </si>
+  <si>
+    <t>lắp dặt hệ thống NLMT</t>
+  </si>
+  <si>
+    <t>Công ty TNHH dịch vụ quản lý điện nước thành tín</t>
   </si>
 </sst>
 </file>
@@ -1631,7 +1640,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1770,11 +1779,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1987,16 +2009,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -2004,9 +2016,16 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2399,7 +2418,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F457DF4-8092-4544-B88B-9AF42554C254}">
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.375" customWidth="1"/>
@@ -2459,27 +2478,27 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="82" t="s">
         <v>49</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89" t="s">
+      <c r="F2" s="83"/>
+      <c r="G2" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I2" s="83"/>
       <c r="J2" s="83" t="s">
@@ -2492,27 +2511,27 @@
       <c r="M2" s="83"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="82" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="88" t="s">
+      <c r="E3" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89" t="s">
+      <c r="F3" s="83"/>
+      <c r="G3" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H3" s="7">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="I3" s="83"/>
       <c r="J3" s="83" t="s">
@@ -2525,27 +2544,27 @@
       <c r="M3" s="83"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="84" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="88" t="s">
+      <c r="B4" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="88" t="s">
+      <c r="C4" s="82" t="s">
         <v>158</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="90" t="s">
+      <c r="E4" s="84" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89" t="s">
+      <c r="F4" s="83"/>
+      <c r="G4" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="7">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>70</v>
@@ -2562,27 +2581,27 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="82" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="88" t="s">
+      <c r="E5" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89" t="s">
+      <c r="F5" s="83"/>
+      <c r="G5" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H5" s="7">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I5" s="83"/>
       <c r="J5" s="83" t="s">
@@ -2597,27 +2616,27 @@
       <c r="M5" s="83"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C6" s="82" t="s">
         <v>63</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="88" t="s">
+      <c r="E6" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89" t="s">
+      <c r="F6" s="83"/>
+      <c r="G6" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H6" s="7">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="I6" s="83"/>
       <c r="J6" s="83" t="s">
@@ -2632,27 +2651,27 @@
       <c r="M6" s="83"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="88" t="s">
+      <c r="A7" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="88" t="s">
+      <c r="B7" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="88" t="s">
+      <c r="C7" s="82" t="s">
         <v>67</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="88" t="s">
+      <c r="E7" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="89"/>
-      <c r="G7" s="89" t="s">
+      <c r="F7" s="83"/>
+      <c r="G7" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H7" s="7">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="I7" s="83" t="s">
         <v>70</v>
@@ -2671,27 +2690,27 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="88" t="s">
+      <c r="C8" s="82" t="s">
         <v>73</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="88" t="s">
+      <c r="E8" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89" t="s">
+      <c r="F8" s="83"/>
+      <c r="G8" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H8" s="7">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I8" s="83"/>
       <c r="J8" s="83" t="s">
@@ -2708,33 +2727,33 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="88" t="s">
+      <c r="B9" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="82" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="88" t="s">
+      <c r="E9" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89" t="s">
+      <c r="F9" s="83"/>
+      <c r="G9" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H9" s="7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I9" s="83" t="s">
         <v>70</v>
       </c>
       <c r="J9" s="83" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="K9" s="83" t="s">
         <v>53</v>
@@ -2743,27 +2762,27 @@
       <c r="M9" s="83"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="88" t="s">
+      <c r="A10" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="82" t="s">
         <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="88" t="s">
+      <c r="E10" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89" t="s">
+      <c r="F10" s="83"/>
+      <c r="G10" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H10" s="7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I10" s="83" t="s">
         <v>70</v>
@@ -2778,23 +2797,23 @@
       <c r="M10" s="83"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="88" t="s">
+      <c r="A11" s="82" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="88" t="s">
+      <c r="B11" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="82" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="88" t="s">
+      <c r="E11" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="89"/>
-      <c r="G11" s="89" t="s">
+      <c r="F11" s="83"/>
+      <c r="G11" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H11" s="7">
@@ -2813,23 +2832,23 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="88" t="s">
+      <c r="A12" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="82" t="s">
         <v>89</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="88" t="s">
+      <c r="E12" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89" t="s">
+      <c r="F12" s="83"/>
+      <c r="G12" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H12" s="7">
@@ -2850,23 +2869,23 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="88" t="s">
+      <c r="B13" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="82" t="s">
         <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="91" t="s">
+      <c r="E13" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="89"/>
-      <c r="G13" s="89" t="s">
+      <c r="F13" s="83"/>
+      <c r="G13" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="7">
@@ -2887,27 +2906,27 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="88" t="s">
+      <c r="B14" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="82" t="s">
         <v>76</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="88" t="e">
+      <c r="E14" s="82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89" t="s">
+      <c r="F14" s="83"/>
+      <c r="G14" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H14" s="7">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I14" s="83"/>
       <c r="J14" s="83" t="s">
@@ -2920,27 +2939,27 @@
       <c r="M14" s="83"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="88" t="s">
+      <c r="B15" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="88" t="s">
+      <c r="C15" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="88" t="s">
+      <c r="E15" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89" t="s">
+      <c r="F15" s="83"/>
+      <c r="G15" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H15" s="7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I15" s="83"/>
       <c r="J15" s="83" t="s">
@@ -2953,27 +2972,27 @@
       <c r="M15" s="83"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="82" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="88" t="s">
+      <c r="B16" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="82" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="88" t="s">
+      <c r="E16" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89" t="s">
+      <c r="F16" s="83"/>
+      <c r="G16" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I16" s="83"/>
       <c r="J16" s="83" t="s">
@@ -2986,27 +3005,27 @@
       <c r="M16" s="83"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="88" t="s">
+      <c r="C17" s="82" t="s">
         <v>101</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="90" t="s">
+      <c r="E17" s="84" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="89"/>
-      <c r="G17" s="89" t="s">
+      <c r="F17" s="83"/>
+      <c r="G17" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H17" s="7">
-        <v>4876</v>
+        <v>0</v>
       </c>
       <c r="I17" s="83"/>
       <c r="J17" s="83" t="s">
@@ -3019,27 +3038,27 @@
       <c r="M17" s="83"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="88" t="s">
+      <c r="A18" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="82" t="s">
         <v>104</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="88" t="s">
+      <c r="E18" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89" t="s">
+      <c r="F18" s="83"/>
+      <c r="G18" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H18" s="7">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I18" s="83"/>
       <c r="J18" s="83" t="s">
@@ -3054,23 +3073,23 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="88" t="s">
+      <c r="A19" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="88" t="s">
+      <c r="B19" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C19" s="82" t="s">
         <v>107</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="88" t="s">
+      <c r="E19" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89" t="s">
+      <c r="F19" s="83"/>
+      <c r="G19" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H19" s="7">
@@ -3091,27 +3110,27 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="88" t="s">
+      <c r="C20" s="82" t="s">
         <v>110</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="88" t="s">
+      <c r="E20" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89" t="s">
+      <c r="F20" s="83"/>
+      <c r="G20" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H20" s="7">
-        <v>1218</v>
+        <v>0</v>
       </c>
       <c r="I20" s="83"/>
       <c r="J20" s="83" t="s">
@@ -3124,27 +3143,27 @@
       <c r="M20" s="83"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="88" t="s">
+      <c r="A21" s="82" t="s">
         <v>112</v>
       </c>
-      <c r="B21" s="88" t="s">
+      <c r="B21" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="88" t="s">
+      <c r="C21" s="82" t="s">
         <v>114</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="88" t="s">
+      <c r="E21" s="82" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89" t="s">
+      <c r="F21" s="83"/>
+      <c r="G21" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H21" s="7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I21" s="83" t="s">
         <v>70</v>
@@ -3161,27 +3180,27 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="88" t="s">
+      <c r="A22" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="88" t="s">
+      <c r="B22" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="88" t="s">
+      <c r="C22" s="82" t="s">
         <v>117</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="88" t="s">
+      <c r="E22" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89" t="s">
+      <c r="F22" s="83"/>
+      <c r="G22" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H22" s="7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I22" s="83" t="s">
         <v>70</v>
@@ -3200,27 +3219,27 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="88" t="s">
+      <c r="A23" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="B23" s="88" t="s">
+      <c r="B23" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="82" t="s">
         <v>120</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="88" t="s">
+      <c r="E23" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="F23" s="89"/>
-      <c r="G23" s="89" t="s">
+      <c r="F23" s="83"/>
+      <c r="G23" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H23" s="7">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="I23" s="83" t="s">
         <v>70</v>
@@ -3237,25 +3256,25 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="82" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="88" t="s">
+      <c r="B24" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="89"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="88" t="s">
+      <c r="E24" s="82" t="s">
         <v>123</v>
       </c>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89" t="s">
+      <c r="F24" s="83"/>
+      <c r="G24" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H24" s="7">
-        <v>1326</v>
+        <v>0</v>
       </c>
       <c r="I24" s="83" t="s">
         <v>70</v>
@@ -3274,27 +3293,27 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="88" t="s">
+      <c r="A25" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="88" t="s">
+      <c r="B25" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="88" t="s">
+      <c r="C25" s="82" t="s">
         <v>125</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="88" t="s">
+      <c r="E25" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="89"/>
-      <c r="G25" s="89" t="s">
+      <c r="F25" s="83"/>
+      <c r="G25" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H25" s="7">
-        <v>1626</v>
+        <v>0</v>
       </c>
       <c r="I25" s="83" t="s">
         <v>70</v>
@@ -3313,27 +3332,27 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="90" t="s">
+      <c r="A26" s="84" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="88" t="s">
+      <c r="B26" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="88" t="s">
+      <c r="C26" s="82" t="s">
         <v>128</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="90" t="s">
+      <c r="E26" s="84" t="s">
         <v>129</v>
       </c>
-      <c r="F26" s="89"/>
-      <c r="G26" s="89" t="s">
+      <c r="F26" s="83"/>
+      <c r="G26" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H26" s="7">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="I26" s="83" t="s">
         <v>70</v>
@@ -3352,27 +3371,27 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="82" t="s">
         <v>132</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="88" t="s">
+      <c r="E27" s="82" t="s">
         <v>133</v>
       </c>
-      <c r="F27" s="89"/>
-      <c r="G27" s="89" t="s">
+      <c r="F27" s="83"/>
+      <c r="G27" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H27" s="7">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I27" s="83" t="s">
         <v>70</v>
@@ -3389,27 +3408,27 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="88" t="s">
+      <c r="A28" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="88" t="s">
+      <c r="C28" s="82" t="s">
         <v>135</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="88" t="s">
+      <c r="E28" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89" t="s">
+      <c r="F28" s="83"/>
+      <c r="G28" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H28" s="7">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="I28" s="83" t="s">
         <v>70</v>
@@ -3426,27 +3445,27 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="88" t="s">
+      <c r="A29" s="82" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="88" t="s">
+      <c r="B29" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="88" t="s">
+      <c r="C29" s="82" t="s">
         <v>138</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="88" t="s">
+      <c r="E29" s="82" t="s">
         <v>139</v>
       </c>
-      <c r="F29" s="89"/>
-      <c r="G29" s="89" t="s">
+      <c r="F29" s="83"/>
+      <c r="G29" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H29" s="7">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I29" s="83" t="s">
         <v>70</v>
@@ -3463,27 +3482,27 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="88" t="s">
+      <c r="A30" s="82" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="88" t="s">
+      <c r="B30" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="88" t="s">
+      <c r="C30" s="82" t="s">
         <v>142</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="88" t="s">
+      <c r="E30" s="82" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89" t="s">
+      <c r="F30" s="83"/>
+      <c r="G30" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H30" s="7">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I30" s="83" t="s">
         <v>70</v>
@@ -3502,27 +3521,27 @@
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="88" t="s">
+      <c r="A31" s="82" t="s">
         <v>145</v>
       </c>
-      <c r="B31" s="88" t="s">
+      <c r="B31" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C31" s="88" t="s">
+      <c r="C31" s="82" t="s">
         <v>146</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="88" t="s">
+      <c r="E31" s="82" t="s">
         <v>147</v>
       </c>
-      <c r="F31" s="89"/>
-      <c r="G31" s="89" t="s">
+      <c r="F31" s="83"/>
+      <c r="G31" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H31" s="7">
-        <v>1511</v>
+        <v>0</v>
       </c>
       <c r="I31" s="83" t="s">
         <v>70</v>
@@ -3539,27 +3558,27 @@
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="88" t="s">
+      <c r="A32" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="B32" s="88" t="s">
+      <c r="B32" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C32" s="88" t="s">
+      <c r="C32" s="82" t="s">
         <v>149</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="88" t="s">
+      <c r="E32" s="82" t="s">
         <v>150</v>
       </c>
-      <c r="F32" s="89"/>
-      <c r="G32" s="89" t="s">
+      <c r="F32" s="83"/>
+      <c r="G32" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="7">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="I32" s="83" t="s">
         <v>70</v>
@@ -3576,27 +3595,27 @@
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="88" t="s">
+      <c r="A33" s="82" t="s">
         <v>151</v>
       </c>
-      <c r="B33" s="88" t="s">
+      <c r="B33" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="88" t="s">
+      <c r="C33" s="82" t="s">
         <v>152</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="88" t="s">
+      <c r="E33" s="82" t="s">
         <v>153</v>
       </c>
-      <c r="F33" s="89"/>
-      <c r="G33" s="89" t="s">
+      <c r="F33" s="83"/>
+      <c r="G33" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H33" s="7">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="I33" s="83" t="s">
         <v>70</v>
@@ -3615,27 +3634,27 @@
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="90" t="s">
+      <c r="A34" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="B34" s="88" t="s">
+      <c r="B34" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="82" t="s">
         <v>155</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="90" t="s">
+      <c r="E34" s="84" t="s">
         <v>156</v>
       </c>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89" t="s">
+      <c r="F34" s="83"/>
+      <c r="G34" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H34" s="7">
-        <v>1704</v>
+        <v>0</v>
       </c>
       <c r="I34" s="83" t="s">
         <v>70</v>
@@ -3652,27 +3671,27 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="90" t="s">
+      <c r="A35" s="84" t="s">
         <v>160</v>
       </c>
-      <c r="B35" s="88" t="s">
+      <c r="B35" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="88" t="s">
+      <c r="C35" s="82" t="s">
         <v>161</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="90" t="s">
+      <c r="E35" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89" t="s">
+      <c r="F35" s="83"/>
+      <c r="G35" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H35" s="7">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I35" s="83" t="s">
         <v>70</v>
@@ -3689,27 +3708,27 @@
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="88" t="s">
+      <c r="A36" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="88" t="s">
+      <c r="B36" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="88" t="s">
+      <c r="C36" s="82" t="s">
         <v>164</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E36" s="88" t="s">
+      <c r="E36" s="82" t="s">
         <v>156</v>
       </c>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89" t="s">
+      <c r="F36" s="83"/>
+      <c r="G36" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H36" s="7">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="I36" s="83" t="s">
         <v>70</v>
@@ -3726,27 +3745,27 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="88" t="s">
+      <c r="A37" s="82" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="88" t="s">
+      <c r="B37" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="88" t="s">
+      <c r="C37" s="82" t="s">
         <v>164</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E37" s="88" t="s">
+      <c r="E37" s="82" t="s">
         <v>166</v>
       </c>
-      <c r="F37" s="89"/>
-      <c r="G37" s="89" t="s">
+      <c r="F37" s="83"/>
+      <c r="G37" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H37" s="7">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="I37" s="83" t="s">
         <v>167</v>
@@ -3763,27 +3782,27 @@
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="88">
+      <c r="A38" s="82">
         <v>20251678</v>
       </c>
-      <c r="B38" s="88" t="s">
+      <c r="B38" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C38" s="88" t="s">
+      <c r="C38" s="82" t="s">
         <v>168</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E38" s="88" t="s">
+      <c r="E38" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89" t="s">
+      <c r="F38" s="83"/>
+      <c r="G38" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H38" s="7">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="I38" s="83" t="s">
         <v>70</v>
@@ -3802,27 +3821,27 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="88" t="s">
+      <c r="A39" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B39" s="88" t="s">
+      <c r="B39" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="88" t="s">
+      <c r="C39" s="82" t="s">
         <v>171</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="88" t="s">
+      <c r="E39" s="82" t="s">
         <v>172</v>
       </c>
-      <c r="F39" s="89"/>
-      <c r="G39" s="89" t="s">
+      <c r="F39" s="83"/>
+      <c r="G39" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H39" s="7">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="I39" s="83" t="s">
         <v>70</v>
@@ -3841,27 +3860,27 @@
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="88" t="s">
+      <c r="A40" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C40" s="88" t="s">
+      <c r="C40" s="82" t="s">
         <v>174</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E40" s="88" t="s">
+      <c r="E40" s="82" t="s">
         <v>175</v>
       </c>
-      <c r="F40" s="89"/>
-      <c r="G40" s="89" t="s">
+      <c r="F40" s="83"/>
+      <c r="G40" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H40" s="7">
-        <v>1229</v>
+        <v>0</v>
       </c>
       <c r="I40" s="83" t="s">
         <v>70</v>
@@ -3878,27 +3897,27 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="88" t="s">
+      <c r="A41" s="82" t="s">
         <v>176</v>
       </c>
-      <c r="B41" s="88" t="s">
+      <c r="B41" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="88" t="s">
+      <c r="C41" s="82" t="s">
         <v>177</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E41" s="88">
-        <v>0</v>
-      </c>
-      <c r="F41" s="89"/>
-      <c r="G41" s="89" t="s">
+      <c r="E41" s="82">
+        <v>0</v>
+      </c>
+      <c r="F41" s="83"/>
+      <c r="G41" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H41" s="7">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I41" s="83" t="s">
         <v>70</v>
@@ -3915,27 +3934,27 @@
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="88" t="s">
+      <c r="A42" s="82" t="s">
         <v>178</v>
       </c>
-      <c r="B42" s="88" t="s">
+      <c r="B42" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="88" t="s">
+      <c r="C42" s="82" t="s">
         <v>179</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="88" t="e">
+      <c r="E42" s="82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="F42" s="89"/>
-      <c r="G42" s="89" t="s">
+      <c r="F42" s="83"/>
+      <c r="G42" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H42" s="7">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I42" s="83" t="s">
         <v>70</v>
@@ -3954,27 +3973,27 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="88" t="s">
+      <c r="A43" s="82" t="s">
         <v>180</v>
       </c>
-      <c r="B43" s="88" t="s">
+      <c r="B43" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C43" s="88" t="s">
+      <c r="C43" s="82" t="s">
         <v>181</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="88" t="s">
+      <c r="E43" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="F43" s="89"/>
-      <c r="G43" s="89" t="s">
+      <c r="F43" s="83"/>
+      <c r="G43" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H43" s="7">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="I43" s="83" t="s">
         <v>70</v>
@@ -3993,27 +4012,27 @@
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="88" t="s">
+      <c r="A44" s="82" t="s">
         <v>183</v>
       </c>
-      <c r="B44" s="88" t="s">
+      <c r="B44" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="88" t="s">
+      <c r="C44" s="82" t="s">
         <v>184</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="88" t="s">
+      <c r="E44" s="82" t="s">
         <v>185</v>
       </c>
-      <c r="F44" s="89"/>
-      <c r="G44" s="89" t="s">
+      <c r="F44" s="83"/>
+      <c r="G44" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H44" s="7">
-        <v>1542</v>
+        <v>0</v>
       </c>
       <c r="I44" s="83" t="s">
         <v>70</v>
@@ -4030,27 +4049,27 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="88" t="s">
+      <c r="A45" s="82" t="s">
         <v>186</v>
       </c>
-      <c r="B45" s="88" t="s">
+      <c r="B45" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C45" s="88" t="s">
+      <c r="C45" s="82" t="s">
         <v>187</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="88" t="s">
+      <c r="E45" s="82" t="s">
         <v>188</v>
       </c>
-      <c r="F45" s="89"/>
-      <c r="G45" s="89" t="s">
+      <c r="F45" s="83"/>
+      <c r="G45" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H45" s="7">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="I45" s="83" t="s">
         <v>70</v>
@@ -4069,27 +4088,27 @@
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="88" t="s">
+      <c r="A46" s="82" t="s">
         <v>189</v>
       </c>
-      <c r="B46" s="88" t="s">
+      <c r="B46" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="88" t="s">
+      <c r="C46" s="82" t="s">
         <v>190</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="88" t="s">
+      <c r="E46" s="82" t="s">
         <v>191</v>
       </c>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89" t="s">
+      <c r="F46" s="83"/>
+      <c r="G46" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H46" s="7">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="I46" s="83"/>
       <c r="J46" s="83" t="s">
@@ -4102,27 +4121,27 @@
       <c r="M46" s="83"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="90" t="s">
+      <c r="A47" s="84" t="s">
         <v>192</v>
       </c>
-      <c r="B47" s="88" t="s">
+      <c r="B47" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="88" t="s">
+      <c r="C47" s="82" t="s">
         <v>193</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="90" t="s">
+      <c r="E47" s="84" t="s">
         <v>194</v>
       </c>
-      <c r="F47" s="89"/>
-      <c r="G47" s="89" t="s">
+      <c r="F47" s="83"/>
+      <c r="G47" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H47" s="7">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="I47" s="83"/>
       <c r="J47" s="83" t="s">
@@ -4137,25 +4156,25 @@
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="88" t="s">
+      <c r="A48" s="82" t="s">
         <v>195</v>
       </c>
-      <c r="B48" s="88" t="s">
+      <c r="B48" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="89"/>
+      <c r="C48" s="83"/>
       <c r="D48" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="88" t="s">
+      <c r="E48" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="F48" s="89"/>
-      <c r="G48" s="89" t="s">
+      <c r="F48" s="83"/>
+      <c r="G48" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H48" s="7">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="I48" s="83"/>
       <c r="J48" s="83" t="s">
@@ -4170,27 +4189,27 @@
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="88" t="s">
+      <c r="A49" s="82" t="s">
         <v>197</v>
       </c>
-      <c r="B49" s="88" t="s">
+      <c r="B49" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="88" t="s">
+      <c r="C49" s="82" t="s">
         <v>198</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="88" t="s">
+      <c r="E49" s="82" t="s">
         <v>199</v>
       </c>
-      <c r="F49" s="89"/>
-      <c r="G49" s="89" t="s">
+      <c r="F49" s="83"/>
+      <c r="G49" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H49" s="7">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="I49" s="83"/>
       <c r="J49" s="83" t="s">
@@ -4205,27 +4224,27 @@
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="88" t="s">
+      <c r="A50" s="82" t="s">
         <v>200</v>
       </c>
-      <c r="B50" s="88" t="s">
+      <c r="B50" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="88" t="s">
+      <c r="C50" s="82" t="s">
         <v>201</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E50" s="88" t="s">
+      <c r="E50" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="F50" s="89"/>
-      <c r="G50" s="89" t="s">
+      <c r="F50" s="83"/>
+      <c r="G50" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H50" s="7">
-        <v>2617</v>
+        <v>0</v>
       </c>
       <c r="I50" s="83"/>
       <c r="J50" s="83" t="s">
@@ -4242,27 +4261,27 @@
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="88" t="s">
+      <c r="A51" s="82" t="s">
         <v>203</v>
       </c>
-      <c r="B51" s="88" t="s">
+      <c r="B51" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="88" t="s">
+      <c r="C51" s="82" t="s">
         <v>204</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="88" t="s">
+      <c r="E51" s="82" t="s">
         <v>205</v>
       </c>
-      <c r="F51" s="89"/>
-      <c r="G51" s="89" t="s">
+      <c r="F51" s="83"/>
+      <c r="G51" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H51" s="7">
-        <v>6768</v>
+        <v>0</v>
       </c>
       <c r="I51" s="83" t="s">
         <v>70</v>
@@ -4279,27 +4298,27 @@
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="88" t="s">
+      <c r="A52" s="82" t="s">
         <v>206</v>
       </c>
-      <c r="B52" s="88" t="s">
+      <c r="B52" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="88" t="s">
+      <c r="C52" s="82" t="s">
         <v>207</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="88" t="s">
+      <c r="E52" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="89"/>
-      <c r="G52" s="89" t="s">
+      <c r="F52" s="83"/>
+      <c r="G52" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H52" s="7">
-        <v>1625</v>
+        <v>0</v>
       </c>
       <c r="I52" s="83"/>
       <c r="J52" s="83" t="s">
@@ -4316,27 +4335,27 @@
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="88" t="s">
+      <c r="A53" s="82" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="88" t="s">
+      <c r="B53" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="88" t="s">
+      <c r="C53" s="82" t="s">
         <v>210</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E53" s="88" t="s">
+      <c r="E53" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F53" s="89"/>
-      <c r="G53" s="89" t="s">
+      <c r="F53" s="83"/>
+      <c r="G53" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H53" s="7">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="I53" s="83"/>
       <c r="J53" s="83" t="s">
@@ -4351,25 +4370,25 @@
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="88" t="s">
+      <c r="A54" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="B54" s="88" t="s">
+      <c r="B54" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="89"/>
+      <c r="C54" s="83"/>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E54" s="88" t="s">
+      <c r="E54" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="F54" s="89"/>
-      <c r="G54" s="89" t="s">
+      <c r="F54" s="83"/>
+      <c r="G54" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H54" s="7">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="I54" s="83"/>
       <c r="J54" s="83" t="s">
@@ -4384,27 +4403,27 @@
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="88" t="s">
+      <c r="A55" s="82" t="s">
         <v>214</v>
       </c>
-      <c r="B55" s="88" t="s">
+      <c r="B55" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="88" t="s">
+      <c r="C55" s="82" t="s">
         <v>215</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E55" s="88" t="s">
+      <c r="E55" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="F55" s="89"/>
-      <c r="G55" s="89" t="s">
+      <c r="F55" s="83"/>
+      <c r="G55" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H55" s="7">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="I55" s="83"/>
       <c r="J55" s="83" t="s">
@@ -4417,25 +4436,25 @@
       <c r="M55" s="83"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="88" t="s">
+      <c r="A56" s="82" t="s">
         <v>217</v>
       </c>
-      <c r="B56" s="88" t="s">
+      <c r="B56" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="89"/>
+      <c r="C56" s="83"/>
       <c r="D56" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="88" t="s">
+      <c r="E56" s="82" t="s">
         <v>218</v>
       </c>
-      <c r="F56" s="89"/>
-      <c r="G56" s="89" t="s">
+      <c r="F56" s="83"/>
+      <c r="G56" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H56" s="7">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="I56" s="83"/>
       <c r="J56" s="83" t="s">
@@ -4448,27 +4467,27 @@
       <c r="M56" s="83"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="88" t="s">
+      <c r="A57" s="82" t="s">
         <v>219</v>
       </c>
-      <c r="B57" s="88" t="s">
+      <c r="B57" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="88" t="s">
+      <c r="C57" s="82" t="s">
         <v>220</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E57" s="88" t="s">
+      <c r="E57" s="82" t="s">
         <v>221</v>
       </c>
-      <c r="F57" s="89"/>
-      <c r="G57" s="89" t="s">
+      <c r="F57" s="83"/>
+      <c r="G57" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H57" s="7">
-        <v>1286</v>
+        <v>0</v>
       </c>
       <c r="I57" s="83"/>
       <c r="J57" s="83" t="s">
@@ -4483,27 +4502,27 @@
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="88" t="s">
+      <c r="A58" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="B58" s="88" t="s">
+      <c r="B58" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="88" t="s">
+      <c r="C58" s="82" t="s">
         <v>76</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E58" s="88" t="s">
+      <c r="E58" s="82" t="s">
         <v>223</v>
       </c>
-      <c r="F58" s="89"/>
-      <c r="G58" s="89" t="s">
+      <c r="F58" s="83"/>
+      <c r="G58" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H58" s="7">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I58" s="83"/>
       <c r="J58" s="83" t="s">
@@ -4518,27 +4537,27 @@
       <c r="M58" s="83"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="92" t="s">
+      <c r="A59" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="B59" s="88" t="s">
+      <c r="B59" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C59" s="88" t="s">
+      <c r="C59" s="82" t="s">
         <v>225</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="88" t="s">
+      <c r="E59" s="82" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="89"/>
-      <c r="G59" s="89" t="s">
+      <c r="F59" s="83"/>
+      <c r="G59" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H59" s="7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I59" s="83"/>
       <c r="J59" s="83" t="s">
@@ -4553,27 +4572,27 @@
       <c r="M59" s="83"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="92" t="s">
+      <c r="A60" s="86" t="s">
         <v>228</v>
       </c>
-      <c r="B60" s="88" t="s">
+      <c r="B60" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C60" s="88" t="s">
+      <c r="C60" s="82" t="s">
         <v>229</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="88" t="s">
+      <c r="E60" s="82" t="s">
         <v>230</v>
       </c>
-      <c r="F60" s="89"/>
-      <c r="G60" s="89" t="s">
+      <c r="F60" s="83"/>
+      <c r="G60" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H60" s="7">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="I60" s="83"/>
       <c r="J60" s="83" t="s">
@@ -4588,27 +4607,27 @@
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="88" t="s">
+      <c r="A61" s="86" t="s">
         <v>228</v>
       </c>
-      <c r="B61" s="88" t="s">
+      <c r="B61" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="88" t="s">
+      <c r="C61" s="82" t="s">
         <v>229</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="88" t="s">
+      <c r="E61" s="82" t="s">
         <v>230</v>
       </c>
-      <c r="F61" s="89"/>
-      <c r="G61" s="89" t="s">
+      <c r="F61" s="83"/>
+      <c r="G61" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H61" s="7">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I61" s="83"/>
       <c r="J61" s="83" t="s">
@@ -4623,27 +4642,27 @@
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="88" t="s">
+      <c r="A62" s="82" t="s">
         <v>231</v>
       </c>
-      <c r="B62" s="88" t="s">
+      <c r="B62" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="88" t="s">
+      <c r="C62" s="82" t="s">
         <v>232</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E62" s="88" t="s">
+      <c r="E62" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="F62" s="89"/>
-      <c r="G62" s="89" t="s">
+      <c r="F62" s="83"/>
+      <c r="G62" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H62" s="7">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="I62" s="83"/>
       <c r="J62" s="83" t="s">
@@ -4660,27 +4679,27 @@
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63" s="88" t="s">
+      <c r="A63" s="82" t="s">
         <v>233</v>
       </c>
-      <c r="B63" s="88" t="s">
+      <c r="B63" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="88" t="s">
+      <c r="C63" s="82" t="s">
         <v>234</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="88" t="s">
+      <c r="E63" s="82" t="s">
         <v>235</v>
       </c>
-      <c r="F63" s="89"/>
-      <c r="G63" s="89" t="s">
+      <c r="F63" s="83"/>
+      <c r="G63" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H63" s="7">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="I63" s="83" t="s">
         <v>70</v>
@@ -4699,27 +4718,27 @@
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="90" t="s">
+      <c r="A64" s="84" t="s">
         <v>236</v>
       </c>
-      <c r="B64" s="88" t="s">
+      <c r="B64" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="88" t="s">
+      <c r="C64" s="82" t="s">
         <v>237</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="90" t="s">
+      <c r="E64" s="84" t="s">
         <v>238</v>
       </c>
-      <c r="F64" s="89"/>
-      <c r="G64" s="89" t="s">
+      <c r="F64" s="83"/>
+      <c r="G64" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H64" s="7">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="I64" s="83" t="s">
         <v>70</v>
@@ -4738,27 +4757,27 @@
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="88" t="s">
+      <c r="A65" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="B65" s="88" t="s">
+      <c r="B65" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C65" s="88" t="s">
+      <c r="C65" s="82" t="s">
         <v>241</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E65" s="88" t="s">
+      <c r="E65" s="82" t="s">
         <v>242</v>
       </c>
-      <c r="F65" s="89"/>
-      <c r="G65" s="89" t="s">
+      <c r="F65" s="83"/>
+      <c r="G65" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H65" s="7">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="I65" s="83" t="s">
         <v>70</v>
@@ -4775,27 +4794,27 @@
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="88" t="s">
+      <c r="A66" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="B66" s="88" t="s">
+      <c r="B66" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="88" t="s">
+      <c r="C66" s="82" t="s">
         <v>244</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E66" s="88" t="s">
+      <c r="E66" s="82" t="s">
         <v>245</v>
       </c>
-      <c r="F66" s="89"/>
-      <c r="G66" s="89" t="s">
+      <c r="F66" s="83"/>
+      <c r="G66" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H66" s="7">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="I66" s="83" t="s">
         <v>70</v>
@@ -4812,27 +4831,27 @@
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="88" t="s">
+      <c r="A67" s="82" t="s">
         <v>246</v>
       </c>
-      <c r="B67" s="88" t="s">
+      <c r="B67" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="88" t="s">
+      <c r="C67" s="82" t="s">
         <v>247</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E67" s="88" t="s">
+      <c r="E67" s="82" t="s">
         <v>248</v>
       </c>
-      <c r="F67" s="89"/>
-      <c r="G67" s="89" t="s">
+      <c r="F67" s="83"/>
+      <c r="G67" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H67" s="7">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="I67" s="83" t="s">
         <v>70</v>
@@ -4851,23 +4870,23 @@
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>249</v>
       </c>
-      <c r="B68" s="88" t="s">
+      <c r="B68" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C68" s="88" t="s">
+      <c r="C68" s="82" t="s">
         <v>250</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E68" s="88" t="s">
+      <c r="E68" s="82" t="s">
         <v>251</v>
       </c>
-      <c r="F68" s="89"/>
-      <c r="G68" s="89" t="s">
+      <c r="F68" s="83"/>
+      <c r="G68" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H68" s="7">
@@ -4888,27 +4907,27 @@
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="90" t="s">
+      <c r="A69" s="84" t="s">
         <v>252</v>
       </c>
-      <c r="B69" s="88" t="s">
+      <c r="B69" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C69" s="88" t="s">
+      <c r="C69" s="82" t="s">
         <v>253</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="90" t="s">
+      <c r="E69" s="84" t="s">
         <v>248</v>
       </c>
-      <c r="F69" s="89"/>
-      <c r="G69" s="89" t="s">
+      <c r="F69" s="83"/>
+      <c r="G69" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H69" s="7">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="I69" s="83" t="s">
         <v>70</v>
@@ -4925,27 +4944,27 @@
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="88" t="s">
+      <c r="A70" s="82" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="88" t="s">
+      <c r="B70" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C70" s="88" t="s">
+      <c r="C70" s="82" t="s">
         <v>255</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="88" t="s">
+      <c r="E70" s="82" t="s">
         <v>256</v>
       </c>
-      <c r="F70" s="89"/>
-      <c r="G70" s="89" t="s">
+      <c r="F70" s="83"/>
+      <c r="G70" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H70" s="7">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="I70" s="83" t="s">
         <v>70</v>
@@ -4962,27 +4981,27 @@
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="88" t="s">
+      <c r="A71" s="82" t="s">
         <v>257</v>
       </c>
-      <c r="B71" s="88" t="s">
+      <c r="B71" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C71" s="88" t="s">
+      <c r="C71" s="82" t="s">
         <v>258</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E71" s="88" t="s">
+      <c r="E71" s="82" t="s">
         <v>259</v>
       </c>
-      <c r="F71" s="89"/>
-      <c r="G71" s="89" t="s">
+      <c r="F71" s="83"/>
+      <c r="G71" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H71" s="7">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="I71" s="83" t="s">
         <v>70</v>
@@ -4999,23 +5018,23 @@
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="88" t="s">
+      <c r="A72" s="82" t="s">
         <v>260</v>
       </c>
-      <c r="B72" s="88" t="s">
+      <c r="B72" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C72" s="88" t="s">
+      <c r="C72" s="82" t="s">
         <v>261</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E72" s="88" t="s">
+      <c r="E72" s="82" t="s">
         <v>262</v>
       </c>
-      <c r="F72" s="89"/>
-      <c r="G72" s="89" t="s">
+      <c r="F72" s="83"/>
+      <c r="G72" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H72" s="7">
@@ -5036,27 +5055,27 @@
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="88" t="s">
+      <c r="A73" s="82" t="s">
         <v>264</v>
       </c>
-      <c r="B73" s="88" t="s">
+      <c r="B73" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C73" s="88" t="s">
+      <c r="C73" s="82" t="s">
         <v>265</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E73" s="88" t="s">
+      <c r="E73" s="82" t="s">
         <v>266</v>
       </c>
-      <c r="F73" s="89"/>
-      <c r="G73" s="89" t="s">
+      <c r="F73" s="83"/>
+      <c r="G73" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H73" s="7">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I73" s="83" t="s">
         <v>70</v>
@@ -5075,27 +5094,27 @@
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="88" t="s">
+      <c r="A74" s="82" t="s">
         <v>267</v>
       </c>
-      <c r="B74" s="88" t="s">
+      <c r="B74" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C74" s="88" t="s">
+      <c r="C74" s="82" t="s">
         <v>268</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E74" s="88" t="s">
+      <c r="E74" s="82" t="s">
         <v>269</v>
       </c>
-      <c r="F74" s="89"/>
-      <c r="G74" s="89" t="s">
+      <c r="F74" s="83"/>
+      <c r="G74" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H74" s="7">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="I74" s="83" t="s">
         <v>167</v>
@@ -5112,27 +5131,27 @@
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="88" t="s">
+      <c r="A75" s="82" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="88" t="s">
+      <c r="B75" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C75" s="88" t="s">
+      <c r="C75" s="82" t="s">
         <v>271</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E75" s="88" t="s">
+      <c r="E75" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="F75" s="89"/>
-      <c r="G75" s="89" t="s">
+      <c r="F75" s="83"/>
+      <c r="G75" s="92" t="s">
         <v>51</v>
       </c>
       <c r="H75" s="7">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I75" s="83" t="s">
         <v>70</v>
@@ -5149,27 +5168,27 @@
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="84" t="s">
         <v>273</v>
       </c>
-      <c r="B76" s="88" t="s">
+      <c r="B76" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="88" t="s">
+      <c r="C76" s="82" t="s">
         <v>274</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="90" t="s">
+      <c r="E76" s="84" t="s">
         <v>275</v>
       </c>
-      <c r="F76" s="89"/>
-      <c r="G76" s="89" t="s">
+      <c r="F76" s="83"/>
+      <c r="G76" s="92" t="s">
         <v>69</v>
       </c>
       <c r="H76" s="7">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="I76" s="83" t="s">
         <v>70</v>
@@ -5188,352 +5207,352 @@
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="93" t="s">
+      <c r="A77" s="87" t="s">
         <v>276</v>
       </c>
-      <c r="B77" s="93" t="s">
+      <c r="B77" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C77" s="93" t="s">
+      <c r="C77" s="87" t="s">
         <v>277</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E77" s="93" t="s">
+      <c r="E77" s="87" t="s">
         <v>278</v>
       </c>
-      <c r="F77" s="89"/>
+      <c r="F77" s="83"/>
       <c r="G77" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H77" s="7">
-        <v>408</v>
-      </c>
-      <c r="I77" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I77" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J77" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K77" s="85" t="s">
+      <c r="J77" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K77" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L77" s="83"/>
-      <c r="M77" s="85" t="s">
+      <c r="M77" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="93" t="s">
+      <c r="A78" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="B78" s="93" t="s">
+      <c r="B78" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C78" s="93" t="s">
+      <c r="C78" s="87" t="s">
         <v>280</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E78" s="93" t="s">
+      <c r="E78" s="87" t="s">
         <v>281</v>
       </c>
-      <c r="F78" s="89"/>
+      <c r="F78" s="83"/>
       <c r="G78" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H78" s="7">
-        <v>832</v>
-      </c>
-      <c r="I78" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I78" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J78" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K78" s="85" t="s">
+      <c r="J78" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K78" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L78" s="83"/>
-      <c r="M78" s="85" t="s">
+      <c r="M78" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="93" t="s">
+      <c r="A79" s="87" t="s">
         <v>282</v>
       </c>
-      <c r="B79" s="93" t="s">
+      <c r="B79" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C79" s="93" t="s">
+      <c r="C79" s="87" t="s">
         <v>76</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E79" s="93" t="s">
+      <c r="E79" s="87" t="s">
         <v>283</v>
       </c>
-      <c r="F79" s="89"/>
+      <c r="F79" s="83"/>
       <c r="G79" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H79" s="7">
-        <v>450</v>
-      </c>
-      <c r="I79" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I79" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J79" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K79" s="85" t="s">
+      <c r="J79" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K79" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L79" s="83"/>
-      <c r="M79" s="85" t="s">
+      <c r="M79" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="93" t="s">
+      <c r="A80" s="87" t="s">
         <v>284</v>
       </c>
-      <c r="B80" s="93" t="s">
+      <c r="B80" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C80" s="93" t="s">
+      <c r="C80" s="87" t="s">
         <v>285</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E80" s="93" t="s">
+      <c r="E80" s="87" t="s">
         <v>286</v>
       </c>
-      <c r="F80" s="89"/>
+      <c r="F80" s="83"/>
       <c r="G80" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H80" s="7">
-        <v>312</v>
-      </c>
-      <c r="I80" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I80" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J80" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K80" s="85" t="s">
+      <c r="J80" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K80" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L80" s="83"/>
-      <c r="M80" s="85" t="s">
+      <c r="M80" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="93" t="s">
+      <c r="A81" s="87" t="s">
         <v>287</v>
       </c>
-      <c r="B81" s="93" t="s">
+      <c r="B81" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C81" s="93" t="s">
+      <c r="C81" s="87" t="s">
         <v>288</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E81" s="93" t="s">
+      <c r="E81" s="87" t="s">
         <v>289</v>
       </c>
-      <c r="F81" s="89"/>
+      <c r="F81" s="83"/>
       <c r="G81" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H81" s="7">
-        <v>387</v>
-      </c>
-      <c r="I81" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I81" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J81" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K81" s="85" t="s">
+      <c r="J81" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K81" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L81" s="83"/>
-      <c r="M81" s="85" t="s">
+      <c r="M81" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="93" t="s">
+      <c r="A82" s="87" t="s">
         <v>290</v>
       </c>
-      <c r="B82" s="93" t="s">
+      <c r="B82" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="93" t="s">
+      <c r="C82" s="87" t="s">
         <v>291</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E82" s="93" t="s">
+      <c r="E82" s="87" t="s">
         <v>292</v>
       </c>
-      <c r="F82" s="89"/>
+      <c r="F82" s="83"/>
       <c r="G82" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H82" s="7">
-        <v>1400</v>
-      </c>
-      <c r="I82" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I82" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J82" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K82" s="85" t="s">
+      <c r="J82" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K82" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L82" s="83"/>
-      <c r="M82" s="85" t="s">
+      <c r="M82" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="93" t="s">
+      <c r="A83" s="87" t="s">
         <v>293</v>
       </c>
-      <c r="B83" s="93" t="s">
+      <c r="B83" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C83" s="93" t="s">
+      <c r="C83" s="87" t="s">
         <v>294</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E83" s="93" t="s">
+      <c r="E83" s="87" t="s">
         <v>295</v>
       </c>
-      <c r="F83" s="89"/>
+      <c r="F83" s="83"/>
       <c r="G83" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H83" s="7">
-        <v>720</v>
-      </c>
-      <c r="I83" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I83" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J83" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K83" s="86" t="s">
+      <c r="J83" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K83" s="94" t="s">
         <v>53</v>
       </c>
       <c r="L83" s="83"/>
-      <c r="M83" s="85" t="s">
+      <c r="M83" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="87" t="s">
         <v>296</v>
       </c>
-      <c r="B84" s="93" t="s">
+      <c r="B84" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C84" s="93" t="s">
+      <c r="C84" s="87" t="s">
         <v>297</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="93" t="s">
+      <c r="E84" s="87" t="s">
         <v>298</v>
       </c>
-      <c r="F84" s="89"/>
+      <c r="F84" s="83"/>
       <c r="G84" s="93" t="s">
         <v>1</v>
       </c>
       <c r="H84" s="7">
-        <v>219</v>
-      </c>
-      <c r="I84" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I84" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J84" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K84" s="85" t="s">
+      <c r="J84" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K84" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L84" s="83"/>
-      <c r="M84" s="85" t="s">
+      <c r="M84" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="93" t="s">
+      <c r="A85" s="87" t="s">
         <v>299</v>
       </c>
-      <c r="B85" s="93" t="s">
+      <c r="B85" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="93" t="s">
+      <c r="C85" s="87" t="s">
         <v>300</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="93" t="s">
+      <c r="E85" s="87" t="s">
         <v>301</v>
       </c>
-      <c r="F85" s="89"/>
+      <c r="F85" s="83"/>
       <c r="G85" s="93" t="s">
         <v>87</v>
       </c>
       <c r="H85" s="7">
-        <v>1524</v>
-      </c>
-      <c r="I85" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I85" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="J85" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K85" s="85" t="s">
+      <c r="J85" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K85" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L85" s="83"/>
-      <c r="M85" s="85" t="s">
+      <c r="M85" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="93" t="s">
+      <c r="A86" s="87" t="s">
         <v>302</v>
       </c>
-      <c r="B86" s="93" t="s">
+      <c r="B86" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C86" s="93" t="s">
+      <c r="C86" s="87" t="s">
         <v>303</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="93" t="s">
+      <c r="E86" s="87" t="s">
         <v>304</v>
       </c>
       <c r="F86" s="10">
@@ -5543,36 +5562,36 @@
         <v>1</v>
       </c>
       <c r="H86" s="7">
-        <v>320</v>
-      </c>
-      <c r="I86" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I86" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J86" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K86" s="85" t="s">
+      <c r="J86" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K86" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L86" s="83"/>
-      <c r="M86" s="85" t="s">
+      <c r="M86" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="93" t="s">
+      <c r="A87" s="87" t="s">
         <v>305</v>
       </c>
-      <c r="B87" s="93" t="s">
+      <c r="B87" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C87" s="93" t="s">
+      <c r="C87" s="87" t="s">
         <v>306</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E87" s="93" t="s">
+      <c r="E87" s="87" t="s">
         <v>202</v>
       </c>
       <c r="F87" s="10">
@@ -5582,36 +5601,36 @@
         <v>1</v>
       </c>
       <c r="H87" s="7">
-        <v>2342</v>
-      </c>
-      <c r="I87" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I87" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J87" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K87" s="85" t="s">
+      <c r="J87" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K87" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L87" s="83"/>
-      <c r="M87" s="85" t="s">
+      <c r="M87" s="87" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="93" t="s">
+      <c r="A88" s="87" t="s">
         <v>307</v>
       </c>
-      <c r="B88" s="93" t="s">
+      <c r="B88" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C88" s="93" t="s">
+      <c r="C88" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E88" s="93" t="s">
+      <c r="E88" s="87" t="s">
         <v>309</v>
       </c>
       <c r="F88" s="10">
@@ -5621,36 +5640,36 @@
         <v>1</v>
       </c>
       <c r="H88" s="7">
-        <v>34</v>
-      </c>
-      <c r="I88" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I88" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J88" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K88" s="85" t="s">
+      <c r="J88" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K88" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L88" s="83"/>
-      <c r="M88" s="85" t="s">
+      <c r="M88" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="94" t="s">
+      <c r="A89" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="B89" s="93" t="s">
+      <c r="B89" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C89" s="93" t="s">
+      <c r="C89" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E89" s="93" t="s">
+      <c r="E89" s="87" t="s">
         <v>311</v>
       </c>
       <c r="F89" s="10">
@@ -5660,36 +5679,36 @@
         <v>1</v>
       </c>
       <c r="H89" s="7">
-        <v>224</v>
-      </c>
-      <c r="I89" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I89" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J89" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K89" s="85" t="s">
+      <c r="J89" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K89" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L89" s="83"/>
-      <c r="M89" s="85" t="s">
+      <c r="M89" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="93" t="s">
+      <c r="A90" s="87" t="s">
         <v>350</v>
       </c>
-      <c r="B90" s="93" t="s">
+      <c r="B90" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C90" s="93" t="s">
+      <c r="C90" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E90" s="93" t="s">
+      <c r="E90" s="87" t="s">
         <v>312</v>
       </c>
       <c r="F90" s="10">
@@ -5699,36 +5718,36 @@
         <v>1</v>
       </c>
       <c r="H90" s="7">
-        <v>138</v>
-      </c>
-      <c r="I90" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I90" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J90" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K90" s="85" t="s">
+      <c r="J90" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K90" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L90" s="83"/>
-      <c r="M90" s="85" t="s">
+      <c r="M90" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="93" t="s">
+      <c r="A91" s="87" t="s">
         <v>313</v>
       </c>
-      <c r="B91" s="93" t="s">
+      <c r="B91" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="93" t="s">
+      <c r="C91" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E91" s="93" t="s">
+      <c r="E91" s="87" t="s">
         <v>314</v>
       </c>
       <c r="F91" s="10">
@@ -5738,46 +5757,46 @@
         <v>1</v>
       </c>
       <c r="H91" s="7">
-        <v>56</v>
-      </c>
-      <c r="I91" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I91" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J91" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K91" s="85" t="s">
+      <c r="J91" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K91" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L91" s="83"/>
-      <c r="M91" s="85" t="s">
+      <c r="M91" s="87" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="88" t="s">
+      <c r="A92" s="82" t="s">
         <v>315</v>
       </c>
-      <c r="B92" s="88" t="s">
+      <c r="B92" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C92" s="88" t="s">
+      <c r="C92" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E92" s="88" t="s">
+      <c r="E92" s="82" t="s">
         <v>316</v>
       </c>
       <c r="F92" s="10">
         <v>2165000000</v>
       </c>
-      <c r="G92" s="89" t="s">
+      <c r="G92" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H92" s="7">
-        <v>928</v>
+        <v>0</v>
       </c>
       <c r="I92" s="83" t="s">
         <v>70</v>
@@ -5794,29 +5813,29 @@
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="88" t="s">
+      <c r="A93" s="82" t="s">
         <v>317</v>
       </c>
-      <c r="B93" s="88" t="s">
+      <c r="B93" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C93" s="88" t="s">
+      <c r="C93" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E93" s="88" t="s">
+      <c r="E93" s="82" t="s">
         <v>318</v>
       </c>
       <c r="F93" s="10">
         <v>2959258280</v>
       </c>
-      <c r="G93" s="89" t="s">
+      <c r="G93" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H93" s="7">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I93" s="83" t="s">
         <v>70</v>
@@ -5833,19 +5852,19 @@
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="89" t="s">
+      <c r="A94" s="83" t="s">
         <v>319</v>
       </c>
-      <c r="B94" s="93" t="s">
+      <c r="B94" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C94" s="93" t="s">
+      <c r="C94" s="87" t="s">
         <v>308</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="93" t="s">
+      <c r="E94" s="87" t="s">
         <v>320</v>
       </c>
       <c r="F94" s="10">
@@ -5855,52 +5874,52 @@
         <v>1</v>
       </c>
       <c r="H94" s="7">
-        <v>33</v>
-      </c>
-      <c r="I94" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="I94" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="J94" s="85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K94" s="85" t="s">
+      <c r="J94" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="K94" s="87" t="s">
         <v>53</v>
       </c>
       <c r="L94" s="83"/>
-      <c r="M94" s="85" t="s">
+      <c r="M94" s="87" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="92" t="s">
+      <c r="A95" s="86" t="s">
         <v>321</v>
       </c>
-      <c r="B95" s="88" t="s">
+      <c r="B95" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C95" s="88" t="s">
+      <c r="C95" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E95" s="88" t="s">
+      <c r="E95" s="82" t="s">
         <v>322</v>
       </c>
       <c r="F95" s="7">
         <v>5915704000</v>
       </c>
-      <c r="G95" s="89" t="s">
+      <c r="G95" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H95" s="7">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="I95" s="83" t="s">
         <v>70</v>
       </c>
       <c r="J95" s="83" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="K95" s="83" t="s">
         <v>53</v>
@@ -5911,25 +5930,25 @@
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="92" t="s">
+      <c r="A96" s="86" t="s">
         <v>323</v>
       </c>
-      <c r="B96" s="91" t="s">
+      <c r="B96" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C96" s="91" t="s">
+      <c r="C96" s="85" t="s">
         <v>308</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E96" s="91" t="s">
+      <c r="E96" s="85" t="s">
         <v>324</v>
       </c>
       <c r="F96" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G96" s="89" t="s">
+      <c r="G96" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H96" s="7">
@@ -5950,25 +5969,25 @@
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A97" s="92" t="s">
+      <c r="A97" s="86" t="s">
         <v>323</v>
       </c>
-      <c r="B97" s="91" t="s">
+      <c r="B97" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C97" s="91" t="s">
+      <c r="C97" s="85" t="s">
         <v>308</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E97" s="91" t="s">
+      <c r="E97" s="85" t="s">
         <v>324</v>
       </c>
       <c r="F97" s="12">
         <v>2899662726</v>
       </c>
-      <c r="G97" s="89" t="s">
+      <c r="G97" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H97" s="7">
@@ -5989,25 +6008,25 @@
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="92" t="s">
+      <c r="A98" s="86" t="s">
         <v>325</v>
       </c>
-      <c r="B98" s="88" t="s">
+      <c r="B98" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C98" s="88" t="s">
+      <c r="C98" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E98" s="88" t="s">
+      <c r="E98" s="82" t="s">
         <v>326</v>
       </c>
       <c r="F98" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G98" s="89" t="s">
+      <c r="G98" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H98" s="7">
@@ -6028,25 +6047,25 @@
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="88" t="s">
+      <c r="A99" s="86" t="s">
         <v>325</v>
       </c>
-      <c r="B99" s="88" t="s">
+      <c r="B99" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C99" s="88" t="s">
+      <c r="C99" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E99" s="88" t="s">
+      <c r="E99" s="82" t="s">
         <v>326</v>
       </c>
       <c r="F99" s="7">
         <v>3567272727</v>
       </c>
-      <c r="G99" s="89" t="s">
+      <c r="G99" s="92" t="s">
         <v>57</v>
       </c>
       <c r="H99" s="7">
@@ -6056,7 +6075,7 @@
         <v>167</v>
       </c>
       <c r="J99" s="83" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="K99" s="83" t="s">
         <v>53</v>
@@ -6067,23 +6086,23 @@
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="88" t="s">
+      <c r="A100" s="82" t="s">
         <v>351</v>
       </c>
-      <c r="B100" s="88" t="s">
+      <c r="B100" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C100" s="88" t="s">
+      <c r="C100" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E100" s="93" t="s">
+      <c r="E100" s="87" t="s">
         <v>202</v>
       </c>
-      <c r="F100" s="89"/>
-      <c r="G100" s="89" t="s">
+      <c r="F100" s="83"/>
+      <c r="G100" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H100" s="7">
@@ -6104,25 +6123,25 @@
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="88" t="s">
+      <c r="A101" s="82" t="s">
         <v>327</v>
       </c>
-      <c r="B101" s="88" t="s">
+      <c r="B101" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C101" s="88" t="s">
+      <c r="C101" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="93" t="s">
+      <c r="E101" s="87" t="s">
         <v>328</v>
       </c>
       <c r="F101" s="7">
         <v>11684429947</v>
       </c>
-      <c r="G101" s="89" t="s">
+      <c r="G101" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H101" s="7">
@@ -6143,23 +6162,23 @@
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="88" t="s">
+      <c r="A102" s="82" t="s">
         <v>329</v>
       </c>
-      <c r="B102" s="88" t="s">
+      <c r="B102" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C102" s="88" t="s">
+      <c r="C102" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E102" s="93" t="s">
+      <c r="E102" s="87" t="s">
         <v>330</v>
       </c>
-      <c r="F102" s="89"/>
-      <c r="G102" s="89" t="s">
+      <c r="F102" s="83"/>
+      <c r="G102" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H102" s="7">
@@ -6180,25 +6199,25 @@
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="88" t="s">
+      <c r="A103" s="82" t="s">
         <v>331</v>
       </c>
-      <c r="B103" s="88" t="s">
+      <c r="B103" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C103" s="88" t="s">
+      <c r="C103" s="82" t="s">
         <v>332</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E103" s="93" t="s">
+      <c r="E103" s="87" t="s">
         <v>333</v>
       </c>
       <c r="F103" s="7">
         <v>2329683517</v>
       </c>
-      <c r="G103" s="89" t="s">
+      <c r="G103" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H103" s="7">
@@ -6219,25 +6238,25 @@
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="88" t="s">
+      <c r="A104" s="82" t="s">
         <v>334</v>
       </c>
-      <c r="B104" s="88" t="s">
+      <c r="B104" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C104" s="88" t="s">
+      <c r="C104" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="93" t="s">
+      <c r="E104" s="87" t="s">
         <v>335</v>
       </c>
       <c r="F104" s="7">
         <v>1545593000</v>
       </c>
-      <c r="G104" s="89" t="s">
+      <c r="G104" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H104" s="7">
@@ -6258,23 +6277,23 @@
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="88" t="s">
+      <c r="A105" s="82" t="s">
         <v>346</v>
       </c>
-      <c r="B105" s="88" t="s">
+      <c r="B105" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C105" s="88" t="s">
+      <c r="C105" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E105" s="93" t="s">
+      <c r="E105" s="87" t="s">
         <v>347</v>
       </c>
-      <c r="F105" s="89"/>
-      <c r="G105" s="89" t="s">
+      <c r="F105" s="83"/>
+      <c r="G105" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H105" s="7">
@@ -6295,25 +6314,25 @@
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="88" t="s">
+      <c r="A106" s="82" t="s">
         <v>348</v>
       </c>
-      <c r="B106" s="88" t="s">
+      <c r="B106" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C106" s="88" t="s">
+      <c r="C106" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E106" s="93" t="s">
+      <c r="E106" s="87" t="s">
         <v>349</v>
       </c>
       <c r="F106" s="7">
         <v>863631818.20000005</v>
       </c>
-      <c r="G106" s="89" t="s">
+      <c r="G106" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H106" s="7">
@@ -6334,25 +6353,25 @@
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="88" t="s">
+      <c r="A107" s="82" t="s">
         <v>352</v>
       </c>
-      <c r="B107" s="88" t="s">
+      <c r="B107" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C107" s="88" t="s">
+      <c r="C107" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E107" s="93" t="s">
+      <c r="E107" s="87" t="s">
         <v>353</v>
       </c>
       <c r="F107" s="7">
         <v>3338181818</v>
       </c>
-      <c r="G107" s="89" t="s">
+      <c r="G107" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H107" s="7">
@@ -6373,23 +6392,23 @@
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="88" t="s">
+      <c r="A108" s="82" t="s">
         <v>354</v>
       </c>
-      <c r="B108" s="88" t="s">
+      <c r="B108" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C108" s="88" t="s">
+      <c r="C108" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E108" s="93" t="s">
+      <c r="E108" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="F108" s="89"/>
-      <c r="G108" s="89" t="s">
+      <c r="F108" s="83"/>
+      <c r="G108" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H108" s="7">
@@ -6410,25 +6429,25 @@
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="88" t="s">
+      <c r="A109" s="82" t="s">
         <v>355</v>
       </c>
-      <c r="B109" s="88" t="s">
+      <c r="B109" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C109" s="88" t="s">
+      <c r="C109" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E109" s="93" t="s">
+      <c r="E109" s="87" t="s">
         <v>356</v>
       </c>
       <c r="F109" s="7">
         <v>719278000</v>
       </c>
-      <c r="G109" s="89" t="s">
+      <c r="G109" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H109" s="7">
@@ -6449,25 +6468,25 @@
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="88" t="s">
+      <c r="A110" s="82" t="s">
         <v>357</v>
       </c>
-      <c r="B110" s="88" t="s">
+      <c r="B110" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C110" s="88" t="s">
+      <c r="C110" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E110" s="93" t="s">
+      <c r="E110" s="87" t="s">
         <v>358</v>
       </c>
       <c r="F110" s="7">
         <v>2186917438</v>
       </c>
-      <c r="G110" s="89" t="s">
+      <c r="G110" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H110" s="7">
@@ -6488,25 +6507,25 @@
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A111" s="88" t="s">
+      <c r="A111" s="82" t="s">
         <v>365</v>
       </c>
-      <c r="B111" s="88" t="s">
+      <c r="B111" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C111" s="88" t="s">
+      <c r="C111" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E111" s="93" t="s">
+      <c r="E111" s="87" t="s">
         <v>366</v>
       </c>
       <c r="F111" s="7">
         <v>69307272.730000004</v>
       </c>
-      <c r="G111" s="89" t="s">
+      <c r="G111" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H111" s="7">
@@ -6527,25 +6546,25 @@
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A112" s="88" t="s">
+      <c r="A112" s="82" t="s">
         <v>367</v>
       </c>
-      <c r="B112" s="88" t="s">
+      <c r="B112" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C112" s="88" t="s">
+      <c r="C112" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="93" t="s">
+      <c r="E112" s="87" t="s">
         <v>368</v>
       </c>
       <c r="F112" s="7">
         <v>140818181.80000001</v>
       </c>
-      <c r="G112" s="89" t="s">
+      <c r="G112" s="92" t="s">
         <v>1</v>
       </c>
       <c r="H112" s="7">
@@ -6566,25 +6585,25 @@
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="88" t="s">
+      <c r="A113" s="82" t="s">
         <v>369</v>
       </c>
-      <c r="B113" s="88" t="s">
+      <c r="B113" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C113" s="88" t="s">
+      <c r="C113" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E113" s="93" t="s">
+      <c r="E113" s="87" t="s">
         <v>370</v>
       </c>
       <c r="F113" s="7">
         <v>1196969505</v>
       </c>
-      <c r="G113" s="89" t="s">
+      <c r="G113" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H113" s="7">
@@ -6605,25 +6624,25 @@
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="88" t="s">
+      <c r="A114" s="82" t="s">
         <v>371</v>
       </c>
-      <c r="B114" s="88" t="s">
+      <c r="B114" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C114" s="88" t="s">
+      <c r="C114" s="82" t="s">
         <v>372</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E114" s="93" t="s">
+      <c r="E114" s="87" t="s">
         <v>373</v>
       </c>
       <c r="F114" s="7">
         <v>3761066864</v>
       </c>
-      <c r="G114" s="89" t="s">
+      <c r="G114" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H114" s="7">
@@ -6644,25 +6663,25 @@
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="88" t="s">
+      <c r="A115" s="82" t="s">
         <v>374</v>
       </c>
-      <c r="B115" s="88" t="s">
+      <c r="B115" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="C115" s="88" t="s">
+      <c r="C115" s="82" t="s">
         <v>375</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E115" s="93" t="s">
+      <c r="E115" s="87" t="s">
         <v>376</v>
       </c>
-      <c r="F115" s="7">
+      <c r="F115" s="79">
         <v>1188000000</v>
       </c>
-      <c r="G115" s="89" t="s">
+      <c r="G115" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H115" s="7">
@@ -6683,25 +6702,25 @@
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="88" t="s">
+      <c r="A116" s="82" t="s">
         <v>377</v>
       </c>
-      <c r="B116" s="88" t="s">
+      <c r="B116" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C116" s="88" t="s">
+      <c r="C116" s="82" t="s">
         <v>378</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E116" s="93" t="s">
+      <c r="E116" s="87" t="s">
         <v>379</v>
       </c>
       <c r="F116" s="7">
         <v>8578824307</v>
       </c>
-      <c r="G116" s="89" t="s">
+      <c r="G116" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H116" s="7">
@@ -6722,25 +6741,25 @@
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="88" t="s">
+      <c r="A117" s="82" t="s">
         <v>380</v>
       </c>
-      <c r="B117" s="88" t="s">
+      <c r="B117" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C117" s="88" t="s">
+      <c r="C117" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E117" s="93" t="s">
+      <c r="E117" s="87" t="s">
         <v>381</v>
       </c>
       <c r="F117" s="7">
         <v>2842500250</v>
       </c>
-      <c r="G117" s="89" t="s">
+      <c r="G117" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H117" s="7">
@@ -6761,21 +6780,21 @@
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="88" t="s">
+      <c r="A118" s="82" t="s">
         <v>382</v>
       </c>
-      <c r="B118" s="89"/>
-      <c r="C118" s="89"/>
+      <c r="B118" s="83"/>
+      <c r="C118" s="83"/>
       <c r="D118" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E118" s="93" t="s">
+      <c r="E118" s="87" t="s">
         <v>383</v>
       </c>
       <c r="F118" s="9">
         <v>459000000</v>
       </c>
-      <c r="G118" s="89" t="s">
+      <c r="G118" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H118" s="7">
@@ -6794,25 +6813,25 @@
       <c r="M118" s="83"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="88" t="s">
+      <c r="A119" s="82" t="s">
         <v>384</v>
       </c>
-      <c r="B119" s="88" t="s">
+      <c r="B119" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C119" s="88" t="s">
+      <c r="C119" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E119" s="93" t="s">
+      <c r="E119" s="87" t="s">
         <v>384</v>
       </c>
       <c r="F119" s="7">
         <v>602440000</v>
       </c>
-      <c r="G119" s="89" t="s">
+      <c r="G119" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H119" s="7">
@@ -6831,25 +6850,25 @@
       <c r="M119" s="83"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="93" t="s">
+      <c r="A120" s="87" t="s">
         <v>385</v>
       </c>
-      <c r="B120" s="88" t="s">
+      <c r="B120" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C120" s="93" t="s">
+      <c r="C120" s="87" t="s">
         <v>386</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E120" s="93" t="s">
+      <c r="E120" s="87" t="s">
         <v>387</v>
       </c>
       <c r="F120" s="7">
         <v>1847633000</v>
       </c>
-      <c r="G120" s="89" t="s">
+      <c r="G120" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H120" s="7">
@@ -6870,25 +6889,25 @@
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="93" t="s">
+      <c r="A121" s="87" t="s">
         <v>388</v>
       </c>
-      <c r="B121" s="88" t="s">
+      <c r="B121" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C121" s="93" t="s">
+      <c r="C121" s="87" t="s">
         <v>389</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E121" s="93" t="s">
+      <c r="E121" s="87" t="s">
         <v>390</v>
       </c>
       <c r="F121" s="7">
         <v>685000000</v>
       </c>
-      <c r="G121" s="89" t="s">
+      <c r="G121" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H121" s="7">
@@ -6909,25 +6928,25 @@
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="88" t="s">
+      <c r="A122" s="82" t="s">
         <v>391</v>
       </c>
-      <c r="B122" s="88" t="s">
+      <c r="B122" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C122" s="93" t="s">
+      <c r="C122" s="87" t="s">
         <v>392</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E122" s="93" t="s">
+      <c r="E122" s="87" t="s">
         <v>391</v>
       </c>
       <c r="F122" s="7">
         <v>854545455</v>
       </c>
-      <c r="G122" s="89" t="s">
+      <c r="G122" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H122" s="7">
@@ -6948,25 +6967,25 @@
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="93" t="s">
+      <c r="A123" s="82" t="s">
         <v>393</v>
       </c>
-      <c r="B123" s="88" t="s">
+      <c r="B123" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C123" s="93" t="s">
+      <c r="C123" s="82" t="s">
         <v>394</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="93" t="s">
+      <c r="E123" s="87" t="s">
         <v>395</v>
       </c>
       <c r="F123" s="7">
         <v>800000000</v>
       </c>
-      <c r="G123" s="89" t="s">
+      <c r="G123" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H123" s="7">
@@ -6987,25 +7006,25 @@
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="93" t="s">
+      <c r="A124" s="87" t="s">
         <v>396</v>
       </c>
-      <c r="B124" s="88" t="s">
+      <c r="B124" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C124" s="93" t="s">
+      <c r="C124" s="87" t="s">
         <v>397</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E124" s="93" t="s">
+      <c r="E124" s="87" t="s">
         <v>398</v>
       </c>
       <c r="F124" s="7">
         <v>1374545455</v>
       </c>
-      <c r="G124" s="89" t="s">
+      <c r="G124" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H124" s="7">
@@ -7026,25 +7045,25 @@
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="93" t="s">
+      <c r="A125" s="82" t="s">
         <v>399</v>
       </c>
-      <c r="B125" s="88" t="s">
+      <c r="B125" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C125" s="93" t="s">
+      <c r="C125" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E125" s="93" t="s">
+      <c r="E125" s="87" t="s">
         <v>401</v>
       </c>
       <c r="F125" s="7">
         <v>214789091</v>
       </c>
-      <c r="G125" s="89" t="s">
+      <c r="G125" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H125" s="7">
@@ -7065,23 +7084,23 @@
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="93" t="s">
+      <c r="A126" s="82" t="s">
         <v>402</v>
       </c>
-      <c r="B126" s="88" t="s">
+      <c r="B126" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C126" s="93" t="s">
+      <c r="C126" s="82" t="s">
         <v>403</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E126" s="93" t="s">
+      <c r="E126" s="87" t="s">
         <v>404</v>
       </c>
-      <c r="F126" s="89"/>
-      <c r="G126" s="89" t="s">
+      <c r="F126" s="83"/>
+      <c r="G126" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H126" s="7">
@@ -7102,25 +7121,25 @@
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="93" t="s">
+      <c r="A127" s="82" t="s">
         <v>405</v>
       </c>
-      <c r="B127" s="88" t="s">
+      <c r="B127" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C127" s="93" t="s">
+      <c r="C127" s="82" t="s">
         <v>406</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E127" s="93" t="s">
+      <c r="E127" s="87" t="s">
         <v>407</v>
       </c>
       <c r="F127" s="7">
         <v>6320909091</v>
       </c>
-      <c r="G127" s="89" t="s">
+      <c r="G127" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H127" s="7">
@@ -7139,25 +7158,25 @@
       <c r="M127" s="83"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="89" t="s">
+      <c r="A128" s="82" t="s">
         <v>408</v>
       </c>
-      <c r="B128" s="88" t="s">
+      <c r="B128" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C128" s="89" t="s">
+      <c r="C128" s="82" t="s">
         <v>409</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E128" s="93" t="s">
+      <c r="E128" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="F128" s="89">
+      <c r="F128" s="7">
         <v>401749000</v>
       </c>
-      <c r="G128" s="89" t="s">
+      <c r="G128" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H128" s="7">
@@ -7178,25 +7197,25 @@
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="89" t="s">
+      <c r="A129" s="82" t="s">
         <v>411</v>
       </c>
-      <c r="B129" s="88" t="s">
+      <c r="B129" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C129" s="89" t="s">
+      <c r="C129" s="82" t="s">
         <v>412</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E129" s="93" t="s">
+      <c r="E129" s="87" t="s">
         <v>413</v>
       </c>
-      <c r="F129" s="89">
+      <c r="F129" s="7">
         <v>134556481</v>
       </c>
-      <c r="G129" s="89" t="s">
+      <c r="G129" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H129" s="7">
@@ -7217,25 +7236,25 @@
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A130" s="93" t="s">
+      <c r="A130" s="82" t="s">
         <v>421</v>
       </c>
-      <c r="B130" s="88" t="s">
+      <c r="B130" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C130" s="93" t="s">
+      <c r="C130" s="82" t="s">
         <v>412</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E130" s="93" t="s">
+      <c r="E130" s="87" t="s">
         <v>414</v>
       </c>
       <c r="F130" s="7">
         <v>318666815</v>
       </c>
-      <c r="G130" s="89" t="s">
+      <c r="G130" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H130" s="7">
@@ -7256,25 +7275,25 @@
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="89" t="s">
+      <c r="A131" s="82" t="s">
         <v>415</v>
       </c>
-      <c r="B131" s="88" t="s">
+      <c r="B131" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C131" s="89" t="s">
+      <c r="C131" s="82" t="s">
         <v>412</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E131" s="93" t="s">
+      <c r="E131" s="87" t="s">
         <v>416</v>
       </c>
-      <c r="F131" s="89">
+      <c r="F131" s="7">
         <v>380721000</v>
       </c>
-      <c r="G131" s="89" t="s">
+      <c r="G131" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H131" s="7">
@@ -7295,25 +7314,25 @@
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="93" t="s">
+      <c r="A132" s="87" t="s">
         <v>417</v>
       </c>
-      <c r="B132" s="88" t="s">
+      <c r="B132" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C132" s="93" t="s">
+      <c r="C132" s="87" t="s">
         <v>412</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E132" s="93" t="s">
+      <c r="E132" s="87" t="s">
         <v>418</v>
       </c>
       <c r="F132" s="7">
         <v>234545454.5</v>
       </c>
-      <c r="G132" s="89" t="s">
+      <c r="G132" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H132" s="7">
@@ -7334,25 +7353,25 @@
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="93" t="s">
+      <c r="A133" s="82" t="s">
         <v>419</v>
       </c>
-      <c r="B133" s="88" t="s">
+      <c r="B133" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="C133" s="93" t="s">
+      <c r="C133" s="82" t="s">
         <v>412</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="93" t="s">
+      <c r="E133" s="87" t="s">
         <v>420</v>
       </c>
-      <c r="F133" s="7">
+      <c r="F133" s="79">
         <v>313269865</v>
       </c>
-      <c r="G133" s="89" t="s">
+      <c r="G133" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H133" s="7">
@@ -7371,25 +7390,25 @@
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="93" t="s">
+      <c r="A134" s="82" t="s">
         <v>422</v>
       </c>
-      <c r="B134" s="88" t="s">
+      <c r="B134" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C134" s="93" t="s">
+      <c r="C134" s="82" t="s">
         <v>308</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E134" s="93" t="s">
+      <c r="E134" s="87" t="s">
         <v>423</v>
       </c>
       <c r="F134" s="7">
         <v>970417742</v>
       </c>
-      <c r="G134" s="89" t="s">
+      <c r="G134" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H134" s="7">
@@ -7408,25 +7427,25 @@
       <c r="M134" s="83"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A135" s="93" t="s">
+      <c r="A135" s="82" t="s">
         <v>424</v>
       </c>
-      <c r="B135" s="88" t="s">
+      <c r="B135" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="C135" s="93" t="s">
+      <c r="C135" s="82" t="s">
         <v>412</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E135" s="93" t="s">
+      <c r="E135" s="87" t="s">
         <v>425</v>
       </c>
-      <c r="F135" s="7">
+      <c r="F135" s="79">
         <v>694444444</v>
       </c>
-      <c r="G135" s="89" t="s">
+      <c r="G135" s="92" t="s">
         <v>11</v>
       </c>
       <c r="H135" s="7">
@@ -7439,7 +7458,7 @@
         <v>52</v>
       </c>
       <c r="K135" s="83" t="s">
-        <v>79</v>
+        <v>463</v>
       </c>
       <c r="L135" s="83"/>
       <c r="M135" s="83" t="s">
@@ -7447,25 +7466,25 @@
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A136" s="93" t="s">
+      <c r="A136" s="87" t="s">
         <v>426</v>
       </c>
-      <c r="B136" s="88" t="s">
+      <c r="B136" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C136" s="93" t="s">
+      <c r="C136" s="87" t="s">
         <v>427</v>
       </c>
-      <c r="D136" s="6" t="s">
+      <c r="D136" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="E136" s="93" t="s">
+      <c r="E136" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="F136" s="82">
+      <c r="F136" s="89">
         <v>178334509</v>
       </c>
-      <c r="G136" s="89" t="s">
+      <c r="G136" s="92" t="s">
         <v>9</v>
       </c>
       <c r="H136" s="7">
@@ -7484,576 +7503,617 @@
       <c r="M136" s="83"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="95" t="s">
+      <c r="A137" s="87" t="s">
         <v>428</v>
       </c>
-      <c r="B137" s="95" t="s">
+      <c r="B137" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C137" s="95" t="s">
+      <c r="C137" s="87" t="s">
         <v>429</v>
       </c>
-      <c r="D137" s="95" t="s">
+      <c r="D137" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="E137" s="95" t="s">
+      <c r="E137" s="87" t="s">
         <v>430</v>
       </c>
-      <c r="F137" s="96">
+      <c r="F137" s="89">
         <v>206363636</v>
       </c>
-      <c r="G137" s="95" t="s">
+      <c r="G137" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="H137" s="84">
-        <v>0</v>
-      </c>
-      <c r="I137" s="84" t="s">
+      <c r="H137" s="7">
+        <v>0</v>
+      </c>
+      <c r="I137" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J137" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="K137" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="L137" s="84"/>
-      <c r="M137" s="84"/>
+      <c r="J137" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K137" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L137" s="83"/>
+      <c r="M137" s="83"/>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A138" s="95" t="s">
+      <c r="A138" s="87" t="s">
         <v>431</v>
       </c>
-      <c r="B138" s="95" t="s">
+      <c r="B138" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C138" s="95" t="s">
+      <c r="C138" s="87" t="s">
         <v>432</v>
       </c>
       <c r="D138" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="E138" s="95" t="s">
+      <c r="E138" s="87" t="s">
         <v>433</v>
       </c>
-      <c r="F138" s="96">
+      <c r="F138" s="89">
         <v>2787523658</v>
       </c>
-      <c r="G138" s="95" t="s">
+      <c r="G138" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H138" s="84">
-        <v>0</v>
-      </c>
-      <c r="I138" s="84" t="s">
+      <c r="H138" s="7">
+        <v>0</v>
+      </c>
+      <c r="I138" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J138" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="K138" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="L138" s="84"/>
-      <c r="M138" s="84"/>
+      <c r="J138" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K138" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L138" s="83"/>
+      <c r="M138" s="83"/>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A139" s="95" t="s">
+      <c r="A139" s="87" t="s">
         <v>434</v>
       </c>
-      <c r="B139" s="95" t="s">
+      <c r="B139" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C139" s="95" t="s">
+      <c r="C139" s="87" t="s">
         <v>435</v>
       </c>
-      <c r="D139" s="87" t="s">
+      <c r="D139" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="E139" s="95" t="s">
+      <c r="E139" s="83" t="s">
         <v>436</v>
       </c>
-      <c r="F139" s="96">
+      <c r="F139" s="90">
         <v>183500000</v>
       </c>
-      <c r="G139" s="95" t="s">
+      <c r="G139" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H139" s="84">
+      <c r="H139" s="7">
         <v>32</v>
       </c>
-      <c r="I139" s="84" t="s">
+      <c r="I139" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J139" s="84"/>
+      <c r="J139" s="83"/>
       <c r="K139" s="83"/>
-      <c r="L139" s="84"/>
-      <c r="M139" s="84"/>
+      <c r="L139" s="83"/>
+      <c r="M139" s="83"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A140" s="95" t="s">
+      <c r="A140" s="87" t="s">
         <v>437</v>
       </c>
-      <c r="B140" s="95" t="s">
+      <c r="B140" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C140" s="95" t="s">
+      <c r="C140" s="87" t="s">
         <v>438</v>
       </c>
-      <c r="D140" s="95" t="s">
+      <c r="D140" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="E140" s="95" t="s">
+      <c r="E140" s="87" t="s">
         <v>439</v>
       </c>
-      <c r="F140" s="96">
+      <c r="F140" s="89">
         <v>107018182</v>
       </c>
-      <c r="G140" s="95" t="s">
+      <c r="G140" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="H140" s="84">
-        <v>0</v>
-      </c>
-      <c r="I140" s="84" t="s">
+      <c r="H140" s="7">
+        <v>0</v>
+      </c>
+      <c r="I140" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J140" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="K140" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="L140" s="84"/>
-      <c r="M140" s="84" t="s">
+      <c r="J140" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K140" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L140" s="83"/>
+      <c r="M140" s="83" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A141" s="95" t="s">
+      <c r="A141" s="87" t="s">
         <v>440</v>
       </c>
-      <c r="B141" s="95" t="s">
+      <c r="B141" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C141" s="95" t="s">
+      <c r="C141" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="D141" s="87" t="s">
+      <c r="D141" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E141" s="95" t="s">
+      <c r="E141" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="F141" s="96">
+      <c r="F141" s="91">
         <v>131753127</v>
       </c>
-      <c r="G141" s="95" t="s">
+      <c r="G141" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H141" s="84">
-        <v>0</v>
-      </c>
-      <c r="I141" s="84"/>
-      <c r="J141" s="84"/>
+      <c r="H141" s="7">
+        <v>0</v>
+      </c>
+      <c r="I141" s="83"/>
+      <c r="J141" s="83"/>
       <c r="K141" s="83"/>
-      <c r="L141" s="84"/>
-      <c r="M141" s="84"/>
+      <c r="L141" s="83"/>
+      <c r="M141" s="83"/>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A142" s="95" t="s">
+      <c r="A142" s="87" t="s">
         <v>441</v>
       </c>
-      <c r="B142" s="95" t="s">
+      <c r="B142" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="95" t="s">
+      <c r="C142" s="87" t="s">
         <v>427</v>
       </c>
-      <c r="D142" s="87" t="s">
+      <c r="D142" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="E142" s="95" t="s">
+      <c r="E142" s="83" t="s">
         <v>442</v>
       </c>
-      <c r="F142" s="96">
+      <c r="F142" s="90">
         <v>2209199764</v>
       </c>
-      <c r="G142" s="95" t="s">
+      <c r="G142" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H142" s="84"/>
-      <c r="I142" s="84" t="s">
-        <v>167</v>
-      </c>
-      <c r="J142" s="84" t="s">
-        <v>78</v>
+      <c r="H142" s="83"/>
+      <c r="I142" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="J142" s="83" t="s">
+        <v>52</v>
       </c>
       <c r="K142" s="83" t="s">
-        <v>79</v>
-      </c>
-      <c r="L142" s="84"/>
-      <c r="M142" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L142" s="83"/>
+      <c r="M142" s="83" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A143" s="95" t="s">
+      <c r="A143" s="87" t="s">
         <v>443</v>
       </c>
-      <c r="B143" s="95" t="s">
+      <c r="B143" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C143" s="95" t="s">
+      <c r="C143" s="87" t="s">
         <v>444</v>
       </c>
-      <c r="D143" s="87" t="s">
+      <c r="D143" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="E143" s="95" t="s">
+      <c r="E143" s="87" t="s">
         <v>445</v>
       </c>
-      <c r="F143" s="96">
+      <c r="F143" s="91">
         <v>2292994051</v>
       </c>
-      <c r="G143" s="95" t="s">
+      <c r="G143" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H143" s="84">
-        <v>0</v>
-      </c>
-      <c r="I143" s="84" t="s">
+      <c r="H143" s="7">
+        <v>0</v>
+      </c>
+      <c r="I143" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J143" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="K143" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="L143" s="84"/>
-      <c r="M143" s="84" t="s">
+      <c r="J143" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K143" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L143" s="83"/>
+      <c r="M143" s="83" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A144" s="95" t="s">
+      <c r="A144" s="87" t="s">
         <v>446</v>
       </c>
-      <c r="B144" s="95" t="s">
+      <c r="B144" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="C144" s="95" t="s">
+      <c r="C144" s="83" t="s">
         <v>447</v>
       </c>
-      <c r="D144" s="87" t="s">
+      <c r="D144" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="E144" s="95" t="s">
+      <c r="E144" s="83" t="s">
         <v>188</v>
       </c>
-      <c r="F144" s="95">
+      <c r="F144" s="7">
         <v>955130246</v>
       </c>
-      <c r="G144" s="95" t="s">
+      <c r="G144" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H144" s="84">
-        <v>0</v>
-      </c>
-      <c r="I144" s="84" t="s">
+      <c r="H144" s="7">
+        <v>0</v>
+      </c>
+      <c r="I144" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J144" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="K144" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="L144" s="84"/>
-      <c r="M144" s="84" t="s">
+      <c r="J144" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K144" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L144" s="83"/>
+      <c r="M144" s="83" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A145" s="95" t="s">
+      <c r="A145" s="87" t="s">
         <v>448</v>
       </c>
-      <c r="B145" s="95" t="s">
+      <c r="B145" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="C145" s="95" t="s">
+      <c r="C145" s="83" t="s">
         <v>412</v>
       </c>
-      <c r="D145" s="95" t="s">
+      <c r="D145" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="E145" s="95" t="s">
+      <c r="E145" s="83" t="s">
         <v>449</v>
       </c>
-      <c r="F145" s="95">
+      <c r="F145" s="7">
         <v>1728000000</v>
       </c>
-      <c r="G145" s="95" t="s">
+      <c r="G145" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="H145" s="84">
-        <v>0</v>
-      </c>
-      <c r="I145" s="84" t="s">
+      <c r="H145" s="7">
+        <v>0</v>
+      </c>
+      <c r="I145" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J145" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="K145" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="L145" s="84"/>
-      <c r="M145" s="84" t="s">
+      <c r="J145" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K145" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L145" s="83"/>
+      <c r="M145" s="83" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A146" s="95" t="s">
+      <c r="A146" s="87" t="s">
         <v>450</v>
       </c>
-      <c r="B146" s="95"/>
-      <c r="C146" s="95" t="s">
+      <c r="B146" s="83"/>
+      <c r="C146" s="87" t="s">
         <v>400</v>
       </c>
-      <c r="D146" s="87" t="s">
+      <c r="D146" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E146" s="95"/>
-      <c r="F146" s="96">
+      <c r="E146" s="83"/>
+      <c r="F146" s="91">
         <v>174715000</v>
       </c>
-      <c r="G146" s="95" t="s">
+      <c r="G146" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H146" s="84">
+      <c r="H146" s="7">
         <v>20</v>
       </c>
-      <c r="I146" s="84"/>
-      <c r="J146" s="84"/>
+      <c r="I146" s="83"/>
+      <c r="J146" s="83"/>
       <c r="K146" s="83"/>
-      <c r="L146" s="84"/>
-      <c r="M146" s="84"/>
+      <c r="L146" s="83"/>
+      <c r="M146" s="83"/>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A147" s="95" t="s">
+      <c r="A147" s="87" t="s">
         <v>451</v>
       </c>
-      <c r="B147" s="95" t="s">
+      <c r="B147" s="83" t="s">
         <v>113</v>
       </c>
-      <c r="C147" s="95" t="s">
+      <c r="C147" s="87" t="s">
         <v>452</v>
       </c>
       <c r="D147" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="95"/>
-      <c r="F147" s="96">
+      <c r="E147" s="83"/>
+      <c r="F147" s="10">
         <v>128812000</v>
       </c>
-      <c r="G147" s="95" t="s">
+      <c r="G147" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H147" s="84">
-        <v>0</v>
-      </c>
-      <c r="I147" s="84" t="s">
+      <c r="H147" s="7">
+        <v>0</v>
+      </c>
+      <c r="I147" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J147" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="K147" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="L147" s="84"/>
-      <c r="M147" s="84"/>
+      <c r="J147" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K147" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L147" s="83"/>
+      <c r="M147" s="83"/>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A148" s="95" t="s">
+      <c r="A148" s="87" t="s">
         <v>453</v>
       </c>
-      <c r="B148" s="95" t="s">
+      <c r="B148" s="83" t="s">
         <v>113</v>
       </c>
-      <c r="C148" s="95" t="s">
+      <c r="C148" s="87" t="s">
         <v>454</v>
       </c>
-      <c r="D148" s="87" t="s">
+      <c r="D148" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E148" s="95"/>
-      <c r="F148" s="96">
+      <c r="E148" s="83"/>
+      <c r="F148" s="91">
         <v>2106000000</v>
       </c>
-      <c r="G148" s="95" t="s">
+      <c r="G148" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H148" s="84">
+      <c r="H148" s="7">
         <v>720</v>
       </c>
-      <c r="I148" s="84" t="s">
+      <c r="I148" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J148" s="84" t="s">
+      <c r="J148" s="83" t="s">
         <v>78</v>
       </c>
       <c r="K148" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="L148" s="84"/>
-      <c r="M148" s="84"/>
+      <c r="L148" s="83"/>
+      <c r="M148" s="83"/>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A149" s="95" t="s">
+      <c r="A149" s="87" t="s">
         <v>455</v>
       </c>
-      <c r="B149" s="95" t="s">
+      <c r="B149" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C149" s="95" t="s">
+      <c r="C149" s="87" t="s">
         <v>456</v>
       </c>
-      <c r="D149" s="95" t="s">
+      <c r="D149" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="E149" s="95" t="s">
+      <c r="E149" s="87" t="s">
         <v>439</v>
       </c>
-      <c r="F149" s="96">
+      <c r="F149" s="10">
         <v>170640000</v>
       </c>
-      <c r="G149" s="95" t="s">
+      <c r="G149" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="H149" s="84">
-        <v>0</v>
-      </c>
-      <c r="I149" s="84" t="s">
+      <c r="H149" s="7">
+        <v>0</v>
+      </c>
+      <c r="I149" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J149" s="84" t="s">
-        <v>52</v>
-      </c>
-      <c r="K149" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="L149" s="84"/>
-      <c r="M149" s="84" t="s">
+      <c r="J149" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K149" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L149" s="83"/>
+      <c r="M149" s="83" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A150" s="95" t="s">
+      <c r="A150" s="87" t="s">
         <v>457</v>
       </c>
-      <c r="B150" s="95" t="s">
+      <c r="B150" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C150" s="95" t="s">
+      <c r="C150" s="87" t="s">
         <v>458</v>
       </c>
-      <c r="D150" s="87" t="s">
+      <c r="D150" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E150" s="95" t="s">
+      <c r="E150" s="83" t="s">
         <v>459</v>
       </c>
-      <c r="F150" s="95">
+      <c r="F150" s="79">
         <v>4875624485</v>
       </c>
-      <c r="G150" s="95" t="s">
+      <c r="G150" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H150" s="84">
+      <c r="H150" s="7">
         <v>1008</v>
       </c>
-      <c r="I150" s="84" t="s">
+      <c r="I150" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J150" s="84" t="s">
-        <v>78</v>
+      <c r="J150" s="83" t="s">
+        <v>52</v>
       </c>
       <c r="K150" s="83" t="s">
-        <v>79</v>
-      </c>
-      <c r="L150" s="84"/>
-      <c r="M150" s="84" t="s">
+        <v>463</v>
+      </c>
+      <c r="L150" s="83"/>
+      <c r="M150" s="83" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A151" s="95" t="s">
+      <c r="A151" s="87" t="s">
         <v>460</v>
       </c>
-      <c r="B151" s="95" t="s">
+      <c r="B151" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="C151" s="95" t="s">
+      <c r="C151" s="87" t="s">
         <v>461</v>
       </c>
-      <c r="D151" s="87" t="s">
+      <c r="D151" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="E151" s="95" t="s">
+      <c r="E151" s="87" t="s">
         <v>462</v>
       </c>
-      <c r="F151" s="96">
+      <c r="F151" s="10">
         <v>125710000</v>
       </c>
-      <c r="G151" s="95" t="s">
+      <c r="G151" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H151" s="84">
+      <c r="H151" s="7">
         <v>12</v>
       </c>
-      <c r="I151" s="84" t="s">
+      <c r="I151" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="J151" s="84" t="s">
+      <c r="J151" s="83" t="s">
         <v>52</v>
       </c>
       <c r="K151" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="L151" s="84"/>
-      <c r="M151" s="84"/>
+      <c r="L151" s="83"/>
+      <c r="M151" s="83"/>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A152" s="97" t="s">
+      <c r="A152" s="87" t="s">
         <v>464</v>
       </c>
-      <c r="B152" s="97" t="s">
+      <c r="B152" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C152" s="97" t="s">
+      <c r="C152" s="83" t="s">
         <v>465</v>
       </c>
-      <c r="D152" s="97" t="s">
+      <c r="D152" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="E152" s="97" t="s">
+      <c r="E152" s="83" t="s">
         <v>466</v>
       </c>
-      <c r="F152" s="97">
+      <c r="F152" s="7">
         <v>1057743460</v>
       </c>
-      <c r="G152" s="97" t="s">
+      <c r="G152" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="H152">
+      <c r="H152" s="7">
         <v>344</v>
       </c>
-      <c r="I152" t="s">
+      <c r="I152" s="83" t="s">
         <v>70</v>
       </c>
+      <c r="J152" s="83"/>
+      <c r="K152" s="83"/>
+      <c r="L152" s="83"/>
+      <c r="M152" s="83"/>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" s="87" t="s">
+        <v>467</v>
+      </c>
+      <c r="B153" s="87" t="s">
+        <v>48</v>
+      </c>
+      <c r="C153" s="83" t="s">
+        <v>468</v>
+      </c>
+      <c r="D153" s="79" t="s">
+        <v>28</v>
+      </c>
+      <c r="E153" s="83" t="s">
+        <v>469</v>
+      </c>
+      <c r="F153" s="7">
+        <v>3176694288</v>
+      </c>
+      <c r="G153" s="92" t="s">
+        <v>11</v>
+      </c>
+      <c r="H153" s="7">
+        <v>128</v>
+      </c>
+      <c r="I153" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="J153" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="K153" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L153" s="83"/>
+      <c r="M153" s="83"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M151" xr:uid="{1F457DF4-8092-4544-B88B-9AF42554C254}"/>
